--- a/Nhom3_BDCLPM_TH.xlsx
+++ b/Nhom3_BDCLPM_TH.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phamn\BaoDamChatLuongPM\ThucHanh\DoAnCuoiKy_TH\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA5E69E2-3912-45B3-B986-8F0316610FD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2691A9E4-EE73-48AE-97D3-39ED3AF8A9F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{23F3E367-7927-4520-A748-866283E286BB}"/>
   </bookViews>
   <sheets>
     <sheet name="Tong_Quan_Du_An" sheetId="2" r:id="rId1"/>
-    <sheet name="TC_Nguyen" sheetId="1" r:id="rId2"/>
-    <sheet name="TC_Tram" sheetId="3" r:id="rId3"/>
+    <sheet name="Test_Requirements" sheetId="4" r:id="rId2"/>
+    <sheet name="TC_Nguyen" sheetId="1" r:id="rId3"/>
+    <sheet name="TC_Tram" sheetId="3" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191028" fullCalcOnLoad="1" fullPrecision="1"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="569">
   <si>
     <t>Tên dự án:</t>
   </si>
@@ -52,14 +53,14 @@
     <t>Các thành viên:</t>
   </si>
   <si>
-    <t xml:space="preserve">Phạm Ngọc Khôi Nguyên
+    <t>Phạm Ngọc Khôi Nguyên
 Nguyễn Thị Bích Trâm</t>
   </si>
   <si>
     <t>Trong file gồm bao nhiêu sheet? Mỗi Sheet có tên là gì?</t>
   </si>
   <si>
-    <t xml:space="preserve">Sheet 1: Tong_Quan_Du_An
+    <t>Sheet 1: Tong_Quan_Du_An
 Sheet 2: TC_Nguyen
 Sheet 3: TC_Tram</t>
   </si>
@@ -1198,7 +1199,7 @@
     <t>Mở trang Register</t>
   </si>
   <si>
-    <t xml:space="preserve">Tất cả các textbox trên trang Register hiển thị đúng.
+    <t>Tất cả các textbox trên trang Register hiển thị đúng.
 Người dùng có thể nhập dữ liệu vào các field.
 Dữ liệu nhập hiển thị đúng trong textbox</t>
   </si>
@@ -1340,10 +1341,10 @@
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
         <family val="2"/>
-        <color theme="1"/>
-        <sz val="11"/>
       </rPr>
       <t>Request Loan</t>
     </r>
@@ -1357,10 +1358,10 @@
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
         <family val="2"/>
-        <color theme="1"/>
-        <sz val="11"/>
       </rPr>
       <t>From account # hiển thị</t>
     </r>
@@ -1371,10 +1372,10 @@
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
         <family val="2"/>
-        <color theme="1"/>
-        <sz val="11"/>
       </rPr>
       <t>From account # hiển thị</t>
     </r>
@@ -1385,10 +1386,10 @@
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
         <family val="2"/>
-        <color theme="1"/>
-        <sz val="11"/>
       </rPr>
       <t>From account #</t>
     </r>
@@ -1418,7 +1419,7 @@
     <t>Smoke: Register → Login → Bill Pay → Logout thành công</t>
   </si>
   <si>
-    <t xml:space="preserve">Cả 4 bước Register, Login, Bill Pay, Logout đều thành công.
+    <t>Cả 4 bước Register, Login, Bill Pay, Logout đều thành công.
 Hệ thống hoạt động đúng trong toàn bộ luồng chính</t>
   </si>
   <si>
@@ -1427,10 +1428,10 @@
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
         <family val="2"/>
-        <color theme="1"/>
-        <sz val="11"/>
       </rPr>
       <t>Register</t>
     </r>
@@ -1483,10 +1484,10 @@
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
         <family val="2"/>
-        <color theme="1"/>
-        <sz val="11"/>
       </rPr>
       <t>Account Overview hiển thị</t>
     </r>
@@ -1497,10 +1498,10 @@
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
         <family val="2"/>
-        <color theme="1"/>
-        <sz val="11"/>
       </rPr>
       <t>Bill Pay</t>
     </r>
@@ -1528,14 +1529,357 @@
   </si>
   <si>
     <t>Kiểm tra trở về trang Login</t>
+  </si>
+  <si>
+    <t>General Information</t>
+  </si>
+  <si>
+    <t>Project</t>
+  </si>
+  <si>
+    <t>ParaBank – Selenium Automation Testing</t>
+  </si>
+  <si>
+    <t>Module</t>
+  </si>
+  <si>
+    <t>ParaBank Web Application</t>
+  </si>
+  <si>
+    <t>Test Designed By</t>
+  </si>
+  <si>
+    <t>Phạm Ngọc Khôi Nguyên, Nguyễn Thị Bích Trâm</t>
+  </si>
+  <si>
+    <t>Reviewed By</t>
+  </si>
+  <si>
+    <t>Test Designed Date</t>
+  </si>
+  <si>
+    <t>09-03-2026</t>
+  </si>
+  <si>
+    <t>Reviewed Date</t>
+  </si>
+  <si>
+    <t>List of Test Requirements</t>
+  </si>
+  <si>
+    <t>No.</t>
+  </si>
+  <si>
+    <t>Test Requirement ID</t>
+  </si>
+  <si>
+    <t>Requirement Functions</t>
+  </si>
+  <si>
+    <t>Mô tả chức năng</t>
+  </si>
+  <si>
+    <t>Test Requirement Description</t>
+  </si>
+  <si>
+    <t>Test Type</t>
+  </si>
+  <si>
+    <t>Importance</t>
+  </si>
+  <si>
+    <t>Number of TCs</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>Test GUI</t>
+  </si>
+  <si>
+    <t>Test Case</t>
+  </si>
+  <si>
+    <t>Scenario</t>
+  </si>
+  <si>
+    <t>F1</t>
+  </si>
+  <si>
+    <t>Login / Logout</t>
+  </si>
+  <si>
+    <t>Xác thực người dùng đăng nhập và đăng xuất khỏi hệ thống ParaBank</t>
+  </si>
+  <si>
+    <t>Kiểm tra đăng nhập thành công, thất bại (sai username/password, trường rỗng), và đăng xuất</t>
+  </si>
+  <si>
+    <t>Positive + Negative</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Complete</t>
+  </si>
+  <si>
+    <t>TC_Nguyen: TC_01 → TC_05</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập thành công với username/password hợp lệ
+2. Đăng nhập thất bại với username không tồn tại
+3. Đăng nhập thất bại với password sai
+4. Đăng nhập khi để trống username
+5. Đăng nhập khi để trống password</t>
+  </si>
+  <si>
+    <t>F2</t>
+  </si>
+  <si>
+    <t>Transfer Funds</t>
+  </si>
+  <si>
+    <t>Chuyển tiền giữa các tài khoản trong hệ thống</t>
+  </si>
+  <si>
+    <t>Kiểm tra chuyển tiền thành công, số dư cập nhật đúng, lịch sử giao dịch, và validate dữ liệu đầu vào (vượt số dư, amount = 0, âm)</t>
+  </si>
+  <si>
+    <t>TC_Nguyen: TC_06 → TC_11</t>
+  </si>
+  <si>
+    <t>1. Chuyển tiền thành công giữa hai tài khoản
+2. Kiểm tra số dư cập nhật đúng sau khi chuyển
+3. Giao dịch hiển thị đúng trong lịch sử
+4. Chuyển tiền vượt quá số dư hiện có
+5. Chuyển tiền với số tiền = 0
+6. Chuyển tiền với số tiền âm</t>
+  </si>
+  <si>
+    <t>F3</t>
+  </si>
+  <si>
+    <t>Open New Account</t>
+  </si>
+  <si>
+    <t>Mở tài khoản Checking hoặc Savings mới trong hệ thống</t>
+  </si>
+  <si>
+    <t>Kiểm tra mở tài khoản Checking thành công, mở tài khoản Savings thành công, xác nhận tài khoản hiển thị trong Account Overview</t>
+  </si>
+  <si>
+    <t>TC_Nguyen: TC_12 → TC_17</t>
+  </si>
+  <si>
+    <t>1. Mở tài khoản Checking Account thành công
+2. Checking Account xuất hiện trong Account Overview
+3. Xem chi tiết Checking Account
+4. Mở tài khoản Savings Account thành công
+5. Savings Account xuất hiện trong Account Overview
+6. Chuyển tiền vào Savings Account mới mở</t>
+  </si>
+  <si>
+    <t>F4</t>
+  </si>
+  <si>
+    <t>Update Contact Info</t>
+  </si>
+  <si>
+    <t>Cập nhật thông tin liên hệ cá nhân của người dùng</t>
+  </si>
+  <si>
+    <t>Kiểm tra cập nhật thông tin hợp lệ thành công, validate trường bắt buộc không được để trống, dữ liệu được lưu bền vững</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>TC_Nguyen: TC_18 → TC_20</t>
+  </si>
+  <si>
+    <t>1. Cập nhật thông tin liên hệ với dữ liệu hợp lệ
+2. Cập nhật thất bại khi First Name để trống
+3. Xác nhận thông tin được lưu bền vững sau cập nhật</t>
+  </si>
+  <si>
+    <t>F5</t>
+  </si>
+  <si>
+    <t>GUI – Giao diện (Nguyên)</t>
+  </si>
+  <si>
+    <t>Kiểm tra các phần tử giao diện người dùng trên các màn hình do Nguyên phụ trách</t>
+  </si>
+  <si>
+    <t>Kiểm tra nút Login hiển thị và click được, textbox nhập liệu, link Register điều hướng đúng, thông báo lỗi hiển thị đúng vị trí và biến mất khi hợp lệ</t>
+  </si>
+  <si>
+    <t>LooknFeel</t>
+  </si>
+  <si>
+    <t>GUI TRANG LOGIN
+GUI TRANSFER FUNDS</t>
+  </si>
+  <si>
+    <t>TC_Nguyen: TC_21 → TC_26</t>
+  </si>
+  <si>
+    <t>1. Nút Login hiển thị và có thể click
+2. Textbox username và password nhận input
+3. Link Register điều hướng đến trang đăng ký
+4. Thông báo lỗi login hiển thị đúng vị trí
+5. Thông báo lỗi biến mất khi nhập thông tin hợp lệ
+6. Thông báo lỗi Transfer hiển thị đúng</t>
+  </si>
+  <si>
+    <t>F6</t>
+  </si>
+  <si>
+    <t>Smoke Test (Nguyên)</t>
+  </si>
+  <si>
+    <t>Kiểm tra nhanh các luồng nghiệp vụ chính do Nguyên phụ trách</t>
+  </si>
+  <si>
+    <t>Smoke test luồng Login → Transfer Funds → Logout thành công; kiểm tra các menu chính sau đăng nhập; kiểm tra session bảo mật sau Logout</t>
+  </si>
+  <si>
+    <t>Positive</t>
+  </si>
+  <si>
+    <t>TC_Nguyen: TC_27 → TC_29</t>
+  </si>
+  <si>
+    <t>1. Smoke test: Login → Transfer Funds → Logout thành công
+2. Kiểm tra các menu chính hiển thị sau khi đăng nhập
+3. Session bị hủy và bảo mật sau khi Logout</t>
+  </si>
+  <si>
+    <t>F7</t>
+  </si>
+  <si>
+    <t>Đăng ký tài khoản người dùng mới trên hệ thống ParaBank</t>
+  </si>
+  <si>
+    <t>Kiểm tra đăng ký thành công với dữ liệu hợp lệ, validate form (thiếu trường bắt buộc, trùng username, password không khớp)</t>
+  </si>
+  <si>
+    <t>TC_Tram: TC_01 → TC_05</t>
+  </si>
+  <si>
+    <t>1. Đăng ký tài khoản mới với đầy đủ thông tin hợp lệ
+2. Đăng ký thất bại khi thiếu trường bắt buộc
+3. Đăng ký thất bại khi username đã tồn tại
+4. Đăng ký thất bại khi password không khớp
+5. Đăng ký thất bại khi để trống toàn bộ form</t>
+  </si>
+  <si>
+    <t>F8</t>
+  </si>
+  <si>
+    <t>Thanh toán hóa đơn cho người nhận (payee)</t>
+  </si>
+  <si>
+    <t>Kiểm tra thanh toán thành công, validate thông tin payee (tên, tài khoản, số tiền), kiểm tra trường hợp dữ liệu không hợp lệ</t>
+  </si>
+  <si>
+    <t>TC_Tram: TC_06 → TC_09</t>
+  </si>
+  <si>
+    <t>1. Thanh toán hóa đơn thành công với thông tin hợp lệ
+2. Thanh toán thất bại khi thông tin payee không hợp lệ
+3. Validate trường bắt buộc để trống
+4. Validate số tiền thanh toán không hợp lệ</t>
+  </si>
+  <si>
+    <t>F9</t>
+  </si>
+  <si>
+    <t>Tìm kiếm giao dịch theo các tiêu chí khác nhau</t>
+  </si>
+  <si>
+    <t>Kiểm tra tìm kiếm theo Transaction ID, ngày giao dịch (From/To date), số tiền chính xác và khoảng số tiền; kiểm tra kết quả không tồn tại</t>
+  </si>
+  <si>
+    <t>TC_Tram: TC_10 → TC_20</t>
+  </si>
+  <si>
+    <t>1. Tìm giao dịch theo Transaction ID hợp lệ
+2. Tìm giao dịch theo ngày (khoảng ngày có kết quả)
+3. Tìm giao dịch theo số tiền chính xác
+4. Tìm giao dịch theo khoảng số tiền
+5. Tìm kiếm không có kết quả phù hợp
+6. Tìm kiếm với ID không tồn tại</t>
+  </si>
+  <si>
+    <t>F10</t>
+  </si>
+  <si>
+    <t>Yêu cầu vay vốn từ ngân hàng</t>
+  </si>
+  <si>
+    <t>Kiểm tra yêu cầu vay được duyệt khi đủ điều kiện (số dư đủ, down payment hợp lệ), bị từ chối khi không đủ điều kiện, validate dữ liệu đầu vào</t>
+  </si>
+  <si>
+    <t>TC_Tram: TC_21 → TC_25</t>
+  </si>
+  <si>
+    <t>1. Yêu cầu vay được duyệt (Approved) khi đủ điều kiện
+2. Yêu cầu vay bị từ chối (Denied) khi không đủ điều kiện
+3. Validate amount và down payment không hợp lệ
+4. Yêu cầu vay với loan amount = 0
+5. Yêu cầu vay với down payment vượt số dư</t>
+  </si>
+  <si>
+    <t>F11</t>
+  </si>
+  <si>
+    <t>GUI – Giao diện (Trâm)</t>
+  </si>
+  <si>
+    <t>Kiểm tra các phần tử giao diện người dùng trên các màn hình do Trâm phụ trách</t>
+  </si>
+  <si>
+    <t>Kiểm tra các phần tử UI trên trang Register (form, nút, thông báo lỗi) và trang Bill Pay (form điền thông tin, nút Submit)</t>
+  </si>
+  <si>
+    <t>GUI TRANG REGISTER
+GUI TRANG BILL PAY</t>
+  </si>
+  <si>
+    <t>TC_Tram: TC_26 → TC_29</t>
+  </si>
+  <si>
+    <t>1. Kiểm tra form Register hiển thị đầy đủ các trường
+2. Kiểm tra thông báo lỗi trên trang Register
+3. Kiểm tra form Bill Pay hiển thị đầy đủ các trường
+4. Kiểm tra nút Submit và Cancel trên Bill Pay</t>
+  </si>
+  <si>
+    <t>F12</t>
+  </si>
+  <si>
+    <t>Smoke Test (Trâm)</t>
+  </si>
+  <si>
+    <t>Kiểm tra nhanh các luồng nghiệp vụ chính do Trâm phụ trách</t>
+  </si>
+  <si>
+    <t>Smoke test luồng chính: Register → Login → Bill Pay → Logout thành công</t>
+  </si>
+  <si>
+    <t>TC_Tram: TC_30</t>
+  </si>
+  <si>
+    <t>1. Smoke test: Register → Login → Bill Pay → Logout thành công</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1607,8 +1951,44 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF374151"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF4444"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF006600"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF9900"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1617,7 +1997,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.0999786370433668"/>
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -1632,8 +2012,13 @@
         <fgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCFFCC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="69">
+  <borders count="70">
     <border>
       <left/>
       <right/>
@@ -2521,12 +2906,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="9" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="133">
+  <cellXfs count="145">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2534,10 +2934,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2546,353 +2946,385 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="9" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" applyFont="1" fillId="2" applyFill="1" borderId="17" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" applyFont="1" fillId="2" applyFill="1" borderId="18" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" applyFont="1" fillId="2" applyFill="1" borderId="20" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" applyFont="1" fillId="2" applyFill="1" borderId="21" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" applyFont="1" fillId="2" applyFill="1" borderId="19" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" applyFont="1" fillId="0" borderId="22" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" applyFont="1" fillId="0" borderId="22" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="9" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" applyFont="1" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" applyNumberFormat="1" fontId="0" fillId="0" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" applyFont="1" fillId="2" applyFill="1" borderId="32" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="24" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="35" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="35" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="36" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="37" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="34" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="38" applyBorder="1" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="38" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="39" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="40" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="41" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="42" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="4" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="43" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="44" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="43" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="6" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="5" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="45" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="46" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="48" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="47" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="33" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="49" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="5" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="50" applyBorder="1" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="50" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="13" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="52" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="31" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="13" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="60" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="60" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" applyFont="1" fillId="0" borderId="25" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="7" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="12" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" applyFont="1" fillId="0" borderId="51" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="51" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="4" applyFill="1" borderId="29" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="3" applyFill="1" borderId="55" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" applyFill="1" borderId="15" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="25" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="4" applyFill="1" borderId="28" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" applyFill="1" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" applyFill="1" borderId="13" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" applyFill="1" borderId="4" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" applyFill="1" borderId="6" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" applyFill="1" borderId="16" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" applyFill="1" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" applyFill="1" borderId="13" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="3" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" applyFill="1" borderId="60" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="60" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" applyFill="1" borderId="24" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" applyFill="1" borderId="5" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" applyFill="1" borderId="14" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" applyFill="1" borderId="60" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="60" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" applyFill="1" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" applyFill="1" borderId="63" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="63" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" applyFont="1" fillId="0" borderId="64" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="68" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="4" applyFill="1" borderId="65" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="58" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" applyFill="1" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="3" applyFill="1" borderId="10" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" applyFill="1" borderId="23" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="56" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="57" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="59" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="53" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" applyFont="1" fillId="0" borderId="53" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="7" applyFont="1" fillId="0" borderId="54" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" applyFont="1" fillId="0" borderId="25" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3212,29 +3644,29 @@
   <dimension ref="B2:C6"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" bestFit="1" width="46.19921875" customWidth="1"/>
-    <col min="3" max="3" bestFit="1" width="24.3984375" customWidth="1"/>
+    <col min="2" max="2" width="46.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="40.2" customHeight="1" s="1" customFormat="1">
+    <row r="2" spans="2:3" s="1" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="24" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="25"/>
     </row>
-    <row r="3" ht="40.2" customHeight="1" s="1" customFormat="1">
+    <row r="3" spans="2:3" s="1" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="25"/>
     </row>
-    <row r="4" ht="40.2" customHeight="1" s="1" customFormat="1">
+    <row r="4" spans="2:3" s="1" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="24" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="25"/>
     </row>
-    <row r="5" ht="40.2" customHeight="1" s="1" customFormat="1">
+    <row r="5" spans="2:3" s="1" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="24" t="s">
         <v>3</v>
       </c>
@@ -3242,7 +3674,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" ht="54.6" customHeight="1" s="1" customFormat="1">
+    <row r="6" spans="2:3" s="1" customFormat="1" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="26" t="s">
         <v>5</v>
       </c>
@@ -3252,32 +3684,595 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34E85281-F6BE-40FC-B302-A76A415B368D}">
+  <dimension ref="B1:N20"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="23.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="28" customWidth="1"/>
+    <col min="6" max="6" width="38" customWidth="1"/>
+    <col min="7" max="7" width="25" customWidth="1"/>
+    <col min="8" max="8" width="10.796875" customWidth="1"/>
+    <col min="9" max="11" width="12" customWidth="1"/>
+    <col min="12" max="13" width="22" customWidth="1"/>
+    <col min="14" max="14" width="50" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="133" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="2" spans="2:14" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="B2" s="134" t="s">
+        <v>470</v>
+      </c>
+      <c r="D2" s="135" t="s">
+        <v>471</v>
+      </c>
+      <c r="G2" s="134" t="s">
+        <v>472</v>
+      </c>
+      <c r="H2" s="135" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="B3" s="134" t="s">
+        <v>474</v>
+      </c>
+      <c r="D3" s="135" t="s">
+        <v>475</v>
+      </c>
+      <c r="G3" s="134" t="s">
+        <v>476</v>
+      </c>
+      <c r="H3" s="135" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B4" s="134" t="s">
+        <v>477</v>
+      </c>
+      <c r="D4" s="135" t="s">
+        <v>478</v>
+      </c>
+      <c r="G4" s="134" t="s">
+        <v>479</v>
+      </c>
+      <c r="H4" s="135" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B7" s="136" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="B8" s="134" t="s">
+        <v>481</v>
+      </c>
+      <c r="C8" s="134" t="s">
+        <v>482</v>
+      </c>
+      <c r="D8" s="134" t="s">
+        <v>483</v>
+      </c>
+      <c r="E8" s="134" t="s">
+        <v>484</v>
+      </c>
+      <c r="F8" s="134" t="s">
+        <v>485</v>
+      </c>
+      <c r="G8" s="134" t="s">
+        <v>486</v>
+      </c>
+      <c r="H8" s="134" t="s">
+        <v>487</v>
+      </c>
+      <c r="I8" s="134" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" s="134" t="s">
+        <v>488</v>
+      </c>
+      <c r="K8" s="134" t="s">
+        <v>489</v>
+      </c>
+      <c r="L8" s="134" t="s">
+        <v>490</v>
+      </c>
+      <c r="M8" s="134" t="s">
+        <v>491</v>
+      </c>
+      <c r="N8" s="134" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" ht="66" x14ac:dyDescent="0.25">
+      <c r="B9" s="137">
+        <v>1</v>
+      </c>
+      <c r="C9" s="137" t="s">
+        <v>493</v>
+      </c>
+      <c r="D9" s="138" t="s">
+        <v>494</v>
+      </c>
+      <c r="E9" s="139" t="s">
+        <v>495</v>
+      </c>
+      <c r="F9" s="140" t="s">
+        <v>496</v>
+      </c>
+      <c r="G9" s="137" t="s">
+        <v>497</v>
+      </c>
+      <c r="H9" s="141" t="s">
+        <v>498</v>
+      </c>
+      <c r="I9" s="142" t="s">
+        <v>499</v>
+      </c>
+      <c r="J9" s="143">
+        <v>5</v>
+      </c>
+      <c r="K9" s="139"/>
+      <c r="L9" s="139"/>
+      <c r="M9" s="139" t="s">
+        <v>500</v>
+      </c>
+      <c r="N9" s="139" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" ht="79.2" x14ac:dyDescent="0.25">
+      <c r="B10" s="137">
+        <v>2</v>
+      </c>
+      <c r="C10" s="137" t="s">
+        <v>502</v>
+      </c>
+      <c r="D10" s="138" t="s">
+        <v>503</v>
+      </c>
+      <c r="E10" s="139" t="s">
+        <v>504</v>
+      </c>
+      <c r="F10" s="140" t="s">
+        <v>505</v>
+      </c>
+      <c r="G10" s="137" t="s">
+        <v>497</v>
+      </c>
+      <c r="H10" s="141" t="s">
+        <v>498</v>
+      </c>
+      <c r="I10" s="142" t="s">
+        <v>499</v>
+      </c>
+      <c r="J10" s="143">
+        <v>6</v>
+      </c>
+      <c r="K10" s="139"/>
+      <c r="L10" s="139"/>
+      <c r="M10" s="139" t="s">
+        <v>506</v>
+      </c>
+      <c r="N10" s="139" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" ht="79.2" x14ac:dyDescent="0.25">
+      <c r="B11" s="137">
+        <v>3</v>
+      </c>
+      <c r="C11" s="137" t="s">
+        <v>508</v>
+      </c>
+      <c r="D11" s="138" t="s">
+        <v>509</v>
+      </c>
+      <c r="E11" s="139" t="s">
+        <v>510</v>
+      </c>
+      <c r="F11" s="140" t="s">
+        <v>511</v>
+      </c>
+      <c r="G11" s="137" t="s">
+        <v>497</v>
+      </c>
+      <c r="H11" s="141" t="s">
+        <v>498</v>
+      </c>
+      <c r="I11" s="142" t="s">
+        <v>499</v>
+      </c>
+      <c r="J11" s="143">
+        <v>6</v>
+      </c>
+      <c r="K11" s="139"/>
+      <c r="L11" s="139"/>
+      <c r="M11" s="139" t="s">
+        <v>512</v>
+      </c>
+      <c r="N11" s="139" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="B12" s="137">
+        <v>4</v>
+      </c>
+      <c r="C12" s="137" t="s">
+        <v>514</v>
+      </c>
+      <c r="D12" s="138" t="s">
+        <v>515</v>
+      </c>
+      <c r="E12" s="139" t="s">
+        <v>516</v>
+      </c>
+      <c r="F12" s="140" t="s">
+        <v>517</v>
+      </c>
+      <c r="G12" s="137" t="s">
+        <v>497</v>
+      </c>
+      <c r="H12" s="144" t="s">
+        <v>518</v>
+      </c>
+      <c r="I12" s="142" t="s">
+        <v>499</v>
+      </c>
+      <c r="J12" s="143">
+        <v>3</v>
+      </c>
+      <c r="K12" s="139"/>
+      <c r="L12" s="139"/>
+      <c r="M12" s="139" t="s">
+        <v>519</v>
+      </c>
+      <c r="N12" s="139" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" ht="79.2" x14ac:dyDescent="0.25">
+      <c r="B13" s="137">
+        <v>5</v>
+      </c>
+      <c r="C13" s="137" t="s">
+        <v>521</v>
+      </c>
+      <c r="D13" s="138" t="s">
+        <v>522</v>
+      </c>
+      <c r="E13" s="139" t="s">
+        <v>523</v>
+      </c>
+      <c r="F13" s="140" t="s">
+        <v>524</v>
+      </c>
+      <c r="G13" s="137" t="s">
+        <v>525</v>
+      </c>
+      <c r="H13" s="144" t="s">
+        <v>518</v>
+      </c>
+      <c r="I13" s="142" t="s">
+        <v>499</v>
+      </c>
+      <c r="J13" s="143">
+        <v>6</v>
+      </c>
+      <c r="K13" s="139"/>
+      <c r="L13" s="139" t="s">
+        <v>526</v>
+      </c>
+      <c r="M13" s="139" t="s">
+        <v>527</v>
+      </c>
+      <c r="N13" s="139" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="B14" s="137">
+        <v>6</v>
+      </c>
+      <c r="C14" s="137" t="s">
+        <v>529</v>
+      </c>
+      <c r="D14" s="138" t="s">
+        <v>530</v>
+      </c>
+      <c r="E14" s="139" t="s">
+        <v>531</v>
+      </c>
+      <c r="F14" s="140" t="s">
+        <v>532</v>
+      </c>
+      <c r="G14" s="137" t="s">
+        <v>533</v>
+      </c>
+      <c r="H14" s="141" t="s">
+        <v>498</v>
+      </c>
+      <c r="I14" s="142" t="s">
+        <v>499</v>
+      </c>
+      <c r="J14" s="143">
+        <v>3</v>
+      </c>
+      <c r="K14" s="139"/>
+      <c r="L14" s="139"/>
+      <c r="M14" s="139" t="s">
+        <v>534</v>
+      </c>
+      <c r="N14" s="139" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" ht="66" x14ac:dyDescent="0.25">
+      <c r="B15" s="137">
+        <v>7</v>
+      </c>
+      <c r="C15" s="137" t="s">
+        <v>536</v>
+      </c>
+      <c r="D15" s="138" t="s">
+        <v>275</v>
+      </c>
+      <c r="E15" s="139" t="s">
+        <v>537</v>
+      </c>
+      <c r="F15" s="140" t="s">
+        <v>538</v>
+      </c>
+      <c r="G15" s="137" t="s">
+        <v>497</v>
+      </c>
+      <c r="H15" s="141" t="s">
+        <v>498</v>
+      </c>
+      <c r="I15" s="142" t="s">
+        <v>499</v>
+      </c>
+      <c r="J15" s="143">
+        <v>5</v>
+      </c>
+      <c r="K15" s="139"/>
+      <c r="L15" s="139"/>
+      <c r="M15" s="139" t="s">
+        <v>539</v>
+      </c>
+      <c r="N15" s="139" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="B16" s="137">
+        <v>8</v>
+      </c>
+      <c r="C16" s="137" t="s">
+        <v>541</v>
+      </c>
+      <c r="D16" s="138" t="s">
+        <v>306</v>
+      </c>
+      <c r="E16" s="139" t="s">
+        <v>542</v>
+      </c>
+      <c r="F16" s="140" t="s">
+        <v>543</v>
+      </c>
+      <c r="G16" s="137" t="s">
+        <v>497</v>
+      </c>
+      <c r="H16" s="141" t="s">
+        <v>498</v>
+      </c>
+      <c r="I16" s="142" t="s">
+        <v>499</v>
+      </c>
+      <c r="J16" s="143">
+        <v>4</v>
+      </c>
+      <c r="K16" s="139"/>
+      <c r="L16" s="139"/>
+      <c r="M16" s="139" t="s">
+        <v>544</v>
+      </c>
+      <c r="N16" s="139" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14" ht="79.2" x14ac:dyDescent="0.25">
+      <c r="B17" s="137">
+        <v>9</v>
+      </c>
+      <c r="C17" s="137" t="s">
+        <v>546</v>
+      </c>
+      <c r="D17" s="138" t="s">
+        <v>331</v>
+      </c>
+      <c r="E17" s="139" t="s">
+        <v>547</v>
+      </c>
+      <c r="F17" s="140" t="s">
+        <v>548</v>
+      </c>
+      <c r="G17" s="137" t="s">
+        <v>497</v>
+      </c>
+      <c r="H17" s="144" t="s">
+        <v>518</v>
+      </c>
+      <c r="I17" s="142" t="s">
+        <v>499</v>
+      </c>
+      <c r="J17" s="143">
+        <v>11</v>
+      </c>
+      <c r="K17" s="139"/>
+      <c r="L17" s="139"/>
+      <c r="M17" s="139" t="s">
+        <v>549</v>
+      </c>
+      <c r="N17" s="139" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14" ht="66" x14ac:dyDescent="0.25">
+      <c r="B18" s="137">
+        <v>10</v>
+      </c>
+      <c r="C18" s="137" t="s">
+        <v>551</v>
+      </c>
+      <c r="D18" s="138" t="s">
+        <v>365</v>
+      </c>
+      <c r="E18" s="139" t="s">
+        <v>552</v>
+      </c>
+      <c r="F18" s="140" t="s">
+        <v>553</v>
+      </c>
+      <c r="G18" s="137" t="s">
+        <v>497</v>
+      </c>
+      <c r="H18" s="144" t="s">
+        <v>518</v>
+      </c>
+      <c r="I18" s="142" t="s">
+        <v>499</v>
+      </c>
+      <c r="J18" s="143">
+        <v>5</v>
+      </c>
+      <c r="K18" s="139"/>
+      <c r="L18" s="139"/>
+      <c r="M18" s="139" t="s">
+        <v>554</v>
+      </c>
+      <c r="N18" s="139" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="B19" s="137">
+        <v>11</v>
+      </c>
+      <c r="C19" s="137" t="s">
+        <v>556</v>
+      </c>
+      <c r="D19" s="138" t="s">
+        <v>557</v>
+      </c>
+      <c r="E19" s="139" t="s">
+        <v>558</v>
+      </c>
+      <c r="F19" s="140" t="s">
+        <v>559</v>
+      </c>
+      <c r="G19" s="137" t="s">
+        <v>525</v>
+      </c>
+      <c r="H19" s="144" t="s">
+        <v>518</v>
+      </c>
+      <c r="I19" s="142" t="s">
+        <v>499</v>
+      </c>
+      <c r="J19" s="143">
+        <v>4</v>
+      </c>
+      <c r="K19" s="139"/>
+      <c r="L19" s="139" t="s">
+        <v>560</v>
+      </c>
+      <c r="M19" s="139" t="s">
+        <v>561</v>
+      </c>
+      <c r="N19" s="139" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="B20" s="137">
+        <v>12</v>
+      </c>
+      <c r="C20" s="137" t="s">
+        <v>563</v>
+      </c>
+      <c r="D20" s="138" t="s">
+        <v>564</v>
+      </c>
+      <c r="E20" s="139" t="s">
+        <v>565</v>
+      </c>
+      <c r="F20" s="140" t="s">
+        <v>566</v>
+      </c>
+      <c r="G20" s="137" t="s">
+        <v>533</v>
+      </c>
+      <c r="H20" s="141" t="s">
+        <v>498</v>
+      </c>
+      <c r="I20" s="142" t="s">
+        <v>499</v>
+      </c>
+      <c r="J20" s="143">
+        <v>1</v>
+      </c>
+      <c r="K20" s="139"/>
+      <c r="L20" s="139"/>
+      <c r="M20" s="139" t="s">
+        <v>567</v>
+      </c>
+      <c r="N20" s="139" t="s">
+        <v>568</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{615D2199-4443-4EB8-91CE-D5359D3AE841}">
   <dimension ref="A1:P265"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" bestFit="1" width="17.19921875" customWidth="1"/>
-    <col min="3" max="3" bestFit="1" width="21.69921875" customWidth="1" style="6"/>
-    <col min="4" max="4" width="20.59765625" customWidth="1" style="6"/>
+    <col min="2" max="2" width="17.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.69921875" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.59765625" style="6" customWidth="1"/>
     <col min="5" max="5" width="17.5" customWidth="1"/>
-    <col min="6" max="6" bestFit="1" width="18.59765625" customWidth="1"/>
+    <col min="6" max="6" width="18.59765625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.3984375" customWidth="1"/>
     <col min="8" max="8" width="26" customWidth="1"/>
-    <col min="9" max="9" width="6.3984375" customWidth="1" style="6"/>
-    <col min="10" max="10" bestFit="1" width="34.69921875" customWidth="1"/>
-    <col min="11" max="12" width="27.3984375" customWidth="1"/>
-    <col min="13" max="13" width="19.59765625" customWidth="1"/>
+    <col min="9" max="9" width="6.3984375" style="6" customWidth="1"/>
+    <col min="10" max="10" width="34.69921875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="27.3984375" customWidth="1"/>
+    <col min="12" max="12" width="40.8984375" customWidth="1"/>
+    <col min="13" max="13" width="34.19921875" customWidth="1"/>
     <col min="14" max="14" width="15.59765625" customWidth="1"/>
-    <col min="15" max="15" width="11.69921875" customWidth="1"/>
+    <col min="15" max="15" width="76.59765625" customWidth="1"/>
     <col min="16" max="16" width="11.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40.2" customHeight="1">
+    <row r="1" spans="1:16" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
@@ -3298,7 +4293,7 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
     </row>
-    <row r="2" ht="40.2" customHeight="1">
+    <row r="2" spans="1:16" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="4" t="s">
         <v>8</v>
       </c>
@@ -3319,7 +4314,7 @@
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
     </row>
-    <row r="3" ht="40.2" customHeight="1">
+    <row r="3" spans="1:16" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="8"/>
       <c r="C3" s="9"/>
       <c r="D3" s="10"/>
@@ -3338,7 +4333,7 @@
       <c r="O3" s="8"/>
       <c r="P3" s="8"/>
     </row>
-    <row r="4" ht="40.2" customHeight="1" s="6" customFormat="1">
+    <row r="4" spans="1:16" s="6" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="13"/>
       <c r="B4" s="17" t="s">
         <v>12</v>
@@ -3386,7 +4381,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" ht="14.4" customHeight="1">
+    <row r="5" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7"/>
       <c r="B5" s="78">
         <v>1</v>
@@ -3426,7 +4421,7 @@
       <c r="O5" s="119"/>
       <c r="P5" s="121"/>
     </row>
-    <row r="6" ht="14.4" customHeight="1">
+    <row r="6" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7"/>
       <c r="B6" s="78"/>
       <c r="C6" s="73"/>
@@ -3452,7 +4447,7 @@
       <c r="O6" s="98"/>
       <c r="P6" s="88"/>
     </row>
-    <row r="7" ht="14.4" customHeight="1">
+    <row r="7" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7"/>
       <c r="B7" s="78"/>
       <c r="C7" s="73"/>
@@ -3478,7 +4473,7 @@
       <c r="O7" s="98"/>
       <c r="P7" s="88"/>
     </row>
-    <row r="8" ht="14.4" customHeight="1">
+    <row r="8" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7"/>
       <c r="B8" s="78"/>
       <c r="C8" s="73"/>
@@ -3502,7 +4497,7 @@
       <c r="O8" s="98"/>
       <c r="P8" s="88"/>
     </row>
-    <row r="9" ht="14.4" customHeight="1">
+    <row r="9" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7"/>
       <c r="B9" s="78"/>
       <c r="C9" s="74"/>
@@ -3526,7 +4521,7 @@
       <c r="O9" s="99"/>
       <c r="P9" s="122"/>
     </row>
-    <row r="10" ht="14.4" customHeight="1">
+    <row r="10" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7"/>
       <c r="B10" s="123">
         <v>2</v>
@@ -3566,7 +4561,7 @@
       <c r="O10" s="105"/>
       <c r="P10" s="87"/>
     </row>
-    <row r="11" ht="14.4" customHeight="1">
+    <row r="11" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7"/>
       <c r="B11" s="124"/>
       <c r="C11" s="73"/>
@@ -3590,7 +4585,7 @@
       <c r="O11" s="98"/>
       <c r="P11" s="88"/>
     </row>
-    <row r="12" ht="14.4" customHeight="1">
+    <row r="12" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7"/>
       <c r="B12" s="124"/>
       <c r="C12" s="73"/>
@@ -3614,7 +4609,7 @@
       <c r="O12" s="98"/>
       <c r="P12" s="88"/>
     </row>
-    <row r="13">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="7"/>
       <c r="B13" s="124"/>
       <c r="C13" s="73"/>
@@ -3636,7 +4631,7 @@
       <c r="O13" s="98"/>
       <c r="P13" s="88"/>
     </row>
-    <row r="14" ht="14.4" customHeight="1">
+    <row r="14" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7"/>
       <c r="B14" s="125"/>
       <c r="C14" s="74"/>
@@ -3658,7 +4653,7 @@
       <c r="O14" s="99"/>
       <c r="P14" s="122"/>
     </row>
-    <row r="15" ht="14.4" customHeight="1">
+    <row r="15" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7"/>
       <c r="B15" s="78">
         <v>3</v>
@@ -3698,7 +4693,7 @@
       <c r="O15" s="105"/>
       <c r="P15" s="87"/>
     </row>
-    <row r="16" ht="14.4" customHeight="1">
+    <row r="16" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7"/>
       <c r="B16" s="78"/>
       <c r="C16" s="73"/>
@@ -3722,7 +4717,7 @@
       <c r="O16" s="98"/>
       <c r="P16" s="88"/>
     </row>
-    <row r="17" ht="14.4" customHeight="1">
+    <row r="17" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7"/>
       <c r="B17" s="79"/>
       <c r="C17" s="74"/>
@@ -3744,7 +4739,7 @@
       <c r="O17" s="99"/>
       <c r="P17" s="89"/>
     </row>
-    <row r="18" ht="14.4" customHeight="1">
+    <row r="18" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7"/>
       <c r="B18" s="123">
         <v>4</v>
@@ -3784,7 +4779,7 @@
       </c>
       <c r="P18" s="87"/>
     </row>
-    <row r="19" ht="14.4" customHeight="1">
+    <row r="19" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7"/>
       <c r="B19" s="124"/>
       <c r="C19" s="73"/>
@@ -3808,7 +4803,7 @@
       <c r="O19" s="98"/>
       <c r="P19" s="88"/>
     </row>
-    <row r="20" ht="14.4" customHeight="1">
+    <row r="20" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7"/>
       <c r="B20" s="124"/>
       <c r="C20" s="73"/>
@@ -3830,7 +4825,7 @@
       <c r="O20" s="98"/>
       <c r="P20" s="88"/>
     </row>
-    <row r="21" ht="14.4" customHeight="1">
+    <row r="21" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7"/>
       <c r="B21" s="125"/>
       <c r="C21" s="74"/>
@@ -3852,7 +4847,7 @@
       <c r="O21" s="99"/>
       <c r="P21" s="89"/>
     </row>
-    <row r="22" ht="14.4" customHeight="1">
+    <row r="22" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7"/>
       <c r="B22" s="78">
         <v>5</v>
@@ -3892,7 +4887,7 @@
       <c r="O22" s="119"/>
       <c r="P22" s="121"/>
     </row>
-    <row r="23" ht="14.4" customHeight="1">
+    <row r="23" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7"/>
       <c r="B23" s="78"/>
       <c r="C23" s="73"/>
@@ -3914,7 +4909,7 @@
       <c r="O23" s="98"/>
       <c r="P23" s="88"/>
     </row>
-    <row r="24" ht="14.4" customHeight="1">
+    <row r="24" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7"/>
       <c r="B24" s="78"/>
       <c r="C24" s="73"/>
@@ -3936,7 +4931,7 @@
       <c r="O24" s="98"/>
       <c r="P24" s="88"/>
     </row>
-    <row r="25" ht="14.4" customHeight="1">
+    <row r="25" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7"/>
       <c r="B25" s="79"/>
       <c r="C25" s="74"/>
@@ -3958,7 +4953,7 @@
       <c r="O25" s="120"/>
       <c r="P25" s="122"/>
     </row>
-    <row r="26" ht="14.4" customHeight="1">
+    <row r="26" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7"/>
       <c r="B26" s="78">
         <v>6</v>
@@ -3992,7 +4987,7 @@
       <c r="O26" s="105"/>
       <c r="P26" s="87"/>
     </row>
-    <row r="27" ht="14.4" customHeight="1">
+    <row r="27" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7"/>
       <c r="B27" s="78"/>
       <c r="C27" s="73"/>
@@ -4016,7 +5011,7 @@
       <c r="O27" s="98"/>
       <c r="P27" s="88"/>
     </row>
-    <row r="28" ht="14.4" customHeight="1">
+    <row r="28" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7"/>
       <c r="B28" s="78"/>
       <c r="C28" s="73"/>
@@ -4040,7 +5035,7 @@
       <c r="O28" s="98"/>
       <c r="P28" s="88"/>
     </row>
-    <row r="29" ht="14.4" customHeight="1">
+    <row r="29" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7"/>
       <c r="B29" s="78"/>
       <c r="C29" s="73"/>
@@ -4064,7 +5059,7 @@
       <c r="O29" s="98"/>
       <c r="P29" s="88"/>
     </row>
-    <row r="30" ht="14.4" customHeight="1">
+    <row r="30" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="7"/>
       <c r="B30" s="78"/>
       <c r="C30" s="73"/>
@@ -4086,7 +5081,7 @@
       <c r="O30" s="98"/>
       <c r="P30" s="88"/>
     </row>
-    <row r="31" ht="14.4" customHeight="1">
+    <row r="31" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="7"/>
       <c r="B31" s="78"/>
       <c r="C31" s="73"/>
@@ -4108,7 +5103,7 @@
       <c r="O31" s="98"/>
       <c r="P31" s="88"/>
     </row>
-    <row r="32" ht="14.4" customHeight="1">
+    <row r="32" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="7"/>
       <c r="B32" s="78"/>
       <c r="C32" s="73"/>
@@ -4128,7 +5123,7 @@
       <c r="O32" s="98"/>
       <c r="P32" s="88"/>
     </row>
-    <row r="33" ht="14.4" customHeight="1">
+    <row r="33" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="7"/>
       <c r="B33" s="78"/>
       <c r="C33" s="73"/>
@@ -4148,7 +5143,7 @@
       <c r="O33" s="98"/>
       <c r="P33" s="88"/>
     </row>
-    <row r="34" ht="14.4" customHeight="1">
+    <row r="34" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="7"/>
       <c r="B34" s="78"/>
       <c r="C34" s="73"/>
@@ -4168,7 +5163,7 @@
       <c r="O34" s="98"/>
       <c r="P34" s="88"/>
     </row>
-    <row r="35" ht="14.4" customHeight="1">
+    <row r="35" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="7"/>
       <c r="B35" s="79"/>
       <c r="C35" s="74"/>
@@ -4188,7 +5183,7 @@
       <c r="O35" s="99"/>
       <c r="P35" s="89"/>
     </row>
-    <row r="36" ht="14.4" customHeight="1">
+    <row r="36" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="7"/>
       <c r="B36" s="78">
         <v>7</v>
@@ -4222,7 +5217,7 @@
       <c r="O36" s="98"/>
       <c r="P36" s="100"/>
     </row>
-    <row r="37" ht="14.4" customHeight="1">
+    <row r="37" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="7"/>
       <c r="B37" s="78"/>
       <c r="C37" s="73"/>
@@ -4246,7 +5241,7 @@
       <c r="O37" s="98"/>
       <c r="P37" s="88"/>
     </row>
-    <row r="38" ht="14.4" customHeight="1">
+    <row r="38" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="7"/>
       <c r="B38" s="78"/>
       <c r="C38" s="73"/>
@@ -4270,7 +5265,7 @@
       <c r="O38" s="98"/>
       <c r="P38" s="88"/>
     </row>
-    <row r="39" ht="14.4" customHeight="1">
+    <row r="39" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="7"/>
       <c r="B39" s="78"/>
       <c r="C39" s="73"/>
@@ -4290,7 +5285,7 @@
       <c r="O39" s="98"/>
       <c r="P39" s="88"/>
     </row>
-    <row r="40" ht="14.4" customHeight="1">
+    <row r="40" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7"/>
       <c r="B40" s="78"/>
       <c r="C40" s="73"/>
@@ -4310,7 +5305,7 @@
       <c r="O40" s="98"/>
       <c r="P40" s="88"/>
     </row>
-    <row r="41" ht="14.4" customHeight="1">
+    <row r="41" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="7"/>
       <c r="B41" s="78"/>
       <c r="C41" s="73"/>
@@ -4330,7 +5325,7 @@
       <c r="O41" s="98"/>
       <c r="P41" s="88"/>
     </row>
-    <row r="42" ht="14.4" customHeight="1">
+    <row r="42" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="7"/>
       <c r="B42" s="78"/>
       <c r="C42" s="73"/>
@@ -4350,7 +5345,7 @@
       <c r="O42" s="98"/>
       <c r="P42" s="88"/>
     </row>
-    <row r="43" ht="14.4" customHeight="1">
+    <row r="43" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="7"/>
       <c r="B43" s="78"/>
       <c r="C43" s="73"/>
@@ -4370,7 +5365,7 @@
       <c r="O43" s="98"/>
       <c r="P43" s="88"/>
     </row>
-    <row r="44" ht="14.4" customHeight="1">
+    <row r="44" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="7"/>
       <c r="B44" s="78"/>
       <c r="C44" s="73"/>
@@ -4390,7 +5385,7 @@
       <c r="O44" s="98"/>
       <c r="P44" s="88"/>
     </row>
-    <row r="45" ht="14.4" customHeight="1">
+    <row r="45" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="7"/>
       <c r="B45" s="79"/>
       <c r="C45" s="74"/>
@@ -4410,7 +5405,7 @@
       <c r="O45" s="99"/>
       <c r="P45" s="89"/>
     </row>
-    <row r="46" ht="27.6">
+    <row r="46" spans="1:16" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A46" s="7"/>
       <c r="B46" s="78">
         <v>8</v>
@@ -4444,7 +5439,7 @@
       <c r="O46" s="119"/>
       <c r="P46" s="121"/>
     </row>
-    <row r="47" ht="27.6">
+    <row r="47" spans="1:16" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A47" s="7"/>
       <c r="B47" s="78"/>
       <c r="C47" s="73"/>
@@ -4466,7 +5461,7 @@
       <c r="O47" s="98"/>
       <c r="P47" s="88"/>
     </row>
-    <row r="48" ht="14.4" customHeight="1">
+    <row r="48" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="7"/>
       <c r="B48" s="78"/>
       <c r="C48" s="73"/>
@@ -4490,7 +5485,7 @@
       <c r="O48" s="98"/>
       <c r="P48" s="88"/>
     </row>
-    <row r="49" ht="14.4" customHeight="1">
+    <row r="49" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="7"/>
       <c r="B49" s="78"/>
       <c r="C49" s="73"/>
@@ -4514,7 +5509,7 @@
       <c r="O49" s="98"/>
       <c r="P49" s="88"/>
     </row>
-    <row r="50" ht="14.4" customHeight="1">
+    <row r="50" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="7"/>
       <c r="B50" s="78"/>
       <c r="C50" s="73"/>
@@ -4534,7 +5529,7 @@
       <c r="O50" s="98"/>
       <c r="P50" s="88"/>
     </row>
-    <row r="51" ht="14.4" customHeight="1">
+    <row r="51" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="7"/>
       <c r="B51" s="78"/>
       <c r="C51" s="73"/>
@@ -4554,7 +5549,7 @@
       <c r="O51" s="98"/>
       <c r="P51" s="88"/>
     </row>
-    <row r="52" ht="14.4" customHeight="1">
+    <row r="52" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="7"/>
       <c r="B52" s="78"/>
       <c r="C52" s="73"/>
@@ -4574,7 +5569,7 @@
       <c r="O52" s="98"/>
       <c r="P52" s="88"/>
     </row>
-    <row r="53" ht="14.4" customHeight="1">
+    <row r="53" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="7"/>
       <c r="B53" s="78"/>
       <c r="C53" s="73"/>
@@ -4594,7 +5589,7 @@
       <c r="O53" s="98"/>
       <c r="P53" s="88"/>
     </row>
-    <row r="54" ht="14.4" customHeight="1">
+    <row r="54" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="7"/>
       <c r="B54" s="78"/>
       <c r="C54" s="73"/>
@@ -4614,7 +5609,7 @@
       <c r="O54" s="98"/>
       <c r="P54" s="88"/>
     </row>
-    <row r="55" ht="14.4" customHeight="1">
+    <row r="55" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="7"/>
       <c r="B55" s="79"/>
       <c r="C55" s="74"/>
@@ -4634,7 +5629,7 @@
       <c r="O55" s="99"/>
       <c r="P55" s="89"/>
     </row>
-    <row r="56" ht="14.4" customHeight="1">
+    <row r="56" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="7"/>
       <c r="B56" s="78">
         <v>9</v>
@@ -4668,7 +5663,7 @@
       <c r="O56" s="98"/>
       <c r="P56" s="100"/>
     </row>
-    <row r="57" ht="14.4" customHeight="1">
+    <row r="57" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="7"/>
       <c r="B57" s="78"/>
       <c r="C57" s="73"/>
@@ -4692,7 +5687,7 @@
       <c r="O57" s="98"/>
       <c r="P57" s="88"/>
     </row>
-    <row r="58" ht="14.4" customHeight="1">
+    <row r="58" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="7"/>
       <c r="B58" s="78"/>
       <c r="C58" s="73"/>
@@ -4716,7 +5711,7 @@
       <c r="O58" s="98"/>
       <c r="P58" s="88"/>
     </row>
-    <row r="59" ht="14.4" customHeight="1">
+    <row r="59" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="7"/>
       <c r="B59" s="78"/>
       <c r="C59" s="73"/>
@@ -4740,7 +5735,7 @@
       <c r="O59" s="98"/>
       <c r="P59" s="88"/>
     </row>
-    <row r="60" ht="14.4" customHeight="1">
+    <row r="60" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="7"/>
       <c r="B60" s="78"/>
       <c r="C60" s="73"/>
@@ -4762,7 +5757,7 @@
       <c r="O60" s="98"/>
       <c r="P60" s="88"/>
     </row>
-    <row r="61" ht="14.4" customHeight="1">
+    <row r="61" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="7"/>
       <c r="B61" s="78"/>
       <c r="C61" s="73"/>
@@ -4784,7 +5779,7 @@
       <c r="O61" s="98"/>
       <c r="P61" s="88"/>
     </row>
-    <row r="62" ht="14.4" customHeight="1">
+    <row r="62" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="7"/>
       <c r="B62" s="78"/>
       <c r="C62" s="73"/>
@@ -4804,7 +5799,7 @@
       <c r="O62" s="98"/>
       <c r="P62" s="88"/>
     </row>
-    <row r="63" ht="14.4" customHeight="1">
+    <row r="63" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="7"/>
       <c r="B63" s="78"/>
       <c r="C63" s="73"/>
@@ -4824,7 +5819,7 @@
       <c r="O63" s="98"/>
       <c r="P63" s="88"/>
     </row>
-    <row r="64" ht="14.4" customHeight="1">
+    <row r="64" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="7"/>
       <c r="B64" s="78"/>
       <c r="C64" s="73"/>
@@ -4844,7 +5839,7 @@
       <c r="O64" s="98"/>
       <c r="P64" s="88"/>
     </row>
-    <row r="65" ht="14.4" customHeight="1">
+    <row r="65" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="7"/>
       <c r="B65" s="79"/>
       <c r="C65" s="74"/>
@@ -4864,7 +5859,7 @@
       <c r="O65" s="99"/>
       <c r="P65" s="89"/>
     </row>
-    <row r="66" ht="14.4" customHeight="1">
+    <row r="66" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="7"/>
       <c r="B66" s="78">
         <v>10</v>
@@ -4898,7 +5893,7 @@
       <c r="O66" s="119"/>
       <c r="P66" s="121"/>
     </row>
-    <row r="67" ht="14.4" customHeight="1">
+    <row r="67" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="7"/>
       <c r="B67" s="78"/>
       <c r="C67" s="73"/>
@@ -4920,7 +5915,7 @@
       <c r="O67" s="98"/>
       <c r="P67" s="88"/>
     </row>
-    <row r="68" ht="14.4" customHeight="1">
+    <row r="68" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="7"/>
       <c r="B68" s="78"/>
       <c r="C68" s="73"/>
@@ -4944,7 +5939,7 @@
       <c r="O68" s="98"/>
       <c r="P68" s="88"/>
     </row>
-    <row r="69" ht="14.4" customHeight="1">
+    <row r="69" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="7"/>
       <c r="B69" s="78"/>
       <c r="C69" s="73"/>
@@ -4966,7 +5961,7 @@
       <c r="O69" s="98"/>
       <c r="P69" s="88"/>
     </row>
-    <row r="70" ht="14.4" customHeight="1">
+    <row r="70" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="7"/>
       <c r="B70" s="78"/>
       <c r="C70" s="73"/>
@@ -4988,7 +5983,7 @@
       <c r="O70" s="98"/>
       <c r="P70" s="88"/>
     </row>
-    <row r="71" ht="14.4" customHeight="1">
+    <row r="71" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="7"/>
       <c r="B71" s="78"/>
       <c r="C71" s="73"/>
@@ -5008,7 +6003,7 @@
       <c r="O71" s="98"/>
       <c r="P71" s="88"/>
     </row>
-    <row r="72" ht="14.4" customHeight="1">
+    <row r="72" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="7"/>
       <c r="B72" s="78"/>
       <c r="C72" s="73"/>
@@ -5028,7 +6023,7 @@
       <c r="O72" s="98"/>
       <c r="P72" s="88"/>
     </row>
-    <row r="73" ht="14.4" customHeight="1">
+    <row r="73" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="7"/>
       <c r="B73" s="78"/>
       <c r="C73" s="73"/>
@@ -5048,7 +6043,7 @@
       <c r="O73" s="98"/>
       <c r="P73" s="88"/>
     </row>
-    <row r="74" ht="14.4" customHeight="1">
+    <row r="74" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="7"/>
       <c r="B74" s="78"/>
       <c r="C74" s="73"/>
@@ -5068,7 +6063,7 @@
       <c r="O74" s="98"/>
       <c r="P74" s="88"/>
     </row>
-    <row r="75" ht="14.4" customHeight="1">
+    <row r="75" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="7"/>
       <c r="B75" s="79"/>
       <c r="C75" s="74"/>
@@ -5088,7 +6083,7 @@
       <c r="O75" s="99"/>
       <c r="P75" s="89"/>
     </row>
-    <row r="76" ht="14.4" customHeight="1">
+    <row r="76" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="7"/>
       <c r="B76" s="78">
         <v>11</v>
@@ -5122,7 +6117,7 @@
       <c r="O76" s="98"/>
       <c r="P76" s="100"/>
     </row>
-    <row r="77" ht="14.4" customHeight="1">
+    <row r="77" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="7"/>
       <c r="B77" s="78"/>
       <c r="C77" s="73"/>
@@ -5144,7 +6139,7 @@
       <c r="O77" s="98"/>
       <c r="P77" s="88"/>
     </row>
-    <row r="78" ht="14.4" customHeight="1">
+    <row r="78" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="7"/>
       <c r="B78" s="78"/>
       <c r="C78" s="73"/>
@@ -5168,7 +6163,7 @@
       <c r="O78" s="98"/>
       <c r="P78" s="88"/>
     </row>
-    <row r="79" ht="14.4" customHeight="1">
+    <row r="79" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="7"/>
       <c r="B79" s="78"/>
       <c r="C79" s="73"/>
@@ -5190,7 +6185,7 @@
       <c r="O79" s="98"/>
       <c r="P79" s="88"/>
     </row>
-    <row r="80" ht="14.4" customHeight="1">
+    <row r="80" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="7"/>
       <c r="B80" s="78"/>
       <c r="C80" s="73"/>
@@ -5212,7 +6207,7 @@
       <c r="O80" s="98"/>
       <c r="P80" s="88"/>
     </row>
-    <row r="81" ht="14.4" customHeight="1">
+    <row r="81" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="7"/>
       <c r="B81" s="78"/>
       <c r="C81" s="73"/>
@@ -5232,7 +6227,7 @@
       <c r="O81" s="98"/>
       <c r="P81" s="88"/>
     </row>
-    <row r="82" ht="14.4" customHeight="1">
+    <row r="82" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="7"/>
       <c r="B82" s="78"/>
       <c r="C82" s="73"/>
@@ -5252,7 +6247,7 @@
       <c r="O82" s="98"/>
       <c r="P82" s="88"/>
     </row>
-    <row r="83" ht="14.4" customHeight="1">
+    <row r="83" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="7"/>
       <c r="B83" s="78"/>
       <c r="C83" s="73"/>
@@ -5272,7 +6267,7 @@
       <c r="O83" s="98"/>
       <c r="P83" s="88"/>
     </row>
-    <row r="84" ht="14.4" customHeight="1">
+    <row r="84" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="7"/>
       <c r="B84" s="78"/>
       <c r="C84" s="73"/>
@@ -5292,7 +6287,7 @@
       <c r="O84" s="98"/>
       <c r="P84" s="88"/>
     </row>
-    <row r="85" ht="14.4" customHeight="1">
+    <row r="85" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="7"/>
       <c r="B85" s="79"/>
       <c r="C85" s="74"/>
@@ -5312,7 +6307,7 @@
       <c r="O85" s="99"/>
       <c r="P85" s="89"/>
     </row>
-    <row r="86" ht="14.4" customHeight="1">
+    <row r="86" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="7"/>
       <c r="B86" s="78">
         <v>12</v>
@@ -5346,7 +6341,7 @@
       <c r="O86" s="119"/>
       <c r="P86" s="121"/>
     </row>
-    <row r="87" ht="14.4" customHeight="1">
+    <row r="87" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="7"/>
       <c r="B87" s="78"/>
       <c r="C87" s="73"/>
@@ -5370,7 +6365,7 @@
       <c r="O87" s="98"/>
       <c r="P87" s="88"/>
     </row>
-    <row r="88" ht="14.4" customHeight="1">
+    <row r="88" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="7"/>
       <c r="B88" s="78"/>
       <c r="C88" s="73"/>
@@ -5394,7 +6389,7 @@
       <c r="O88" s="98"/>
       <c r="P88" s="88"/>
     </row>
-    <row r="89" ht="14.4" customHeight="1">
+    <row r="89" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="7"/>
       <c r="B89" s="78"/>
       <c r="C89" s="73"/>
@@ -5416,7 +6411,7 @@
       <c r="O89" s="98"/>
       <c r="P89" s="88"/>
     </row>
-    <row r="90" ht="14.4" customHeight="1">
+    <row r="90" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="7"/>
       <c r="B90" s="78"/>
       <c r="C90" s="73"/>
@@ -5438,7 +6433,7 @@
       <c r="O90" s="98"/>
       <c r="P90" s="88"/>
     </row>
-    <row r="91" ht="14.4" customHeight="1">
+    <row r="91" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="7"/>
       <c r="B91" s="78"/>
       <c r="C91" s="73"/>
@@ -5458,7 +6453,7 @@
       <c r="O91" s="98"/>
       <c r="P91" s="88"/>
     </row>
-    <row r="92" ht="14.4" customHeight="1">
+    <row r="92" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="7"/>
       <c r="B92" s="78"/>
       <c r="C92" s="73"/>
@@ -5478,7 +6473,7 @@
       <c r="O92" s="98"/>
       <c r="P92" s="88"/>
     </row>
-    <row r="93" ht="14.4" customHeight="1">
+    <row r="93" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="7"/>
       <c r="B93" s="78"/>
       <c r="C93" s="73"/>
@@ -5498,7 +6493,7 @@
       <c r="O93" s="98"/>
       <c r="P93" s="88"/>
     </row>
-    <row r="94" ht="14.4" customHeight="1">
+    <row r="94" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="7"/>
       <c r="B94" s="78"/>
       <c r="C94" s="73"/>
@@ -5518,7 +6513,7 @@
       <c r="O94" s="98"/>
       <c r="P94" s="88"/>
     </row>
-    <row r="95" ht="14.4" customHeight="1">
+    <row r="95" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="7"/>
       <c r="B95" s="79"/>
       <c r="C95" s="74"/>
@@ -5538,7 +6533,7 @@
       <c r="O95" s="99"/>
       <c r="P95" s="89"/>
     </row>
-    <row r="96" ht="14.4" customHeight="1">
+    <row r="96" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="7"/>
       <c r="B96" s="78">
         <v>13</v>
@@ -5572,7 +6567,7 @@
       <c r="O96" s="98"/>
       <c r="P96" s="100"/>
     </row>
-    <row r="97" ht="14.4" customHeight="1">
+    <row r="97" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="7"/>
       <c r="B97" s="78"/>
       <c r="C97" s="73"/>
@@ -5594,7 +6589,7 @@
       <c r="O97" s="98"/>
       <c r="P97" s="88"/>
     </row>
-    <row r="98" ht="14.4" customHeight="1">
+    <row r="98" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="7"/>
       <c r="B98" s="78"/>
       <c r="C98" s="73"/>
@@ -5618,7 +6613,7 @@
       <c r="O98" s="98"/>
       <c r="P98" s="88"/>
     </row>
-    <row r="99" ht="14.4" customHeight="1">
+    <row r="99" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="7"/>
       <c r="B99" s="78"/>
       <c r="C99" s="73"/>
@@ -5640,7 +6635,7 @@
       <c r="O99" s="98"/>
       <c r="P99" s="88"/>
     </row>
-    <row r="100" ht="14.4" customHeight="1">
+    <row r="100" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="7"/>
       <c r="B100" s="78"/>
       <c r="C100" s="73"/>
@@ -5660,7 +6655,7 @@
       <c r="O100" s="98"/>
       <c r="P100" s="88"/>
     </row>
-    <row r="101" ht="14.4" customHeight="1">
+    <row r="101" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="7"/>
       <c r="B101" s="78"/>
       <c r="C101" s="73"/>
@@ -5680,7 +6675,7 @@
       <c r="O101" s="98"/>
       <c r="P101" s="88"/>
     </row>
-    <row r="102" ht="14.4" customHeight="1">
+    <row r="102" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="7"/>
       <c r="B102" s="78"/>
       <c r="C102" s="73"/>
@@ -5700,7 +6695,7 @@
       <c r="O102" s="98"/>
       <c r="P102" s="88"/>
     </row>
-    <row r="103" ht="14.4" customHeight="1">
+    <row r="103" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="7"/>
       <c r="B103" s="78"/>
       <c r="C103" s="73"/>
@@ -5720,7 +6715,7 @@
       <c r="O103" s="98"/>
       <c r="P103" s="88"/>
     </row>
-    <row r="104" ht="14.4" customHeight="1">
+    <row r="104" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="7"/>
       <c r="B104" s="78"/>
       <c r="C104" s="73"/>
@@ -5740,7 +6735,7 @@
       <c r="O104" s="98"/>
       <c r="P104" s="88"/>
     </row>
-    <row r="105" ht="14.4" customHeight="1">
+    <row r="105" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="7"/>
       <c r="B105" s="79"/>
       <c r="C105" s="74"/>
@@ -5760,7 +6755,7 @@
       <c r="O105" s="99"/>
       <c r="P105" s="89"/>
     </row>
-    <row r="106" ht="14.4" customHeight="1">
+    <row r="106" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="7"/>
       <c r="B106" s="78">
         <v>14</v>
@@ -5794,7 +6789,7 @@
       <c r="O106" s="119"/>
       <c r="P106" s="121"/>
     </row>
-    <row r="107" ht="14.4" customHeight="1">
+    <row r="107" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="7"/>
       <c r="B107" s="78"/>
       <c r="C107" s="73"/>
@@ -5816,7 +6811,7 @@
       <c r="O107" s="98"/>
       <c r="P107" s="88"/>
     </row>
-    <row r="108" ht="14.4" customHeight="1">
+    <row r="108" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="7"/>
       <c r="B108" s="78"/>
       <c r="C108" s="73"/>
@@ -5838,7 +6833,7 @@
       <c r="O108" s="98"/>
       <c r="P108" s="88"/>
     </row>
-    <row r="109" ht="14.4" customHeight="1">
+    <row r="109" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="7"/>
       <c r="B109" s="78"/>
       <c r="C109" s="73"/>
@@ -5860,7 +6855,7 @@
       <c r="O109" s="98"/>
       <c r="P109" s="88"/>
     </row>
-    <row r="110" ht="14.4" customHeight="1">
+    <row r="110" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="7"/>
       <c r="B110" s="78"/>
       <c r="C110" s="73"/>
@@ -5880,7 +6875,7 @@
       <c r="O110" s="98"/>
       <c r="P110" s="88"/>
     </row>
-    <row r="111" ht="14.4" customHeight="1">
+    <row r="111" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="7"/>
       <c r="B111" s="78"/>
       <c r="C111" s="73"/>
@@ -5900,7 +6895,7 @@
       <c r="O111" s="98"/>
       <c r="P111" s="88"/>
     </row>
-    <row r="112" ht="14.4" customHeight="1">
+    <row r="112" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="7"/>
       <c r="B112" s="78"/>
       <c r="C112" s="73"/>
@@ -5920,7 +6915,7 @@
       <c r="O112" s="98"/>
       <c r="P112" s="88"/>
     </row>
-    <row r="113" ht="14.4" customHeight="1">
+    <row r="113" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="7"/>
       <c r="B113" s="78"/>
       <c r="C113" s="73"/>
@@ -5940,7 +6935,7 @@
       <c r="O113" s="98"/>
       <c r="P113" s="88"/>
     </row>
-    <row r="114" ht="14.4" customHeight="1">
+    <row r="114" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="7"/>
       <c r="B114" s="78"/>
       <c r="C114" s="73"/>
@@ -5960,7 +6955,7 @@
       <c r="O114" s="98"/>
       <c r="P114" s="88"/>
     </row>
-    <row r="115" ht="14.4" customHeight="1">
+    <row r="115" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="7"/>
       <c r="B115" s="79"/>
       <c r="C115" s="74"/>
@@ -5980,7 +6975,7 @@
       <c r="O115" s="99"/>
       <c r="P115" s="89"/>
     </row>
-    <row r="116" ht="14.4" customHeight="1">
+    <row r="116" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="7"/>
       <c r="B116" s="78">
         <v>15</v>
@@ -6014,7 +7009,7 @@
       <c r="O116" s="119"/>
       <c r="P116" s="121"/>
     </row>
-    <row r="117" ht="14.4" customHeight="1">
+    <row r="117" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="7"/>
       <c r="B117" s="78"/>
       <c r="C117" s="73"/>
@@ -6038,7 +7033,7 @@
       <c r="O117" s="98"/>
       <c r="P117" s="88"/>
     </row>
-    <row r="118" ht="14.4" customHeight="1">
+    <row r="118" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="7"/>
       <c r="B118" s="78"/>
       <c r="C118" s="73"/>
@@ -6062,7 +7057,7 @@
       <c r="O118" s="98"/>
       <c r="P118" s="88"/>
     </row>
-    <row r="119" ht="14.4" customHeight="1">
+    <row r="119" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="7"/>
       <c r="B119" s="78"/>
       <c r="C119" s="73"/>
@@ -6084,7 +7079,7 @@
       <c r="O119" s="98"/>
       <c r="P119" s="88"/>
     </row>
-    <row r="120" ht="27.6">
+    <row r="120" spans="1:16" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A120" s="7"/>
       <c r="B120" s="78"/>
       <c r="C120" s="73"/>
@@ -6106,7 +7101,7 @@
       <c r="O120" s="98"/>
       <c r="P120" s="88"/>
     </row>
-    <row r="121" ht="14.4" customHeight="1">
+    <row r="121" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="7"/>
       <c r="B121" s="78"/>
       <c r="C121" s="73"/>
@@ -6126,7 +7121,7 @@
       <c r="O121" s="98"/>
       <c r="P121" s="88"/>
     </row>
-    <row r="122" ht="14.4" customHeight="1">
+    <row r="122" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="7"/>
       <c r="B122" s="78"/>
       <c r="C122" s="73"/>
@@ -6146,7 +7141,7 @@
       <c r="O122" s="98"/>
       <c r="P122" s="88"/>
     </row>
-    <row r="123" ht="14.4" customHeight="1">
+    <row r="123" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="7"/>
       <c r="B123" s="78"/>
       <c r="C123" s="73"/>
@@ -6166,7 +7161,7 @@
       <c r="O123" s="98"/>
       <c r="P123" s="88"/>
     </row>
-    <row r="124" ht="14.4" customHeight="1">
+    <row r="124" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="7"/>
       <c r="B124" s="78"/>
       <c r="C124" s="73"/>
@@ -6186,7 +7181,7 @@
       <c r="O124" s="98"/>
       <c r="P124" s="88"/>
     </row>
-    <row r="125" ht="14.4" customHeight="1">
+    <row r="125" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="7"/>
       <c r="B125" s="79"/>
       <c r="C125" s="74"/>
@@ -6206,7 +7201,7 @@
       <c r="O125" s="99"/>
       <c r="P125" s="89"/>
     </row>
-    <row r="126" ht="14.4" customHeight="1">
+    <row r="126" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="7"/>
       <c r="B126" s="78">
         <v>16</v>
@@ -6240,7 +7235,7 @@
       <c r="O126" s="98"/>
       <c r="P126" s="100"/>
     </row>
-    <row r="127" ht="14.4" customHeight="1">
+    <row r="127" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="7"/>
       <c r="B127" s="78"/>
       <c r="C127" s="73"/>
@@ -6262,7 +7257,7 @@
       <c r="O127" s="98"/>
       <c r="P127" s="88"/>
     </row>
-    <row r="128" ht="14.4" customHeight="1">
+    <row r="128" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="7"/>
       <c r="B128" s="78"/>
       <c r="C128" s="73"/>
@@ -6286,7 +7281,7 @@
       <c r="O128" s="98"/>
       <c r="P128" s="88"/>
     </row>
-    <row r="129" ht="14.4" customHeight="1">
+    <row r="129" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="7"/>
       <c r="B129" s="78"/>
       <c r="C129" s="73"/>
@@ -6308,7 +7303,7 @@
       <c r="O129" s="98"/>
       <c r="P129" s="88"/>
     </row>
-    <row r="130" ht="14.4" customHeight="1">
+    <row r="130" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="7"/>
       <c r="B130" s="78"/>
       <c r="C130" s="73"/>
@@ -6328,7 +7323,7 @@
       <c r="O130" s="98"/>
       <c r="P130" s="88"/>
     </row>
-    <row r="131" ht="14.4" customHeight="1">
+    <row r="131" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="7"/>
       <c r="B131" s="78"/>
       <c r="C131" s="73"/>
@@ -6348,7 +7343,7 @@
       <c r="O131" s="98"/>
       <c r="P131" s="88"/>
     </row>
-    <row r="132" ht="14.4" customHeight="1">
+    <row r="132" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="7"/>
       <c r="B132" s="78"/>
       <c r="C132" s="73"/>
@@ -6368,7 +7363,7 @@
       <c r="O132" s="98"/>
       <c r="P132" s="88"/>
     </row>
-    <row r="133" ht="14.4" customHeight="1">
+    <row r="133" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="7"/>
       <c r="B133" s="78"/>
       <c r="C133" s="73"/>
@@ -6388,7 +7383,7 @@
       <c r="O133" s="98"/>
       <c r="P133" s="88"/>
     </row>
-    <row r="134" ht="14.4" customHeight="1">
+    <row r="134" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="7"/>
       <c r="B134" s="78"/>
       <c r="C134" s="73"/>
@@ -6408,7 +7403,7 @@
       <c r="O134" s="98"/>
       <c r="P134" s="88"/>
     </row>
-    <row r="135" ht="14.4" customHeight="1">
+    <row r="135" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="7"/>
       <c r="B135" s="79"/>
       <c r="C135" s="74"/>
@@ -6428,7 +7423,7 @@
       <c r="O135" s="99"/>
       <c r="P135" s="89"/>
     </row>
-    <row r="136" ht="14.4" customHeight="1">
+    <row r="136" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="7"/>
       <c r="B136" s="78">
         <v>17</v>
@@ -6462,7 +7457,7 @@
       <c r="O136" s="119"/>
       <c r="P136" s="121"/>
     </row>
-    <row r="137" ht="14.4" customHeight="1">
+    <row r="137" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="7"/>
       <c r="B137" s="78"/>
       <c r="C137" s="73"/>
@@ -6486,7 +7481,7 @@
       <c r="O137" s="98"/>
       <c r="P137" s="88"/>
     </row>
-    <row r="138" ht="14.4" customHeight="1">
+    <row r="138" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="7"/>
       <c r="B138" s="78"/>
       <c r="C138" s="73"/>
@@ -6508,7 +7503,7 @@
       <c r="O138" s="98"/>
       <c r="P138" s="88"/>
     </row>
-    <row r="139" ht="14.4" customHeight="1">
+    <row r="139" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="7"/>
       <c r="B139" s="78"/>
       <c r="C139" s="73"/>
@@ -6532,7 +7527,7 @@
       <c r="O139" s="98"/>
       <c r="P139" s="88"/>
     </row>
-    <row r="140" ht="14.4" customHeight="1">
+    <row r="140" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="7"/>
       <c r="B140" s="78"/>
       <c r="C140" s="73"/>
@@ -6554,7 +7549,7 @@
       <c r="O140" s="98"/>
       <c r="P140" s="88"/>
     </row>
-    <row r="141" ht="14.4" customHeight="1">
+    <row r="141" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="7"/>
       <c r="B141" s="78"/>
       <c r="C141" s="73"/>
@@ -6576,7 +7571,7 @@
       <c r="O141" s="98"/>
       <c r="P141" s="88"/>
     </row>
-    <row r="142" ht="14.4" customHeight="1">
+    <row r="142" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="7"/>
       <c r="B142" s="78"/>
       <c r="C142" s="73"/>
@@ -6596,7 +7591,7 @@
       <c r="O142" s="98"/>
       <c r="P142" s="88"/>
     </row>
-    <row r="143" ht="14.4" customHeight="1">
+    <row r="143" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="7"/>
       <c r="B143" s="78"/>
       <c r="C143" s="73"/>
@@ -6616,7 +7611,7 @@
       <c r="O143" s="98"/>
       <c r="P143" s="88"/>
     </row>
-    <row r="144" ht="14.4" customHeight="1">
+    <row r="144" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="7"/>
       <c r="B144" s="78"/>
       <c r="C144" s="73"/>
@@ -6636,7 +7631,7 @@
       <c r="O144" s="98"/>
       <c r="P144" s="88"/>
     </row>
-    <row r="145" ht="14.4" customHeight="1">
+    <row r="145" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="7"/>
       <c r="B145" s="79"/>
       <c r="C145" s="74"/>
@@ -6656,7 +7651,7 @@
       <c r="O145" s="99"/>
       <c r="P145" s="89"/>
     </row>
-    <row r="146" ht="14.4" customHeight="1">
+    <row r="146" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="7"/>
       <c r="B146" s="78">
         <v>18</v>
@@ -6690,7 +7685,7 @@
       <c r="O146" s="98"/>
       <c r="P146" s="100"/>
     </row>
-    <row r="147" ht="14.4" customHeight="1">
+    <row r="147" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="7"/>
       <c r="B147" s="78"/>
       <c r="C147" s="73"/>
@@ -6714,7 +7709,7 @@
       <c r="O147" s="98"/>
       <c r="P147" s="88"/>
     </row>
-    <row r="148" ht="14.4" customHeight="1">
+    <row r="148" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="7"/>
       <c r="B148" s="78"/>
       <c r="C148" s="73"/>
@@ -6738,7 +7733,7 @@
       <c r="O148" s="98"/>
       <c r="P148" s="88"/>
     </row>
-    <row r="149" ht="14.4" customHeight="1">
+    <row r="149" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="7"/>
       <c r="B149" s="78"/>
       <c r="C149" s="73"/>
@@ -6762,7 +7757,7 @@
       <c r="O149" s="98"/>
       <c r="P149" s="88"/>
     </row>
-    <row r="150" ht="14.4" customHeight="1">
+    <row r="150" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="7"/>
       <c r="B150" s="78"/>
       <c r="C150" s="73"/>
@@ -6786,7 +7781,7 @@
       <c r="O150" s="98"/>
       <c r="P150" s="88"/>
     </row>
-    <row r="151" ht="14.4" customHeight="1">
+    <row r="151" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="7"/>
       <c r="B151" s="78"/>
       <c r="C151" s="73"/>
@@ -6808,7 +7803,7 @@
       <c r="O151" s="98"/>
       <c r="P151" s="88"/>
     </row>
-    <row r="152" ht="14.4" customHeight="1">
+    <row r="152" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="7"/>
       <c r="B152" s="78"/>
       <c r="C152" s="73"/>
@@ -6830,7 +7825,7 @@
       <c r="O152" s="98"/>
       <c r="P152" s="88"/>
     </row>
-    <row r="153" ht="14.4" customHeight="1">
+    <row r="153" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="7"/>
       <c r="B153" s="78"/>
       <c r="C153" s="73"/>
@@ -6850,7 +7845,7 @@
       <c r="O153" s="98"/>
       <c r="P153" s="88"/>
     </row>
-    <row r="154" ht="14.4" customHeight="1">
+    <row r="154" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="7"/>
       <c r="B154" s="78"/>
       <c r="C154" s="73"/>
@@ -6870,7 +7865,7 @@
       <c r="O154" s="98"/>
       <c r="P154" s="88"/>
     </row>
-    <row r="155" ht="14.4" customHeight="1">
+    <row r="155" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="7"/>
       <c r="B155" s="79"/>
       <c r="C155" s="74"/>
@@ -6890,7 +7885,7 @@
       <c r="O155" s="99"/>
       <c r="P155" s="89"/>
     </row>
-    <row r="156" ht="14.4" customHeight="1">
+    <row r="156" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="7"/>
       <c r="B156" s="78">
         <v>19</v>
@@ -6924,7 +7919,7 @@
       <c r="O156" s="119"/>
       <c r="P156" s="121"/>
     </row>
-    <row r="157" ht="14.4" customHeight="1">
+    <row r="157" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="7"/>
       <c r="B157" s="78"/>
       <c r="C157" s="73"/>
@@ -6946,7 +7941,7 @@
       <c r="O157" s="98"/>
       <c r="P157" s="88"/>
     </row>
-    <row r="158" ht="14.4" customHeight="1">
+    <row r="158" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="7"/>
       <c r="B158" s="78"/>
       <c r="C158" s="73"/>
@@ -6968,7 +7963,7 @@
       <c r="O158" s="98"/>
       <c r="P158" s="88"/>
     </row>
-    <row r="159" ht="14.4" customHeight="1">
+    <row r="159" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="7"/>
       <c r="B159" s="78"/>
       <c r="C159" s="73"/>
@@ -6990,7 +7985,7 @@
       <c r="O159" s="98"/>
       <c r="P159" s="88"/>
     </row>
-    <row r="160" ht="14.4" customHeight="1">
+    <row r="160" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="7"/>
       <c r="B160" s="78"/>
       <c r="C160" s="73"/>
@@ -7012,7 +8007,7 @@
       <c r="O160" s="98"/>
       <c r="P160" s="88"/>
     </row>
-    <row r="161" ht="14.4" customHeight="1">
+    <row r="161" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="7"/>
       <c r="B161" s="78"/>
       <c r="C161" s="73"/>
@@ -7032,7 +8027,7 @@
       <c r="O161" s="98"/>
       <c r="P161" s="88"/>
     </row>
-    <row r="162" ht="14.4" customHeight="1">
+    <row r="162" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="7"/>
       <c r="B162" s="78"/>
       <c r="C162" s="73"/>
@@ -7052,7 +8047,7 @@
       <c r="O162" s="98"/>
       <c r="P162" s="88"/>
     </row>
-    <row r="163" ht="14.4" customHeight="1">
+    <row r="163" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="7"/>
       <c r="B163" s="78"/>
       <c r="C163" s="73"/>
@@ -7072,7 +8067,7 @@
       <c r="O163" s="98"/>
       <c r="P163" s="88"/>
     </row>
-    <row r="164" ht="14.4" customHeight="1">
+    <row r="164" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="7"/>
       <c r="B164" s="78"/>
       <c r="C164" s="73"/>
@@ -7092,7 +8087,7 @@
       <c r="O164" s="98"/>
       <c r="P164" s="88"/>
     </row>
-    <row r="165" ht="14.4" customHeight="1">
+    <row r="165" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="7"/>
       <c r="B165" s="79"/>
       <c r="C165" s="74"/>
@@ -7112,7 +8107,7 @@
       <c r="O165" s="99"/>
       <c r="P165" s="89"/>
     </row>
-    <row r="166" ht="14.4" customHeight="1">
+    <row r="166" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="7"/>
       <c r="B166" s="78">
         <v>20</v>
@@ -7146,7 +8141,7 @@
       <c r="O166" s="98"/>
       <c r="P166" s="100"/>
     </row>
-    <row r="167" ht="14.4" customHeight="1">
+    <row r="167" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="7"/>
       <c r="B167" s="78"/>
       <c r="C167" s="73"/>
@@ -7170,7 +8165,7 @@
       <c r="O167" s="98"/>
       <c r="P167" s="88"/>
     </row>
-    <row r="168" ht="14.4" customHeight="1">
+    <row r="168" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="7"/>
       <c r="B168" s="78"/>
       <c r="C168" s="73"/>
@@ -7192,7 +8187,7 @@
       <c r="O168" s="98"/>
       <c r="P168" s="88"/>
     </row>
-    <row r="169" ht="27.6">
+    <row r="169" spans="1:16" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A169" s="7"/>
       <c r="B169" s="78"/>
       <c r="C169" s="73"/>
@@ -7214,7 +8209,7 @@
       <c r="O169" s="98"/>
       <c r="P169" s="88"/>
     </row>
-    <row r="170" ht="14.4" customHeight="1">
+    <row r="170" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="7"/>
       <c r="B170" s="78"/>
       <c r="C170" s="73"/>
@@ -7234,7 +8229,7 @@
       <c r="O170" s="98"/>
       <c r="P170" s="88"/>
     </row>
-    <row r="171" ht="14.4" customHeight="1">
+    <row r="171" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="7"/>
       <c r="B171" s="78"/>
       <c r="C171" s="73"/>
@@ -7254,7 +8249,7 @@
       <c r="O171" s="98"/>
       <c r="P171" s="88"/>
     </row>
-    <row r="172" ht="14.4" customHeight="1">
+    <row r="172" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="7"/>
       <c r="B172" s="78"/>
       <c r="C172" s="73"/>
@@ -7274,7 +8269,7 @@
       <c r="O172" s="98"/>
       <c r="P172" s="88"/>
     </row>
-    <row r="173" ht="14.4" customHeight="1">
+    <row r="173" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="7"/>
       <c r="B173" s="78"/>
       <c r="C173" s="73"/>
@@ -7294,7 +8289,7 @@
       <c r="O173" s="98"/>
       <c r="P173" s="88"/>
     </row>
-    <row r="174" ht="14.4" customHeight="1">
+    <row r="174" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="7"/>
       <c r="B174" s="78"/>
       <c r="C174" s="73"/>
@@ -7314,7 +8309,7 @@
       <c r="O174" s="98"/>
       <c r="P174" s="88"/>
     </row>
-    <row r="175" ht="14.4" customHeight="1">
+    <row r="175" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="7"/>
       <c r="B175" s="79"/>
       <c r="C175" s="74"/>
@@ -7334,7 +8329,7 @@
       <c r="O175" s="99"/>
       <c r="P175" s="89"/>
     </row>
-    <row r="176" ht="14.4" customHeight="1">
+    <row r="176" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="7"/>
       <c r="B176" s="78">
         <v>21</v>
@@ -7368,7 +8363,7 @@
       <c r="O176" s="119"/>
       <c r="P176" s="121"/>
     </row>
-    <row r="177" ht="14.4" customHeight="1">
+    <row r="177" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="7"/>
       <c r="B177" s="78"/>
       <c r="C177" s="73"/>
@@ -7390,7 +8385,7 @@
       <c r="O177" s="98"/>
       <c r="P177" s="88"/>
     </row>
-    <row r="178" ht="14.4" customHeight="1">
+    <row r="178" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="7"/>
       <c r="B178" s="78"/>
       <c r="C178" s="73"/>
@@ -7412,7 +8407,7 @@
       <c r="O178" s="98"/>
       <c r="P178" s="88"/>
     </row>
-    <row r="179" ht="14.4" customHeight="1">
+    <row r="179" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="7"/>
       <c r="B179" s="78"/>
       <c r="C179" s="73"/>
@@ -7434,7 +8429,7 @@
       <c r="O179" s="98"/>
       <c r="P179" s="88"/>
     </row>
-    <row r="180" ht="14.4" customHeight="1">
+    <row r="180" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="7"/>
       <c r="B180" s="78"/>
       <c r="C180" s="73"/>
@@ -7454,7 +8449,7 @@
       <c r="O180" s="98"/>
       <c r="P180" s="88"/>
     </row>
-    <row r="181" ht="14.4" customHeight="1">
+    <row r="181" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="7"/>
       <c r="B181" s="78"/>
       <c r="C181" s="73"/>
@@ -7474,7 +8469,7 @@
       <c r="O181" s="98"/>
       <c r="P181" s="88"/>
     </row>
-    <row r="182" ht="14.4" customHeight="1">
+    <row r="182" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="7"/>
       <c r="B182" s="78"/>
       <c r="C182" s="73"/>
@@ -7494,7 +8489,7 @@
       <c r="O182" s="98"/>
       <c r="P182" s="88"/>
     </row>
-    <row r="183" ht="14.4" customHeight="1">
+    <row r="183" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="7"/>
       <c r="B183" s="78"/>
       <c r="C183" s="73"/>
@@ -7514,7 +8509,7 @@
       <c r="O183" s="98"/>
       <c r="P183" s="88"/>
     </row>
-    <row r="184" ht="14.4" customHeight="1">
+    <row r="184" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="7"/>
       <c r="B184" s="78"/>
       <c r="C184" s="73"/>
@@ -7534,7 +8529,7 @@
       <c r="O184" s="98"/>
       <c r="P184" s="88"/>
     </row>
-    <row r="185" ht="14.4" customHeight="1">
+    <row r="185" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="7"/>
       <c r="B185" s="79"/>
       <c r="C185" s="74"/>
@@ -7554,7 +8549,7 @@
       <c r="O185" s="99"/>
       <c r="P185" s="89"/>
     </row>
-    <row r="186" ht="14.4" customHeight="1">
+    <row r="186" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="7"/>
       <c r="B186" s="78">
         <v>22</v>
@@ -7588,7 +8583,7 @@
       <c r="O186" s="98"/>
       <c r="P186" s="100"/>
     </row>
-    <row r="187" ht="14.4" customHeight="1">
+    <row r="187" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="7"/>
       <c r="B187" s="78"/>
       <c r="C187" s="73"/>
@@ -7612,7 +8607,7 @@
       <c r="O187" s="98"/>
       <c r="P187" s="88"/>
     </row>
-    <row r="188" ht="14.4" customHeight="1">
+    <row r="188" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="7"/>
       <c r="B188" s="78"/>
       <c r="C188" s="73"/>
@@ -7636,7 +8631,7 @@
       <c r="O188" s="98"/>
       <c r="P188" s="88"/>
     </row>
-    <row r="189" ht="14.4" customHeight="1">
+    <row r="189" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="7"/>
       <c r="B189" s="78"/>
       <c r="C189" s="73"/>
@@ -7658,7 +8653,7 @@
       <c r="O189" s="98"/>
       <c r="P189" s="88"/>
     </row>
-    <row r="190" ht="14.4" customHeight="1">
+    <row r="190" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="7"/>
       <c r="B190" s="78"/>
       <c r="C190" s="73"/>
@@ -7682,7 +8677,7 @@
       <c r="O190" s="98"/>
       <c r="P190" s="88"/>
     </row>
-    <row r="191" ht="13.8" customHeight="1">
+    <row r="191" spans="1:16" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="7"/>
       <c r="B191" s="78"/>
       <c r="C191" s="73"/>
@@ -7704,7 +8699,7 @@
       <c r="O191" s="98"/>
       <c r="P191" s="88"/>
     </row>
-    <row r="192" ht="14.4" customHeight="1">
+    <row r="192" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="7"/>
       <c r="B192" s="78"/>
       <c r="C192" s="73"/>
@@ -7724,7 +8719,7 @@
       <c r="O192" s="98"/>
       <c r="P192" s="88"/>
     </row>
-    <row r="193" ht="14.4" customHeight="1">
+    <row r="193" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="7"/>
       <c r="B193" s="78"/>
       <c r="C193" s="73"/>
@@ -7744,7 +8739,7 @@
       <c r="O193" s="98"/>
       <c r="P193" s="88"/>
     </row>
-    <row r="194" ht="14.4" customHeight="1">
+    <row r="194" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="7"/>
       <c r="B194" s="78"/>
       <c r="C194" s="73"/>
@@ -7764,7 +8759,7 @@
       <c r="O194" s="98"/>
       <c r="P194" s="88"/>
     </row>
-    <row r="195" ht="14.4" customHeight="1">
+    <row r="195" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="7"/>
       <c r="B195" s="79"/>
       <c r="C195" s="74"/>
@@ -7784,7 +8779,7 @@
       <c r="O195" s="99"/>
       <c r="P195" s="89"/>
     </row>
-    <row r="196" ht="14.4" customHeight="1">
+    <row r="196" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="7"/>
       <c r="B196" s="78">
         <v>23</v>
@@ -7818,7 +8813,7 @@
       <c r="O196" s="119"/>
       <c r="P196" s="121"/>
     </row>
-    <row r="197" ht="14.4" customHeight="1">
+    <row r="197" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="7"/>
       <c r="B197" s="78"/>
       <c r="C197" s="73"/>
@@ -7840,7 +8835,7 @@
       <c r="O197" s="98"/>
       <c r="P197" s="88"/>
     </row>
-    <row r="198" ht="13.8" customHeight="1">
+    <row r="198" spans="1:16" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="7"/>
       <c r="B198" s="78"/>
       <c r="C198" s="73"/>
@@ -7862,7 +8857,7 @@
       <c r="O198" s="98"/>
       <c r="P198" s="88"/>
     </row>
-    <row r="199" ht="14.4" customHeight="1">
+    <row r="199" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="7"/>
       <c r="B199" s="78"/>
       <c r="C199" s="73"/>
@@ -7884,7 +8879,7 @@
       <c r="O199" s="98"/>
       <c r="P199" s="88"/>
     </row>
-    <row r="200" ht="14.4" customHeight="1">
+    <row r="200" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="7"/>
       <c r="B200" s="78"/>
       <c r="C200" s="73"/>
@@ -7904,7 +8899,7 @@
       <c r="O200" s="98"/>
       <c r="P200" s="88"/>
     </row>
-    <row r="201" ht="14.4" customHeight="1">
+    <row r="201" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="7"/>
       <c r="B201" s="78"/>
       <c r="C201" s="73"/>
@@ -7924,7 +8919,7 @@
       <c r="O201" s="98"/>
       <c r="P201" s="88"/>
     </row>
-    <row r="202" ht="14.4" customHeight="1">
+    <row r="202" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="7"/>
       <c r="B202" s="78"/>
       <c r="C202" s="73"/>
@@ -7944,7 +8939,7 @@
       <c r="O202" s="98"/>
       <c r="P202" s="88"/>
     </row>
-    <row r="203" ht="14.4" customHeight="1">
+    <row r="203" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="7"/>
       <c r="B203" s="78"/>
       <c r="C203" s="73"/>
@@ -7964,7 +8959,7 @@
       <c r="O203" s="98"/>
       <c r="P203" s="88"/>
     </row>
-    <row r="204" ht="14.4" customHeight="1">
+    <row r="204" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="7"/>
       <c r="B204" s="78"/>
       <c r="C204" s="73"/>
@@ -7984,7 +8979,7 @@
       <c r="O204" s="98"/>
       <c r="P204" s="88"/>
     </row>
-    <row r="205" ht="14.4" customHeight="1">
+    <row r="205" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="7"/>
       <c r="B205" s="79"/>
       <c r="C205" s="74"/>
@@ -8004,7 +8999,7 @@
       <c r="O205" s="99"/>
       <c r="P205" s="89"/>
     </row>
-    <row r="206" ht="14.4" customHeight="1">
+    <row r="206" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="7"/>
       <c r="B206" s="78">
         <v>24</v>
@@ -8040,7 +9035,7 @@
       <c r="O206" s="98"/>
       <c r="P206" s="100"/>
     </row>
-    <row r="207" ht="14.4" customHeight="1">
+    <row r="207" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="7"/>
       <c r="B207" s="78"/>
       <c r="C207" s="73"/>
@@ -8064,7 +9059,7 @@
       <c r="O207" s="98"/>
       <c r="P207" s="88"/>
     </row>
-    <row r="208" ht="14.4" customHeight="1">
+    <row r="208" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="7"/>
       <c r="B208" s="78"/>
       <c r="C208" s="73"/>
@@ -8086,7 +9081,7 @@
       <c r="O208" s="98"/>
       <c r="P208" s="88"/>
     </row>
-    <row r="209" ht="27.6">
+    <row r="209" spans="1:16" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A209" s="7"/>
       <c r="B209" s="78"/>
       <c r="C209" s="73"/>
@@ -8108,7 +9103,7 @@
       <c r="O209" s="98"/>
       <c r="P209" s="88"/>
     </row>
-    <row r="210" ht="27.6">
+    <row r="210" spans="1:16" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A210" s="7"/>
       <c r="B210" s="78"/>
       <c r="C210" s="73"/>
@@ -8130,7 +9125,7 @@
       <c r="O210" s="98"/>
       <c r="P210" s="88"/>
     </row>
-    <row r="211" ht="14.4" customHeight="1">
+    <row r="211" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="7"/>
       <c r="B211" s="78"/>
       <c r="C211" s="73"/>
@@ -8150,7 +9145,7 @@
       <c r="O211" s="98"/>
       <c r="P211" s="88"/>
     </row>
-    <row r="212" ht="14.4" customHeight="1">
+    <row r="212" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="7"/>
       <c r="B212" s="78"/>
       <c r="C212" s="73"/>
@@ -8170,7 +9165,7 @@
       <c r="O212" s="98"/>
       <c r="P212" s="88"/>
     </row>
-    <row r="213" ht="14.4" customHeight="1">
+    <row r="213" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="7"/>
       <c r="B213" s="78"/>
       <c r="C213" s="73"/>
@@ -8190,7 +9185,7 @@
       <c r="O213" s="98"/>
       <c r="P213" s="88"/>
     </row>
-    <row r="214" ht="14.4" customHeight="1">
+    <row r="214" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="7"/>
       <c r="B214" s="78"/>
       <c r="C214" s="73"/>
@@ -8210,7 +9205,7 @@
       <c r="O214" s="98"/>
       <c r="P214" s="88"/>
     </row>
-    <row r="215" ht="14.4" customHeight="1">
+    <row r="215" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="7"/>
       <c r="B215" s="79"/>
       <c r="C215" s="74"/>
@@ -8230,7 +9225,7 @@
       <c r="O215" s="99"/>
       <c r="P215" s="89"/>
     </row>
-    <row r="216" ht="13.8" customHeight="1">
+    <row r="216" spans="1:16" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="7"/>
       <c r="B216" s="78">
         <v>25</v>
@@ -8266,7 +9261,7 @@
       <c r="O216" s="119"/>
       <c r="P216" s="121"/>
     </row>
-    <row r="217" ht="13.8" customHeight="1">
+    <row r="217" spans="1:16" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="7"/>
       <c r="B217" s="78"/>
       <c r="C217" s="73"/>
@@ -8290,7 +9285,7 @@
       <c r="O217" s="98"/>
       <c r="P217" s="88"/>
     </row>
-    <row r="218" ht="14.4" customHeight="1">
+    <row r="218" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="7"/>
       <c r="B218" s="78"/>
       <c r="C218" s="73"/>
@@ -8312,7 +9307,7 @@
       <c r="O218" s="98"/>
       <c r="P218" s="88"/>
     </row>
-    <row r="219" ht="13.8" customHeight="1">
+    <row r="219" spans="1:16" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="7"/>
       <c r="B219" s="78"/>
       <c r="C219" s="73"/>
@@ -8334,7 +9329,7 @@
       <c r="O219" s="98"/>
       <c r="P219" s="88"/>
     </row>
-    <row r="220" ht="14.4" customHeight="1">
+    <row r="220" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="7"/>
       <c r="B220" s="78"/>
       <c r="C220" s="73"/>
@@ -8356,7 +9351,7 @@
       <c r="O220" s="98"/>
       <c r="P220" s="88"/>
     </row>
-    <row r="221" ht="14.4" customHeight="1">
+    <row r="221" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="7"/>
       <c r="B221" s="78"/>
       <c r="C221" s="73"/>
@@ -8376,7 +9371,7 @@
       <c r="O221" s="98"/>
       <c r="P221" s="88"/>
     </row>
-    <row r="222" ht="14.4" customHeight="1">
+    <row r="222" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="7"/>
       <c r="B222" s="78"/>
       <c r="C222" s="73"/>
@@ -8396,7 +9391,7 @@
       <c r="O222" s="98"/>
       <c r="P222" s="88"/>
     </row>
-    <row r="223" ht="14.4" customHeight="1">
+    <row r="223" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="7"/>
       <c r="B223" s="78"/>
       <c r="C223" s="73"/>
@@ -8416,7 +9411,7 @@
       <c r="O223" s="98"/>
       <c r="P223" s="88"/>
     </row>
-    <row r="224" ht="14.4" customHeight="1">
+    <row r="224" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="7"/>
       <c r="B224" s="78"/>
       <c r="C224" s="73"/>
@@ -8436,7 +9431,7 @@
       <c r="O224" s="98"/>
       <c r="P224" s="88"/>
     </row>
-    <row r="225" ht="14.4" customHeight="1">
+    <row r="225" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="7"/>
       <c r="B225" s="79"/>
       <c r="C225" s="74"/>
@@ -8456,7 +9451,7 @@
       <c r="O225" s="99"/>
       <c r="P225" s="89"/>
     </row>
-    <row r="226" ht="14.4" customHeight="1">
+    <row r="226" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="7"/>
       <c r="B226" s="78">
         <v>26</v>
@@ -8490,7 +9485,7 @@
       <c r="O226" s="98"/>
       <c r="P226" s="100"/>
     </row>
-    <row r="227" ht="14.4" customHeight="1">
+    <row r="227" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="7"/>
       <c r="B227" s="78"/>
       <c r="C227" s="73"/>
@@ -8512,7 +9507,7 @@
       <c r="O227" s="98"/>
       <c r="P227" s="88"/>
     </row>
-    <row r="228" ht="14.4" customHeight="1">
+    <row r="228" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="7"/>
       <c r="B228" s="78"/>
       <c r="C228" s="73"/>
@@ -8534,7 +9529,7 @@
       <c r="O228" s="98"/>
       <c r="P228" s="88"/>
     </row>
-    <row r="229" ht="14.4" customHeight="1">
+    <row r="229" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="7"/>
       <c r="B229" s="78"/>
       <c r="C229" s="73"/>
@@ -8556,7 +9551,7 @@
       <c r="O229" s="98"/>
       <c r="P229" s="88"/>
     </row>
-    <row r="230" ht="14.4" customHeight="1">
+    <row r="230" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="7"/>
       <c r="B230" s="78"/>
       <c r="C230" s="73"/>
@@ -8578,7 +9573,7 @@
       <c r="O230" s="98"/>
       <c r="P230" s="88"/>
     </row>
-    <row r="231" ht="14.4" customHeight="1">
+    <row r="231" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="7"/>
       <c r="B231" s="78"/>
       <c r="C231" s="73"/>
@@ -8598,7 +9593,7 @@
       <c r="O231" s="98"/>
       <c r="P231" s="88"/>
     </row>
-    <row r="232" ht="14.4" customHeight="1">
+    <row r="232" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="7"/>
       <c r="B232" s="78"/>
       <c r="C232" s="73"/>
@@ -8618,7 +9613,7 @@
       <c r="O232" s="98"/>
       <c r="P232" s="88"/>
     </row>
-    <row r="233" ht="14.4" customHeight="1">
+    <row r="233" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="7"/>
       <c r="B233" s="78"/>
       <c r="C233" s="73"/>
@@ -8638,7 +9633,7 @@
       <c r="O233" s="98"/>
       <c r="P233" s="88"/>
     </row>
-    <row r="234" ht="14.4" customHeight="1">
+    <row r="234" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="7"/>
       <c r="B234" s="78"/>
       <c r="C234" s="73"/>
@@ -8658,7 +9653,7 @@
       <c r="O234" s="98"/>
       <c r="P234" s="88"/>
     </row>
-    <row r="235" ht="14.4" customHeight="1">
+    <row r="235" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="7"/>
       <c r="B235" s="79"/>
       <c r="C235" s="74"/>
@@ -8678,7 +9673,7 @@
       <c r="O235" s="99"/>
       <c r="P235" s="89"/>
     </row>
-    <row r="236" ht="14.4" customHeight="1">
+    <row r="236" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="7"/>
       <c r="B236" s="78">
         <v>27</v>
@@ -8712,7 +9707,7 @@
       <c r="O236" s="119"/>
       <c r="P236" s="121"/>
     </row>
-    <row r="237" ht="14.4" customHeight="1">
+    <row r="237" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="7"/>
       <c r="B237" s="78"/>
       <c r="C237" s="73"/>
@@ -8736,7 +9731,7 @@
       <c r="O237" s="98"/>
       <c r="P237" s="88"/>
     </row>
-    <row r="238" ht="14.4" customHeight="1">
+    <row r="238" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="7"/>
       <c r="B238" s="78"/>
       <c r="C238" s="73"/>
@@ -8758,7 +9753,7 @@
       <c r="O238" s="98"/>
       <c r="P238" s="88"/>
     </row>
-    <row r="239" ht="14.4" customHeight="1">
+    <row r="239" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="7"/>
       <c r="B239" s="78"/>
       <c r="C239" s="73"/>
@@ -8782,7 +9777,7 @@
       <c r="O239" s="98"/>
       <c r="P239" s="88"/>
     </row>
-    <row r="240" ht="14.4" customHeight="1">
+    <row r="240" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="7"/>
       <c r="B240" s="78"/>
       <c r="C240" s="73"/>
@@ -8804,7 +9799,7 @@
       <c r="O240" s="98"/>
       <c r="P240" s="88"/>
     </row>
-    <row r="241" ht="14.4" customHeight="1">
+    <row r="241" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="7"/>
       <c r="B241" s="78"/>
       <c r="C241" s="73"/>
@@ -8826,7 +9821,7 @@
       <c r="O241" s="98"/>
       <c r="P241" s="88"/>
     </row>
-    <row r="242" ht="14.4" customHeight="1">
+    <row r="242" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="7"/>
       <c r="B242" s="78"/>
       <c r="C242" s="73"/>
@@ -8848,7 +9843,7 @@
       <c r="O242" s="98"/>
       <c r="P242" s="88"/>
     </row>
-    <row r="243" ht="14.4" customHeight="1">
+    <row r="243" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="7"/>
       <c r="B243" s="78"/>
       <c r="C243" s="73"/>
@@ -8868,7 +9863,7 @@
       <c r="O243" s="98"/>
       <c r="P243" s="88"/>
     </row>
-    <row r="244" ht="14.4" customHeight="1">
+    <row r="244" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="7"/>
       <c r="B244" s="78"/>
       <c r="C244" s="73"/>
@@ -8888,7 +9883,7 @@
       <c r="O244" s="98"/>
       <c r="P244" s="88"/>
     </row>
-    <row r="245" ht="14.4" customHeight="1">
+    <row r="245" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="7"/>
       <c r="B245" s="79"/>
       <c r="C245" s="74"/>
@@ -8908,7 +9903,7 @@
       <c r="O245" s="99"/>
       <c r="P245" s="89"/>
     </row>
-    <row r="246" ht="27.6">
+    <row r="246" spans="1:16" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A246" s="7"/>
       <c r="B246" s="78">
         <v>28</v>
@@ -8942,7 +9937,7 @@
       <c r="O246" s="98"/>
       <c r="P246" s="100"/>
     </row>
-    <row r="247" ht="27.6">
+    <row r="247" spans="1:16" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A247" s="7"/>
       <c r="B247" s="78"/>
       <c r="C247" s="73"/>
@@ -8964,7 +9959,7 @@
       <c r="O247" s="98"/>
       <c r="P247" s="88"/>
     </row>
-    <row r="248" ht="13.8" customHeight="1">
+    <row r="248" spans="1:16" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="7"/>
       <c r="B248" s="78"/>
       <c r="C248" s="73"/>
@@ -8986,7 +9981,7 @@
       <c r="O248" s="98"/>
       <c r="P248" s="88"/>
     </row>
-    <row r="249" ht="13.8" customHeight="1">
+    <row r="249" spans="1:16" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="7"/>
       <c r="B249" s="78"/>
       <c r="C249" s="73"/>
@@ -9008,7 +10003,7 @@
       <c r="O249" s="98"/>
       <c r="P249" s="88"/>
     </row>
-    <row r="250" ht="27.6">
+    <row r="250" spans="1:16" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A250" s="7"/>
       <c r="B250" s="78"/>
       <c r="C250" s="73"/>
@@ -9030,7 +10025,7 @@
       <c r="O250" s="98"/>
       <c r="P250" s="88"/>
     </row>
-    <row r="251" ht="27.6">
+    <row r="251" spans="1:16" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A251" s="7"/>
       <c r="B251" s="78"/>
       <c r="C251" s="73"/>
@@ -9052,7 +10047,7 @@
       <c r="O251" s="98"/>
       <c r="P251" s="88"/>
     </row>
-    <row r="252" ht="13.8" customHeight="1">
+    <row r="252" spans="1:16" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="7"/>
       <c r="B252" s="78"/>
       <c r="C252" s="73"/>
@@ -9074,7 +10069,7 @@
       <c r="O252" s="98"/>
       <c r="P252" s="88"/>
     </row>
-    <row r="253" ht="14.4" customHeight="1">
+    <row r="253" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="7"/>
       <c r="B253" s="78"/>
       <c r="C253" s="73"/>
@@ -9096,7 +10091,7 @@
       <c r="O253" s="98"/>
       <c r="P253" s="88"/>
     </row>
-    <row r="254" ht="14.4" customHeight="1">
+    <row r="254" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="7"/>
       <c r="B254" s="78"/>
       <c r="C254" s="73"/>
@@ -9116,7 +10111,7 @@
       <c r="O254" s="98"/>
       <c r="P254" s="88"/>
     </row>
-    <row r="255" ht="14.4" customHeight="1">
+    <row r="255" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="7"/>
       <c r="B255" s="79"/>
       <c r="C255" s="74"/>
@@ -9136,7 +10131,7 @@
       <c r="O255" s="99"/>
       <c r="P255" s="89"/>
     </row>
-    <row r="256" ht="14.4" customHeight="1">
+    <row r="256" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="7"/>
       <c r="B256" s="78">
         <v>29</v>
@@ -9170,7 +10165,7 @@
       <c r="O256" s="119"/>
       <c r="P256" s="121"/>
     </row>
-    <row r="257" ht="27.6">
+    <row r="257" spans="1:16" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A257" s="7"/>
       <c r="B257" s="78"/>
       <c r="C257" s="73"/>
@@ -9192,7 +10187,7 @@
       <c r="O257" s="98"/>
       <c r="P257" s="88"/>
     </row>
-    <row r="258" ht="14.4" customHeight="1">
+    <row r="258" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="7"/>
       <c r="B258" s="78"/>
       <c r="C258" s="73"/>
@@ -9214,7 +10209,7 @@
       <c r="O258" s="98"/>
       <c r="P258" s="88"/>
     </row>
-    <row r="259" ht="14.4" customHeight="1">
+    <row r="259" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="7"/>
       <c r="B259" s="78"/>
       <c r="C259" s="73"/>
@@ -9236,7 +10231,7 @@
       <c r="O259" s="98"/>
       <c r="P259" s="88"/>
     </row>
-    <row r="260" ht="27.6">
+    <row r="260" spans="1:16" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A260" s="7"/>
       <c r="B260" s="78"/>
       <c r="C260" s="73"/>
@@ -9258,7 +10253,7 @@
       <c r="O260" s="98"/>
       <c r="P260" s="88"/>
     </row>
-    <row r="261" ht="14.4" customHeight="1">
+    <row r="261" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="7"/>
       <c r="B261" s="78"/>
       <c r="C261" s="73"/>
@@ -9278,7 +10273,7 @@
       <c r="O261" s="98"/>
       <c r="P261" s="88"/>
     </row>
-    <row r="262" ht="14.4" customHeight="1">
+    <row r="262" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="7"/>
       <c r="B262" s="78"/>
       <c r="C262" s="73"/>
@@ -9298,7 +10293,7 @@
       <c r="O262" s="98"/>
       <c r="P262" s="88"/>
     </row>
-    <row r="263" ht="14.4" customHeight="1">
+    <row r="263" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="7"/>
       <c r="B263" s="78"/>
       <c r="C263" s="73"/>
@@ -9318,7 +10313,7 @@
       <c r="O263" s="98"/>
       <c r="P263" s="88"/>
     </row>
-    <row r="264" ht="14.4" customHeight="1">
+    <row r="264" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="7"/>
       <c r="B264" s="78"/>
       <c r="C264" s="73"/>
@@ -9338,7 +10333,7 @@
       <c r="O264" s="98"/>
       <c r="P264" s="88"/>
     </row>
-    <row r="265" ht="14.4" customHeight="1">
+    <row r="265" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="7"/>
       <c r="B265" s="79"/>
       <c r="C265" s="74"/>
@@ -9359,7 +10354,7 @@
       <c r="P265" s="89"/>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="348">
     <mergeCell ref="N226:N235"/>
     <mergeCell ref="O226:O235"/>
     <mergeCell ref="P226:P235"/>
@@ -9372,16 +10367,22 @@
     <mergeCell ref="L246:L255"/>
     <mergeCell ref="M246:M255"/>
     <mergeCell ref="M226:M235"/>
+    <mergeCell ref="C216:C225"/>
+    <mergeCell ref="D216:D225"/>
+    <mergeCell ref="E216:E225"/>
+    <mergeCell ref="F216:F225"/>
+    <mergeCell ref="G216:G225"/>
     <mergeCell ref="C226:C235"/>
     <mergeCell ref="D226:D235"/>
     <mergeCell ref="E226:E235"/>
     <mergeCell ref="F226:F235"/>
     <mergeCell ref="G226:G235"/>
-    <mergeCell ref="C216:C225"/>
-    <mergeCell ref="D216:D225"/>
-    <mergeCell ref="E216:E225"/>
-    <mergeCell ref="F216:F225"/>
-    <mergeCell ref="G216:G225"/>
+    <mergeCell ref="P186:P195"/>
+    <mergeCell ref="M216:M225"/>
+    <mergeCell ref="N216:N225"/>
+    <mergeCell ref="O216:O225"/>
+    <mergeCell ref="P216:P225"/>
+    <mergeCell ref="N196:N205"/>
     <mergeCell ref="M46:M55"/>
     <mergeCell ref="N46:N55"/>
     <mergeCell ref="O46:O55"/>
@@ -9390,24 +10391,10 @@
     <mergeCell ref="M56:M65"/>
     <mergeCell ref="N56:N65"/>
     <mergeCell ref="O56:O65"/>
-    <mergeCell ref="N186:N195"/>
-    <mergeCell ref="O186:O195"/>
-    <mergeCell ref="P186:P195"/>
-    <mergeCell ref="M216:M225"/>
-    <mergeCell ref="N216:N225"/>
-    <mergeCell ref="O216:O225"/>
-    <mergeCell ref="P216:P225"/>
-    <mergeCell ref="N196:N205"/>
-    <mergeCell ref="P166:P175"/>
-    <mergeCell ref="L176:L185"/>
-    <mergeCell ref="M176:M185"/>
-    <mergeCell ref="N176:N185"/>
-    <mergeCell ref="O176:O185"/>
-    <mergeCell ref="P176:P185"/>
-    <mergeCell ref="L166:L175"/>
-    <mergeCell ref="M166:M175"/>
-    <mergeCell ref="N166:N175"/>
-    <mergeCell ref="O166:O175"/>
+    <mergeCell ref="N86:N95"/>
+    <mergeCell ref="O86:O95"/>
+    <mergeCell ref="P96:P105"/>
+    <mergeCell ref="M106:M115"/>
     <mergeCell ref="N156:N165"/>
     <mergeCell ref="O156:O165"/>
     <mergeCell ref="N96:N105"/>
@@ -9418,27 +10405,9 @@
     <mergeCell ref="O106:O115"/>
     <mergeCell ref="O136:O145"/>
     <mergeCell ref="O126:O135"/>
-    <mergeCell ref="H86:H95"/>
-    <mergeCell ref="L86:L95"/>
-    <mergeCell ref="M86:M95"/>
-    <mergeCell ref="L156:L165"/>
-    <mergeCell ref="P156:P165"/>
-    <mergeCell ref="P86:P95"/>
-    <mergeCell ref="H96:H105"/>
-    <mergeCell ref="L96:L105"/>
-    <mergeCell ref="M96:M105"/>
-    <mergeCell ref="L116:L125"/>
-    <mergeCell ref="M116:M125"/>
-    <mergeCell ref="H116:H125"/>
-    <mergeCell ref="N86:N95"/>
-    <mergeCell ref="O86:O95"/>
-    <mergeCell ref="P96:P105"/>
-    <mergeCell ref="M106:M115"/>
-    <mergeCell ref="C76:C85"/>
-    <mergeCell ref="D76:D85"/>
-    <mergeCell ref="E76:E85"/>
-    <mergeCell ref="F96:F105"/>
-    <mergeCell ref="G96:G105"/>
+    <mergeCell ref="N66:N75"/>
+    <mergeCell ref="O66:O75"/>
+    <mergeCell ref="P66:P75"/>
     <mergeCell ref="F46:F55"/>
     <mergeCell ref="G46:G55"/>
     <mergeCell ref="F156:F165"/>
@@ -9455,12 +10424,11 @@
     <mergeCell ref="G56:G65"/>
     <mergeCell ref="F106:F115"/>
     <mergeCell ref="F116:F125"/>
-    <mergeCell ref="M76:M85"/>
-    <mergeCell ref="M66:M75"/>
-    <mergeCell ref="N66:N75"/>
-    <mergeCell ref="O66:O75"/>
-    <mergeCell ref="P66:P75"/>
-    <mergeCell ref="H76:H85"/>
+    <mergeCell ref="F96:F105"/>
+    <mergeCell ref="G96:G105"/>
+    <mergeCell ref="H86:H95"/>
+    <mergeCell ref="L86:L95"/>
+    <mergeCell ref="M86:M95"/>
     <mergeCell ref="H46:H55"/>
     <mergeCell ref="L46:L55"/>
     <mergeCell ref="H66:H75"/>
@@ -9468,7 +10436,8 @@
     <mergeCell ref="L56:L65"/>
     <mergeCell ref="H56:H65"/>
     <mergeCell ref="L76:L85"/>
-    <mergeCell ref="P126:P135"/>
+    <mergeCell ref="M76:M85"/>
+    <mergeCell ref="M66:M75"/>
     <mergeCell ref="N76:N85"/>
     <mergeCell ref="O76:O85"/>
     <mergeCell ref="P76:P85"/>
@@ -9484,8 +10453,15 @@
     <mergeCell ref="H156:H165"/>
     <mergeCell ref="L136:L145"/>
     <mergeCell ref="M156:M165"/>
-    <mergeCell ref="L186:L195"/>
-    <mergeCell ref="M186:M195"/>
+    <mergeCell ref="H76:H85"/>
+    <mergeCell ref="L156:L165"/>
+    <mergeCell ref="P156:P165"/>
+    <mergeCell ref="P86:P95"/>
+    <mergeCell ref="H96:H105"/>
+    <mergeCell ref="L96:L105"/>
+    <mergeCell ref="M96:M105"/>
+    <mergeCell ref="L116:L125"/>
+    <mergeCell ref="M116:M125"/>
     <mergeCell ref="P116:P125"/>
     <mergeCell ref="N126:N135"/>
     <mergeCell ref="C126:C135"/>
@@ -9500,6 +10476,16 @@
     <mergeCell ref="G126:G135"/>
     <mergeCell ref="H126:H135"/>
     <mergeCell ref="L126:L135"/>
+    <mergeCell ref="P126:P135"/>
+    <mergeCell ref="H116:H125"/>
+    <mergeCell ref="P166:P175"/>
+    <mergeCell ref="L176:L185"/>
+    <mergeCell ref="M176:M185"/>
+    <mergeCell ref="N176:N185"/>
+    <mergeCell ref="O176:O185"/>
+    <mergeCell ref="P176:P185"/>
+    <mergeCell ref="L166:L175"/>
+    <mergeCell ref="M166:M175"/>
     <mergeCell ref="B106:B115"/>
     <mergeCell ref="C106:C115"/>
     <mergeCell ref="D106:D115"/>
@@ -9508,6 +10494,11 @@
     <mergeCell ref="B116:B125"/>
     <mergeCell ref="C116:C125"/>
     <mergeCell ref="D116:D125"/>
+    <mergeCell ref="L186:L195"/>
+    <mergeCell ref="F256:F265"/>
+    <mergeCell ref="G256:G265"/>
+    <mergeCell ref="H256:H265"/>
+    <mergeCell ref="L256:L265"/>
     <mergeCell ref="D196:D205"/>
     <mergeCell ref="E196:E205"/>
     <mergeCell ref="F196:F205"/>
@@ -9519,32 +10510,6 @@
     <mergeCell ref="G246:G255"/>
     <mergeCell ref="H216:H225"/>
     <mergeCell ref="L216:L225"/>
-    <mergeCell ref="N256:N265"/>
-    <mergeCell ref="C256:C265"/>
-    <mergeCell ref="D256:D265"/>
-    <mergeCell ref="E256:E265"/>
-    <mergeCell ref="F256:F265"/>
-    <mergeCell ref="G256:G265"/>
-    <mergeCell ref="H256:H265"/>
-    <mergeCell ref="L256:L265"/>
-    <mergeCell ref="B246:B255"/>
-    <mergeCell ref="B256:B265"/>
-    <mergeCell ref="H166:H175"/>
-    <mergeCell ref="C176:C185"/>
-    <mergeCell ref="D176:D185"/>
-    <mergeCell ref="E176:E185"/>
-    <mergeCell ref="F176:F185"/>
-    <mergeCell ref="G176:G185"/>
-    <mergeCell ref="C166:C175"/>
-    <mergeCell ref="D166:D175"/>
-    <mergeCell ref="F166:F175"/>
-    <mergeCell ref="G166:G175"/>
-    <mergeCell ref="C246:C255"/>
-    <mergeCell ref="D246:D255"/>
-    <mergeCell ref="E246:E255"/>
-    <mergeCell ref="F246:F255"/>
-    <mergeCell ref="B196:B205"/>
-    <mergeCell ref="C196:C205"/>
     <mergeCell ref="O256:O265"/>
     <mergeCell ref="P256:P265"/>
     <mergeCell ref="B236:B245"/>
@@ -9559,9 +10524,16 @@
     <mergeCell ref="N236:N245"/>
     <mergeCell ref="O236:O245"/>
     <mergeCell ref="P236:P245"/>
-    <mergeCell ref="B216:B225"/>
-    <mergeCell ref="B226:B235"/>
-    <mergeCell ref="O196:O205"/>
+    <mergeCell ref="B246:B255"/>
+    <mergeCell ref="B256:B265"/>
+    <mergeCell ref="C246:C255"/>
+    <mergeCell ref="D246:D255"/>
+    <mergeCell ref="E246:E255"/>
+    <mergeCell ref="F246:F255"/>
+    <mergeCell ref="N256:N265"/>
+    <mergeCell ref="C256:C265"/>
+    <mergeCell ref="D256:D265"/>
+    <mergeCell ref="E256:E265"/>
     <mergeCell ref="P196:P205"/>
     <mergeCell ref="B206:B215"/>
     <mergeCell ref="C206:C215"/>
@@ -9575,14 +10547,32 @@
     <mergeCell ref="N206:N215"/>
     <mergeCell ref="O206:O215"/>
     <mergeCell ref="P206:P215"/>
-    <mergeCell ref="B156:B165"/>
-    <mergeCell ref="B166:B175"/>
+    <mergeCell ref="B196:B205"/>
+    <mergeCell ref="C196:C205"/>
     <mergeCell ref="B176:B185"/>
     <mergeCell ref="B186:B195"/>
     <mergeCell ref="E166:E175"/>
     <mergeCell ref="C156:C165"/>
     <mergeCell ref="D156:D165"/>
     <mergeCell ref="E156:E165"/>
+    <mergeCell ref="B216:B225"/>
+    <mergeCell ref="B226:B235"/>
+    <mergeCell ref="O196:O205"/>
+    <mergeCell ref="H166:H175"/>
+    <mergeCell ref="C176:C185"/>
+    <mergeCell ref="D176:D185"/>
+    <mergeCell ref="E176:E185"/>
+    <mergeCell ref="F176:F185"/>
+    <mergeCell ref="G176:G185"/>
+    <mergeCell ref="C166:C175"/>
+    <mergeCell ref="D166:D175"/>
+    <mergeCell ref="F166:F175"/>
+    <mergeCell ref="G166:G175"/>
+    <mergeCell ref="M186:M195"/>
+    <mergeCell ref="N166:N175"/>
+    <mergeCell ref="O166:O175"/>
+    <mergeCell ref="N186:N195"/>
+    <mergeCell ref="O186:O195"/>
     <mergeCell ref="M126:M135"/>
     <mergeCell ref="F136:F145"/>
     <mergeCell ref="B136:B145"/>
@@ -9590,9 +10580,8 @@
     <mergeCell ref="D136:D145"/>
     <mergeCell ref="E136:E145"/>
     <mergeCell ref="B126:B135"/>
-    <mergeCell ref="B5:B9"/>
-    <mergeCell ref="C5:C9"/>
-    <mergeCell ref="D5:D9"/>
+    <mergeCell ref="B156:B165"/>
+    <mergeCell ref="B166:B175"/>
     <mergeCell ref="P136:P145"/>
     <mergeCell ref="B146:B155"/>
     <mergeCell ref="C146:C155"/>
@@ -9606,21 +10595,23 @@
     <mergeCell ref="N146:N155"/>
     <mergeCell ref="O146:O155"/>
     <mergeCell ref="P146:P155"/>
-    <mergeCell ref="G10:G14"/>
-    <mergeCell ref="H10:H14"/>
-    <mergeCell ref="L10:L14"/>
-    <mergeCell ref="M10:M14"/>
-    <mergeCell ref="N10:N14"/>
+    <mergeCell ref="E5:E9"/>
+    <mergeCell ref="F5:F9"/>
+    <mergeCell ref="G5:G9"/>
+    <mergeCell ref="H5:H9"/>
+    <mergeCell ref="L5:L9"/>
     <mergeCell ref="B10:B14"/>
     <mergeCell ref="C10:C14"/>
     <mergeCell ref="D10:D14"/>
     <mergeCell ref="E10:E14"/>
     <mergeCell ref="F10:F14"/>
-    <mergeCell ref="E5:E9"/>
-    <mergeCell ref="F5:F9"/>
-    <mergeCell ref="G5:G9"/>
-    <mergeCell ref="H5:H9"/>
-    <mergeCell ref="L5:L9"/>
+    <mergeCell ref="G10:G14"/>
+    <mergeCell ref="H10:H14"/>
+    <mergeCell ref="L10:L14"/>
+    <mergeCell ref="B5:B9"/>
+    <mergeCell ref="C5:C9"/>
+    <mergeCell ref="D5:D9"/>
+    <mergeCell ref="N15:N17"/>
     <mergeCell ref="O15:O17"/>
     <mergeCell ref="P15:P17"/>
     <mergeCell ref="M5:M9"/>
@@ -9629,16 +10620,17 @@
     <mergeCell ref="P5:P9"/>
     <mergeCell ref="O10:O14"/>
     <mergeCell ref="P10:P14"/>
-    <mergeCell ref="G15:G17"/>
-    <mergeCell ref="H15:H17"/>
-    <mergeCell ref="L15:L17"/>
-    <mergeCell ref="M15:M17"/>
-    <mergeCell ref="N15:N17"/>
+    <mergeCell ref="M10:M14"/>
+    <mergeCell ref="N10:N14"/>
     <mergeCell ref="B15:B17"/>
     <mergeCell ref="C15:C17"/>
     <mergeCell ref="D15:D17"/>
     <mergeCell ref="E15:E17"/>
     <mergeCell ref="F15:F17"/>
+    <mergeCell ref="G15:G17"/>
+    <mergeCell ref="H15:H17"/>
+    <mergeCell ref="L15:L17"/>
+    <mergeCell ref="M15:M17"/>
     <mergeCell ref="P18:P21"/>
     <mergeCell ref="B22:B25"/>
     <mergeCell ref="C22:C25"/>
@@ -9655,17 +10647,22 @@
     <mergeCell ref="B18:B21"/>
     <mergeCell ref="C18:C21"/>
     <mergeCell ref="D18:D21"/>
-    <mergeCell ref="E18:E21"/>
-    <mergeCell ref="F18:F21"/>
-    <mergeCell ref="G18:G21"/>
-    <mergeCell ref="H18:H21"/>
-    <mergeCell ref="L18:L21"/>
     <mergeCell ref="M18:M21"/>
     <mergeCell ref="N26:N35"/>
     <mergeCell ref="O26:O35"/>
     <mergeCell ref="M26:M35"/>
     <mergeCell ref="N18:N21"/>
     <mergeCell ref="O18:O21"/>
+    <mergeCell ref="E18:E21"/>
+    <mergeCell ref="F18:F21"/>
+    <mergeCell ref="G18:G21"/>
+    <mergeCell ref="H18:H21"/>
+    <mergeCell ref="L18:L21"/>
+    <mergeCell ref="E26:E35"/>
+    <mergeCell ref="F26:F35"/>
+    <mergeCell ref="G26:G35"/>
+    <mergeCell ref="H26:H35"/>
+    <mergeCell ref="L26:L35"/>
     <mergeCell ref="P26:P35"/>
     <mergeCell ref="B36:B45"/>
     <mergeCell ref="C36:C45"/>
@@ -9682,16 +10679,6 @@
     <mergeCell ref="B26:B35"/>
     <mergeCell ref="C26:C35"/>
     <mergeCell ref="D26:D35"/>
-    <mergeCell ref="E26:E35"/>
-    <mergeCell ref="F26:F35"/>
-    <mergeCell ref="G26:G35"/>
-    <mergeCell ref="H26:H35"/>
-    <mergeCell ref="L26:L35"/>
-    <mergeCell ref="B46:B55"/>
-    <mergeCell ref="B56:B65"/>
-    <mergeCell ref="B66:B75"/>
-    <mergeCell ref="B76:B85"/>
-    <mergeCell ref="B86:B95"/>
     <mergeCell ref="B96:B105"/>
     <mergeCell ref="C96:C105"/>
     <mergeCell ref="D96:D105"/>
@@ -9699,6 +10686,14 @@
     <mergeCell ref="C86:C95"/>
     <mergeCell ref="D86:D95"/>
     <mergeCell ref="E86:E95"/>
+    <mergeCell ref="B46:B55"/>
+    <mergeCell ref="B56:B65"/>
+    <mergeCell ref="B66:B75"/>
+    <mergeCell ref="B76:B85"/>
+    <mergeCell ref="B86:B95"/>
+    <mergeCell ref="C76:C85"/>
+    <mergeCell ref="D76:D85"/>
+    <mergeCell ref="E76:E85"/>
     <mergeCell ref="C66:C75"/>
     <mergeCell ref="D66:D75"/>
     <mergeCell ref="E66:E75"/>
@@ -9711,27 +10706,26 @@
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="K5" r:id="rId1"/>
-    <hyperlink ref="K10" r:id="rId2"/>
+    <hyperlink ref="K5" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="K10" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0CA0C7C-33F6-4153-8307-C6BAD474B8A9}">
   <dimension ref="A1:P367"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" bestFit="1" width="17.19921875" customWidth="1"/>
-    <col min="3" max="3" bestFit="1" width="19.19921875" customWidth="1" style="6"/>
-    <col min="4" max="4" width="20.59765625" customWidth="1" style="6"/>
-    <col min="5" max="5" width="17.5" customWidth="1" style="6"/>
-    <col min="6" max="6" bestFit="1" width="18.59765625" customWidth="1" style="6"/>
-    <col min="7" max="7" width="18.3984375" customWidth="1" style="6"/>
-    <col min="8" max="8" width="14.19921875" customWidth="1" style="6"/>
-    <col min="9" max="9" width="6.3984375" customWidth="1" style="6"/>
+    <col min="2" max="2" width="17.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.19921875" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.59765625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="17.5" style="6" customWidth="1"/>
+    <col min="6" max="6" width="18.59765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.3984375" style="6" customWidth="1"/>
+    <col min="8" max="8" width="14.19921875" style="6" customWidth="1"/>
+    <col min="9" max="9" width="6.3984375" style="6" customWidth="1"/>
     <col min="10" max="10" width="29.69921875" customWidth="1"/>
     <col min="11" max="11" width="27.3984375" customWidth="1"/>
     <col min="12" max="12" width="16.5" customWidth="1"/>
@@ -9741,7 +10735,7 @@
     <col min="16" max="16" width="11.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40.2" customHeight="1">
+    <row r="1" spans="1:16" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
@@ -9760,7 +10754,7 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
     </row>
-    <row r="2" ht="40.2" customHeight="1">
+    <row r="2" spans="1:16" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="4" t="s">
         <v>8</v>
       </c>
@@ -9781,7 +10775,7 @@
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
     </row>
-    <row r="3" ht="40.2" customHeight="1">
+    <row r="3" spans="1:16" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="8"/>
       <c r="C3" s="9"/>
       <c r="D3" s="10"/>
@@ -9800,7 +10794,7 @@
       <c r="O3" s="8"/>
       <c r="P3" s="8"/>
     </row>
-    <row r="4" ht="40.2" customHeight="1" s="6" customFormat="1">
+    <row r="4" spans="1:16" s="6" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="13"/>
       <c r="B4" s="17" t="s">
         <v>12</v>
@@ -9848,7 +10842,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" ht="14.4" customHeight="1">
+    <row r="5" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7"/>
       <c r="B5" s="78">
         <v>1</v>
@@ -9886,7 +10880,7 @@
       <c r="O5" s="119"/>
       <c r="P5" s="121"/>
     </row>
-    <row r="6" ht="14.4" customHeight="1">
+    <row r="6" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7"/>
       <c r="B6" s="78"/>
       <c r="C6" s="73"/>
@@ -9910,7 +10904,7 @@
       <c r="O6" s="98"/>
       <c r="P6" s="88"/>
     </row>
-    <row r="7" ht="14.4" customHeight="1">
+    <row r="7" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7"/>
       <c r="B7" s="78"/>
       <c r="C7" s="73"/>
@@ -9934,7 +10928,7 @@
       <c r="O7" s="98"/>
       <c r="P7" s="88"/>
     </row>
-    <row r="8" ht="14.4" customHeight="1">
+    <row r="8" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7"/>
       <c r="B8" s="78"/>
       <c r="C8" s="73"/>
@@ -9958,7 +10952,7 @@
       <c r="O8" s="98"/>
       <c r="P8" s="88"/>
     </row>
-    <row r="9" ht="14.4" customHeight="1">
+    <row r="9" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7"/>
       <c r="B9" s="78"/>
       <c r="C9" s="73"/>
@@ -9982,7 +10976,7 @@
       <c r="O9" s="98"/>
       <c r="P9" s="88"/>
     </row>
-    <row r="10" ht="14.4" customHeight="1">
+    <row r="10" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7"/>
       <c r="B10" s="78"/>
       <c r="C10" s="73"/>
@@ -10006,7 +11000,7 @@
       <c r="O10" s="98"/>
       <c r="P10" s="88"/>
     </row>
-    <row r="11" ht="14.4" customHeight="1">
+    <row r="11" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7"/>
       <c r="B11" s="78"/>
       <c r="C11" s="73"/>
@@ -10030,7 +11024,7 @@
       <c r="O11" s="98"/>
       <c r="P11" s="88"/>
     </row>
-    <row r="12" ht="14.4" customHeight="1">
+    <row r="12" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7"/>
       <c r="B12" s="78"/>
       <c r="C12" s="73"/>
@@ -10054,7 +11048,7 @@
       <c r="O12" s="98"/>
       <c r="P12" s="88"/>
     </row>
-    <row r="13" ht="14.4" customHeight="1">
+    <row r="13" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7"/>
       <c r="B13" s="78"/>
       <c r="C13" s="73"/>
@@ -10078,7 +11072,7 @@
       <c r="O13" s="98"/>
       <c r="P13" s="88"/>
     </row>
-    <row r="14" ht="14.4" customHeight="1">
+    <row r="14" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7"/>
       <c r="B14" s="78"/>
       <c r="C14" s="73"/>
@@ -10102,7 +11096,7 @@
       <c r="O14" s="120"/>
       <c r="P14" s="122"/>
     </row>
-    <row r="15" ht="14.4" customHeight="1">
+    <row r="15" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7"/>
       <c r="B15" s="78"/>
       <c r="C15" s="73"/>
@@ -10126,7 +11120,7 @@
       <c r="O15" s="120"/>
       <c r="P15" s="122"/>
     </row>
-    <row r="16" ht="14.4" customHeight="1">
+    <row r="16" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7"/>
       <c r="B16" s="78"/>
       <c r="C16" s="73"/>
@@ -10150,7 +11144,7 @@
       <c r="O16" s="120"/>
       <c r="P16" s="122"/>
     </row>
-    <row r="17" ht="14.4" customHeight="1">
+    <row r="17" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7"/>
       <c r="B17" s="79"/>
       <c r="C17" s="74"/>
@@ -10172,7 +11166,7 @@
       <c r="O17" s="99"/>
       <c r="P17" s="89"/>
     </row>
-    <row r="18" ht="14.4" customHeight="1">
+    <row r="18" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7"/>
       <c r="B18" s="78">
         <v>2</v>
@@ -10208,7 +11202,7 @@
       <c r="O18" s="98"/>
       <c r="P18" s="100"/>
     </row>
-    <row r="19" ht="14.4" customHeight="1">
+    <row r="19" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7"/>
       <c r="B19" s="78"/>
       <c r="C19" s="73"/>
@@ -10232,7 +11226,7 @@
       <c r="O19" s="98"/>
       <c r="P19" s="88"/>
     </row>
-    <row r="20" ht="14.4" customHeight="1">
+    <row r="20" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7"/>
       <c r="B20" s="78"/>
       <c r="C20" s="73"/>
@@ -10256,7 +11250,7 @@
       <c r="O20" s="98"/>
       <c r="P20" s="88"/>
     </row>
-    <row r="21" ht="14.4" customHeight="1">
+    <row r="21" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7"/>
       <c r="B21" s="78"/>
       <c r="C21" s="73"/>
@@ -10280,7 +11274,7 @@
       <c r="O21" s="98"/>
       <c r="P21" s="88"/>
     </row>
-    <row r="22" ht="14.4" customHeight="1">
+    <row r="22" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7"/>
       <c r="B22" s="78"/>
       <c r="C22" s="73"/>
@@ -10304,7 +11298,7 @@
       <c r="O22" s="98"/>
       <c r="P22" s="88"/>
     </row>
-    <row r="23" ht="14.4" customHeight="1">
+    <row r="23" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7"/>
       <c r="B23" s="78"/>
       <c r="C23" s="73"/>
@@ -10326,7 +11320,7 @@
       <c r="O23" s="98"/>
       <c r="P23" s="88"/>
     </row>
-    <row r="24" ht="14.4" customHeight="1">
+    <row r="24" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7"/>
       <c r="B24" s="78"/>
       <c r="C24" s="73"/>
@@ -10348,7 +11342,7 @@
       <c r="O24" s="98"/>
       <c r="P24" s="88"/>
     </row>
-    <row r="25" ht="14.4" customHeight="1">
+    <row r="25" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7"/>
       <c r="B25" s="78"/>
       <c r="C25" s="73"/>
@@ -10372,7 +11366,7 @@
       <c r="O25" s="98"/>
       <c r="P25" s="88"/>
     </row>
-    <row r="26" ht="14.4" customHeight="1">
+    <row r="26" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7"/>
       <c r="B26" s="78"/>
       <c r="C26" s="73"/>
@@ -10394,7 +11388,7 @@
       <c r="O26" s="98"/>
       <c r="P26" s="88"/>
     </row>
-    <row r="27" ht="14.4" customHeight="1">
+    <row r="27" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7"/>
       <c r="B27" s="78"/>
       <c r="C27" s="73"/>
@@ -10418,7 +11412,7 @@
       <c r="O27" s="98"/>
       <c r="P27" s="88"/>
     </row>
-    <row r="28" ht="14.4" customHeight="1">
+    <row r="28" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7"/>
       <c r="B28" s="78"/>
       <c r="C28" s="73"/>
@@ -10442,7 +11436,7 @@
       <c r="O28" s="98"/>
       <c r="P28" s="88"/>
     </row>
-    <row r="29" ht="14.4" customHeight="1">
+    <row r="29" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7"/>
       <c r="B29" s="78"/>
       <c r="C29" s="73"/>
@@ -10466,7 +11460,7 @@
       <c r="O29" s="120"/>
       <c r="P29" s="122"/>
     </row>
-    <row r="30" ht="14.4" customHeight="1">
+    <row r="30" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="7"/>
       <c r="B30" s="79"/>
       <c r="C30" s="74"/>
@@ -10488,7 +11482,7 @@
       <c r="O30" s="99"/>
       <c r="P30" s="89"/>
     </row>
-    <row r="31" ht="14.4" customHeight="1">
+    <row r="31" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="7"/>
       <c r="B31" s="78">
         <v>3</v>
@@ -10526,7 +11520,7 @@
       <c r="O31" s="119"/>
       <c r="P31" s="121"/>
     </row>
-    <row r="32" ht="14.4" customHeight="1">
+    <row r="32" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="7"/>
       <c r="B32" s="78"/>
       <c r="C32" s="73"/>
@@ -10550,7 +11544,7 @@
       <c r="O32" s="98"/>
       <c r="P32" s="88"/>
     </row>
-    <row r="33" ht="14.4" customHeight="1">
+    <row r="33" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="7"/>
       <c r="B33" s="78"/>
       <c r="C33" s="73"/>
@@ -10574,7 +11568,7 @@
       <c r="O33" s="98"/>
       <c r="P33" s="88"/>
     </row>
-    <row r="34" ht="14.4" customHeight="1">
+    <row r="34" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="7"/>
       <c r="B34" s="78"/>
       <c r="C34" s="73"/>
@@ -10598,7 +11592,7 @@
       <c r="O34" s="98"/>
       <c r="P34" s="88"/>
     </row>
-    <row r="35" ht="14.4" customHeight="1">
+    <row r="35" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="7"/>
       <c r="B35" s="78"/>
       <c r="C35" s="73"/>
@@ -10622,7 +11616,7 @@
       <c r="O35" s="98"/>
       <c r="P35" s="88"/>
     </row>
-    <row r="36" ht="14.4" customHeight="1">
+    <row r="36" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="7"/>
       <c r="B36" s="78"/>
       <c r="C36" s="73"/>
@@ -10646,7 +11640,7 @@
       <c r="O36" s="98"/>
       <c r="P36" s="88"/>
     </row>
-    <row r="37" ht="14.4" customHeight="1">
+    <row r="37" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="7"/>
       <c r="B37" s="78"/>
       <c r="C37" s="73"/>
@@ -10670,7 +11664,7 @@
       <c r="O37" s="98"/>
       <c r="P37" s="88"/>
     </row>
-    <row r="38" ht="14.4" customHeight="1">
+    <row r="38" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="7"/>
       <c r="B38" s="78"/>
       <c r="C38" s="73"/>
@@ -10694,7 +11688,7 @@
       <c r="O38" s="98"/>
       <c r="P38" s="88"/>
     </row>
-    <row r="39" ht="14.4" customHeight="1">
+    <row r="39" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="7"/>
       <c r="B39" s="78"/>
       <c r="C39" s="73"/>
@@ -10718,7 +11712,7 @@
       <c r="O39" s="98"/>
       <c r="P39" s="88"/>
     </row>
-    <row r="40" ht="14.4" customHeight="1">
+    <row r="40" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7"/>
       <c r="B40" s="78"/>
       <c r="C40" s="73"/>
@@ -10742,7 +11736,7 @@
       <c r="O40" s="98"/>
       <c r="P40" s="88"/>
     </row>
-    <row r="41" ht="14.4" customHeight="1">
+    <row r="41" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="7"/>
       <c r="B41" s="78"/>
       <c r="C41" s="73"/>
@@ -10766,7 +11760,7 @@
       <c r="O41" s="98"/>
       <c r="P41" s="88"/>
     </row>
-    <row r="42" ht="14.4" customHeight="1">
+    <row r="42" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="7"/>
       <c r="B42" s="78"/>
       <c r="C42" s="73"/>
@@ -10790,7 +11784,7 @@
       <c r="O42" s="98"/>
       <c r="P42" s="88"/>
     </row>
-    <row r="43" ht="14.4" customHeight="1">
+    <row r="43" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="7"/>
       <c r="B43" s="79"/>
       <c r="C43" s="74"/>
@@ -10812,7 +11806,7 @@
       <c r="O43" s="99"/>
       <c r="P43" s="89"/>
     </row>
-    <row r="44" ht="14.4" customHeight="1">
+    <row r="44" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="7"/>
       <c r="B44" s="78">
         <v>4</v>
@@ -10848,7 +11842,7 @@
       <c r="O44" s="98"/>
       <c r="P44" s="100"/>
     </row>
-    <row r="45" ht="14.4" customHeight="1">
+    <row r="45" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="7"/>
       <c r="B45" s="78"/>
       <c r="C45" s="73"/>
@@ -10872,7 +11866,7 @@
       <c r="O45" s="98"/>
       <c r="P45" s="88"/>
     </row>
-    <row r="46" ht="14.4" customHeight="1">
+    <row r="46" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="7"/>
       <c r="B46" s="78"/>
       <c r="C46" s="73"/>
@@ -10896,7 +11890,7 @@
       <c r="O46" s="98"/>
       <c r="P46" s="88"/>
     </row>
-    <row r="47" ht="14.4" customHeight="1">
+    <row r="47" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="7"/>
       <c r="B47" s="78"/>
       <c r="C47" s="73"/>
@@ -10920,7 +11914,7 @@
       <c r="O47" s="98"/>
       <c r="P47" s="88"/>
     </row>
-    <row r="48" ht="14.4" customHeight="1">
+    <row r="48" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="7"/>
       <c r="B48" s="78"/>
       <c r="C48" s="73"/>
@@ -10944,7 +11938,7 @@
       <c r="O48" s="98"/>
       <c r="P48" s="88"/>
     </row>
-    <row r="49" ht="14.4" customHeight="1">
+    <row r="49" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="7"/>
       <c r="B49" s="78"/>
       <c r="C49" s="73"/>
@@ -10968,7 +11962,7 @@
       <c r="O49" s="98"/>
       <c r="P49" s="88"/>
     </row>
-    <row r="50" ht="14.4" customHeight="1">
+    <row r="50" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="7"/>
       <c r="B50" s="78"/>
       <c r="C50" s="73"/>
@@ -10992,7 +11986,7 @@
       <c r="O50" s="98"/>
       <c r="P50" s="88"/>
     </row>
-    <row r="51" ht="14.4" customHeight="1">
+    <row r="51" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="7"/>
       <c r="B51" s="78"/>
       <c r="C51" s="73"/>
@@ -11016,7 +12010,7 @@
       <c r="O51" s="98"/>
       <c r="P51" s="88"/>
     </row>
-    <row r="52" ht="14.4" customHeight="1">
+    <row r="52" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="7"/>
       <c r="B52" s="78"/>
       <c r="C52" s="73"/>
@@ -11040,7 +12034,7 @@
       <c r="O52" s="98"/>
       <c r="P52" s="88"/>
     </row>
-    <row r="53" ht="14.4" customHeight="1">
+    <row r="53" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="7"/>
       <c r="B53" s="78"/>
       <c r="C53" s="73"/>
@@ -11064,7 +12058,7 @@
       <c r="O53" s="98"/>
       <c r="P53" s="88"/>
     </row>
-    <row r="54" ht="14.4" customHeight="1">
+    <row r="54" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="7"/>
       <c r="B54" s="78"/>
       <c r="C54" s="73"/>
@@ -11088,7 +12082,7 @@
       <c r="O54" s="98"/>
       <c r="P54" s="88"/>
     </row>
-    <row r="55" ht="14.4" customHeight="1">
+    <row r="55" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="7"/>
       <c r="B55" s="78"/>
       <c r="C55" s="73"/>
@@ -11112,7 +12106,7 @@
       <c r="O55" s="120"/>
       <c r="P55" s="122"/>
     </row>
-    <row r="56" ht="14.4" customHeight="1">
+    <row r="56" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="7"/>
       <c r="B56" s="79"/>
       <c r="C56" s="74"/>
@@ -11134,7 +12128,7 @@
       <c r="O56" s="99"/>
       <c r="P56" s="89"/>
     </row>
-    <row r="57" ht="14.4" customHeight="1">
+    <row r="57" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="7"/>
       <c r="B57" s="78">
         <v>5</v>
@@ -11170,7 +12164,7 @@
       <c r="O57" s="119"/>
       <c r="P57" s="121"/>
     </row>
-    <row r="58" ht="14.4" customHeight="1">
+    <row r="58" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="7"/>
       <c r="B58" s="78"/>
       <c r="C58" s="73"/>
@@ -11194,7 +12188,7 @@
       <c r="O58" s="98"/>
       <c r="P58" s="88"/>
     </row>
-    <row r="59" ht="14.4" customHeight="1">
+    <row r="59" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="7"/>
       <c r="B59" s="78"/>
       <c r="C59" s="73"/>
@@ -11218,7 +12212,7 @@
       <c r="O59" s="98"/>
       <c r="P59" s="88"/>
     </row>
-    <row r="60" ht="14.4" customHeight="1">
+    <row r="60" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="7"/>
       <c r="B60" s="78"/>
       <c r="C60" s="73"/>
@@ -11242,7 +12236,7 @@
       <c r="O60" s="98"/>
       <c r="P60" s="88"/>
     </row>
-    <row r="61" ht="14.4" customHeight="1">
+    <row r="61" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="7"/>
       <c r="B61" s="78"/>
       <c r="C61" s="73"/>
@@ -11266,7 +12260,7 @@
       <c r="O61" s="98"/>
       <c r="P61" s="88"/>
     </row>
-    <row r="62" ht="14.4" customHeight="1">
+    <row r="62" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="7"/>
       <c r="B62" s="78"/>
       <c r="C62" s="73"/>
@@ -11290,7 +12284,7 @@
       <c r="O62" s="98"/>
       <c r="P62" s="88"/>
     </row>
-    <row r="63" ht="14.4" customHeight="1">
+    <row r="63" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="7"/>
       <c r="B63" s="78"/>
       <c r="C63" s="73"/>
@@ -11314,7 +12308,7 @@
       <c r="O63" s="98"/>
       <c r="P63" s="88"/>
     </row>
-    <row r="64" ht="14.4" customHeight="1">
+    <row r="64" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="7"/>
       <c r="B64" s="78"/>
       <c r="C64" s="73"/>
@@ -11330,7 +12324,7 @@
         <v>291</v>
       </c>
       <c r="K64" s="14">
-        <v>22681371823.6667</v>
+        <v>22681371823.666698</v>
       </c>
       <c r="L64" s="93"/>
       <c r="M64" s="93"/>
@@ -11338,7 +12332,7 @@
       <c r="O64" s="98"/>
       <c r="P64" s="88"/>
     </row>
-    <row r="65" ht="14.4" customHeight="1">
+    <row r="65" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="7"/>
       <c r="B65" s="78"/>
       <c r="C65" s="73"/>
@@ -11354,7 +12348,7 @@
         <v>292</v>
       </c>
       <c r="K65" s="14">
-        <v>28837590874.6667</v>
+        <v>28837590874.666698</v>
       </c>
       <c r="L65" s="93"/>
       <c r="M65" s="93"/>
@@ -11362,7 +12356,7 @@
       <c r="O65" s="98"/>
       <c r="P65" s="88"/>
     </row>
-    <row r="66" ht="14.4" customHeight="1">
+    <row r="66" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="7"/>
       <c r="B66" s="78"/>
       <c r="C66" s="73"/>
@@ -11386,7 +12380,7 @@
       <c r="O66" s="98"/>
       <c r="P66" s="88"/>
     </row>
-    <row r="67" ht="14.4" customHeight="1">
+    <row r="67" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="7"/>
       <c r="B67" s="78"/>
       <c r="C67" s="73"/>
@@ -11410,7 +12404,7 @@
       <c r="O67" s="98"/>
       <c r="P67" s="88"/>
     </row>
-    <row r="68" ht="14.4" customHeight="1">
+    <row r="68" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="7"/>
       <c r="B68" s="78"/>
       <c r="C68" s="73"/>
@@ -11434,7 +12428,7 @@
       <c r="O68" s="120"/>
       <c r="P68" s="122"/>
     </row>
-    <row r="69" ht="14.4" customHeight="1">
+    <row r="69" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="7"/>
       <c r="B69" s="79"/>
       <c r="C69" s="74"/>
@@ -11456,7 +12450,7 @@
       <c r="O69" s="99"/>
       <c r="P69" s="89"/>
     </row>
-    <row r="70" ht="14.4" customHeight="1">
+    <row r="70" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="7"/>
       <c r="B70" s="78">
         <v>6</v>
@@ -11494,7 +12488,7 @@
       <c r="O70" s="98"/>
       <c r="P70" s="100"/>
     </row>
-    <row r="71" ht="14.4" customHeight="1">
+    <row r="71" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="7"/>
       <c r="B71" s="78"/>
       <c r="C71" s="73"/>
@@ -11518,7 +12512,7 @@
       <c r="O71" s="98"/>
       <c r="P71" s="88"/>
     </row>
-    <row r="72" ht="14.4" customHeight="1">
+    <row r="72" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="7"/>
       <c r="B72" s="78"/>
       <c r="C72" s="73"/>
@@ -11542,7 +12536,7 @@
       <c r="O72" s="98"/>
       <c r="P72" s="88"/>
     </row>
-    <row r="73" ht="14.4" customHeight="1">
+    <row r="73" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="7"/>
       <c r="B73" s="78"/>
       <c r="C73" s="73"/>
@@ -11566,7 +12560,7 @@
       <c r="O73" s="98"/>
       <c r="P73" s="88"/>
     </row>
-    <row r="74" ht="14.4" customHeight="1">
+    <row r="74" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="7"/>
       <c r="B74" s="78"/>
       <c r="C74" s="73"/>
@@ -11590,7 +12584,7 @@
       <c r="O74" s="98"/>
       <c r="P74" s="88"/>
     </row>
-    <row r="75" ht="14.4" customHeight="1">
+    <row r="75" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="7"/>
       <c r="B75" s="78"/>
       <c r="C75" s="73"/>
@@ -11614,7 +12608,7 @@
       <c r="O75" s="98"/>
       <c r="P75" s="88"/>
     </row>
-    <row r="76" ht="14.4" customHeight="1">
+    <row r="76" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="7"/>
       <c r="B76" s="78"/>
       <c r="C76" s="73"/>
@@ -11638,7 +12632,7 @@
       <c r="O76" s="98"/>
       <c r="P76" s="88"/>
     </row>
-    <row r="77" ht="14.4" customHeight="1">
+    <row r="77" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="7"/>
       <c r="B77" s="78"/>
       <c r="C77" s="73"/>
@@ -11662,7 +12656,7 @@
       <c r="O77" s="98"/>
       <c r="P77" s="88"/>
     </row>
-    <row r="78" ht="14.4" customHeight="1">
+    <row r="78" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="7"/>
       <c r="B78" s="78"/>
       <c r="C78" s="73"/>
@@ -11686,7 +12680,7 @@
       <c r="O78" s="98"/>
       <c r="P78" s="88"/>
     </row>
-    <row r="79" ht="14.4" customHeight="1">
+    <row r="79" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="7"/>
       <c r="B79" s="78"/>
       <c r="C79" s="73"/>
@@ -11710,7 +12704,7 @@
       <c r="O79" s="120"/>
       <c r="P79" s="122"/>
     </row>
-    <row r="80" ht="14.4" customHeight="1">
+    <row r="80" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="7"/>
       <c r="B80" s="79"/>
       <c r="C80" s="74"/>
@@ -11732,7 +12726,7 @@
       <c r="O80" s="99"/>
       <c r="P80" s="89"/>
     </row>
-    <row r="81" ht="14.4" customHeight="1">
+    <row r="81" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="7"/>
       <c r="B81" s="78">
         <v>7</v>
@@ -11770,7 +12764,7 @@
       <c r="O81" s="119"/>
       <c r="P81" s="121"/>
     </row>
-    <row r="82" ht="14.4" customHeight="1">
+    <row r="82" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="7"/>
       <c r="B82" s="78"/>
       <c r="C82" s="73"/>
@@ -11794,7 +12788,7 @@
       <c r="O82" s="98"/>
       <c r="P82" s="88"/>
     </row>
-    <row r="83" ht="14.4" customHeight="1">
+    <row r="83" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="7"/>
       <c r="B83" s="78"/>
       <c r="C83" s="73"/>
@@ -11818,7 +12812,7 @@
       <c r="O83" s="98"/>
       <c r="P83" s="88"/>
     </row>
-    <row r="84" ht="14.4" customHeight="1">
+    <row r="84" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="7"/>
       <c r="B84" s="78"/>
       <c r="C84" s="73"/>
@@ -11842,7 +12836,7 @@
       <c r="O84" s="98"/>
       <c r="P84" s="88"/>
     </row>
-    <row r="85" ht="14.4" customHeight="1">
+    <row r="85" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="7"/>
       <c r="B85" s="78"/>
       <c r="C85" s="73"/>
@@ -11866,7 +12860,7 @@
       <c r="O85" s="98"/>
       <c r="P85" s="88"/>
     </row>
-    <row r="86" ht="14.4" customHeight="1">
+    <row r="86" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="7"/>
       <c r="B86" s="78"/>
       <c r="C86" s="73"/>
@@ -11890,7 +12884,7 @@
       <c r="O86" s="98"/>
       <c r="P86" s="88"/>
     </row>
-    <row r="87" ht="14.4" customHeight="1">
+    <row r="87" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="7"/>
       <c r="B87" s="78"/>
       <c r="C87" s="73"/>
@@ -11914,7 +12908,7 @@
       <c r="O87" s="98"/>
       <c r="P87" s="88"/>
     </row>
-    <row r="88" ht="14.4" customHeight="1">
+    <row r="88" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="7"/>
       <c r="B88" s="78"/>
       <c r="C88" s="73"/>
@@ -11938,7 +12932,7 @@
       <c r="O88" s="98"/>
       <c r="P88" s="88"/>
     </row>
-    <row r="89" ht="14.4" customHeight="1">
+    <row r="89" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="7"/>
       <c r="B89" s="78"/>
       <c r="C89" s="73"/>
@@ -11962,7 +12956,7 @@
       <c r="O89" s="98"/>
       <c r="P89" s="88"/>
     </row>
-    <row r="90" ht="14.4" customHeight="1">
+    <row r="90" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="7"/>
       <c r="B90" s="78"/>
       <c r="C90" s="73"/>
@@ -11986,7 +12980,7 @@
       <c r="O90" s="120"/>
       <c r="P90" s="122"/>
     </row>
-    <row r="91" ht="14.4" customHeight="1">
+    <row r="91" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="7"/>
       <c r="B91" s="79"/>
       <c r="C91" s="74"/>
@@ -12008,7 +13002,7 @@
       <c r="O91" s="99"/>
       <c r="P91" s="89"/>
     </row>
-    <row r="92" ht="14.4" customHeight="1">
+    <row r="92" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="7"/>
       <c r="B92" s="78">
         <v>8</v>
@@ -12046,7 +13040,7 @@
       <c r="O92" s="98"/>
       <c r="P92" s="100"/>
     </row>
-    <row r="93" ht="14.4" customHeight="1">
+    <row r="93" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="7"/>
       <c r="B93" s="78"/>
       <c r="C93" s="73"/>
@@ -12070,7 +13064,7 @@
       <c r="O93" s="98"/>
       <c r="P93" s="88"/>
     </row>
-    <row r="94" ht="14.4" customHeight="1">
+    <row r="94" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="7"/>
       <c r="B94" s="78"/>
       <c r="C94" s="73"/>
@@ -12094,7 +13088,7 @@
       <c r="O94" s="98"/>
       <c r="P94" s="88"/>
     </row>
-    <row r="95" ht="14.4" customHeight="1">
+    <row r="95" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="7"/>
       <c r="B95" s="78"/>
       <c r="C95" s="73"/>
@@ -12118,7 +13112,7 @@
       <c r="O95" s="98"/>
       <c r="P95" s="88"/>
     </row>
-    <row r="96" ht="14.4" customHeight="1">
+    <row r="96" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="7"/>
       <c r="B96" s="78"/>
       <c r="C96" s="73"/>
@@ -12142,7 +13136,7 @@
       <c r="O96" s="98"/>
       <c r="P96" s="88"/>
     </row>
-    <row r="97" ht="14.4" customHeight="1">
+    <row r="97" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="7"/>
       <c r="B97" s="78"/>
       <c r="C97" s="73"/>
@@ -12166,7 +13160,7 @@
       <c r="O97" s="98"/>
       <c r="P97" s="88"/>
     </row>
-    <row r="98" ht="14.4" customHeight="1">
+    <row r="98" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="7"/>
       <c r="B98" s="78"/>
       <c r="C98" s="73"/>
@@ -12190,7 +13184,7 @@
       <c r="O98" s="98"/>
       <c r="P98" s="88"/>
     </row>
-    <row r="99" ht="14.4" customHeight="1">
+    <row r="99" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="7"/>
       <c r="B99" s="78"/>
       <c r="C99" s="73"/>
@@ -12214,7 +13208,7 @@
       <c r="O99" s="98"/>
       <c r="P99" s="88"/>
     </row>
-    <row r="100" ht="14.4" customHeight="1">
+    <row r="100" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="7"/>
       <c r="B100" s="78"/>
       <c r="C100" s="73"/>
@@ -12238,7 +13232,7 @@
       <c r="O100" s="98"/>
       <c r="P100" s="88"/>
     </row>
-    <row r="101" ht="14.4" customHeight="1">
+    <row r="101" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="7"/>
       <c r="B101" s="78"/>
       <c r="C101" s="73"/>
@@ -12262,7 +13256,7 @@
       <c r="O101" s="120"/>
       <c r="P101" s="122"/>
     </row>
-    <row r="102" ht="14.4" customHeight="1">
+    <row r="102" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="7"/>
       <c r="B102" s="79"/>
       <c r="C102" s="74"/>
@@ -12284,7 +13278,7 @@
       <c r="O102" s="99"/>
       <c r="P102" s="89"/>
     </row>
-    <row r="103" ht="14.4" customHeight="1">
+    <row r="103" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="7"/>
       <c r="B103" s="78">
         <v>9</v>
@@ -12322,7 +13316,7 @@
       <c r="O103" s="119"/>
       <c r="P103" s="121"/>
     </row>
-    <row r="104" ht="14.4" customHeight="1">
+    <row r="104" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="7"/>
       <c r="B104" s="78"/>
       <c r="C104" s="73"/>
@@ -12346,7 +13340,7 @@
       <c r="O104" s="98"/>
       <c r="P104" s="88"/>
     </row>
-    <row r="105" ht="14.4" customHeight="1">
+    <row r="105" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="7"/>
       <c r="B105" s="78"/>
       <c r="C105" s="73"/>
@@ -12370,7 +13364,7 @@
       <c r="O105" s="98"/>
       <c r="P105" s="88"/>
     </row>
-    <row r="106" ht="14.4" customHeight="1">
+    <row r="106" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="7"/>
       <c r="B106" s="78"/>
       <c r="C106" s="73"/>
@@ -12394,7 +13388,7 @@
       <c r="O106" s="98"/>
       <c r="P106" s="88"/>
     </row>
-    <row r="107" ht="14.4" customHeight="1">
+    <row r="107" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="7"/>
       <c r="B107" s="78"/>
       <c r="C107" s="73"/>
@@ -12418,7 +13412,7 @@
       <c r="O107" s="98"/>
       <c r="P107" s="88"/>
     </row>
-    <row r="108" ht="14.4" customHeight="1">
+    <row r="108" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="7"/>
       <c r="B108" s="78"/>
       <c r="C108" s="73"/>
@@ -12442,7 +13436,7 @@
       <c r="O108" s="98"/>
       <c r="P108" s="88"/>
     </row>
-    <row r="109" ht="14.4" customHeight="1">
+    <row r="109" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="7"/>
       <c r="B109" s="78"/>
       <c r="C109" s="73"/>
@@ -12466,7 +13460,7 @@
       <c r="O109" s="98"/>
       <c r="P109" s="88"/>
     </row>
-    <row r="110" ht="14.4" customHeight="1">
+    <row r="110" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="7"/>
       <c r="B110" s="78"/>
       <c r="C110" s="73"/>
@@ -12490,7 +13484,7 @@
       <c r="O110" s="98"/>
       <c r="P110" s="88"/>
     </row>
-    <row r="111" ht="14.4" customHeight="1">
+    <row r="111" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="7"/>
       <c r="B111" s="78"/>
       <c r="C111" s="73"/>
@@ -12514,7 +13508,7 @@
       <c r="O111" s="98"/>
       <c r="P111" s="88"/>
     </row>
-    <row r="112" ht="14.4" customHeight="1">
+    <row r="112" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="7"/>
       <c r="B112" s="78"/>
       <c r="C112" s="73"/>
@@ -12536,7 +13530,7 @@
       <c r="O112" s="120"/>
       <c r="P112" s="122"/>
     </row>
-    <row r="113" ht="14.4" customHeight="1">
+    <row r="113" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="7"/>
       <c r="B113" s="79"/>
       <c r="C113" s="74"/>
@@ -12558,7 +13552,7 @@
       <c r="O113" s="99"/>
       <c r="P113" s="89"/>
     </row>
-    <row r="114" ht="14.4" customHeight="1">
+    <row r="114" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="7"/>
       <c r="B114" s="78">
         <v>10</v>
@@ -12596,7 +13590,7 @@
       <c r="O114" s="98"/>
       <c r="P114" s="100"/>
     </row>
-    <row r="115" ht="14.4" customHeight="1">
+    <row r="115" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="7"/>
       <c r="B115" s="78"/>
       <c r="C115" s="73"/>
@@ -12620,7 +13614,7 @@
       <c r="O115" s="98"/>
       <c r="P115" s="88"/>
     </row>
-    <row r="116" ht="14.4" customHeight="1">
+    <row r="116" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="7"/>
       <c r="B116" s="78"/>
       <c r="C116" s="73"/>
@@ -12642,7 +13636,7 @@
       <c r="O116" s="98"/>
       <c r="P116" s="88"/>
     </row>
-    <row r="117" ht="14.4" customHeight="1">
+    <row r="117" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="7"/>
       <c r="B117" s="78"/>
       <c r="C117" s="73"/>
@@ -12662,7 +13656,7 @@
       <c r="O117" s="98"/>
       <c r="P117" s="88"/>
     </row>
-    <row r="118" ht="14.4" customHeight="1">
+    <row r="118" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="7"/>
       <c r="B118" s="78"/>
       <c r="C118" s="73"/>
@@ -12682,7 +13676,7 @@
       <c r="O118" s="98"/>
       <c r="P118" s="88"/>
     </row>
-    <row r="119" ht="14.4" customHeight="1">
+    <row r="119" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="7"/>
       <c r="B119" s="78"/>
       <c r="C119" s="73"/>
@@ -12702,7 +13696,7 @@
       <c r="O119" s="98"/>
       <c r="P119" s="88"/>
     </row>
-    <row r="120" ht="14.4" customHeight="1">
+    <row r="120" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="7"/>
       <c r="B120" s="78"/>
       <c r="C120" s="73"/>
@@ -12722,7 +13716,7 @@
       <c r="O120" s="98"/>
       <c r="P120" s="88"/>
     </row>
-    <row r="121" ht="14.4" customHeight="1">
+    <row r="121" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="7"/>
       <c r="B121" s="78"/>
       <c r="C121" s="73"/>
@@ -12742,7 +13736,7 @@
       <c r="O121" s="98"/>
       <c r="P121" s="88"/>
     </row>
-    <row r="122" ht="14.4" customHeight="1">
+    <row r="122" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="7"/>
       <c r="B122" s="78"/>
       <c r="C122" s="73"/>
@@ -12762,7 +13756,7 @@
       <c r="O122" s="98"/>
       <c r="P122" s="88"/>
     </row>
-    <row r="123">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A123" s="7"/>
       <c r="B123" s="79"/>
       <c r="C123" s="74"/>
@@ -12782,7 +13776,7 @@
       <c r="O123" s="99"/>
       <c r="P123" s="89"/>
     </row>
-    <row r="124" ht="14.4" customHeight="1">
+    <row r="124" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="7"/>
       <c r="B124" s="78">
         <v>11</v>
@@ -12820,7 +13814,7 @@
       <c r="O124" s="119"/>
       <c r="P124" s="121"/>
     </row>
-    <row r="125" ht="14.4" customHeight="1">
+    <row r="125" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="7"/>
       <c r="B125" s="78"/>
       <c r="C125" s="73"/>
@@ -12844,7 +13838,7 @@
       <c r="O125" s="98"/>
       <c r="P125" s="88"/>
     </row>
-    <row r="126" ht="14.4" customHeight="1">
+    <row r="126" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="7"/>
       <c r="B126" s="78"/>
       <c r="C126" s="73"/>
@@ -12866,7 +13860,7 @@
       <c r="O126" s="98"/>
       <c r="P126" s="88"/>
     </row>
-    <row r="127" ht="14.4" customHeight="1">
+    <row r="127" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="7"/>
       <c r="B127" s="78"/>
       <c r="C127" s="73"/>
@@ -12886,7 +13880,7 @@
       <c r="O127" s="98"/>
       <c r="P127" s="88"/>
     </row>
-    <row r="128" ht="14.4" customHeight="1">
+    <row r="128" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="7"/>
       <c r="B128" s="78"/>
       <c r="C128" s="73"/>
@@ -12906,7 +13900,7 @@
       <c r="O128" s="98"/>
       <c r="P128" s="88"/>
     </row>
-    <row r="129" ht="14.4" customHeight="1">
+    <row r="129" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="7"/>
       <c r="B129" s="78"/>
       <c r="C129" s="73"/>
@@ -12926,7 +13920,7 @@
       <c r="O129" s="98"/>
       <c r="P129" s="88"/>
     </row>
-    <row r="130" ht="14.4" customHeight="1">
+    <row r="130" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="7"/>
       <c r="B130" s="78"/>
       <c r="C130" s="73"/>
@@ -12946,7 +13940,7 @@
       <c r="O130" s="98"/>
       <c r="P130" s="88"/>
     </row>
-    <row r="131" ht="14.4" customHeight="1">
+    <row r="131" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="7"/>
       <c r="B131" s="78"/>
       <c r="C131" s="73"/>
@@ -12966,7 +13960,7 @@
       <c r="O131" s="98"/>
       <c r="P131" s="88"/>
     </row>
-    <row r="132" ht="14.4" customHeight="1">
+    <row r="132" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="7"/>
       <c r="B132" s="78"/>
       <c r="C132" s="73"/>
@@ -12986,7 +13980,7 @@
       <c r="O132" s="98"/>
       <c r="P132" s="88"/>
     </row>
-    <row r="133" ht="14.4" customHeight="1">
+    <row r="133" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="7"/>
       <c r="B133" s="79"/>
       <c r="C133" s="74"/>
@@ -13006,7 +14000,7 @@
       <c r="O133" s="99"/>
       <c r="P133" s="89"/>
     </row>
-    <row r="134" ht="14.4" customHeight="1">
+    <row r="134" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="7"/>
       <c r="B134" s="78">
         <v>12</v>
@@ -13044,7 +14038,7 @@
       <c r="O134" s="98"/>
       <c r="P134" s="100"/>
     </row>
-    <row r="135" ht="14.4" customHeight="1">
+    <row r="135" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="7"/>
       <c r="B135" s="78"/>
       <c r="C135" s="73"/>
@@ -13068,7 +14062,7 @@
       <c r="O135" s="98"/>
       <c r="P135" s="88"/>
     </row>
-    <row r="136" ht="14.4" customHeight="1">
+    <row r="136" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="7"/>
       <c r="B136" s="78"/>
       <c r="C136" s="73"/>
@@ -13090,7 +14084,7 @@
       <c r="O136" s="98"/>
       <c r="P136" s="88"/>
     </row>
-    <row r="137" ht="14.4" customHeight="1">
+    <row r="137" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="7"/>
       <c r="B137" s="78"/>
       <c r="C137" s="73"/>
@@ -13110,7 +14104,7 @@
       <c r="O137" s="98"/>
       <c r="P137" s="88"/>
     </row>
-    <row r="138" ht="14.4" customHeight="1">
+    <row r="138" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="7"/>
       <c r="B138" s="78"/>
       <c r="C138" s="73"/>
@@ -13130,7 +14124,7 @@
       <c r="O138" s="98"/>
       <c r="P138" s="88"/>
     </row>
-    <row r="139" ht="14.4" customHeight="1">
+    <row r="139" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="7"/>
       <c r="B139" s="78"/>
       <c r="C139" s="73"/>
@@ -13150,7 +14144,7 @@
       <c r="O139" s="98"/>
       <c r="P139" s="88"/>
     </row>
-    <row r="140" ht="14.4" customHeight="1">
+    <row r="140" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="7"/>
       <c r="B140" s="78"/>
       <c r="C140" s="73"/>
@@ -13170,7 +14164,7 @@
       <c r="O140" s="98"/>
       <c r="P140" s="88"/>
     </row>
-    <row r="141" ht="14.4" customHeight="1">
+    <row r="141" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="7"/>
       <c r="B141" s="78"/>
       <c r="C141" s="73"/>
@@ -13190,7 +14184,7 @@
       <c r="O141" s="98"/>
       <c r="P141" s="88"/>
     </row>
-    <row r="142" ht="14.4" customHeight="1">
+    <row r="142" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="7"/>
       <c r="B142" s="78"/>
       <c r="C142" s="73"/>
@@ -13210,7 +14204,7 @@
       <c r="O142" s="98"/>
       <c r="P142" s="88"/>
     </row>
-    <row r="143" ht="14.4" customHeight="1">
+    <row r="143" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="7"/>
       <c r="B143" s="79"/>
       <c r="C143" s="74"/>
@@ -13230,7 +14224,7 @@
       <c r="O143" s="99"/>
       <c r="P143" s="89"/>
     </row>
-    <row r="144" ht="14.4" customHeight="1">
+    <row r="144" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="7"/>
       <c r="B144" s="78">
         <v>13</v>
@@ -13268,7 +14262,7 @@
       <c r="O144" s="119"/>
       <c r="P144" s="121"/>
     </row>
-    <row r="145" ht="14.4" customHeight="1">
+    <row r="145" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="7"/>
       <c r="B145" s="78"/>
       <c r="C145" s="73"/>
@@ -13292,7 +14286,7 @@
       <c r="O145" s="98"/>
       <c r="P145" s="88"/>
     </row>
-    <row r="146" ht="14.4" customHeight="1">
+    <row r="146" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="7"/>
       <c r="B146" s="78"/>
       <c r="C146" s="73"/>
@@ -13314,7 +14308,7 @@
       <c r="O146" s="98"/>
       <c r="P146" s="88"/>
     </row>
-    <row r="147" ht="14.4" customHeight="1">
+    <row r="147" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="7"/>
       <c r="B147" s="78"/>
       <c r="C147" s="73"/>
@@ -13334,7 +14328,7 @@
       <c r="O147" s="98"/>
       <c r="P147" s="88"/>
     </row>
-    <row r="148" ht="14.4" customHeight="1">
+    <row r="148" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="7"/>
       <c r="B148" s="78"/>
       <c r="C148" s="73"/>
@@ -13354,7 +14348,7 @@
       <c r="O148" s="98"/>
       <c r="P148" s="88"/>
     </row>
-    <row r="149" ht="14.4" customHeight="1">
+    <row r="149" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="7"/>
       <c r="B149" s="78"/>
       <c r="C149" s="73"/>
@@ -13374,7 +14368,7 @@
       <c r="O149" s="98"/>
       <c r="P149" s="88"/>
     </row>
-    <row r="150" ht="14.4" customHeight="1">
+    <row r="150" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="7"/>
       <c r="B150" s="78"/>
       <c r="C150" s="73"/>
@@ -13394,7 +14388,7 @@
       <c r="O150" s="98"/>
       <c r="P150" s="88"/>
     </row>
-    <row r="151" ht="14.4" customHeight="1">
+    <row r="151" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="7"/>
       <c r="B151" s="78"/>
       <c r="C151" s="73"/>
@@ -13414,7 +14408,7 @@
       <c r="O151" s="98"/>
       <c r="P151" s="88"/>
     </row>
-    <row r="152" ht="14.4" customHeight="1">
+    <row r="152" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="7"/>
       <c r="B152" s="78"/>
       <c r="C152" s="73"/>
@@ -13434,7 +14428,7 @@
       <c r="O152" s="98"/>
       <c r="P152" s="88"/>
     </row>
-    <row r="153" ht="14.4" customHeight="1">
+    <row r="153" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="7"/>
       <c r="B153" s="79"/>
       <c r="C153" s="74"/>
@@ -13454,7 +14448,7 @@
       <c r="O153" s="99"/>
       <c r="P153" s="89"/>
     </row>
-    <row r="154" ht="14.4" customHeight="1">
+    <row r="154" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="7"/>
       <c r="B154" s="78">
         <v>14</v>
@@ -13492,7 +14486,7 @@
       <c r="O154" s="98"/>
       <c r="P154" s="100"/>
     </row>
-    <row r="155" ht="14.4" customHeight="1">
+    <row r="155" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="7"/>
       <c r="B155" s="78"/>
       <c r="C155" s="73"/>
@@ -13516,7 +14510,7 @@
       <c r="O155" s="98"/>
       <c r="P155" s="88"/>
     </row>
-    <row r="156" ht="14.4" customHeight="1">
+    <row r="156" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="7"/>
       <c r="B156" s="78"/>
       <c r="C156" s="73"/>
@@ -13538,7 +14532,7 @@
       <c r="O156" s="98"/>
       <c r="P156" s="88"/>
     </row>
-    <row r="157" ht="14.4" customHeight="1">
+    <row r="157" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="7"/>
       <c r="B157" s="78"/>
       <c r="C157" s="73"/>
@@ -13558,7 +14552,7 @@
       <c r="O157" s="98"/>
       <c r="P157" s="88"/>
     </row>
-    <row r="158" ht="14.4" customHeight="1">
+    <row r="158" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="7"/>
       <c r="B158" s="78"/>
       <c r="C158" s="73"/>
@@ -13578,7 +14572,7 @@
       <c r="O158" s="98"/>
       <c r="P158" s="88"/>
     </row>
-    <row r="159" ht="14.4" customHeight="1">
+    <row r="159" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="7"/>
       <c r="B159" s="78"/>
       <c r="C159" s="73"/>
@@ -13598,7 +14592,7 @@
       <c r="O159" s="98"/>
       <c r="P159" s="88"/>
     </row>
-    <row r="160" ht="14.4" customHeight="1">
+    <row r="160" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="7"/>
       <c r="B160" s="78"/>
       <c r="C160" s="73"/>
@@ -13618,7 +14612,7 @@
       <c r="O160" s="98"/>
       <c r="P160" s="88"/>
     </row>
-    <row r="161" ht="14.4" customHeight="1">
+    <row r="161" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="7"/>
       <c r="B161" s="78"/>
       <c r="C161" s="73"/>
@@ -13638,7 +14632,7 @@
       <c r="O161" s="98"/>
       <c r="P161" s="88"/>
     </row>
-    <row r="162" ht="14.4" customHeight="1">
+    <row r="162" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="7"/>
       <c r="B162" s="78"/>
       <c r="C162" s="73"/>
@@ -13658,7 +14652,7 @@
       <c r="O162" s="98"/>
       <c r="P162" s="88"/>
     </row>
-    <row r="163" ht="14.4" customHeight="1">
+    <row r="163" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="7"/>
       <c r="B163" s="79"/>
       <c r="C163" s="74"/>
@@ -13678,7 +14672,7 @@
       <c r="O163" s="99"/>
       <c r="P163" s="89"/>
     </row>
-    <row r="164" ht="14.4" customHeight="1">
+    <row r="164" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="7"/>
       <c r="B164" s="78">
         <v>15</v>
@@ -13716,7 +14710,7 @@
       <c r="O164" s="119"/>
       <c r="P164" s="121"/>
     </row>
-    <row r="165" ht="14.4" customHeight="1">
+    <row r="165" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="7"/>
       <c r="B165" s="78"/>
       <c r="C165" s="73"/>
@@ -13740,7 +14734,7 @@
       <c r="O165" s="98"/>
       <c r="P165" s="88"/>
     </row>
-    <row r="166" ht="14.4" customHeight="1">
+    <row r="166" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="7"/>
       <c r="B166" s="78"/>
       <c r="C166" s="73"/>
@@ -13762,7 +14756,7 @@
       <c r="O166" s="98"/>
       <c r="P166" s="88"/>
     </row>
-    <row r="167" ht="14.4" customHeight="1">
+    <row r="167" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="7"/>
       <c r="B167" s="78"/>
       <c r="C167" s="73"/>
@@ -13782,7 +14776,7 @@
       <c r="O167" s="98"/>
       <c r="P167" s="88"/>
     </row>
-    <row r="168" ht="14.4" customHeight="1">
+    <row r="168" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="7"/>
       <c r="B168" s="78"/>
       <c r="C168" s="73"/>
@@ -13802,7 +14796,7 @@
       <c r="O168" s="98"/>
       <c r="P168" s="88"/>
     </row>
-    <row r="169" ht="14.4" customHeight="1">
+    <row r="169" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="7"/>
       <c r="B169" s="78"/>
       <c r="C169" s="73"/>
@@ -13822,7 +14816,7 @@
       <c r="O169" s="98"/>
       <c r="P169" s="88"/>
     </row>
-    <row r="170" ht="14.4" customHeight="1">
+    <row r="170" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="7"/>
       <c r="B170" s="78"/>
       <c r="C170" s="73"/>
@@ -13842,7 +14836,7 @@
       <c r="O170" s="98"/>
       <c r="P170" s="88"/>
     </row>
-    <row r="171" ht="14.4" customHeight="1">
+    <row r="171" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="7"/>
       <c r="B171" s="78"/>
       <c r="C171" s="73"/>
@@ -13862,7 +14856,7 @@
       <c r="O171" s="98"/>
       <c r="P171" s="88"/>
     </row>
-    <row r="172" ht="14.4" customHeight="1">
+    <row r="172" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="7"/>
       <c r="B172" s="78"/>
       <c r="C172" s="73"/>
@@ -13882,7 +14876,7 @@
       <c r="O172" s="98"/>
       <c r="P172" s="88"/>
     </row>
-    <row r="173" ht="14.4" customHeight="1">
+    <row r="173" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="7"/>
       <c r="B173" s="79"/>
       <c r="C173" s="74"/>
@@ -13902,7 +14896,7 @@
       <c r="O173" s="99"/>
       <c r="P173" s="89"/>
     </row>
-    <row r="174" ht="14.4" customHeight="1">
+    <row r="174" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="7"/>
       <c r="B174" s="78">
         <v>16</v>
@@ -13940,7 +14934,7 @@
       <c r="O174" s="119"/>
       <c r="P174" s="121"/>
     </row>
-    <row r="175" ht="14.4" customHeight="1">
+    <row r="175" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="7"/>
       <c r="B175" s="78"/>
       <c r="C175" s="73"/>
@@ -13964,7 +14958,7 @@
       <c r="O175" s="98"/>
       <c r="P175" s="88"/>
     </row>
-    <row r="176" ht="14.4" customHeight="1">
+    <row r="176" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="7"/>
       <c r="B176" s="78"/>
       <c r="C176" s="73"/>
@@ -13986,7 +14980,7 @@
       <c r="O176" s="98"/>
       <c r="P176" s="88"/>
     </row>
-    <row r="177" ht="14.4" customHeight="1">
+    <row r="177" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="7"/>
       <c r="B177" s="78"/>
       <c r="C177" s="73"/>
@@ -14006,7 +15000,7 @@
       <c r="O177" s="98"/>
       <c r="P177" s="88"/>
     </row>
-    <row r="178" ht="14.4" customHeight="1">
+    <row r="178" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="7"/>
       <c r="B178" s="78"/>
       <c r="C178" s="73"/>
@@ -14026,7 +15020,7 @@
       <c r="O178" s="98"/>
       <c r="P178" s="88"/>
     </row>
-    <row r="179" ht="14.4" customHeight="1">
+    <row r="179" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="7"/>
       <c r="B179" s="78"/>
       <c r="C179" s="73"/>
@@ -14046,7 +15040,7 @@
       <c r="O179" s="98"/>
       <c r="P179" s="88"/>
     </row>
-    <row r="180" ht="14.4" customHeight="1">
+    <row r="180" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="7"/>
       <c r="B180" s="78"/>
       <c r="C180" s="73"/>
@@ -14066,7 +15060,7 @@
       <c r="O180" s="98"/>
       <c r="P180" s="88"/>
     </row>
-    <row r="181" ht="14.4" customHeight="1">
+    <row r="181" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="7"/>
       <c r="B181" s="78"/>
       <c r="C181" s="73"/>
@@ -14086,7 +15080,7 @@
       <c r="O181" s="98"/>
       <c r="P181" s="88"/>
     </row>
-    <row r="182" ht="14.4" customHeight="1">
+    <row r="182" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="7"/>
       <c r="B182" s="78"/>
       <c r="C182" s="73"/>
@@ -14106,7 +15100,7 @@
       <c r="O182" s="98"/>
       <c r="P182" s="88"/>
     </row>
-    <row r="183" ht="14.4" customHeight="1">
+    <row r="183" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="7"/>
       <c r="B183" s="79"/>
       <c r="C183" s="74"/>
@@ -14126,7 +15120,7 @@
       <c r="O183" s="99"/>
       <c r="P183" s="89"/>
     </row>
-    <row r="184" ht="14.4" customHeight="1">
+    <row r="184" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="7"/>
       <c r="B184" s="78">
         <v>17</v>
@@ -14162,7 +15156,7 @@
       <c r="O184" s="98"/>
       <c r="P184" s="100"/>
     </row>
-    <row r="185" ht="14.4" customHeight="1">
+    <row r="185" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="7"/>
       <c r="B185" s="78"/>
       <c r="C185" s="73"/>
@@ -14184,7 +15178,7 @@
       <c r="O185" s="98"/>
       <c r="P185" s="88"/>
     </row>
-    <row r="186" ht="14.4" customHeight="1">
+    <row r="186" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="7"/>
       <c r="B186" s="78"/>
       <c r="C186" s="73"/>
@@ -14206,7 +15200,7 @@
       <c r="O186" s="98"/>
       <c r="P186" s="88"/>
     </row>
-    <row r="187" ht="14.4" customHeight="1">
+    <row r="187" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="7"/>
       <c r="B187" s="78"/>
       <c r="C187" s="73"/>
@@ -14226,7 +15220,7 @@
       <c r="O187" s="98"/>
       <c r="P187" s="88"/>
     </row>
-    <row r="188" ht="14.4" customHeight="1">
+    <row r="188" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="7"/>
       <c r="B188" s="78"/>
       <c r="C188" s="73"/>
@@ -14246,7 +15240,7 @@
       <c r="O188" s="98"/>
       <c r="P188" s="88"/>
     </row>
-    <row r="189" ht="14.4" customHeight="1">
+    <row r="189" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="7"/>
       <c r="B189" s="78"/>
       <c r="C189" s="73"/>
@@ -14266,7 +15260,7 @@
       <c r="O189" s="98"/>
       <c r="P189" s="88"/>
     </row>
-    <row r="190" ht="14.4" customHeight="1">
+    <row r="190" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="7"/>
       <c r="B190" s="78"/>
       <c r="C190" s="73"/>
@@ -14286,7 +15280,7 @@
       <c r="O190" s="98"/>
       <c r="P190" s="88"/>
     </row>
-    <row r="191" ht="14.4" customHeight="1">
+    <row r="191" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="7"/>
       <c r="B191" s="78"/>
       <c r="C191" s="73"/>
@@ -14306,7 +15300,7 @@
       <c r="O191" s="98"/>
       <c r="P191" s="88"/>
     </row>
-    <row r="192" ht="14.4" customHeight="1">
+    <row r="192" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="7"/>
       <c r="B192" s="78"/>
       <c r="C192" s="73"/>
@@ -14326,7 +15320,7 @@
       <c r="O192" s="98"/>
       <c r="P192" s="88"/>
     </row>
-    <row r="193" ht="14.4" customHeight="1">
+    <row r="193" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="7"/>
       <c r="B193" s="79"/>
       <c r="C193" s="74"/>
@@ -14346,7 +15340,7 @@
       <c r="O193" s="99"/>
       <c r="P193" s="89"/>
     </row>
-    <row r="194" ht="14.4" customHeight="1">
+    <row r="194" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="7"/>
       <c r="B194" s="78">
         <v>18</v>
@@ -14382,7 +15376,7 @@
       <c r="O194" s="119"/>
       <c r="P194" s="121"/>
     </row>
-    <row r="195" ht="14.4" customHeight="1">
+    <row r="195" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="7"/>
       <c r="B195" s="78"/>
       <c r="C195" s="73"/>
@@ -14404,7 +15398,7 @@
       <c r="O195" s="98"/>
       <c r="P195" s="88"/>
     </row>
-    <row r="196" ht="14.4" customHeight="1">
+    <row r="196" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="7"/>
       <c r="B196" s="78"/>
       <c r="C196" s="73"/>
@@ -14426,7 +15420,7 @@
       <c r="O196" s="98"/>
       <c r="P196" s="88"/>
     </row>
-    <row r="197" ht="14.4" customHeight="1">
+    <row r="197" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="7"/>
       <c r="B197" s="78"/>
       <c r="C197" s="73"/>
@@ -14446,7 +15440,7 @@
       <c r="O197" s="98"/>
       <c r="P197" s="88"/>
     </row>
-    <row r="198" ht="14.4" customHeight="1">
+    <row r="198" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="7"/>
       <c r="B198" s="78"/>
       <c r="C198" s="73"/>
@@ -14466,7 +15460,7 @@
       <c r="O198" s="98"/>
       <c r="P198" s="88"/>
     </row>
-    <row r="199" ht="14.4" customHeight="1">
+    <row r="199" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="7"/>
       <c r="B199" s="78"/>
       <c r="C199" s="73"/>
@@ -14486,7 +15480,7 @@
       <c r="O199" s="98"/>
       <c r="P199" s="88"/>
     </row>
-    <row r="200" ht="14.4" customHeight="1">
+    <row r="200" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="7"/>
       <c r="B200" s="78"/>
       <c r="C200" s="73"/>
@@ -14506,7 +15500,7 @@
       <c r="O200" s="98"/>
       <c r="P200" s="88"/>
     </row>
-    <row r="201" ht="14.4" customHeight="1">
+    <row r="201" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="7"/>
       <c r="B201" s="78"/>
       <c r="C201" s="73"/>
@@ -14526,7 +15520,7 @@
       <c r="O201" s="98"/>
       <c r="P201" s="88"/>
     </row>
-    <row r="202" ht="14.4" customHeight="1">
+    <row r="202" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="7"/>
       <c r="B202" s="78"/>
       <c r="C202" s="73"/>
@@ -14546,7 +15540,7 @@
       <c r="O202" s="98"/>
       <c r="P202" s="88"/>
     </row>
-    <row r="203" ht="14.4" customHeight="1">
+    <row r="203" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="7"/>
       <c r="B203" s="79"/>
       <c r="C203" s="74"/>
@@ -14566,7 +15560,7 @@
       <c r="O203" s="99"/>
       <c r="P203" s="89"/>
     </row>
-    <row r="204" ht="14.4" customHeight="1">
+    <row r="204" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="7"/>
       <c r="B204" s="78">
         <v>19</v>
@@ -14602,7 +15596,7 @@
       <c r="O204" s="98"/>
       <c r="P204" s="100"/>
     </row>
-    <row r="205" ht="14.4" customHeight="1">
+    <row r="205" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="7"/>
       <c r="B205" s="78"/>
       <c r="C205" s="73"/>
@@ -14624,7 +15618,7 @@
       <c r="O205" s="98"/>
       <c r="P205" s="88"/>
     </row>
-    <row r="206" ht="14.4" customHeight="1">
+    <row r="206" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="7"/>
       <c r="B206" s="78"/>
       <c r="C206" s="73"/>
@@ -14646,7 +15640,7 @@
       <c r="O206" s="98"/>
       <c r="P206" s="88"/>
     </row>
-    <row r="207" ht="14.4" customHeight="1">
+    <row r="207" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="7"/>
       <c r="B207" s="78"/>
       <c r="C207" s="73"/>
@@ -14666,7 +15660,7 @@
       <c r="O207" s="98"/>
       <c r="P207" s="88"/>
     </row>
-    <row r="208" ht="14.4" customHeight="1">
+    <row r="208" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="7"/>
       <c r="B208" s="78"/>
       <c r="C208" s="73"/>
@@ -14686,7 +15680,7 @@
       <c r="O208" s="98"/>
       <c r="P208" s="88"/>
     </row>
-    <row r="209" ht="14.4" customHeight="1">
+    <row r="209" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="7"/>
       <c r="B209" s="78"/>
       <c r="C209" s="73"/>
@@ -14706,7 +15700,7 @@
       <c r="O209" s="98"/>
       <c r="P209" s="88"/>
     </row>
-    <row r="210" ht="14.4" customHeight="1">
+    <row r="210" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="7"/>
       <c r="B210" s="78"/>
       <c r="C210" s="73"/>
@@ -14726,7 +15720,7 @@
       <c r="O210" s="98"/>
       <c r="P210" s="88"/>
     </row>
-    <row r="211" ht="14.4" customHeight="1">
+    <row r="211" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="7"/>
       <c r="B211" s="78"/>
       <c r="C211" s="73"/>
@@ -14746,7 +15740,7 @@
       <c r="O211" s="98"/>
       <c r="P211" s="88"/>
     </row>
-    <row r="212" ht="14.4" customHeight="1">
+    <row r="212" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="7"/>
       <c r="B212" s="78"/>
       <c r="C212" s="73"/>
@@ -14766,7 +15760,7 @@
       <c r="O212" s="98"/>
       <c r="P212" s="88"/>
     </row>
-    <row r="213" ht="14.4" customHeight="1">
+    <row r="213" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="7"/>
       <c r="B213" s="79"/>
       <c r="C213" s="74"/>
@@ -14786,7 +15780,7 @@
       <c r="O213" s="99"/>
       <c r="P213" s="89"/>
     </row>
-    <row r="214" ht="14.4" customHeight="1">
+    <row r="214" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="7"/>
       <c r="B214" s="78">
         <v>20</v>
@@ -14822,7 +15816,7 @@
       <c r="O214" s="119"/>
       <c r="P214" s="121"/>
     </row>
-    <row r="215" ht="14.4" customHeight="1">
+    <row r="215" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="7"/>
       <c r="B215" s="78"/>
       <c r="C215" s="73"/>
@@ -14844,7 +15838,7 @@
       <c r="O215" s="98"/>
       <c r="P215" s="88"/>
     </row>
-    <row r="216" ht="14.4" customHeight="1">
+    <row r="216" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="7"/>
       <c r="B216" s="78"/>
       <c r="C216" s="73"/>
@@ -14866,7 +15860,7 @@
       <c r="O216" s="98"/>
       <c r="P216" s="88"/>
     </row>
-    <row r="217" ht="14.4" customHeight="1">
+    <row r="217" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="7"/>
       <c r="B217" s="78"/>
       <c r="C217" s="73"/>
@@ -14886,7 +15880,7 @@
       <c r="O217" s="98"/>
       <c r="P217" s="88"/>
     </row>
-    <row r="218" ht="14.4" customHeight="1">
+    <row r="218" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="7"/>
       <c r="B218" s="78"/>
       <c r="C218" s="73"/>
@@ -14906,7 +15900,7 @@
       <c r="O218" s="98"/>
       <c r="P218" s="88"/>
     </row>
-    <row r="219" ht="14.4" customHeight="1">
+    <row r="219" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="7"/>
       <c r="B219" s="78"/>
       <c r="C219" s="73"/>
@@ -14926,7 +15920,7 @@
       <c r="O219" s="98"/>
       <c r="P219" s="88"/>
     </row>
-    <row r="220" ht="14.4" customHeight="1">
+    <row r="220" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="7"/>
       <c r="B220" s="78"/>
       <c r="C220" s="73"/>
@@ -14946,7 +15940,7 @@
       <c r="O220" s="98"/>
       <c r="P220" s="88"/>
     </row>
-    <row r="221" ht="14.4" customHeight="1">
+    <row r="221" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="7"/>
       <c r="B221" s="78"/>
       <c r="C221" s="73"/>
@@ -14966,7 +15960,7 @@
       <c r="O221" s="98"/>
       <c r="P221" s="88"/>
     </row>
-    <row r="222" ht="14.4" customHeight="1">
+    <row r="222" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="7"/>
       <c r="B222" s="78"/>
       <c r="C222" s="73"/>
@@ -14986,7 +15980,7 @@
       <c r="O222" s="98"/>
       <c r="P222" s="88"/>
     </row>
-    <row r="223" ht="14.4" customHeight="1">
+    <row r="223" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="7"/>
       <c r="B223" s="79"/>
       <c r="C223" s="74"/>
@@ -15006,7 +16000,7 @@
       <c r="O223" s="99"/>
       <c r="P223" s="89"/>
     </row>
-    <row r="224" ht="14.4" customHeight="1">
+    <row r="224" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="7"/>
       <c r="B224" s="78">
         <v>21</v>
@@ -15044,7 +16038,7 @@
       <c r="O224" s="98"/>
       <c r="P224" s="100"/>
     </row>
-    <row r="225" ht="14.4" customHeight="1">
+    <row r="225" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="7"/>
       <c r="B225" s="78"/>
       <c r="C225" s="73"/>
@@ -15068,7 +16062,7 @@
       <c r="O225" s="98"/>
       <c r="P225" s="88"/>
     </row>
-    <row r="226" ht="14.4" customHeight="1">
+    <row r="226" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="7"/>
       <c r="B226" s="78"/>
       <c r="C226" s="73"/>
@@ -15092,7 +16086,7 @@
       <c r="O226" s="98"/>
       <c r="P226" s="88"/>
     </row>
-    <row r="227" ht="14.4" customHeight="1">
+    <row r="227" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="7"/>
       <c r="B227" s="78"/>
       <c r="C227" s="73"/>
@@ -15116,7 +16110,7 @@
       <c r="O227" s="98"/>
       <c r="P227" s="88"/>
     </row>
-    <row r="228" ht="14.4" customHeight="1">
+    <row r="228" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="7"/>
       <c r="B228" s="78"/>
       <c r="C228" s="73"/>
@@ -15138,7 +16132,7 @@
       <c r="O228" s="98"/>
       <c r="P228" s="88"/>
     </row>
-    <row r="229" ht="14.4" customHeight="1">
+    <row r="229" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="7"/>
       <c r="B229" s="78"/>
       <c r="C229" s="73"/>
@@ -15158,7 +16152,7 @@
       <c r="O229" s="98"/>
       <c r="P229" s="88"/>
     </row>
-    <row r="230" ht="14.4" customHeight="1">
+    <row r="230" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="7"/>
       <c r="B230" s="78"/>
       <c r="C230" s="73"/>
@@ -15178,7 +16172,7 @@
       <c r="O230" s="98"/>
       <c r="P230" s="88"/>
     </row>
-    <row r="231" ht="14.4" customHeight="1">
+    <row r="231" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="7"/>
       <c r="B231" s="78"/>
       <c r="C231" s="73"/>
@@ -15198,7 +16192,7 @@
       <c r="O231" s="98"/>
       <c r="P231" s="88"/>
     </row>
-    <row r="232" ht="14.4" customHeight="1">
+    <row r="232" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="7"/>
       <c r="B232" s="78"/>
       <c r="C232" s="73"/>
@@ -15218,7 +16212,7 @@
       <c r="O232" s="98"/>
       <c r="P232" s="88"/>
     </row>
-    <row r="233" ht="14.4" customHeight="1">
+    <row r="233" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="7"/>
       <c r="B233" s="79"/>
       <c r="C233" s="74"/>
@@ -15238,7 +16232,7 @@
       <c r="O233" s="99"/>
       <c r="P233" s="89"/>
     </row>
-    <row r="234" ht="14.4" customHeight="1">
+    <row r="234" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="7"/>
       <c r="B234" s="78">
         <v>22</v>
@@ -15276,7 +16270,7 @@
       <c r="O234" s="119"/>
       <c r="P234" s="121"/>
     </row>
-    <row r="235" ht="14.4" customHeight="1">
+    <row r="235" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="7"/>
       <c r="B235" s="78"/>
       <c r="C235" s="73"/>
@@ -15300,7 +16294,7 @@
       <c r="O235" s="98"/>
       <c r="P235" s="88"/>
     </row>
-    <row r="236" ht="14.4" customHeight="1">
+    <row r="236" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="7"/>
       <c r="B236" s="78"/>
       <c r="C236" s="73"/>
@@ -15324,7 +16318,7 @@
       <c r="O236" s="98"/>
       <c r="P236" s="88"/>
     </row>
-    <row r="237" ht="14.4" customHeight="1">
+    <row r="237" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="7"/>
       <c r="B237" s="78"/>
       <c r="C237" s="73"/>
@@ -15348,7 +16342,7 @@
       <c r="O237" s="98"/>
       <c r="P237" s="88"/>
     </row>
-    <row r="238" ht="14.4" customHeight="1">
+    <row r="238" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="7"/>
       <c r="B238" s="78"/>
       <c r="C238" s="73"/>
@@ -15370,7 +16364,7 @@
       <c r="O238" s="98"/>
       <c r="P238" s="88"/>
     </row>
-    <row r="239" ht="14.4" customHeight="1">
+    <row r="239" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="7"/>
       <c r="B239" s="78"/>
       <c r="C239" s="73"/>
@@ -15390,7 +16384,7 @@
       <c r="O239" s="98"/>
       <c r="P239" s="88"/>
     </row>
-    <row r="240" ht="14.4" customHeight="1">
+    <row r="240" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="7"/>
       <c r="B240" s="78"/>
       <c r="C240" s="73"/>
@@ -15410,7 +16404,7 @@
       <c r="O240" s="98"/>
       <c r="P240" s="88"/>
     </row>
-    <row r="241" ht="14.4" customHeight="1">
+    <row r="241" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="7"/>
       <c r="B241" s="78"/>
       <c r="C241" s="73"/>
@@ -15430,7 +16424,7 @@
       <c r="O241" s="98"/>
       <c r="P241" s="88"/>
     </row>
-    <row r="242" ht="14.4" customHeight="1">
+    <row r="242" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="7"/>
       <c r="B242" s="78"/>
       <c r="C242" s="73"/>
@@ -15450,7 +16444,7 @@
       <c r="O242" s="98"/>
       <c r="P242" s="88"/>
     </row>
-    <row r="243">
+    <row r="243" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A243" s="7"/>
       <c r="B243" s="79"/>
       <c r="C243" s="74"/>
@@ -15470,7 +16464,7 @@
       <c r="O243" s="99"/>
       <c r="P243" s="89"/>
     </row>
-    <row r="244" ht="14.4" customHeight="1">
+    <row r="244" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="7"/>
       <c r="B244" s="78">
         <v>23</v>
@@ -15508,7 +16502,7 @@
       <c r="O244" s="98"/>
       <c r="P244" s="100"/>
     </row>
-    <row r="245" ht="14.4" customHeight="1">
+    <row r="245" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="7"/>
       <c r="B245" s="78"/>
       <c r="C245" s="73"/>
@@ -15532,7 +16526,7 @@
       <c r="O245" s="98"/>
       <c r="P245" s="88"/>
     </row>
-    <row r="246" ht="14.4" customHeight="1">
+    <row r="246" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="7"/>
       <c r="B246" s="78"/>
       <c r="C246" s="73"/>
@@ -15556,7 +16550,7 @@
       <c r="O246" s="98"/>
       <c r="P246" s="88"/>
     </row>
-    <row r="247" ht="14.4" customHeight="1">
+    <row r="247" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="7"/>
       <c r="B247" s="78"/>
       <c r="C247" s="73"/>
@@ -15580,7 +16574,7 @@
       <c r="O247" s="98"/>
       <c r="P247" s="88"/>
     </row>
-    <row r="248" ht="14.4" customHeight="1">
+    <row r="248" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="7"/>
       <c r="B248" s="78"/>
       <c r="C248" s="73"/>
@@ -15602,7 +16596,7 @@
       <c r="O248" s="98"/>
       <c r="P248" s="88"/>
     </row>
-    <row r="249" ht="14.4" customHeight="1">
+    <row r="249" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="7"/>
       <c r="B249" s="78"/>
       <c r="C249" s="73"/>
@@ -15622,7 +16616,7 @@
       <c r="O249" s="98"/>
       <c r="P249" s="88"/>
     </row>
-    <row r="250" ht="14.4" customHeight="1">
+    <row r="250" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="7"/>
       <c r="B250" s="78"/>
       <c r="C250" s="73"/>
@@ -15642,7 +16636,7 @@
       <c r="O250" s="98"/>
       <c r="P250" s="88"/>
     </row>
-    <row r="251" ht="14.4" customHeight="1">
+    <row r="251" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="7"/>
       <c r="B251" s="78"/>
       <c r="C251" s="73"/>
@@ -15662,7 +16656,7 @@
       <c r="O251" s="98"/>
       <c r="P251" s="88"/>
     </row>
-    <row r="252" ht="14.4" customHeight="1">
+    <row r="252" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="7"/>
       <c r="B252" s="78"/>
       <c r="C252" s="73"/>
@@ -15682,7 +16676,7 @@
       <c r="O252" s="98"/>
       <c r="P252" s="88"/>
     </row>
-    <row r="253">
+    <row r="253" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A253" s="7"/>
       <c r="B253" s="79"/>
       <c r="C253" s="74"/>
@@ -15702,7 +16696,7 @@
       <c r="O253" s="99"/>
       <c r="P253" s="89"/>
     </row>
-    <row r="254" ht="14.4" customHeight="1">
+    <row r="254" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="7"/>
       <c r="B254" s="78">
         <v>24</v>
@@ -15740,7 +16734,7 @@
       <c r="O254" s="119"/>
       <c r="P254" s="121"/>
     </row>
-    <row r="255" ht="14.4" customHeight="1">
+    <row r="255" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="7"/>
       <c r="B255" s="78"/>
       <c r="C255" s="73"/>
@@ -15762,7 +16756,7 @@
       <c r="O255" s="98"/>
       <c r="P255" s="88"/>
     </row>
-    <row r="256" ht="14.4" customHeight="1">
+    <row r="256" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="7"/>
       <c r="B256" s="78"/>
       <c r="C256" s="73"/>
@@ -15786,7 +16780,7 @@
       <c r="O256" s="98"/>
       <c r="P256" s="88"/>
     </row>
-    <row r="257" ht="14.4" customHeight="1">
+    <row r="257" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="7"/>
       <c r="B257" s="78"/>
       <c r="C257" s="73"/>
@@ -15810,7 +16804,7 @@
       <c r="O257" s="98"/>
       <c r="P257" s="88"/>
     </row>
-    <row r="258" ht="14.4" customHeight="1">
+    <row r="258" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="7"/>
       <c r="B258" s="78"/>
       <c r="C258" s="73"/>
@@ -15832,7 +16826,7 @@
       <c r="O258" s="98"/>
       <c r="P258" s="88"/>
     </row>
-    <row r="259" ht="14.4" customHeight="1">
+    <row r="259" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="7"/>
       <c r="B259" s="78"/>
       <c r="C259" s="73"/>
@@ -15852,7 +16846,7 @@
       <c r="O259" s="98"/>
       <c r="P259" s="88"/>
     </row>
-    <row r="260" ht="14.4" customHeight="1">
+    <row r="260" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="7"/>
       <c r="B260" s="78"/>
       <c r="C260" s="73"/>
@@ -15872,7 +16866,7 @@
       <c r="O260" s="98"/>
       <c r="P260" s="88"/>
     </row>
-    <row r="261" ht="14.4" customHeight="1">
+    <row r="261" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="7"/>
       <c r="B261" s="78"/>
       <c r="C261" s="73"/>
@@ -15892,7 +16886,7 @@
       <c r="O261" s="98"/>
       <c r="P261" s="88"/>
     </row>
-    <row r="262" ht="14.4" customHeight="1">
+    <row r="262" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="7"/>
       <c r="B262" s="78"/>
       <c r="C262" s="73"/>
@@ -15912,7 +16906,7 @@
       <c r="O262" s="98"/>
       <c r="P262" s="88"/>
     </row>
-    <row r="263">
+    <row r="263" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A263" s="7"/>
       <c r="B263" s="79"/>
       <c r="C263" s="74"/>
@@ -15932,7 +16926,7 @@
       <c r="O263" s="99"/>
       <c r="P263" s="89"/>
     </row>
-    <row r="264" ht="14.4" customHeight="1">
+    <row r="264" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="7"/>
       <c r="B264" s="78">
         <v>25</v>
@@ -15970,7 +16964,7 @@
       <c r="O264" s="98"/>
       <c r="P264" s="100"/>
     </row>
-    <row r="265" ht="14.4" customHeight="1">
+    <row r="265" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="7"/>
       <c r="B265" s="78"/>
       <c r="C265" s="73"/>
@@ -15994,7 +16988,7 @@
       <c r="O265" s="98"/>
       <c r="P265" s="88"/>
     </row>
-    <row r="266" ht="14.4" customHeight="1">
+    <row r="266" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="7"/>
       <c r="B266" s="78"/>
       <c r="C266" s="73"/>
@@ -16016,7 +17010,7 @@
       <c r="O266" s="98"/>
       <c r="P266" s="88"/>
     </row>
-    <row r="267" ht="14.4" customHeight="1">
+    <row r="267" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="7"/>
       <c r="B267" s="78"/>
       <c r="C267" s="73"/>
@@ -16040,7 +17034,7 @@
       <c r="O267" s="98"/>
       <c r="P267" s="88"/>
     </row>
-    <row r="268" ht="14.4" customHeight="1">
+    <row r="268" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="7"/>
       <c r="B268" s="78"/>
       <c r="C268" s="73"/>
@@ -16062,7 +17056,7 @@
       <c r="O268" s="98"/>
       <c r="P268" s="88"/>
     </row>
-    <row r="269" ht="14.4" customHeight="1">
+    <row r="269" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="7"/>
       <c r="B269" s="78"/>
       <c r="C269" s="73"/>
@@ -16082,7 +17076,7 @@
       <c r="O269" s="98"/>
       <c r="P269" s="88"/>
     </row>
-    <row r="270" ht="14.4" customHeight="1">
+    <row r="270" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="7"/>
       <c r="B270" s="78"/>
       <c r="C270" s="73"/>
@@ -16102,7 +17096,7 @@
       <c r="O270" s="98"/>
       <c r="P270" s="88"/>
     </row>
-    <row r="271" ht="14.4" customHeight="1">
+    <row r="271" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="7"/>
       <c r="B271" s="78"/>
       <c r="C271" s="73"/>
@@ -16122,7 +17116,7 @@
       <c r="O271" s="98"/>
       <c r="P271" s="88"/>
     </row>
-    <row r="272" ht="14.4" customHeight="1">
+    <row r="272" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="7"/>
       <c r="B272" s="78"/>
       <c r="C272" s="73"/>
@@ -16142,7 +17136,7 @@
       <c r="O272" s="98"/>
       <c r="P272" s="88"/>
     </row>
-    <row r="273" ht="14.4" customHeight="1">
+    <row r="273" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="7"/>
       <c r="B273" s="79"/>
       <c r="C273" s="74"/>
@@ -16162,7 +17156,7 @@
       <c r="O273" s="99"/>
       <c r="P273" s="89"/>
     </row>
-    <row r="274" ht="21" customHeight="1">
+    <row r="274" spans="1:16" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="7"/>
       <c r="B274" s="78">
         <v>26</v>
@@ -16198,7 +17192,7 @@
       <c r="O274" s="119"/>
       <c r="P274" s="121"/>
     </row>
-    <row r="275" ht="33.6" customHeight="1">
+    <row r="275" spans="1:16" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="7"/>
       <c r="B275" s="78"/>
       <c r="C275" s="73"/>
@@ -16220,7 +17214,7 @@
       <c r="O275" s="98"/>
       <c r="P275" s="88"/>
     </row>
-    <row r="276" ht="29.4" customHeight="1">
+    <row r="276" spans="1:16" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="7"/>
       <c r="B276" s="78"/>
       <c r="C276" s="73"/>
@@ -16242,7 +17236,7 @@
       <c r="O276" s="98"/>
       <c r="P276" s="88"/>
     </row>
-    <row r="277" ht="40.2" customHeight="1">
+    <row r="277" spans="1:16" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="7"/>
       <c r="B277" s="78"/>
       <c r="C277" s="73"/>
@@ -16266,7 +17260,7 @@
       <c r="O277" s="98"/>
       <c r="P277" s="88"/>
     </row>
-    <row r="278" ht="31.2" customHeight="1">
+    <row r="278" spans="1:16" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="7"/>
       <c r="B278" s="78"/>
       <c r="C278" s="73"/>
@@ -16290,7 +17284,7 @@
       <c r="O278" s="98"/>
       <c r="P278" s="88"/>
     </row>
-    <row r="279" ht="32.4" customHeight="1">
+    <row r="279" spans="1:16" ht="32.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="7"/>
       <c r="B279" s="78"/>
       <c r="C279" s="73"/>
@@ -16312,7 +17306,7 @@
       <c r="O279" s="98"/>
       <c r="P279" s="88"/>
     </row>
-    <row r="280" ht="26.4" customHeight="1">
+    <row r="280" spans="1:16" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="7"/>
       <c r="B280" s="78"/>
       <c r="C280" s="73"/>
@@ -16334,7 +17328,7 @@
       <c r="O280" s="98"/>
       <c r="P280" s="88"/>
     </row>
-    <row r="281" ht="30.6" customHeight="1">
+    <row r="281" spans="1:16" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="7"/>
       <c r="B281" s="78"/>
       <c r="C281" s="73"/>
@@ -16358,7 +17352,7 @@
       <c r="O281" s="98"/>
       <c r="P281" s="88"/>
     </row>
-    <row r="282" ht="24.6" customHeight="1">
+    <row r="282" spans="1:16" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="7"/>
       <c r="B282" s="78"/>
       <c r="C282" s="73"/>
@@ -16382,7 +17376,7 @@
       <c r="O282" s="98"/>
       <c r="P282" s="88"/>
     </row>
-    <row r="283" ht="21.6" customHeight="1">
+    <row r="283" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="7"/>
       <c r="B283" s="78"/>
       <c r="C283" s="73"/>
@@ -16404,7 +17398,7 @@
       <c r="O283" s="98"/>
       <c r="P283" s="88"/>
     </row>
-    <row r="284" ht="24" customHeight="1">
+    <row r="284" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="7"/>
       <c r="B284" s="78"/>
       <c r="C284" s="73"/>
@@ -16426,7 +17420,7 @@
       <c r="O284" s="98"/>
       <c r="P284" s="88"/>
     </row>
-    <row r="285" ht="24" customHeight="1">
+    <row r="285" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="7"/>
       <c r="B285" s="78"/>
       <c r="C285" s="73"/>
@@ -16450,7 +17444,7 @@
       <c r="O285" s="98"/>
       <c r="P285" s="88"/>
     </row>
-    <row r="286" ht="22.8" customHeight="1">
+    <row r="286" spans="1:16" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="7"/>
       <c r="B286" s="78"/>
       <c r="C286" s="73"/>
@@ -16474,7 +17468,7 @@
       <c r="O286" s="98"/>
       <c r="P286" s="88"/>
     </row>
-    <row r="287" ht="22.8" customHeight="1">
+    <row r="287" spans="1:16" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="7"/>
       <c r="B287" s="78"/>
       <c r="C287" s="73"/>
@@ -16496,7 +17490,7 @@
       <c r="O287" s="98"/>
       <c r="P287" s="88"/>
     </row>
-    <row r="288" ht="22.8" customHeight="1">
+    <row r="288" spans="1:16" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="7"/>
       <c r="B288" s="78"/>
       <c r="C288" s="73"/>
@@ -16518,7 +17512,7 @@
       <c r="O288" s="98"/>
       <c r="P288" s="88"/>
     </row>
-    <row r="289" ht="22.8" customHeight="1">
+    <row r="289" spans="1:16" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="7"/>
       <c r="B289" s="78"/>
       <c r="C289" s="73"/>
@@ -16542,7 +17536,7 @@
       <c r="O289" s="98"/>
       <c r="P289" s="88"/>
     </row>
-    <row r="290" ht="22.8" customHeight="1">
+    <row r="290" spans="1:16" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="7"/>
       <c r="B290" s="78"/>
       <c r="C290" s="73"/>
@@ -16566,7 +17560,7 @@
       <c r="O290" s="98"/>
       <c r="P290" s="88"/>
     </row>
-    <row r="291" ht="22.8" customHeight="1">
+    <row r="291" spans="1:16" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="7"/>
       <c r="B291" s="78"/>
       <c r="C291" s="73"/>
@@ -16588,7 +17582,7 @@
       <c r="O291" s="98"/>
       <c r="P291" s="88"/>
     </row>
-    <row r="292" ht="22.8" customHeight="1">
+    <row r="292" spans="1:16" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="7"/>
       <c r="B292" s="78"/>
       <c r="C292" s="73"/>
@@ -16610,7 +17604,7 @@
       <c r="O292" s="98"/>
       <c r="P292" s="88"/>
     </row>
-    <row r="293" ht="22.8" customHeight="1">
+    <row r="293" spans="1:16" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="7"/>
       <c r="B293" s="78"/>
       <c r="C293" s="73"/>
@@ -16634,7 +17628,7 @@
       <c r="O293" s="98"/>
       <c r="P293" s="88"/>
     </row>
-    <row r="294" ht="22.8" customHeight="1">
+    <row r="294" spans="1:16" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="7"/>
       <c r="B294" s="78"/>
       <c r="C294" s="73"/>
@@ -16658,7 +17652,7 @@
       <c r="O294" s="98"/>
       <c r="P294" s="88"/>
     </row>
-    <row r="295" ht="22.8" customHeight="1">
+    <row r="295" spans="1:16" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="7"/>
       <c r="B295" s="78"/>
       <c r="C295" s="73"/>
@@ -16680,7 +17674,7 @@
       <c r="O295" s="98"/>
       <c r="P295" s="88"/>
     </row>
-    <row r="296" ht="22.8" customHeight="1">
+    <row r="296" spans="1:16" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="7"/>
       <c r="B296" s="78"/>
       <c r="C296" s="73"/>
@@ -16702,7 +17696,7 @@
       <c r="O296" s="98"/>
       <c r="P296" s="88"/>
     </row>
-    <row r="297" ht="22.8" customHeight="1">
+    <row r="297" spans="1:16" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="7"/>
       <c r="B297" s="78"/>
       <c r="C297" s="73"/>
@@ -16726,7 +17720,7 @@
       <c r="O297" s="98"/>
       <c r="P297" s="88"/>
     </row>
-    <row r="298" ht="22.8" customHeight="1">
+    <row r="298" spans="1:16" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="7"/>
       <c r="B298" s="78"/>
       <c r="C298" s="73"/>
@@ -16750,7 +17744,7 @@
       <c r="O298" s="98"/>
       <c r="P298" s="88"/>
     </row>
-    <row r="299" ht="22.8" customHeight="1">
+    <row r="299" spans="1:16" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="7"/>
       <c r="B299" s="78"/>
       <c r="C299" s="73"/>
@@ -16772,7 +17766,7 @@
       <c r="O299" s="98"/>
       <c r="P299" s="88"/>
     </row>
-    <row r="300" ht="22.8" customHeight="1">
+    <row r="300" spans="1:16" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="7"/>
       <c r="B300" s="78"/>
       <c r="C300" s="73"/>
@@ -16794,7 +17788,7 @@
       <c r="O300" s="98"/>
       <c r="P300" s="88"/>
     </row>
-    <row r="301" ht="22.8" customHeight="1">
+    <row r="301" spans="1:16" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="7"/>
       <c r="B301" s="78"/>
       <c r="C301" s="73"/>
@@ -16818,7 +17812,7 @@
       <c r="O301" s="98"/>
       <c r="P301" s="88"/>
     </row>
-    <row r="302" ht="22.8" customHeight="1">
+    <row r="302" spans="1:16" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="7"/>
       <c r="B302" s="78"/>
       <c r="C302" s="73"/>
@@ -16842,7 +17836,7 @@
       <c r="O302" s="98"/>
       <c r="P302" s="88"/>
     </row>
-    <row r="303" ht="22.8" customHeight="1">
+    <row r="303" spans="1:16" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="7"/>
       <c r="B303" s="78"/>
       <c r="C303" s="73"/>
@@ -16864,7 +17858,7 @@
       <c r="O303" s="98"/>
       <c r="P303" s="88"/>
     </row>
-    <row r="304" ht="22.8" customHeight="1">
+    <row r="304" spans="1:16" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="7"/>
       <c r="B304" s="78"/>
       <c r="C304" s="73"/>
@@ -16886,7 +17880,7 @@
       <c r="O304" s="98"/>
       <c r="P304" s="88"/>
     </row>
-    <row r="305" ht="22.8" customHeight="1">
+    <row r="305" spans="1:16" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="7"/>
       <c r="B305" s="78"/>
       <c r="C305" s="73"/>
@@ -16910,7 +17904,7 @@
       <c r="O305" s="98"/>
       <c r="P305" s="88"/>
     </row>
-    <row r="306" ht="32.4" customHeight="1">
+    <row r="306" spans="1:16" ht="32.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="7"/>
       <c r="B306" s="79"/>
       <c r="C306" s="74"/>
@@ -16934,7 +17928,7 @@
       <c r="O306" s="99"/>
       <c r="P306" s="89"/>
     </row>
-    <row r="307" ht="23.4" customHeight="1">
+    <row r="307" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="7"/>
       <c r="B307" s="78">
         <v>27</v>
@@ -16970,7 +17964,7 @@
       <c r="O307" s="98"/>
       <c r="P307" s="100"/>
     </row>
-    <row r="308" ht="27" customHeight="1">
+    <row r="308" spans="1:16" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="7"/>
       <c r="B308" s="78"/>
       <c r="C308" s="73"/>
@@ -16992,7 +17986,7 @@
       <c r="O308" s="98"/>
       <c r="P308" s="88"/>
     </row>
-    <row r="309" ht="28.2" customHeight="1">
+    <row r="309" spans="1:16" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="7"/>
       <c r="B309" s="78"/>
       <c r="C309" s="73"/>
@@ -17016,7 +18010,7 @@
       <c r="O309" s="98"/>
       <c r="P309" s="88"/>
     </row>
-    <row r="310" ht="34.8" customHeight="1">
+    <row r="310" spans="1:16" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="7"/>
       <c r="B310" s="78"/>
       <c r="C310" s="73"/>
@@ -17040,7 +18034,7 @@
       <c r="O310" s="98"/>
       <c r="P310" s="88"/>
     </row>
-    <row r="311" ht="43.2" customHeight="1">
+    <row r="311" spans="1:16" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="7"/>
       <c r="B311" s="78"/>
       <c r="C311" s="73"/>
@@ -17062,7 +18056,7 @@
       <c r="O311" s="98"/>
       <c r="P311" s="88"/>
     </row>
-    <row r="312" ht="24.6" customHeight="1">
+    <row r="312" spans="1:16" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="7"/>
       <c r="B312" s="78"/>
       <c r="C312" s="73"/>
@@ -17084,7 +18078,7 @@
       <c r="O312" s="98"/>
       <c r="P312" s="88"/>
     </row>
-    <row r="313" ht="32.4" customHeight="1">
+    <row r="313" spans="1:16" ht="32.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="7"/>
       <c r="B313" s="78"/>
       <c r="C313" s="73"/>
@@ -17108,7 +18102,7 @@
       <c r="O313" s="98"/>
       <c r="P313" s="88"/>
     </row>
-    <row r="314" ht="35.4" customHeight="1">
+    <row r="314" spans="1:16" ht="35.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="7"/>
       <c r="B314" s="79"/>
       <c r="C314" s="74"/>
@@ -17132,7 +18126,7 @@
       <c r="O314" s="99"/>
       <c r="P314" s="89"/>
     </row>
-    <row r="315" ht="14.4" customHeight="1">
+    <row r="315" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="7"/>
       <c r="B315" s="78">
         <v>28</v>
@@ -17168,7 +18162,7 @@
       <c r="O315" s="119"/>
       <c r="P315" s="121"/>
     </row>
-    <row r="316" ht="14.4" customHeight="1">
+    <row r="316" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="7"/>
       <c r="B316" s="78"/>
       <c r="C316" s="73"/>
@@ -17190,7 +18184,7 @@
       <c r="O316" s="98"/>
       <c r="P316" s="88"/>
     </row>
-    <row r="317" ht="14.4" customHeight="1">
+    <row r="317" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="7"/>
       <c r="B317" s="78"/>
       <c r="C317" s="73"/>
@@ -17212,7 +18206,7 @@
       <c r="O317" s="98"/>
       <c r="P317" s="88"/>
     </row>
-    <row r="318" ht="14.4" customHeight="1">
+    <row r="318" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="7"/>
       <c r="B318" s="78"/>
       <c r="C318" s="73"/>
@@ -17234,7 +18228,7 @@
       <c r="O318" s="98"/>
       <c r="P318" s="88"/>
     </row>
-    <row r="319" ht="14.4" customHeight="1">
+    <row r="319" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="7"/>
       <c r="B319" s="78"/>
       <c r="C319" s="73"/>
@@ -17254,7 +18248,7 @@
       <c r="O319" s="98"/>
       <c r="P319" s="88"/>
     </row>
-    <row r="320" ht="14.4" customHeight="1">
+    <row r="320" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="7"/>
       <c r="B320" s="78"/>
       <c r="C320" s="73"/>
@@ -17274,7 +18268,7 @@
       <c r="O320" s="98"/>
       <c r="P320" s="88"/>
     </row>
-    <row r="321" ht="14.4" customHeight="1">
+    <row r="321" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="7"/>
       <c r="B321" s="78"/>
       <c r="C321" s="73"/>
@@ -17294,7 +18288,7 @@
       <c r="O321" s="98"/>
       <c r="P321" s="88"/>
     </row>
-    <row r="322" ht="14.4" customHeight="1">
+    <row r="322" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="7"/>
       <c r="B322" s="78"/>
       <c r="C322" s="73"/>
@@ -17314,7 +18308,7 @@
       <c r="O322" s="98"/>
       <c r="P322" s="88"/>
     </row>
-    <row r="323" ht="14.4" customHeight="1">
+    <row r="323" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="7"/>
       <c r="B323" s="78"/>
       <c r="C323" s="73"/>
@@ -17334,7 +18328,7 @@
       <c r="O323" s="98"/>
       <c r="P323" s="88"/>
     </row>
-    <row r="324" ht="14.4" customHeight="1">
+    <row r="324" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="7"/>
       <c r="B324" s="79"/>
       <c r="C324" s="74"/>
@@ -17354,7 +18348,7 @@
       <c r="O324" s="99"/>
       <c r="P324" s="89"/>
     </row>
-    <row r="325" ht="14.4" customHeight="1">
+    <row r="325" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="7"/>
       <c r="B325" s="78">
         <v>29</v>
@@ -17392,7 +18386,7 @@
       <c r="O325" s="98"/>
       <c r="P325" s="100"/>
     </row>
-    <row r="326" ht="30.6" customHeight="1">
+    <row r="326" spans="1:16" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="7"/>
       <c r="B326" s="78"/>
       <c r="C326" s="73"/>
@@ -17414,7 +18408,7 @@
       <c r="O326" s="98"/>
       <c r="P326" s="88"/>
     </row>
-    <row r="327" ht="37.2" customHeight="1">
+    <row r="327" spans="1:16" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="7"/>
       <c r="B327" s="78"/>
       <c r="C327" s="73"/>
@@ -17436,7 +18430,7 @@
       <c r="O327" s="98"/>
       <c r="P327" s="88"/>
     </row>
-    <row r="328" ht="32.4" customHeight="1">
+    <row r="328" spans="1:16" ht="32.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="7"/>
       <c r="B328" s="78"/>
       <c r="C328" s="73"/>
@@ -17458,7 +18452,7 @@
       <c r="O328" s="98"/>
       <c r="P328" s="88"/>
     </row>
-    <row r="329" ht="32.4" customHeight="1">
+    <row r="329" spans="1:16" ht="32.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="7"/>
       <c r="B329" s="78"/>
       <c r="C329" s="73"/>
@@ -17480,7 +18474,7 @@
       <c r="O329" s="98"/>
       <c r="P329" s="88"/>
     </row>
-    <row r="330" ht="33" customHeight="1">
+    <row r="330" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="7"/>
       <c r="B330" s="78"/>
       <c r="C330" s="73"/>
@@ -17504,7 +18498,7 @@
       <c r="O330" s="98"/>
       <c r="P330" s="88"/>
     </row>
-    <row r="331" ht="27" customHeight="1">
+    <row r="331" spans="1:16" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="7"/>
       <c r="B331" s="78"/>
       <c r="C331" s="73"/>
@@ -17528,7 +18522,7 @@
       <c r="O331" s="98"/>
       <c r="P331" s="88"/>
     </row>
-    <row r="332" ht="32.4" customHeight="1">
+    <row r="332" spans="1:16" ht="32.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="7"/>
       <c r="B332" s="78"/>
       <c r="C332" s="73"/>
@@ -17550,7 +18544,7 @@
       <c r="O332" s="98"/>
       <c r="P332" s="88"/>
     </row>
-    <row r="333" ht="21" customHeight="1">
+    <row r="333" spans="1:16" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="7"/>
       <c r="B333" s="78"/>
       <c r="C333" s="73"/>
@@ -17574,7 +18568,7 @@
       <c r="O333" s="98"/>
       <c r="P333" s="88"/>
     </row>
-    <row r="334" ht="42" customHeight="1">
+    <row r="334" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="7"/>
       <c r="B334" s="79"/>
       <c r="C334" s="74"/>
@@ -17598,7 +18592,7 @@
       <c r="O334" s="99"/>
       <c r="P334" s="89"/>
     </row>
-    <row r="335" ht="14.4" customHeight="1">
+    <row r="335" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="7"/>
       <c r="B335" s="78">
         <v>30</v>
@@ -17632,7 +18626,7 @@
       <c r="O335" s="119"/>
       <c r="P335" s="121"/>
     </row>
-    <row r="336" ht="14.4" customHeight="1">
+    <row r="336" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="7"/>
       <c r="B336" s="78"/>
       <c r="C336" s="73"/>
@@ -17654,7 +18648,7 @@
       <c r="O336" s="98"/>
       <c r="P336" s="88"/>
     </row>
-    <row r="337" ht="14.4" customHeight="1">
+    <row r="337" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="7"/>
       <c r="B337" s="78"/>
       <c r="C337" s="73"/>
@@ -17676,7 +18670,7 @@
       <c r="O337" s="98"/>
       <c r="P337" s="88"/>
     </row>
-    <row r="338" ht="14.4" customHeight="1">
+    <row r="338" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="7"/>
       <c r="B338" s="78"/>
       <c r="C338" s="73"/>
@@ -17700,7 +18694,7 @@
       <c r="O338" s="98"/>
       <c r="P338" s="88"/>
     </row>
-    <row r="339" ht="14.4" customHeight="1">
+    <row r="339" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="7"/>
       <c r="B339" s="78"/>
       <c r="C339" s="73"/>
@@ -17724,7 +18718,7 @@
       <c r="O339" s="98"/>
       <c r="P339" s="88"/>
     </row>
-    <row r="340" ht="14.4" customHeight="1">
+    <row r="340" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="7"/>
       <c r="B340" s="78"/>
       <c r="C340" s="73"/>
@@ -17748,7 +18742,7 @@
       <c r="O340" s="98"/>
       <c r="P340" s="88"/>
     </row>
-    <row r="341" ht="14.4" customHeight="1">
+    <row r="341" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="7"/>
       <c r="B341" s="78"/>
       <c r="C341" s="73"/>
@@ -17772,7 +18766,7 @@
       <c r="O341" s="98"/>
       <c r="P341" s="88"/>
     </row>
-    <row r="342" ht="14.4" customHeight="1">
+    <row r="342" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="7"/>
       <c r="B342" s="78"/>
       <c r="C342" s="73"/>
@@ -17796,7 +18790,7 @@
       <c r="O342" s="98"/>
       <c r="P342" s="88"/>
     </row>
-    <row r="343" ht="14.4" customHeight="1">
+    <row r="343" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="7"/>
       <c r="B343" s="78"/>
       <c r="C343" s="73"/>
@@ -17820,7 +18814,7 @@
       <c r="O343" s="98"/>
       <c r="P343" s="88"/>
     </row>
-    <row r="344" ht="14.4" customHeight="1">
+    <row r="344" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="7"/>
       <c r="B344" s="78"/>
       <c r="C344" s="73"/>
@@ -17844,7 +18838,7 @@
       <c r="O344" s="98"/>
       <c r="P344" s="88"/>
     </row>
-    <row r="345" ht="14.4" customHeight="1">
+    <row r="345" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="7"/>
       <c r="B345" s="78"/>
       <c r="C345" s="73"/>
@@ -17868,7 +18862,7 @@
       <c r="O345" s="98"/>
       <c r="P345" s="88"/>
     </row>
-    <row r="346" ht="14.4" customHeight="1">
+    <row r="346" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="7"/>
       <c r="B346" s="78"/>
       <c r="C346" s="73"/>
@@ -17892,7 +18886,7 @@
       <c r="O346" s="98"/>
       <c r="P346" s="88"/>
     </row>
-    <row r="347" ht="14.4" customHeight="1">
+    <row r="347" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="7"/>
       <c r="B347" s="78"/>
       <c r="C347" s="73"/>
@@ -17916,7 +18910,7 @@
       <c r="O347" s="98"/>
       <c r="P347" s="88"/>
     </row>
-    <row r="348" ht="14.4" customHeight="1">
+    <row r="348" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="7"/>
       <c r="B348" s="78"/>
       <c r="C348" s="73"/>
@@ -17940,7 +18934,7 @@
       <c r="O348" s="98"/>
       <c r="P348" s="88"/>
     </row>
-    <row r="349" ht="14.4" customHeight="1">
+    <row r="349" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="7"/>
       <c r="B349" s="78"/>
       <c r="C349" s="73"/>
@@ -17962,7 +18956,7 @@
       <c r="O349" s="98"/>
       <c r="P349" s="88"/>
     </row>
-    <row r="350" ht="14.4" customHeight="1">
+    <row r="350" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="7"/>
       <c r="B350" s="78"/>
       <c r="C350" s="73"/>
@@ -17984,7 +18978,7 @@
       <c r="O350" s="98"/>
       <c r="P350" s="88"/>
     </row>
-    <row r="351" ht="14.4" customHeight="1">
+    <row r="351" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="7"/>
       <c r="B351" s="78"/>
       <c r="C351" s="73"/>
@@ -18006,7 +19000,7 @@
       <c r="O351" s="98"/>
       <c r="P351" s="88"/>
     </row>
-    <row r="352" ht="14.4" customHeight="1">
+    <row r="352" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="7"/>
       <c r="B352" s="78"/>
       <c r="C352" s="73"/>
@@ -18030,7 +19024,7 @@
       <c r="O352" s="98"/>
       <c r="P352" s="88"/>
     </row>
-    <row r="353" ht="14.4" customHeight="1">
+    <row r="353" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="7"/>
       <c r="B353" s="78"/>
       <c r="C353" s="73"/>
@@ -18052,7 +19046,7 @@
       <c r="O353" s="98"/>
       <c r="P353" s="88"/>
     </row>
-    <row r="354" ht="14.4" customHeight="1">
+    <row r="354" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="7"/>
       <c r="B354" s="78"/>
       <c r="C354" s="73"/>
@@ -18074,7 +19068,7 @@
       <c r="O354" s="98"/>
       <c r="P354" s="88"/>
     </row>
-    <row r="355" ht="14.4" customHeight="1">
+    <row r="355" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="7"/>
       <c r="B355" s="78"/>
       <c r="C355" s="73"/>
@@ -18098,7 +19092,7 @@
       <c r="O355" s="98"/>
       <c r="P355" s="88"/>
     </row>
-    <row r="356" ht="14.4" customHeight="1">
+    <row r="356" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="7"/>
       <c r="B356" s="78"/>
       <c r="C356" s="73"/>
@@ -18122,7 +19116,7 @@
       <c r="O356" s="98"/>
       <c r="P356" s="88"/>
     </row>
-    <row r="357" ht="14.4" customHeight="1">
+    <row r="357" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="7"/>
       <c r="B357" s="78"/>
       <c r="C357" s="73"/>
@@ -18146,7 +19140,7 @@
       <c r="O357" s="98"/>
       <c r="P357" s="88"/>
     </row>
-    <row r="358" ht="14.4" customHeight="1">
+    <row r="358" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="7"/>
       <c r="B358" s="78"/>
       <c r="C358" s="73"/>
@@ -18170,7 +19164,7 @@
       <c r="O358" s="98"/>
       <c r="P358" s="88"/>
     </row>
-    <row r="359" ht="14.4" customHeight="1">
+    <row r="359" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="7"/>
       <c r="B359" s="78"/>
       <c r="C359" s="73"/>
@@ -18194,7 +19188,7 @@
       <c r="O359" s="98"/>
       <c r="P359" s="88"/>
     </row>
-    <row r="360" ht="14.4" customHeight="1">
+    <row r="360" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="7"/>
       <c r="B360" s="78"/>
       <c r="C360" s="73"/>
@@ -18218,7 +19212,7 @@
       <c r="O360" s="98"/>
       <c r="P360" s="88"/>
     </row>
-    <row r="361" ht="14.4" customHeight="1">
+    <row r="361" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="7"/>
       <c r="B361" s="78"/>
       <c r="C361" s="73"/>
@@ -18242,7 +19236,7 @@
       <c r="O361" s="98"/>
       <c r="P361" s="88"/>
     </row>
-    <row r="362" ht="14.4" customHeight="1">
+    <row r="362" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="7"/>
       <c r="B362" s="78"/>
       <c r="C362" s="73"/>
@@ -18266,7 +19260,7 @@
       <c r="O362" s="98"/>
       <c r="P362" s="88"/>
     </row>
-    <row r="363" ht="14.4" customHeight="1">
+    <row r="363" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="7"/>
       <c r="B363" s="78"/>
       <c r="C363" s="73"/>
@@ -18290,7 +19284,7 @@
       <c r="O363" s="98"/>
       <c r="P363" s="88"/>
     </row>
-    <row r="364" ht="14.4" customHeight="1">
+    <row r="364" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="7"/>
       <c r="B364" s="78"/>
       <c r="C364" s="73"/>
@@ -18312,7 +19306,7 @@
       <c r="O364" s="98"/>
       <c r="P364" s="88"/>
     </row>
-    <row r="365" ht="14.4" customHeight="1">
+    <row r="365" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="7"/>
       <c r="B365" s="78"/>
       <c r="C365" s="73"/>
@@ -18334,7 +19328,7 @@
       <c r="O365" s="98"/>
       <c r="P365" s="88"/>
     </row>
-    <row r="366" ht="14.4" customHeight="1">
+    <row r="366" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="7"/>
       <c r="B366" s="78"/>
       <c r="C366" s="73"/>
@@ -18356,7 +19350,7 @@
       <c r="O366" s="98"/>
       <c r="P366" s="88"/>
     </row>
-    <row r="367" ht="14.4" customHeight="1">
+    <row r="367" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="7"/>
       <c r="B367" s="79"/>
       <c r="C367" s="74"/>
@@ -18379,7 +19373,7 @@
       <c r="P367" s="89"/>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="360">
     <mergeCell ref="P5:P17"/>
     <mergeCell ref="B5:B17"/>
     <mergeCell ref="C5:C17"/>
@@ -18743,11 +19737,5 @@
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
-</file>
-
-<file path=EPPlusLicense.txt>This workbook was created with the EPPlus library, licensed to DoAnCuoiKy_TH under the Polyform Noncommercial license, see https://polyformproject.org/licenses/noncommercial/1.0.0
-For more information about EPPlus, see https://epplussoftware.com/
-
 </file>
--- a/Nhom3_BDCLPM_TH.xlsx
+++ b/Nhom3_BDCLPM_TH.xlsx
@@ -18,7 +18,7 @@
     <sheet name="TC_Nguyen" sheetId="1" r:id="rId3"/>
     <sheet name="TC_Tram" sheetId="3" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" fullCalcOnLoad="1" fullPrecision="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1069" uniqueCount="573">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="573">
   <si>
     <t>Tên dự án:</t>
   </si>
@@ -53,14 +53,14 @@
     <t>Các thành viên:</t>
   </si>
   <si>
-    <t>Phạm Ngọc Khôi Nguyên
+    <t xml:space="preserve">Phạm Ngọc Khôi Nguyên
 Nguyễn Thị Bích Trâm</t>
   </si>
   <si>
     <t>Trong file gồm bao nhiêu sheet? Mỗi Sheet có tên là gì?</t>
   </si>
   <si>
-    <t>Sheet 1: Tong_Quan_Du_An
+    <t xml:space="preserve">Sheet 1: Tong_Quan_Du_An
 Sheet 2: TC_Nguyen
 Sheet 3: TC_Tram</t>
   </si>
@@ -164,7 +164,7 @@
     <t>TC_Nguyen: TC_01 → TC_05</t>
   </si>
   <si>
-    <t>1. Đăng nhập thành công với username/password hợp lệ
+    <t xml:space="preserve">1. Đăng nhập thành công với username/password hợp lệ
 2. Đăng nhập thất bại với username không tồn tại
 3. Đăng nhập thất bại với password sai
 4. Đăng nhập khi để trống username
@@ -186,7 +186,7 @@
     <t>TC_Nguyen: TC_06 → TC_11</t>
   </si>
   <si>
-    <t>1. Chuyển tiền thành công giữa hai tài khoản
+    <t xml:space="preserve">1. Chuyển tiền thành công giữa hai tài khoản
 2. Kiểm tra số dư cập nhật đúng sau khi chuyển
 3. Giao dịch hiển thị đúng trong lịch sử
 4. Chuyển tiền vượt quá số dư hiện có
@@ -209,7 +209,7 @@
     <t>TC_Nguyen: TC_12 → TC_17</t>
   </si>
   <si>
-    <t>1. Mở tài khoản Checking Account thành công
+    <t xml:space="preserve">1. Mở tài khoản Checking Account thành công
 2. Checking Account xuất hiện trong Account Overview
 3. Xem chi tiết Checking Account
 4. Mở tài khoản Savings Account thành công
@@ -235,7 +235,7 @@
     <t>TC_Nguyen: TC_18 → TC_20</t>
   </si>
   <si>
-    <t>1. Cập nhật thông tin liên hệ với dữ liệu hợp lệ
+    <t xml:space="preserve">1. Cập nhật thông tin liên hệ với dữ liệu hợp lệ
 2. Cập nhật thất bại khi First Name để trống
 3. Xác nhận thông tin được lưu bền vững sau cập nhật</t>
   </si>
@@ -255,14 +255,14 @@
     <t>LooknFeel</t>
   </si>
   <si>
-    <t>GUI TRANG LOGIN
+    <t xml:space="preserve">GUI TRANG LOGIN
 GUI TRANSFER FUNDS</t>
   </si>
   <si>
     <t>TC_Nguyen: TC_21 → TC_26</t>
   </si>
   <si>
-    <t>1. Nút Login hiển thị và có thể click
+    <t xml:space="preserve">1. Nút Login hiển thị và có thể click
 2. Textbox username và password nhận input
 3. Link Register điều hướng đến trang đăng ký
 4. Thông báo lỗi login hiển thị đúng vị trí
@@ -288,7 +288,7 @@
     <t>TC_Nguyen: TC_27 → TC_29</t>
   </si>
   <si>
-    <t>1. Smoke test: Login → Transfer Funds → Logout thành công
+    <t xml:space="preserve">1. Smoke test: Login → Transfer Funds → Logout thành công
 2. Kiểm tra các menu chính hiển thị sau khi đăng nhập
 3. Session bị hủy và bảo mật sau khi Logout</t>
   </si>
@@ -308,7 +308,7 @@
     <t>TC_Tram: TC_01 → TC_05</t>
   </si>
   <si>
-    <t>1. Đăng ký tài khoản mới với đầy đủ thông tin hợp lệ
+    <t xml:space="preserve">1. Đăng ký tài khoản mới với đầy đủ thông tin hợp lệ
 2. Đăng ký thất bại khi thiếu trường bắt buộc
 3. Đăng ký thất bại khi username đã tồn tại
 4. Đăng ký thất bại khi password không khớp
@@ -330,7 +330,7 @@
     <t>TC_Tram: TC_06 → TC_09</t>
   </si>
   <si>
-    <t>1. Thanh toán hóa đơn thành công với thông tin hợp lệ
+    <t xml:space="preserve">1. Thanh toán hóa đơn thành công với thông tin hợp lệ
 2. Thanh toán thất bại khi thông tin payee không hợp lệ
 3. Validate trường bắt buộc để trống
 4. Validate số tiền thanh toán không hợp lệ</t>
@@ -351,7 +351,7 @@
     <t>TC_Tram: TC_10 → TC_20</t>
   </si>
   <si>
-    <t>1. Tìm giao dịch theo Transaction ID hợp lệ
+    <t xml:space="preserve">1. Tìm giao dịch theo Transaction ID hợp lệ
 2. Tìm giao dịch theo ngày (khoảng ngày có kết quả)
 3. Tìm giao dịch theo số tiền chính xác
 4. Tìm giao dịch theo khoảng số tiền
@@ -374,7 +374,7 @@
     <t>TC_Tram: TC_21 → TC_25</t>
   </si>
   <si>
-    <t>1. Yêu cầu vay được duyệt (Approved) khi đủ điều kiện
+    <t xml:space="preserve">1. Yêu cầu vay được duyệt (Approved) khi đủ điều kiện
 2. Yêu cầu vay bị từ chối (Denied) khi không đủ điều kiện
 3. Validate amount và down payment không hợp lệ
 4. Yêu cầu vay với loan amount = 0
@@ -393,14 +393,14 @@
     <t>Kiểm tra các phần tử UI trên trang Register (form, nút, thông báo lỗi) và trang Bill Pay (form điền thông tin, nút Submit)</t>
   </si>
   <si>
-    <t>GUI TRANG REGISTER
+    <t xml:space="preserve">GUI TRANG REGISTER
 GUI TRANG BILL PAY</t>
   </si>
   <si>
     <t>TC_Tram: TC_26 → TC_29</t>
   </si>
   <si>
-    <t>1. Kiểm tra form Register hiển thị đầy đủ các trường
+    <t xml:space="preserve">1. Kiểm tra form Register hiển thị đầy đủ các trường
 2. Kiểm tra thông báo lỗi trên trang Register
 3. Kiểm tra form Bill Pay hiển thị đầy đủ các trường
 4. Kiểm tra nút Submit và Cancel trên Bill Pay</t>
@@ -1246,63 +1246,63 @@
     <t>Đăng ký thành công</t>
   </si>
   <si>
+    <t>Screenshot: C:\Users\nnm21\Documents\BaoDam\TH_CuoiKy\DoAnCuoiKy_TH\bin\Debug\net10.0\Screenshots\TC_01_20260322_165911.png</t>
+  </si>
+  <si>
+    <t>Nhập first name</t>
+  </si>
+  <si>
+    <t>Nhập last name</t>
+  </si>
+  <si>
+    <t>Pham</t>
+  </si>
+  <si>
+    <t>Nhập address</t>
+  </si>
+  <si>
+    <t>Hóc Môn</t>
+  </si>
+  <si>
+    <t>Nhập City</t>
+  </si>
+  <si>
+    <t>TP.HCM</t>
+  </si>
+  <si>
+    <t>Nhập State</t>
+  </si>
+  <si>
+    <t>Nhập Zip Code</t>
+  </si>
+  <si>
+    <t>Nhập Phone #</t>
+  </si>
+  <si>
+    <t>Nhập SSN</t>
+  </si>
+  <si>
+    <t>Nhập confirm</t>
+  </si>
+  <si>
+    <t>Nhấn register</t>
+  </si>
+  <si>
+    <t>Thiếu trường bắt buộc</t>
+  </si>
+  <si>
+    <t>Thông báo lỗi, yêu cầu nhập đầy đủ thông tin</t>
+  </si>
+  <si>
+    <t>Tên đăng nhập trùng</t>
+  </si>
+  <si>
+    <t>Tên đăng nhập đã tồn tại</t>
+  </si>
+  <si>
     <t>Hiển thị lỗi người dùng đã tồn tại</t>
   </si>
   <si>
-    <t>Screenshot: C:\Users\nnm21\Documents\BaoDam\TH_CuoiKy\DoAnCuoiKy_TH\bin\Debug\net10.0\Screenshots\TC_01_20260322_165911.png</t>
-  </si>
-  <si>
-    <t>Nhập first name</t>
-  </si>
-  <si>
-    <t>Nhập last name</t>
-  </si>
-  <si>
-    <t>Pham</t>
-  </si>
-  <si>
-    <t>Nhập address</t>
-  </si>
-  <si>
-    <t>Hóc Môn</t>
-  </si>
-  <si>
-    <t>Nhập City</t>
-  </si>
-  <si>
-    <t>TP.HCM</t>
-  </si>
-  <si>
-    <t>Nhập State</t>
-  </si>
-  <si>
-    <t>Nhập Zip Code</t>
-  </si>
-  <si>
-    <t>Nhập Phone #</t>
-  </si>
-  <si>
-    <t>Nhập SSN</t>
-  </si>
-  <si>
-    <t>Nhập confirm</t>
-  </si>
-  <si>
-    <t>Nhấn register</t>
-  </si>
-  <si>
-    <t>Thiếu trường bắt buộc</t>
-  </si>
-  <si>
-    <t>Thông báo lỗi, yêu cầu nhập đầy đủ thông tin</t>
-  </si>
-  <si>
-    <t>Tên đăng nhập trùng</t>
-  </si>
-  <si>
-    <t>Tên đăng nhập đã tồn tại</t>
-  </si>
-  <si>
     <t>Xác thực mật khẩu</t>
   </si>
   <si>
@@ -1555,7 +1555,7 @@
     <t>Mở trang Register</t>
   </si>
   <si>
-    <t>Tất cả các textbox trên trang Register hiển thị đúng.
+    <t xml:space="preserve">Tất cả các textbox trên trang Register hiển thị đúng.
 Người dùng có thể nhập dữ liệu vào các field.
 Dữ liệu nhập hiển thị đúng trong textbox</t>
   </si>
@@ -1697,10 +1697,10 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <color theme="1"/>
+        <sz val="11"/>
       </rPr>
       <t>Request Loan</t>
     </r>
@@ -1714,10 +1714,10 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <color theme="1"/>
+        <sz val="11"/>
       </rPr>
       <t>From account # hiển thị</t>
     </r>
@@ -1728,10 +1728,10 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <color theme="1"/>
+        <sz val="11"/>
       </rPr>
       <t>From account # hiển thị</t>
     </r>
@@ -1742,10 +1742,10 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <color theme="1"/>
+        <sz val="11"/>
       </rPr>
       <t>From account #</t>
     </r>
@@ -1775,7 +1775,7 @@
     <t>Smoke: Register → Login → Bill Pay → Logout thành công</t>
   </si>
   <si>
-    <t>Cả 4 bước Register, Login, Bill Pay, Logout đều thành công.
+    <t xml:space="preserve">Cả 4 bước Register, Login, Bill Pay, Logout đều thành công.
 Hệ thống hoạt động đúng trong toàn bộ luồng chính</t>
   </si>
   <si>
@@ -1784,10 +1784,10 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <color theme="1"/>
+        <sz val="11"/>
       </rPr>
       <t>Register</t>
     </r>
@@ -1840,10 +1840,10 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <color theme="1"/>
+        <sz val="11"/>
       </rPr>
       <t>Account Overview hiển thị</t>
     </r>
@@ -1854,10 +1854,10 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <color theme="1"/>
+        <sz val="11"/>
       </rPr>
       <t>Bill Pay</t>
     </r>
@@ -1891,7 +1891,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2009,7 +2010,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <fgColor theme="2" tint="-0.0999786370433668"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -2936,7 +2937,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="9" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
   </cellStyleXfs>
   <cellXfs count="145">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -2946,10 +2947,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2958,384 +2959,384 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="9" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="2" applyFill="1" borderId="17" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="2" applyFill="1" borderId="18" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="2" applyFill="1" borderId="20" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="2" applyFill="1" borderId="21" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="2" applyFill="1" borderId="19" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" applyFont="1" fillId="0" borderId="22" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" applyFont="1" fillId="0" borderId="22" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="9" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" applyFont="1" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" applyNumberFormat="1" fontId="0" fillId="0" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="2" applyFill="1" borderId="32" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="24" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="35" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="35" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="36" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="37" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="34" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="38" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="38" applyBorder="1" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="39" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="40" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="41" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="42" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="4" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="43" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="44" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="43" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="6" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="5" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="45" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="46" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="48" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="47" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="33" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="49" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="5" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="50" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="50" applyBorder="1" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="13" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="52" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="31" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="13" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="60" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="60" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="5" applyFill="1" borderId="69" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" applyFont="1" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" applyFont="1" fillId="0" borderId="69" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="69" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" applyFont="1" fillId="0" borderId="69" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" applyFont="1" fillId="0" borderId="69" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" applyFont="1" fillId="0" borderId="69" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" applyFont="1" fillId="0" borderId="69" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="69" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="0" borderId="69" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" applyFill="1" borderId="4" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" applyFill="1" borderId="6" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" applyFill="1" borderId="16" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" applyFill="1" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" applyFill="1" borderId="13" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="3" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" applyFill="1" borderId="15" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="25" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="4" applyFill="1" borderId="28" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" applyFill="1" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" applyFill="1" borderId="13" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" applyFont="1" fillId="0" borderId="25" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" applyFont="1" fillId="0" borderId="25" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" applyFill="1" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" applyFill="1" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="3" applyFill="1" borderId="10" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="7" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="12" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="53" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" applyFont="1" fillId="0" borderId="53" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="7" applyFont="1" fillId="0" borderId="54" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="56" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="57" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="59" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="58" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="63" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" applyFill="1" borderId="63" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="60" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" applyFill="1" borderId="60" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="3" applyFill="1" borderId="55" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" applyFill="1" borderId="23" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="4" applyFill="1" borderId="29" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="60" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" applyFill="1" borderId="60" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" applyFont="1" fillId="0" borderId="51" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" applyFill="1" borderId="24" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" applyFill="1" borderId="5" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" applyFill="1" borderId="14" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" applyFont="1" fillId="0" borderId="64" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="68" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="4" applyFill="1" borderId="65" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="51" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3656,29 +3657,29 @@
   <dimension ref="B2:C6"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="46.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" bestFit="1" width="46.19921875" customWidth="1"/>
+    <col min="3" max="3" bestFit="1" width="24.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" s="1" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="40.2" customHeight="1" s="1" customFormat="1">
       <c r="B2" s="24" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="25"/>
     </row>
-    <row r="3" spans="2:3" s="1" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="40.2" customHeight="1" s="1" customFormat="1">
       <c r="B3" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="25"/>
     </row>
-    <row r="4" spans="2:3" s="1" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="40.2" customHeight="1" s="1" customFormat="1">
       <c r="B4" s="24" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="25"/>
     </row>
-    <row r="5" spans="2:3" s="1" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="40.2" customHeight="1" s="1" customFormat="1">
       <c r="B5" s="24" t="s">
         <v>3</v>
       </c>
@@ -3686,7 +3687,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:3" s="1" customFormat="1" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="54.6" customHeight="1" s="1" customFormat="1">
       <c r="B6" s="26" t="s">
         <v>5</v>
       </c>
@@ -3696,6 +3697,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -3704,7 +3706,7 @@
   <dimension ref="B1:N20"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="23.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" bestFit="1" width="23.796875" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="22" customWidth="1"/>
     <col min="5" max="5" width="28" customWidth="1"/>
@@ -3716,12 +3718,12 @@
     <col min="14" max="14" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="19.95" customHeight="1">
       <c r="B1" s="73" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="2:14" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="2" ht="39.6">
       <c r="B2" s="74" t="s">
         <v>8</v>
       </c>
@@ -3735,7 +3737,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="2:14" ht="66" x14ac:dyDescent="0.25">
+    <row r="3" ht="66">
       <c r="B3" s="74" t="s">
         <v>12</v>
       </c>
@@ -3749,7 +3751,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="B4" s="74" t="s">
         <v>15</v>
       </c>
@@ -3763,12 +3765,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="B7" s="76" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="2:14" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="8" ht="26.4">
       <c r="B8" s="74" t="s">
         <v>19</v>
       </c>
@@ -3809,7 +3811,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="2:14" ht="66" x14ac:dyDescent="0.25">
+    <row r="9" ht="66">
       <c r="B9" s="77">
         <v>1</v>
       </c>
@@ -3846,7 +3848,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="2:14" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="10" ht="79.2">
       <c r="B10" s="77">
         <v>2</v>
       </c>
@@ -3883,7 +3885,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="2:14" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="11" ht="79.2">
       <c r="B11" s="77">
         <v>3</v>
       </c>
@@ -3920,7 +3922,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="2:14" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="12" ht="39.6">
       <c r="B12" s="77">
         <v>4</v>
       </c>
@@ -3957,7 +3959,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="13" spans="2:14" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="13" ht="79.2">
       <c r="B13" s="77">
         <v>5</v>
       </c>
@@ -3996,7 +3998,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="14" spans="2:14" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="14" ht="39.6">
       <c r="B14" s="77">
         <v>6</v>
       </c>
@@ -4033,7 +4035,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="15" spans="2:14" ht="66" x14ac:dyDescent="0.25">
+    <row r="15" ht="66">
       <c r="B15" s="77">
         <v>7</v>
       </c>
@@ -4070,7 +4072,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="2:14" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="16" ht="52.8">
       <c r="B16" s="77">
         <v>8</v>
       </c>
@@ -4107,7 +4109,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="17" spans="2:14" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="17" ht="79.2">
       <c r="B17" s="77">
         <v>9</v>
       </c>
@@ -4144,7 +4146,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="18" spans="2:14" ht="66" x14ac:dyDescent="0.25">
+    <row r="18" ht="66">
       <c r="B18" s="77">
         <v>10</v>
       </c>
@@ -4181,7 +4183,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="19" spans="2:14" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="19" ht="52.8">
       <c r="B19" s="77">
         <v>11</v>
       </c>
@@ -4220,7 +4222,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="20" spans="2:14" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="20" ht="26.4">
       <c r="B20" s="77">
         <v>12</v>
       </c>
@@ -4259,6 +4261,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -4267,15 +4270,15 @@
   <dimension ref="A1:P265"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.69921875" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.59765625" style="6" customWidth="1"/>
+    <col min="2" max="2" bestFit="1" width="17.19921875" customWidth="1"/>
+    <col min="3" max="3" bestFit="1" width="21.69921875" customWidth="1" style="6"/>
+    <col min="4" max="4" width="20.59765625" customWidth="1" style="6"/>
     <col min="5" max="5" width="17.5" customWidth="1"/>
-    <col min="6" max="6" width="18.59765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" bestFit="1" width="18.59765625" customWidth="1"/>
     <col min="7" max="7" width="18.3984375" customWidth="1"/>
     <col min="8" max="8" width="26" customWidth="1"/>
-    <col min="9" max="9" width="6.3984375" style="6" customWidth="1"/>
-    <col min="10" max="10" width="34.69921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.3984375" customWidth="1" style="6"/>
+    <col min="10" max="10" bestFit="1" width="34.69921875" customWidth="1"/>
     <col min="11" max="11" width="27.3984375" customWidth="1"/>
     <col min="12" max="12" width="40.8984375" customWidth="1"/>
     <col min="13" max="13" width="34.19921875" customWidth="1"/>
@@ -4284,7 +4287,7 @@
     <col min="16" max="16" width="11.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="40.2" customHeight="1">
       <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
@@ -4305,7 +4308,7 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
     </row>
-    <row r="2" spans="1:16" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="40.2" customHeight="1">
       <c r="B2" s="4" t="s">
         <v>113</v>
       </c>
@@ -4326,7 +4329,7 @@
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
     </row>
-    <row r="3" spans="1:16" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="40.2" customHeight="1">
       <c r="B3" s="8"/>
       <c r="C3" s="9"/>
       <c r="D3" s="10"/>
@@ -4345,7 +4348,7 @@
       <c r="O3" s="8"/>
       <c r="P3" s="8"/>
     </row>
-    <row r="4" spans="1:16" s="6" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="40.2" customHeight="1" s="6" customFormat="1">
       <c r="A4" s="13"/>
       <c r="B4" s="17" t="s">
         <v>117</v>
@@ -4393,7 +4396,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="14.4" customHeight="1">
       <c r="A5" s="7"/>
       <c r="B5" s="110">
         <v>1</v>
@@ -4435,7 +4438,7 @@
       </c>
       <c r="P5" s="107"/>
     </row>
-    <row r="6" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="14.4" customHeight="1">
       <c r="A6" s="7"/>
       <c r="B6" s="110"/>
       <c r="C6" s="101"/>
@@ -4461,7 +4464,7 @@
       <c r="O6" s="88"/>
       <c r="P6" s="91"/>
     </row>
-    <row r="7" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="14.4" customHeight="1">
       <c r="A7" s="7"/>
       <c r="B7" s="110"/>
       <c r="C7" s="101"/>
@@ -4487,7 +4490,7 @@
       <c r="O7" s="88"/>
       <c r="P7" s="91"/>
     </row>
-    <row r="8" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="14.4" customHeight="1">
       <c r="A8" s="7"/>
       <c r="B8" s="110"/>
       <c r="C8" s="101"/>
@@ -4511,7 +4514,7 @@
       <c r="O8" s="88"/>
       <c r="P8" s="91"/>
     </row>
-    <row r="9" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="14.4" customHeight="1">
       <c r="A9" s="7"/>
       <c r="B9" s="110"/>
       <c r="C9" s="102"/>
@@ -4535,7 +4538,7 @@
       <c r="O9" s="89"/>
       <c r="P9" s="123"/>
     </row>
-    <row r="10" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="14.4" customHeight="1">
       <c r="A10" s="7"/>
       <c r="B10" s="116">
         <v>2</v>
@@ -4575,7 +4578,7 @@
       <c r="O10" s="121"/>
       <c r="P10" s="122"/>
     </row>
-    <row r="11" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="14.4" customHeight="1">
       <c r="A11" s="7"/>
       <c r="B11" s="117"/>
       <c r="C11" s="101"/>
@@ -4599,7 +4602,7 @@
       <c r="O11" s="88"/>
       <c r="P11" s="91"/>
     </row>
-    <row r="12" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="14.4" customHeight="1">
       <c r="A12" s="7"/>
       <c r="B12" s="117"/>
       <c r="C12" s="101"/>
@@ -4623,7 +4626,7 @@
       <c r="O12" s="88"/>
       <c r="P12" s="91"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" s="7"/>
       <c r="B13" s="117"/>
       <c r="C13" s="101"/>
@@ -4645,7 +4648,7 @@
       <c r="O13" s="88"/>
       <c r="P13" s="91"/>
     </row>
-    <row r="14" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="14.4" customHeight="1">
       <c r="A14" s="7"/>
       <c r="B14" s="118"/>
       <c r="C14" s="102"/>
@@ -4667,7 +4670,7 @@
       <c r="O14" s="89"/>
       <c r="P14" s="123"/>
     </row>
-    <row r="15" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="14.4" customHeight="1">
       <c r="A15" s="7"/>
       <c r="B15" s="110">
         <v>3</v>
@@ -4707,7 +4710,7 @@
       <c r="O15" s="121"/>
       <c r="P15" s="122"/>
     </row>
-    <row r="16" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="14.4" customHeight="1">
       <c r="A16" s="7"/>
       <c r="B16" s="110"/>
       <c r="C16" s="101"/>
@@ -4731,7 +4734,7 @@
       <c r="O16" s="88"/>
       <c r="P16" s="91"/>
     </row>
-    <row r="17" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" ht="14.4" customHeight="1">
       <c r="A17" s="7"/>
       <c r="B17" s="111"/>
       <c r="C17" s="102"/>
@@ -4753,7 +4756,7 @@
       <c r="O17" s="89"/>
       <c r="P17" s="92"/>
     </row>
-    <row r="18" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" ht="14.4" customHeight="1">
       <c r="A18" s="7"/>
       <c r="B18" s="116">
         <v>4</v>
@@ -4793,7 +4796,7 @@
       </c>
       <c r="P18" s="122"/>
     </row>
-    <row r="19" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" ht="14.4" customHeight="1">
       <c r="A19" s="7"/>
       <c r="B19" s="117"/>
       <c r="C19" s="101"/>
@@ -4817,7 +4820,7 @@
       <c r="O19" s="88"/>
       <c r="P19" s="91"/>
     </row>
-    <row r="20" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" ht="14.4" customHeight="1">
       <c r="A20" s="7"/>
       <c r="B20" s="117"/>
       <c r="C20" s="101"/>
@@ -4839,7 +4842,7 @@
       <c r="O20" s="88"/>
       <c r="P20" s="91"/>
     </row>
-    <row r="21" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" ht="14.4" customHeight="1">
       <c r="A21" s="7"/>
       <c r="B21" s="118"/>
       <c r="C21" s="102"/>
@@ -4861,7 +4864,7 @@
       <c r="O21" s="89"/>
       <c r="P21" s="92"/>
     </row>
-    <row r="22" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" ht="14.4" customHeight="1">
       <c r="A22" s="7"/>
       <c r="B22" s="110">
         <v>5</v>
@@ -4901,7 +4904,7 @@
       <c r="O22" s="106"/>
       <c r="P22" s="107"/>
     </row>
-    <row r="23" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" ht="14.4" customHeight="1">
       <c r="A23" s="7"/>
       <c r="B23" s="110"/>
       <c r="C23" s="101"/>
@@ -4923,7 +4926,7 @@
       <c r="O23" s="88"/>
       <c r="P23" s="91"/>
     </row>
-    <row r="24" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" ht="14.4" customHeight="1">
       <c r="A24" s="7"/>
       <c r="B24" s="110"/>
       <c r="C24" s="101"/>
@@ -4945,7 +4948,7 @@
       <c r="O24" s="88"/>
       <c r="P24" s="91"/>
     </row>
-    <row r="25" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" ht="14.4" customHeight="1">
       <c r="A25" s="7"/>
       <c r="B25" s="111"/>
       <c r="C25" s="102"/>
@@ -4967,7 +4970,7 @@
       <c r="O25" s="132"/>
       <c r="P25" s="123"/>
     </row>
-    <row r="26" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" ht="14.4" customHeight="1">
       <c r="A26" s="7"/>
       <c r="B26" s="110">
         <v>6</v>
@@ -5001,7 +5004,7 @@
       <c r="O26" s="121"/>
       <c r="P26" s="122"/>
     </row>
-    <row r="27" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" ht="14.4" customHeight="1">
       <c r="A27" s="7"/>
       <c r="B27" s="110"/>
       <c r="C27" s="101"/>
@@ -5025,7 +5028,7 @@
       <c r="O27" s="88"/>
       <c r="P27" s="91"/>
     </row>
-    <row r="28" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" ht="14.4" customHeight="1">
       <c r="A28" s="7"/>
       <c r="B28" s="110"/>
       <c r="C28" s="101"/>
@@ -5049,7 +5052,7 @@
       <c r="O28" s="88"/>
       <c r="P28" s="91"/>
     </row>
-    <row r="29" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" ht="14.4" customHeight="1">
       <c r="A29" s="7"/>
       <c r="B29" s="110"/>
       <c r="C29" s="101"/>
@@ -5073,7 +5076,7 @@
       <c r="O29" s="88"/>
       <c r="P29" s="91"/>
     </row>
-    <row r="30" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" ht="14.4" customHeight="1">
       <c r="A30" s="7"/>
       <c r="B30" s="110"/>
       <c r="C30" s="101"/>
@@ -5095,7 +5098,7 @@
       <c r="O30" s="88"/>
       <c r="P30" s="91"/>
     </row>
-    <row r="31" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" ht="14.4" customHeight="1">
       <c r="A31" s="7"/>
       <c r="B31" s="110"/>
       <c r="C31" s="101"/>
@@ -5117,7 +5120,7 @@
       <c r="O31" s="88"/>
       <c r="P31" s="91"/>
     </row>
-    <row r="32" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" ht="14.4" customHeight="1">
       <c r="A32" s="7"/>
       <c r="B32" s="110"/>
       <c r="C32" s="101"/>
@@ -5137,7 +5140,7 @@
       <c r="O32" s="88"/>
       <c r="P32" s="91"/>
     </row>
-    <row r="33" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" ht="14.4" customHeight="1">
       <c r="A33" s="7"/>
       <c r="B33" s="110"/>
       <c r="C33" s="101"/>
@@ -5157,7 +5160,7 @@
       <c r="O33" s="88"/>
       <c r="P33" s="91"/>
     </row>
-    <row r="34" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" ht="14.4" customHeight="1">
       <c r="A34" s="7"/>
       <c r="B34" s="110"/>
       <c r="C34" s="101"/>
@@ -5177,7 +5180,7 @@
       <c r="O34" s="88"/>
       <c r="P34" s="91"/>
     </row>
-    <row r="35" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" ht="14.4" customHeight="1">
       <c r="A35" s="7"/>
       <c r="B35" s="111"/>
       <c r="C35" s="102"/>
@@ -5197,7 +5200,7 @@
       <c r="O35" s="89"/>
       <c r="P35" s="92"/>
     </row>
-    <row r="36" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" ht="14.4" customHeight="1">
       <c r="A36" s="7"/>
       <c r="B36" s="110">
         <v>7</v>
@@ -5231,7 +5234,7 @@
       <c r="O36" s="88"/>
       <c r="P36" s="90"/>
     </row>
-    <row r="37" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" ht="14.4" customHeight="1">
       <c r="A37" s="7"/>
       <c r="B37" s="110"/>
       <c r="C37" s="101"/>
@@ -5255,7 +5258,7 @@
       <c r="O37" s="88"/>
       <c r="P37" s="91"/>
     </row>
-    <row r="38" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" ht="14.4" customHeight="1">
       <c r="A38" s="7"/>
       <c r="B38" s="110"/>
       <c r="C38" s="101"/>
@@ -5279,7 +5282,7 @@
       <c r="O38" s="88"/>
       <c r="P38" s="91"/>
     </row>
-    <row r="39" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" ht="14.4" customHeight="1">
       <c r="A39" s="7"/>
       <c r="B39" s="110"/>
       <c r="C39" s="101"/>
@@ -5299,7 +5302,7 @@
       <c r="O39" s="88"/>
       <c r="P39" s="91"/>
     </row>
-    <row r="40" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" ht="14.4" customHeight="1">
       <c r="A40" s="7"/>
       <c r="B40" s="110"/>
       <c r="C40" s="101"/>
@@ -5319,7 +5322,7 @@
       <c r="O40" s="88"/>
       <c r="P40" s="91"/>
     </row>
-    <row r="41" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" ht="14.4" customHeight="1">
       <c r="A41" s="7"/>
       <c r="B41" s="110"/>
       <c r="C41" s="101"/>
@@ -5339,7 +5342,7 @@
       <c r="O41" s="88"/>
       <c r="P41" s="91"/>
     </row>
-    <row r="42" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" ht="14.4" customHeight="1">
       <c r="A42" s="7"/>
       <c r="B42" s="110"/>
       <c r="C42" s="101"/>
@@ -5359,7 +5362,7 @@
       <c r="O42" s="88"/>
       <c r="P42" s="91"/>
     </row>
-    <row r="43" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" ht="14.4" customHeight="1">
       <c r="A43" s="7"/>
       <c r="B43" s="110"/>
       <c r="C43" s="101"/>
@@ -5379,7 +5382,7 @@
       <c r="O43" s="88"/>
       <c r="P43" s="91"/>
     </row>
-    <row r="44" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" ht="14.4" customHeight="1">
       <c r="A44" s="7"/>
       <c r="B44" s="110"/>
       <c r="C44" s="101"/>
@@ -5399,7 +5402,7 @@
       <c r="O44" s="88"/>
       <c r="P44" s="91"/>
     </row>
-    <row r="45" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" ht="14.4" customHeight="1">
       <c r="A45" s="7"/>
       <c r="B45" s="111"/>
       <c r="C45" s="102"/>
@@ -5419,7 +5422,7 @@
       <c r="O45" s="89"/>
       <c r="P45" s="92"/>
     </row>
-    <row r="46" spans="1:16" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="46" ht="27.6">
       <c r="A46" s="7"/>
       <c r="B46" s="110">
         <v>8</v>
@@ -5453,7 +5456,7 @@
       <c r="O46" s="106"/>
       <c r="P46" s="107"/>
     </row>
-    <row r="47" spans="1:16" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="47" ht="27.6">
       <c r="A47" s="7"/>
       <c r="B47" s="110"/>
       <c r="C47" s="101"/>
@@ -5475,7 +5478,7 @@
       <c r="O47" s="88"/>
       <c r="P47" s="91"/>
     </row>
-    <row r="48" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" ht="14.4" customHeight="1">
       <c r="A48" s="7"/>
       <c r="B48" s="110"/>
       <c r="C48" s="101"/>
@@ -5499,7 +5502,7 @@
       <c r="O48" s="88"/>
       <c r="P48" s="91"/>
     </row>
-    <row r="49" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" ht="14.4" customHeight="1">
       <c r="A49" s="7"/>
       <c r="B49" s="110"/>
       <c r="C49" s="101"/>
@@ -5523,7 +5526,7 @@
       <c r="O49" s="88"/>
       <c r="P49" s="91"/>
     </row>
-    <row r="50" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" ht="14.4" customHeight="1">
       <c r="A50" s="7"/>
       <c r="B50" s="110"/>
       <c r="C50" s="101"/>
@@ -5543,7 +5546,7 @@
       <c r="O50" s="88"/>
       <c r="P50" s="91"/>
     </row>
-    <row r="51" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" ht="14.4" customHeight="1">
       <c r="A51" s="7"/>
       <c r="B51" s="110"/>
       <c r="C51" s="101"/>
@@ -5563,7 +5566,7 @@
       <c r="O51" s="88"/>
       <c r="P51" s="91"/>
     </row>
-    <row r="52" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" ht="14.4" customHeight="1">
       <c r="A52" s="7"/>
       <c r="B52" s="110"/>
       <c r="C52" s="101"/>
@@ -5583,7 +5586,7 @@
       <c r="O52" s="88"/>
       <c r="P52" s="91"/>
     </row>
-    <row r="53" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" ht="14.4" customHeight="1">
       <c r="A53" s="7"/>
       <c r="B53" s="110"/>
       <c r="C53" s="101"/>
@@ -5603,7 +5606,7 @@
       <c r="O53" s="88"/>
       <c r="P53" s="91"/>
     </row>
-    <row r="54" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" ht="14.4" customHeight="1">
       <c r="A54" s="7"/>
       <c r="B54" s="110"/>
       <c r="C54" s="101"/>
@@ -5623,7 +5626,7 @@
       <c r="O54" s="88"/>
       <c r="P54" s="91"/>
     </row>
-    <row r="55" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" ht="14.4" customHeight="1">
       <c r="A55" s="7"/>
       <c r="B55" s="111"/>
       <c r="C55" s="102"/>
@@ -5643,7 +5646,7 @@
       <c r="O55" s="89"/>
       <c r="P55" s="92"/>
     </row>
-    <row r="56" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" ht="14.4" customHeight="1">
       <c r="A56" s="7"/>
       <c r="B56" s="110">
         <v>9</v>
@@ -5677,7 +5680,7 @@
       <c r="O56" s="88"/>
       <c r="P56" s="90"/>
     </row>
-    <row r="57" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" ht="14.4" customHeight="1">
       <c r="A57" s="7"/>
       <c r="B57" s="110"/>
       <c r="C57" s="101"/>
@@ -5701,7 +5704,7 @@
       <c r="O57" s="88"/>
       <c r="P57" s="91"/>
     </row>
-    <row r="58" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" ht="14.4" customHeight="1">
       <c r="A58" s="7"/>
       <c r="B58" s="110"/>
       <c r="C58" s="101"/>
@@ -5725,7 +5728,7 @@
       <c r="O58" s="88"/>
       <c r="P58" s="91"/>
     </row>
-    <row r="59" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" ht="14.4" customHeight="1">
       <c r="A59" s="7"/>
       <c r="B59" s="110"/>
       <c r="C59" s="101"/>
@@ -5749,7 +5752,7 @@
       <c r="O59" s="88"/>
       <c r="P59" s="91"/>
     </row>
-    <row r="60" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" ht="14.4" customHeight="1">
       <c r="A60" s="7"/>
       <c r="B60" s="110"/>
       <c r="C60" s="101"/>
@@ -5771,7 +5774,7 @@
       <c r="O60" s="88"/>
       <c r="P60" s="91"/>
     </row>
-    <row r="61" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" ht="14.4" customHeight="1">
       <c r="A61" s="7"/>
       <c r="B61" s="110"/>
       <c r="C61" s="101"/>
@@ -5793,7 +5796,7 @@
       <c r="O61" s="88"/>
       <c r="P61" s="91"/>
     </row>
-    <row r="62" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" ht="14.4" customHeight="1">
       <c r="A62" s="7"/>
       <c r="B62" s="110"/>
       <c r="C62" s="101"/>
@@ -5813,7 +5816,7 @@
       <c r="O62" s="88"/>
       <c r="P62" s="91"/>
     </row>
-    <row r="63" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" ht="14.4" customHeight="1">
       <c r="A63" s="7"/>
       <c r="B63" s="110"/>
       <c r="C63" s="101"/>
@@ -5833,7 +5836,7 @@
       <c r="O63" s="88"/>
       <c r="P63" s="91"/>
     </row>
-    <row r="64" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" ht="14.4" customHeight="1">
       <c r="A64" s="7"/>
       <c r="B64" s="110"/>
       <c r="C64" s="101"/>
@@ -5853,7 +5856,7 @@
       <c r="O64" s="88"/>
       <c r="P64" s="91"/>
     </row>
-    <row r="65" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" ht="14.4" customHeight="1">
       <c r="A65" s="7"/>
       <c r="B65" s="111"/>
       <c r="C65" s="102"/>
@@ -5873,7 +5876,7 @@
       <c r="O65" s="89"/>
       <c r="P65" s="92"/>
     </row>
-    <row r="66" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" ht="14.4" customHeight="1">
       <c r="A66" s="7"/>
       <c r="B66" s="110">
         <v>10</v>
@@ -5907,7 +5910,7 @@
       <c r="O66" s="106"/>
       <c r="P66" s="107"/>
     </row>
-    <row r="67" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" ht="14.4" customHeight="1">
       <c r="A67" s="7"/>
       <c r="B67" s="110"/>
       <c r="C67" s="101"/>
@@ -5929,7 +5932,7 @@
       <c r="O67" s="88"/>
       <c r="P67" s="91"/>
     </row>
-    <row r="68" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" ht="14.4" customHeight="1">
       <c r="A68" s="7"/>
       <c r="B68" s="110"/>
       <c r="C68" s="101"/>
@@ -5953,7 +5956,7 @@
       <c r="O68" s="88"/>
       <c r="P68" s="91"/>
     </row>
-    <row r="69" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" ht="14.4" customHeight="1">
       <c r="A69" s="7"/>
       <c r="B69" s="110"/>
       <c r="C69" s="101"/>
@@ -5975,7 +5978,7 @@
       <c r="O69" s="88"/>
       <c r="P69" s="91"/>
     </row>
-    <row r="70" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" ht="14.4" customHeight="1">
       <c r="A70" s="7"/>
       <c r="B70" s="110"/>
       <c r="C70" s="101"/>
@@ -5997,7 +6000,7 @@
       <c r="O70" s="88"/>
       <c r="P70" s="91"/>
     </row>
-    <row r="71" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" ht="14.4" customHeight="1">
       <c r="A71" s="7"/>
       <c r="B71" s="110"/>
       <c r="C71" s="101"/>
@@ -6017,7 +6020,7 @@
       <c r="O71" s="88"/>
       <c r="P71" s="91"/>
     </row>
-    <row r="72" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" ht="14.4" customHeight="1">
       <c r="A72" s="7"/>
       <c r="B72" s="110"/>
       <c r="C72" s="101"/>
@@ -6037,7 +6040,7 @@
       <c r="O72" s="88"/>
       <c r="P72" s="91"/>
     </row>
-    <row r="73" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" ht="14.4" customHeight="1">
       <c r="A73" s="7"/>
       <c r="B73" s="110"/>
       <c r="C73" s="101"/>
@@ -6057,7 +6060,7 @@
       <c r="O73" s="88"/>
       <c r="P73" s="91"/>
     </row>
-    <row r="74" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" ht="14.4" customHeight="1">
       <c r="A74" s="7"/>
       <c r="B74" s="110"/>
       <c r="C74" s="101"/>
@@ -6077,7 +6080,7 @@
       <c r="O74" s="88"/>
       <c r="P74" s="91"/>
     </row>
-    <row r="75" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" ht="14.4" customHeight="1">
       <c r="A75" s="7"/>
       <c r="B75" s="111"/>
       <c r="C75" s="102"/>
@@ -6097,7 +6100,7 @@
       <c r="O75" s="89"/>
       <c r="P75" s="92"/>
     </row>
-    <row r="76" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" ht="14.4" customHeight="1">
       <c r="A76" s="7"/>
       <c r="B76" s="110">
         <v>11</v>
@@ -6131,7 +6134,7 @@
       <c r="O76" s="88"/>
       <c r="P76" s="90"/>
     </row>
-    <row r="77" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" ht="14.4" customHeight="1">
       <c r="A77" s="7"/>
       <c r="B77" s="110"/>
       <c r="C77" s="101"/>
@@ -6153,7 +6156,7 @@
       <c r="O77" s="88"/>
       <c r="P77" s="91"/>
     </row>
-    <row r="78" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" ht="14.4" customHeight="1">
       <c r="A78" s="7"/>
       <c r="B78" s="110"/>
       <c r="C78" s="101"/>
@@ -6177,7 +6180,7 @@
       <c r="O78" s="88"/>
       <c r="P78" s="91"/>
     </row>
-    <row r="79" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" ht="14.4" customHeight="1">
       <c r="A79" s="7"/>
       <c r="B79" s="110"/>
       <c r="C79" s="101"/>
@@ -6199,7 +6202,7 @@
       <c r="O79" s="88"/>
       <c r="P79" s="91"/>
     </row>
-    <row r="80" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" ht="14.4" customHeight="1">
       <c r="A80" s="7"/>
       <c r="B80" s="110"/>
       <c r="C80" s="101"/>
@@ -6221,7 +6224,7 @@
       <c r="O80" s="88"/>
       <c r="P80" s="91"/>
     </row>
-    <row r="81" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" ht="14.4" customHeight="1">
       <c r="A81" s="7"/>
       <c r="B81" s="110"/>
       <c r="C81" s="101"/>
@@ -6241,7 +6244,7 @@
       <c r="O81" s="88"/>
       <c r="P81" s="91"/>
     </row>
-    <row r="82" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" ht="14.4" customHeight="1">
       <c r="A82" s="7"/>
       <c r="B82" s="110"/>
       <c r="C82" s="101"/>
@@ -6261,7 +6264,7 @@
       <c r="O82" s="88"/>
       <c r="P82" s="91"/>
     </row>
-    <row r="83" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" ht="14.4" customHeight="1">
       <c r="A83" s="7"/>
       <c r="B83" s="110"/>
       <c r="C83" s="101"/>
@@ -6281,7 +6284,7 @@
       <c r="O83" s="88"/>
       <c r="P83" s="91"/>
     </row>
-    <row r="84" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" ht="14.4" customHeight="1">
       <c r="A84" s="7"/>
       <c r="B84" s="110"/>
       <c r="C84" s="101"/>
@@ -6301,7 +6304,7 @@
       <c r="O84" s="88"/>
       <c r="P84" s="91"/>
     </row>
-    <row r="85" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" ht="14.4" customHeight="1">
       <c r="A85" s="7"/>
       <c r="B85" s="111"/>
       <c r="C85" s="102"/>
@@ -6321,7 +6324,7 @@
       <c r="O85" s="89"/>
       <c r="P85" s="92"/>
     </row>
-    <row r="86" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" ht="14.4" customHeight="1">
       <c r="A86" s="7"/>
       <c r="B86" s="110">
         <v>12</v>
@@ -6355,7 +6358,7 @@
       <c r="O86" s="106"/>
       <c r="P86" s="107"/>
     </row>
-    <row r="87" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" ht="14.4" customHeight="1">
       <c r="A87" s="7"/>
       <c r="B87" s="110"/>
       <c r="C87" s="101"/>
@@ -6379,7 +6382,7 @@
       <c r="O87" s="88"/>
       <c r="P87" s="91"/>
     </row>
-    <row r="88" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" ht="14.4" customHeight="1">
       <c r="A88" s="7"/>
       <c r="B88" s="110"/>
       <c r="C88" s="101"/>
@@ -6403,7 +6406,7 @@
       <c r="O88" s="88"/>
       <c r="P88" s="91"/>
     </row>
-    <row r="89" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" ht="14.4" customHeight="1">
       <c r="A89" s="7"/>
       <c r="B89" s="110"/>
       <c r="C89" s="101"/>
@@ -6425,7 +6428,7 @@
       <c r="O89" s="88"/>
       <c r="P89" s="91"/>
     </row>
-    <row r="90" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" ht="14.4" customHeight="1">
       <c r="A90" s="7"/>
       <c r="B90" s="110"/>
       <c r="C90" s="101"/>
@@ -6447,7 +6450,7 @@
       <c r="O90" s="88"/>
       <c r="P90" s="91"/>
     </row>
-    <row r="91" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" ht="14.4" customHeight="1">
       <c r="A91" s="7"/>
       <c r="B91" s="110"/>
       <c r="C91" s="101"/>
@@ -6467,7 +6470,7 @@
       <c r="O91" s="88"/>
       <c r="P91" s="91"/>
     </row>
-    <row r="92" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" ht="14.4" customHeight="1">
       <c r="A92" s="7"/>
       <c r="B92" s="110"/>
       <c r="C92" s="101"/>
@@ -6487,7 +6490,7 @@
       <c r="O92" s="88"/>
       <c r="P92" s="91"/>
     </row>
-    <row r="93" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" ht="14.4" customHeight="1">
       <c r="A93" s="7"/>
       <c r="B93" s="110"/>
       <c r="C93" s="101"/>
@@ -6507,7 +6510,7 @@
       <c r="O93" s="88"/>
       <c r="P93" s="91"/>
     </row>
-    <row r="94" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" ht="14.4" customHeight="1">
       <c r="A94" s="7"/>
       <c r="B94" s="110"/>
       <c r="C94" s="101"/>
@@ -6527,7 +6530,7 @@
       <c r="O94" s="88"/>
       <c r="P94" s="91"/>
     </row>
-    <row r="95" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" ht="14.4" customHeight="1">
       <c r="A95" s="7"/>
       <c r="B95" s="111"/>
       <c r="C95" s="102"/>
@@ -6547,7 +6550,7 @@
       <c r="O95" s="89"/>
       <c r="P95" s="92"/>
     </row>
-    <row r="96" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" ht="14.4" customHeight="1">
       <c r="A96" s="7"/>
       <c r="B96" s="110">
         <v>13</v>
@@ -6581,7 +6584,7 @@
       <c r="O96" s="88"/>
       <c r="P96" s="90"/>
     </row>
-    <row r="97" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" ht="14.4" customHeight="1">
       <c r="A97" s="7"/>
       <c r="B97" s="110"/>
       <c r="C97" s="101"/>
@@ -6603,7 +6606,7 @@
       <c r="O97" s="88"/>
       <c r="P97" s="91"/>
     </row>
-    <row r="98" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" ht="14.4" customHeight="1">
       <c r="A98" s="7"/>
       <c r="B98" s="110"/>
       <c r="C98" s="101"/>
@@ -6627,7 +6630,7 @@
       <c r="O98" s="88"/>
       <c r="P98" s="91"/>
     </row>
-    <row r="99" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" ht="14.4" customHeight="1">
       <c r="A99" s="7"/>
       <c r="B99" s="110"/>
       <c r="C99" s="101"/>
@@ -6649,7 +6652,7 @@
       <c r="O99" s="88"/>
       <c r="P99" s="91"/>
     </row>
-    <row r="100" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" ht="14.4" customHeight="1">
       <c r="A100" s="7"/>
       <c r="B100" s="110"/>
       <c r="C100" s="101"/>
@@ -6669,7 +6672,7 @@
       <c r="O100" s="88"/>
       <c r="P100" s="91"/>
     </row>
-    <row r="101" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" ht="14.4" customHeight="1">
       <c r="A101" s="7"/>
       <c r="B101" s="110"/>
       <c r="C101" s="101"/>
@@ -6689,7 +6692,7 @@
       <c r="O101" s="88"/>
       <c r="P101" s="91"/>
     </row>
-    <row r="102" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" ht="14.4" customHeight="1">
       <c r="A102" s="7"/>
       <c r="B102" s="110"/>
       <c r="C102" s="101"/>
@@ -6709,7 +6712,7 @@
       <c r="O102" s="88"/>
       <c r="P102" s="91"/>
     </row>
-    <row r="103" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" ht="14.4" customHeight="1">
       <c r="A103" s="7"/>
       <c r="B103" s="110"/>
       <c r="C103" s="101"/>
@@ -6729,7 +6732,7 @@
       <c r="O103" s="88"/>
       <c r="P103" s="91"/>
     </row>
-    <row r="104" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" ht="14.4" customHeight="1">
       <c r="A104" s="7"/>
       <c r="B104" s="110"/>
       <c r="C104" s="101"/>
@@ -6749,7 +6752,7 @@
       <c r="O104" s="88"/>
       <c r="P104" s="91"/>
     </row>
-    <row r="105" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" ht="14.4" customHeight="1">
       <c r="A105" s="7"/>
       <c r="B105" s="111"/>
       <c r="C105" s="102"/>
@@ -6769,7 +6772,7 @@
       <c r="O105" s="89"/>
       <c r="P105" s="92"/>
     </row>
-    <row r="106" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" ht="14.4" customHeight="1">
       <c r="A106" s="7"/>
       <c r="B106" s="110">
         <v>14</v>
@@ -6803,7 +6806,7 @@
       <c r="O106" s="106"/>
       <c r="P106" s="107"/>
     </row>
-    <row r="107" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" ht="14.4" customHeight="1">
       <c r="A107" s="7"/>
       <c r="B107" s="110"/>
       <c r="C107" s="101"/>
@@ -6825,7 +6828,7 @@
       <c r="O107" s="88"/>
       <c r="P107" s="91"/>
     </row>
-    <row r="108" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" ht="14.4" customHeight="1">
       <c r="A108" s="7"/>
       <c r="B108" s="110"/>
       <c r="C108" s="101"/>
@@ -6847,7 +6850,7 @@
       <c r="O108" s="88"/>
       <c r="P108" s="91"/>
     </row>
-    <row r="109" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" ht="14.4" customHeight="1">
       <c r="A109" s="7"/>
       <c r="B109" s="110"/>
       <c r="C109" s="101"/>
@@ -6869,7 +6872,7 @@
       <c r="O109" s="88"/>
       <c r="P109" s="91"/>
     </row>
-    <row r="110" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" ht="14.4" customHeight="1">
       <c r="A110" s="7"/>
       <c r="B110" s="110"/>
       <c r="C110" s="101"/>
@@ -6889,7 +6892,7 @@
       <c r="O110" s="88"/>
       <c r="P110" s="91"/>
     </row>
-    <row r="111" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" ht="14.4" customHeight="1">
       <c r="A111" s="7"/>
       <c r="B111" s="110"/>
       <c r="C111" s="101"/>
@@ -6909,7 +6912,7 @@
       <c r="O111" s="88"/>
       <c r="P111" s="91"/>
     </row>
-    <row r="112" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" ht="14.4" customHeight="1">
       <c r="A112" s="7"/>
       <c r="B112" s="110"/>
       <c r="C112" s="101"/>
@@ -6929,7 +6932,7 @@
       <c r="O112" s="88"/>
       <c r="P112" s="91"/>
     </row>
-    <row r="113" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" ht="14.4" customHeight="1">
       <c r="A113" s="7"/>
       <c r="B113" s="110"/>
       <c r="C113" s="101"/>
@@ -6949,7 +6952,7 @@
       <c r="O113" s="88"/>
       <c r="P113" s="91"/>
     </row>
-    <row r="114" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" ht="14.4" customHeight="1">
       <c r="A114" s="7"/>
       <c r="B114" s="110"/>
       <c r="C114" s="101"/>
@@ -6969,7 +6972,7 @@
       <c r="O114" s="88"/>
       <c r="P114" s="91"/>
     </row>
-    <row r="115" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" ht="14.4" customHeight="1">
       <c r="A115" s="7"/>
       <c r="B115" s="111"/>
       <c r="C115" s="102"/>
@@ -6989,7 +6992,7 @@
       <c r="O115" s="89"/>
       <c r="P115" s="92"/>
     </row>
-    <row r="116" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" ht="14.4" customHeight="1">
       <c r="A116" s="7"/>
       <c r="B116" s="110">
         <v>15</v>
@@ -7023,7 +7026,7 @@
       <c r="O116" s="106"/>
       <c r="P116" s="107"/>
     </row>
-    <row r="117" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" ht="14.4" customHeight="1">
       <c r="A117" s="7"/>
       <c r="B117" s="110"/>
       <c r="C117" s="101"/>
@@ -7047,7 +7050,7 @@
       <c r="O117" s="88"/>
       <c r="P117" s="91"/>
     </row>
-    <row r="118" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" ht="14.4" customHeight="1">
       <c r="A118" s="7"/>
       <c r="B118" s="110"/>
       <c r="C118" s="101"/>
@@ -7071,7 +7074,7 @@
       <c r="O118" s="88"/>
       <c r="P118" s="91"/>
     </row>
-    <row r="119" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" ht="14.4" customHeight="1">
       <c r="A119" s="7"/>
       <c r="B119" s="110"/>
       <c r="C119" s="101"/>
@@ -7093,7 +7096,7 @@
       <c r="O119" s="88"/>
       <c r="P119" s="91"/>
     </row>
-    <row r="120" spans="1:16" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="120" ht="27.6">
       <c r="A120" s="7"/>
       <c r="B120" s="110"/>
       <c r="C120" s="101"/>
@@ -7115,7 +7118,7 @@
       <c r="O120" s="88"/>
       <c r="P120" s="91"/>
     </row>
-    <row r="121" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" ht="14.4" customHeight="1">
       <c r="A121" s="7"/>
       <c r="B121" s="110"/>
       <c r="C121" s="101"/>
@@ -7135,7 +7138,7 @@
       <c r="O121" s="88"/>
       <c r="P121" s="91"/>
     </row>
-    <row r="122" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" ht="14.4" customHeight="1">
       <c r="A122" s="7"/>
       <c r="B122" s="110"/>
       <c r="C122" s="101"/>
@@ -7155,7 +7158,7 @@
       <c r="O122" s="88"/>
       <c r="P122" s="91"/>
     </row>
-    <row r="123" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" ht="14.4" customHeight="1">
       <c r="A123" s="7"/>
       <c r="B123" s="110"/>
       <c r="C123" s="101"/>
@@ -7175,7 +7178,7 @@
       <c r="O123" s="88"/>
       <c r="P123" s="91"/>
     </row>
-    <row r="124" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" ht="14.4" customHeight="1">
       <c r="A124" s="7"/>
       <c r="B124" s="110"/>
       <c r="C124" s="101"/>
@@ -7195,7 +7198,7 @@
       <c r="O124" s="88"/>
       <c r="P124" s="91"/>
     </row>
-    <row r="125" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" ht="14.4" customHeight="1">
       <c r="A125" s="7"/>
       <c r="B125" s="111"/>
       <c r="C125" s="102"/>
@@ -7215,7 +7218,7 @@
       <c r="O125" s="89"/>
       <c r="P125" s="92"/>
     </row>
-    <row r="126" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" ht="14.4" customHeight="1">
       <c r="A126" s="7"/>
       <c r="B126" s="110">
         <v>16</v>
@@ -7249,7 +7252,7 @@
       <c r="O126" s="88"/>
       <c r="P126" s="90"/>
     </row>
-    <row r="127" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" ht="14.4" customHeight="1">
       <c r="A127" s="7"/>
       <c r="B127" s="110"/>
       <c r="C127" s="101"/>
@@ -7271,7 +7274,7 @@
       <c r="O127" s="88"/>
       <c r="P127" s="91"/>
     </row>
-    <row r="128" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" ht="14.4" customHeight="1">
       <c r="A128" s="7"/>
       <c r="B128" s="110"/>
       <c r="C128" s="101"/>
@@ -7295,7 +7298,7 @@
       <c r="O128" s="88"/>
       <c r="P128" s="91"/>
     </row>
-    <row r="129" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" ht="14.4" customHeight="1">
       <c r="A129" s="7"/>
       <c r="B129" s="110"/>
       <c r="C129" s="101"/>
@@ -7317,7 +7320,7 @@
       <c r="O129" s="88"/>
       <c r="P129" s="91"/>
     </row>
-    <row r="130" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" ht="14.4" customHeight="1">
       <c r="A130" s="7"/>
       <c r="B130" s="110"/>
       <c r="C130" s="101"/>
@@ -7337,7 +7340,7 @@
       <c r="O130" s="88"/>
       <c r="P130" s="91"/>
     </row>
-    <row r="131" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" ht="14.4" customHeight="1">
       <c r="A131" s="7"/>
       <c r="B131" s="110"/>
       <c r="C131" s="101"/>
@@ -7357,7 +7360,7 @@
       <c r="O131" s="88"/>
       <c r="P131" s="91"/>
     </row>
-    <row r="132" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" ht="14.4" customHeight="1">
       <c r="A132" s="7"/>
       <c r="B132" s="110"/>
       <c r="C132" s="101"/>
@@ -7377,7 +7380,7 @@
       <c r="O132" s="88"/>
       <c r="P132" s="91"/>
     </row>
-    <row r="133" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" ht="14.4" customHeight="1">
       <c r="A133" s="7"/>
       <c r="B133" s="110"/>
       <c r="C133" s="101"/>
@@ -7397,7 +7400,7 @@
       <c r="O133" s="88"/>
       <c r="P133" s="91"/>
     </row>
-    <row r="134" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" ht="14.4" customHeight="1">
       <c r="A134" s="7"/>
       <c r="B134" s="110"/>
       <c r="C134" s="101"/>
@@ -7417,7 +7420,7 @@
       <c r="O134" s="88"/>
       <c r="P134" s="91"/>
     </row>
-    <row r="135" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" ht="14.4" customHeight="1">
       <c r="A135" s="7"/>
       <c r="B135" s="111"/>
       <c r="C135" s="102"/>
@@ -7437,7 +7440,7 @@
       <c r="O135" s="89"/>
       <c r="P135" s="92"/>
     </row>
-    <row r="136" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" ht="14.4" customHeight="1">
       <c r="A136" s="7"/>
       <c r="B136" s="110">
         <v>17</v>
@@ -7471,7 +7474,7 @@
       <c r="O136" s="106"/>
       <c r="P136" s="107"/>
     </row>
-    <row r="137" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" ht="14.4" customHeight="1">
       <c r="A137" s="7"/>
       <c r="B137" s="110"/>
       <c r="C137" s="101"/>
@@ -7495,7 +7498,7 @@
       <c r="O137" s="88"/>
       <c r="P137" s="91"/>
     </row>
-    <row r="138" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" ht="14.4" customHeight="1">
       <c r="A138" s="7"/>
       <c r="B138" s="110"/>
       <c r="C138" s="101"/>
@@ -7517,7 +7520,7 @@
       <c r="O138" s="88"/>
       <c r="P138" s="91"/>
     </row>
-    <row r="139" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" ht="14.4" customHeight="1">
       <c r="A139" s="7"/>
       <c r="B139" s="110"/>
       <c r="C139" s="101"/>
@@ -7541,7 +7544,7 @@
       <c r="O139" s="88"/>
       <c r="P139" s="91"/>
     </row>
-    <row r="140" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" ht="14.4" customHeight="1">
       <c r="A140" s="7"/>
       <c r="B140" s="110"/>
       <c r="C140" s="101"/>
@@ -7563,7 +7566,7 @@
       <c r="O140" s="88"/>
       <c r="P140" s="91"/>
     </row>
-    <row r="141" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" ht="14.4" customHeight="1">
       <c r="A141" s="7"/>
       <c r="B141" s="110"/>
       <c r="C141" s="101"/>
@@ -7585,7 +7588,7 @@
       <c r="O141" s="88"/>
       <c r="P141" s="91"/>
     </row>
-    <row r="142" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" ht="14.4" customHeight="1">
       <c r="A142" s="7"/>
       <c r="B142" s="110"/>
       <c r="C142" s="101"/>
@@ -7605,7 +7608,7 @@
       <c r="O142" s="88"/>
       <c r="P142" s="91"/>
     </row>
-    <row r="143" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" ht="14.4" customHeight="1">
       <c r="A143" s="7"/>
       <c r="B143" s="110"/>
       <c r="C143" s="101"/>
@@ -7625,7 +7628,7 @@
       <c r="O143" s="88"/>
       <c r="P143" s="91"/>
     </row>
-    <row r="144" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" ht="14.4" customHeight="1">
       <c r="A144" s="7"/>
       <c r="B144" s="110"/>
       <c r="C144" s="101"/>
@@ -7645,7 +7648,7 @@
       <c r="O144" s="88"/>
       <c r="P144" s="91"/>
     </row>
-    <row r="145" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" ht="14.4" customHeight="1">
       <c r="A145" s="7"/>
       <c r="B145" s="111"/>
       <c r="C145" s="102"/>
@@ -7665,7 +7668,7 @@
       <c r="O145" s="89"/>
       <c r="P145" s="92"/>
     </row>
-    <row r="146" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" ht="14.4" customHeight="1">
       <c r="A146" s="7"/>
       <c r="B146" s="110">
         <v>18</v>
@@ -7699,7 +7702,7 @@
       <c r="O146" s="88"/>
       <c r="P146" s="90"/>
     </row>
-    <row r="147" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" ht="14.4" customHeight="1">
       <c r="A147" s="7"/>
       <c r="B147" s="110"/>
       <c r="C147" s="101"/>
@@ -7723,7 +7726,7 @@
       <c r="O147" s="88"/>
       <c r="P147" s="91"/>
     </row>
-    <row r="148" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" ht="14.4" customHeight="1">
       <c r="A148" s="7"/>
       <c r="B148" s="110"/>
       <c r="C148" s="101"/>
@@ -7747,7 +7750,7 @@
       <c r="O148" s="88"/>
       <c r="P148" s="91"/>
     </row>
-    <row r="149" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" ht="14.4" customHeight="1">
       <c r="A149" s="7"/>
       <c r="B149" s="110"/>
       <c r="C149" s="101"/>
@@ -7771,7 +7774,7 @@
       <c r="O149" s="88"/>
       <c r="P149" s="91"/>
     </row>
-    <row r="150" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" ht="14.4" customHeight="1">
       <c r="A150" s="7"/>
       <c r="B150" s="110"/>
       <c r="C150" s="101"/>
@@ -7795,7 +7798,7 @@
       <c r="O150" s="88"/>
       <c r="P150" s="91"/>
     </row>
-    <row r="151" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" ht="14.4" customHeight="1">
       <c r="A151" s="7"/>
       <c r="B151" s="110"/>
       <c r="C151" s="101"/>
@@ -7817,7 +7820,7 @@
       <c r="O151" s="88"/>
       <c r="P151" s="91"/>
     </row>
-    <row r="152" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" ht="14.4" customHeight="1">
       <c r="A152" s="7"/>
       <c r="B152" s="110"/>
       <c r="C152" s="101"/>
@@ -7839,7 +7842,7 @@
       <c r="O152" s="88"/>
       <c r="P152" s="91"/>
     </row>
-    <row r="153" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" ht="14.4" customHeight="1">
       <c r="A153" s="7"/>
       <c r="B153" s="110"/>
       <c r="C153" s="101"/>
@@ -7859,7 +7862,7 @@
       <c r="O153" s="88"/>
       <c r="P153" s="91"/>
     </row>
-    <row r="154" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" ht="14.4" customHeight="1">
       <c r="A154" s="7"/>
       <c r="B154" s="110"/>
       <c r="C154" s="101"/>
@@ -7879,7 +7882,7 @@
       <c r="O154" s="88"/>
       <c r="P154" s="91"/>
     </row>
-    <row r="155" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" ht="14.4" customHeight="1">
       <c r="A155" s="7"/>
       <c r="B155" s="111"/>
       <c r="C155" s="102"/>
@@ -7899,7 +7902,7 @@
       <c r="O155" s="89"/>
       <c r="P155" s="92"/>
     </row>
-    <row r="156" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" ht="14.4" customHeight="1">
       <c r="A156" s="7"/>
       <c r="B156" s="110">
         <v>19</v>
@@ -7933,7 +7936,7 @@
       <c r="O156" s="106"/>
       <c r="P156" s="107"/>
     </row>
-    <row r="157" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" ht="14.4" customHeight="1">
       <c r="A157" s="7"/>
       <c r="B157" s="110"/>
       <c r="C157" s="101"/>
@@ -7955,7 +7958,7 @@
       <c r="O157" s="88"/>
       <c r="P157" s="91"/>
     </row>
-    <row r="158" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" ht="14.4" customHeight="1">
       <c r="A158" s="7"/>
       <c r="B158" s="110"/>
       <c r="C158" s="101"/>
@@ -7977,7 +7980,7 @@
       <c r="O158" s="88"/>
       <c r="P158" s="91"/>
     </row>
-    <row r="159" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" ht="14.4" customHeight="1">
       <c r="A159" s="7"/>
       <c r="B159" s="110"/>
       <c r="C159" s="101"/>
@@ -7999,7 +8002,7 @@
       <c r="O159" s="88"/>
       <c r="P159" s="91"/>
     </row>
-    <row r="160" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" ht="14.4" customHeight="1">
       <c r="A160" s="7"/>
       <c r="B160" s="110"/>
       <c r="C160" s="101"/>
@@ -8021,7 +8024,7 @@
       <c r="O160" s="88"/>
       <c r="P160" s="91"/>
     </row>
-    <row r="161" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" ht="14.4" customHeight="1">
       <c r="A161" s="7"/>
       <c r="B161" s="110"/>
       <c r="C161" s="101"/>
@@ -8041,7 +8044,7 @@
       <c r="O161" s="88"/>
       <c r="P161" s="91"/>
     </row>
-    <row r="162" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" ht="14.4" customHeight="1">
       <c r="A162" s="7"/>
       <c r="B162" s="110"/>
       <c r="C162" s="101"/>
@@ -8061,7 +8064,7 @@
       <c r="O162" s="88"/>
       <c r="P162" s="91"/>
     </row>
-    <row r="163" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" ht="14.4" customHeight="1">
       <c r="A163" s="7"/>
       <c r="B163" s="110"/>
       <c r="C163" s="101"/>
@@ -8081,7 +8084,7 @@
       <c r="O163" s="88"/>
       <c r="P163" s="91"/>
     </row>
-    <row r="164" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" ht="14.4" customHeight="1">
       <c r="A164" s="7"/>
       <c r="B164" s="110"/>
       <c r="C164" s="101"/>
@@ -8101,7 +8104,7 @@
       <c r="O164" s="88"/>
       <c r="P164" s="91"/>
     </row>
-    <row r="165" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" ht="14.4" customHeight="1">
       <c r="A165" s="7"/>
       <c r="B165" s="111"/>
       <c r="C165" s="102"/>
@@ -8121,7 +8124,7 @@
       <c r="O165" s="89"/>
       <c r="P165" s="92"/>
     </row>
-    <row r="166" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" ht="14.4" customHeight="1">
       <c r="A166" s="7"/>
       <c r="B166" s="110">
         <v>20</v>
@@ -8155,7 +8158,7 @@
       <c r="O166" s="88"/>
       <c r="P166" s="90"/>
     </row>
-    <row r="167" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" ht="14.4" customHeight="1">
       <c r="A167" s="7"/>
       <c r="B167" s="110"/>
       <c r="C167" s="101"/>
@@ -8179,7 +8182,7 @@
       <c r="O167" s="88"/>
       <c r="P167" s="91"/>
     </row>
-    <row r="168" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" ht="14.4" customHeight="1">
       <c r="A168" s="7"/>
       <c r="B168" s="110"/>
       <c r="C168" s="101"/>
@@ -8201,7 +8204,7 @@
       <c r="O168" s="88"/>
       <c r="P168" s="91"/>
     </row>
-    <row r="169" spans="1:16" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="169" ht="27.6">
       <c r="A169" s="7"/>
       <c r="B169" s="110"/>
       <c r="C169" s="101"/>
@@ -8223,7 +8226,7 @@
       <c r="O169" s="88"/>
       <c r="P169" s="91"/>
     </row>
-    <row r="170" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" ht="14.4" customHeight="1">
       <c r="A170" s="7"/>
       <c r="B170" s="110"/>
       <c r="C170" s="101"/>
@@ -8243,7 +8246,7 @@
       <c r="O170" s="88"/>
       <c r="P170" s="91"/>
     </row>
-    <row r="171" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" ht="14.4" customHeight="1">
       <c r="A171" s="7"/>
       <c r="B171" s="110"/>
       <c r="C171" s="101"/>
@@ -8263,7 +8266,7 @@
       <c r="O171" s="88"/>
       <c r="P171" s="91"/>
     </row>
-    <row r="172" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" ht="14.4" customHeight="1">
       <c r="A172" s="7"/>
       <c r="B172" s="110"/>
       <c r="C172" s="101"/>
@@ -8283,7 +8286,7 @@
       <c r="O172" s="88"/>
       <c r="P172" s="91"/>
     </row>
-    <row r="173" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" ht="14.4" customHeight="1">
       <c r="A173" s="7"/>
       <c r="B173" s="110"/>
       <c r="C173" s="101"/>
@@ -8303,7 +8306,7 @@
       <c r="O173" s="88"/>
       <c r="P173" s="91"/>
     </row>
-    <row r="174" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" ht="14.4" customHeight="1">
       <c r="A174" s="7"/>
       <c r="B174" s="110"/>
       <c r="C174" s="101"/>
@@ -8323,7 +8326,7 @@
       <c r="O174" s="88"/>
       <c r="P174" s="91"/>
     </row>
-    <row r="175" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" ht="14.4" customHeight="1">
       <c r="A175" s="7"/>
       <c r="B175" s="111"/>
       <c r="C175" s="102"/>
@@ -8343,7 +8346,7 @@
       <c r="O175" s="89"/>
       <c r="P175" s="92"/>
     </row>
-    <row r="176" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" ht="14.4" customHeight="1">
       <c r="A176" s="7"/>
       <c r="B176" s="110">
         <v>21</v>
@@ -8377,7 +8380,7 @@
       <c r="O176" s="106"/>
       <c r="P176" s="107"/>
     </row>
-    <row r="177" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" ht="14.4" customHeight="1">
       <c r="A177" s="7"/>
       <c r="B177" s="110"/>
       <c r="C177" s="101"/>
@@ -8399,7 +8402,7 @@
       <c r="O177" s="88"/>
       <c r="P177" s="91"/>
     </row>
-    <row r="178" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" ht="14.4" customHeight="1">
       <c r="A178" s="7"/>
       <c r="B178" s="110"/>
       <c r="C178" s="101"/>
@@ -8421,7 +8424,7 @@
       <c r="O178" s="88"/>
       <c r="P178" s="91"/>
     </row>
-    <row r="179" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" ht="14.4" customHeight="1">
       <c r="A179" s="7"/>
       <c r="B179" s="110"/>
       <c r="C179" s="101"/>
@@ -8443,7 +8446,7 @@
       <c r="O179" s="88"/>
       <c r="P179" s="91"/>
     </row>
-    <row r="180" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" ht="14.4" customHeight="1">
       <c r="A180" s="7"/>
       <c r="B180" s="110"/>
       <c r="C180" s="101"/>
@@ -8463,7 +8466,7 @@
       <c r="O180" s="88"/>
       <c r="P180" s="91"/>
     </row>
-    <row r="181" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" ht="14.4" customHeight="1">
       <c r="A181" s="7"/>
       <c r="B181" s="110"/>
       <c r="C181" s="101"/>
@@ -8483,7 +8486,7 @@
       <c r="O181" s="88"/>
       <c r="P181" s="91"/>
     </row>
-    <row r="182" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" ht="14.4" customHeight="1">
       <c r="A182" s="7"/>
       <c r="B182" s="110"/>
       <c r="C182" s="101"/>
@@ -8503,7 +8506,7 @@
       <c r="O182" s="88"/>
       <c r="P182" s="91"/>
     </row>
-    <row r="183" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" ht="14.4" customHeight="1">
       <c r="A183" s="7"/>
       <c r="B183" s="110"/>
       <c r="C183" s="101"/>
@@ -8523,7 +8526,7 @@
       <c r="O183" s="88"/>
       <c r="P183" s="91"/>
     </row>
-    <row r="184" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" ht="14.4" customHeight="1">
       <c r="A184" s="7"/>
       <c r="B184" s="110"/>
       <c r="C184" s="101"/>
@@ -8543,7 +8546,7 @@
       <c r="O184" s="88"/>
       <c r="P184" s="91"/>
     </row>
-    <row r="185" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" ht="14.4" customHeight="1">
       <c r="A185" s="7"/>
       <c r="B185" s="111"/>
       <c r="C185" s="102"/>
@@ -8563,7 +8566,7 @@
       <c r="O185" s="89"/>
       <c r="P185" s="92"/>
     </row>
-    <row r="186" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" ht="14.4" customHeight="1">
       <c r="A186" s="7"/>
       <c r="B186" s="110">
         <v>22</v>
@@ -8597,7 +8600,7 @@
       <c r="O186" s="88"/>
       <c r="P186" s="90"/>
     </row>
-    <row r="187" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" ht="14.4" customHeight="1">
       <c r="A187" s="7"/>
       <c r="B187" s="110"/>
       <c r="C187" s="101"/>
@@ -8621,7 +8624,7 @@
       <c r="O187" s="88"/>
       <c r="P187" s="91"/>
     </row>
-    <row r="188" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" ht="14.4" customHeight="1">
       <c r="A188" s="7"/>
       <c r="B188" s="110"/>
       <c r="C188" s="101"/>
@@ -8645,7 +8648,7 @@
       <c r="O188" s="88"/>
       <c r="P188" s="91"/>
     </row>
-    <row r="189" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" ht="14.4" customHeight="1">
       <c r="A189" s="7"/>
       <c r="B189" s="110"/>
       <c r="C189" s="101"/>
@@ -8667,7 +8670,7 @@
       <c r="O189" s="88"/>
       <c r="P189" s="91"/>
     </row>
-    <row r="190" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" ht="14.4" customHeight="1">
       <c r="A190" s="7"/>
       <c r="B190" s="110"/>
       <c r="C190" s="101"/>
@@ -8691,7 +8694,7 @@
       <c r="O190" s="88"/>
       <c r="P190" s="91"/>
     </row>
-    <row r="191" spans="1:16" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" ht="13.8" customHeight="1">
       <c r="A191" s="7"/>
       <c r="B191" s="110"/>
       <c r="C191" s="101"/>
@@ -8713,7 +8716,7 @@
       <c r="O191" s="88"/>
       <c r="P191" s="91"/>
     </row>
-    <row r="192" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" ht="14.4" customHeight="1">
       <c r="A192" s="7"/>
       <c r="B192" s="110"/>
       <c r="C192" s="101"/>
@@ -8733,7 +8736,7 @@
       <c r="O192" s="88"/>
       <c r="P192" s="91"/>
     </row>
-    <row r="193" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" ht="14.4" customHeight="1">
       <c r="A193" s="7"/>
       <c r="B193" s="110"/>
       <c r="C193" s="101"/>
@@ -8753,7 +8756,7 @@
       <c r="O193" s="88"/>
       <c r="P193" s="91"/>
     </row>
-    <row r="194" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" ht="14.4" customHeight="1">
       <c r="A194" s="7"/>
       <c r="B194" s="110"/>
       <c r="C194" s="101"/>
@@ -8773,7 +8776,7 @@
       <c r="O194" s="88"/>
       <c r="P194" s="91"/>
     </row>
-    <row r="195" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" ht="14.4" customHeight="1">
       <c r="A195" s="7"/>
       <c r="B195" s="111"/>
       <c r="C195" s="102"/>
@@ -8793,7 +8796,7 @@
       <c r="O195" s="89"/>
       <c r="P195" s="92"/>
     </row>
-    <row r="196" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" ht="14.4" customHeight="1">
       <c r="A196" s="7"/>
       <c r="B196" s="110">
         <v>23</v>
@@ -8827,7 +8830,7 @@
       <c r="O196" s="106"/>
       <c r="P196" s="107"/>
     </row>
-    <row r="197" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" ht="14.4" customHeight="1">
       <c r="A197" s="7"/>
       <c r="B197" s="110"/>
       <c r="C197" s="101"/>
@@ -8849,7 +8852,7 @@
       <c r="O197" s="88"/>
       <c r="P197" s="91"/>
     </row>
-    <row r="198" spans="1:16" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" ht="13.8" customHeight="1">
       <c r="A198" s="7"/>
       <c r="B198" s="110"/>
       <c r="C198" s="101"/>
@@ -8871,7 +8874,7 @@
       <c r="O198" s="88"/>
       <c r="P198" s="91"/>
     </row>
-    <row r="199" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" ht="14.4" customHeight="1">
       <c r="A199" s="7"/>
       <c r="B199" s="110"/>
       <c r="C199" s="101"/>
@@ -8893,7 +8896,7 @@
       <c r="O199" s="88"/>
       <c r="P199" s="91"/>
     </row>
-    <row r="200" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" ht="14.4" customHeight="1">
       <c r="A200" s="7"/>
       <c r="B200" s="110"/>
       <c r="C200" s="101"/>
@@ -8913,7 +8916,7 @@
       <c r="O200" s="88"/>
       <c r="P200" s="91"/>
     </row>
-    <row r="201" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" ht="14.4" customHeight="1">
       <c r="A201" s="7"/>
       <c r="B201" s="110"/>
       <c r="C201" s="101"/>
@@ -8933,7 +8936,7 @@
       <c r="O201" s="88"/>
       <c r="P201" s="91"/>
     </row>
-    <row r="202" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" ht="14.4" customHeight="1">
       <c r="A202" s="7"/>
       <c r="B202" s="110"/>
       <c r="C202" s="101"/>
@@ -8953,7 +8956,7 @@
       <c r="O202" s="88"/>
       <c r="P202" s="91"/>
     </row>
-    <row r="203" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" ht="14.4" customHeight="1">
       <c r="A203" s="7"/>
       <c r="B203" s="110"/>
       <c r="C203" s="101"/>
@@ -8973,7 +8976,7 @@
       <c r="O203" s="88"/>
       <c r="P203" s="91"/>
     </row>
-    <row r="204" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" ht="14.4" customHeight="1">
       <c r="A204" s="7"/>
       <c r="B204" s="110"/>
       <c r="C204" s="101"/>
@@ -8993,7 +8996,7 @@
       <c r="O204" s="88"/>
       <c r="P204" s="91"/>
     </row>
-    <row r="205" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" ht="14.4" customHeight="1">
       <c r="A205" s="7"/>
       <c r="B205" s="111"/>
       <c r="C205" s="102"/>
@@ -9013,7 +9016,7 @@
       <c r="O205" s="89"/>
       <c r="P205" s="92"/>
     </row>
-    <row r="206" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" ht="14.4" customHeight="1">
       <c r="A206" s="7"/>
       <c r="B206" s="110">
         <v>24</v>
@@ -9049,7 +9052,7 @@
       <c r="O206" s="88"/>
       <c r="P206" s="90"/>
     </row>
-    <row r="207" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" ht="14.4" customHeight="1">
       <c r="A207" s="7"/>
       <c r="B207" s="110"/>
       <c r="C207" s="101"/>
@@ -9073,7 +9076,7 @@
       <c r="O207" s="88"/>
       <c r="P207" s="91"/>
     </row>
-    <row r="208" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" ht="14.4" customHeight="1">
       <c r="A208" s="7"/>
       <c r="B208" s="110"/>
       <c r="C208" s="101"/>
@@ -9095,7 +9098,7 @@
       <c r="O208" s="88"/>
       <c r="P208" s="91"/>
     </row>
-    <row r="209" spans="1:16" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="209" ht="27.6">
       <c r="A209" s="7"/>
       <c r="B209" s="110"/>
       <c r="C209" s="101"/>
@@ -9117,7 +9120,7 @@
       <c r="O209" s="88"/>
       <c r="P209" s="91"/>
     </row>
-    <row r="210" spans="1:16" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="210" ht="27.6">
       <c r="A210" s="7"/>
       <c r="B210" s="110"/>
       <c r="C210" s="101"/>
@@ -9139,7 +9142,7 @@
       <c r="O210" s="88"/>
       <c r="P210" s="91"/>
     </row>
-    <row r="211" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" ht="14.4" customHeight="1">
       <c r="A211" s="7"/>
       <c r="B211" s="110"/>
       <c r="C211" s="101"/>
@@ -9159,7 +9162,7 @@
       <c r="O211" s="88"/>
       <c r="P211" s="91"/>
     </row>
-    <row r="212" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" ht="14.4" customHeight="1">
       <c r="A212" s="7"/>
       <c r="B212" s="110"/>
       <c r="C212" s="101"/>
@@ -9179,7 +9182,7 @@
       <c r="O212" s="88"/>
       <c r="P212" s="91"/>
     </row>
-    <row r="213" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" ht="14.4" customHeight="1">
       <c r="A213" s="7"/>
       <c r="B213" s="110"/>
       <c r="C213" s="101"/>
@@ -9199,7 +9202,7 @@
       <c r="O213" s="88"/>
       <c r="P213" s="91"/>
     </row>
-    <row r="214" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" ht="14.4" customHeight="1">
       <c r="A214" s="7"/>
       <c r="B214" s="110"/>
       <c r="C214" s="101"/>
@@ -9219,7 +9222,7 @@
       <c r="O214" s="88"/>
       <c r="P214" s="91"/>
     </row>
-    <row r="215" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" ht="14.4" customHeight="1">
       <c r="A215" s="7"/>
       <c r="B215" s="111"/>
       <c r="C215" s="102"/>
@@ -9239,7 +9242,7 @@
       <c r="O215" s="89"/>
       <c r="P215" s="92"/>
     </row>
-    <row r="216" spans="1:16" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" ht="13.8" customHeight="1">
       <c r="A216" s="7"/>
       <c r="B216" s="110">
         <v>25</v>
@@ -9275,7 +9278,7 @@
       <c r="O216" s="106"/>
       <c r="P216" s="107"/>
     </row>
-    <row r="217" spans="1:16" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" ht="13.8" customHeight="1">
       <c r="A217" s="7"/>
       <c r="B217" s="110"/>
       <c r="C217" s="101"/>
@@ -9299,7 +9302,7 @@
       <c r="O217" s="88"/>
       <c r="P217" s="91"/>
     </row>
-    <row r="218" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" ht="14.4" customHeight="1">
       <c r="A218" s="7"/>
       <c r="B218" s="110"/>
       <c r="C218" s="101"/>
@@ -9321,7 +9324,7 @@
       <c r="O218" s="88"/>
       <c r="P218" s="91"/>
     </row>
-    <row r="219" spans="1:16" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" ht="13.8" customHeight="1">
       <c r="A219" s="7"/>
       <c r="B219" s="110"/>
       <c r="C219" s="101"/>
@@ -9343,7 +9346,7 @@
       <c r="O219" s="88"/>
       <c r="P219" s="91"/>
     </row>
-    <row r="220" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" ht="14.4" customHeight="1">
       <c r="A220" s="7"/>
       <c r="B220" s="110"/>
       <c r="C220" s="101"/>
@@ -9365,7 +9368,7 @@
       <c r="O220" s="88"/>
       <c r="P220" s="91"/>
     </row>
-    <row r="221" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" ht="14.4" customHeight="1">
       <c r="A221" s="7"/>
       <c r="B221" s="110"/>
       <c r="C221" s="101"/>
@@ -9385,7 +9388,7 @@
       <c r="O221" s="88"/>
       <c r="P221" s="91"/>
     </row>
-    <row r="222" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" ht="14.4" customHeight="1">
       <c r="A222" s="7"/>
       <c r="B222" s="110"/>
       <c r="C222" s="101"/>
@@ -9405,7 +9408,7 @@
       <c r="O222" s="88"/>
       <c r="P222" s="91"/>
     </row>
-    <row r="223" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" ht="14.4" customHeight="1">
       <c r="A223" s="7"/>
       <c r="B223" s="110"/>
       <c r="C223" s="101"/>
@@ -9425,7 +9428,7 @@
       <c r="O223" s="88"/>
       <c r="P223" s="91"/>
     </row>
-    <row r="224" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" ht="14.4" customHeight="1">
       <c r="A224" s="7"/>
       <c r="B224" s="110"/>
       <c r="C224" s="101"/>
@@ -9445,7 +9448,7 @@
       <c r="O224" s="88"/>
       <c r="P224" s="91"/>
     </row>
-    <row r="225" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" ht="14.4" customHeight="1">
       <c r="A225" s="7"/>
       <c r="B225" s="111"/>
       <c r="C225" s="102"/>
@@ -9465,7 +9468,7 @@
       <c r="O225" s="89"/>
       <c r="P225" s="92"/>
     </row>
-    <row r="226" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" ht="14.4" customHeight="1">
       <c r="A226" s="7"/>
       <c r="B226" s="110">
         <v>26</v>
@@ -9499,7 +9502,7 @@
       <c r="O226" s="88"/>
       <c r="P226" s="90"/>
     </row>
-    <row r="227" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" ht="14.4" customHeight="1">
       <c r="A227" s="7"/>
       <c r="B227" s="110"/>
       <c r="C227" s="101"/>
@@ -9521,7 +9524,7 @@
       <c r="O227" s="88"/>
       <c r="P227" s="91"/>
     </row>
-    <row r="228" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" ht="14.4" customHeight="1">
       <c r="A228" s="7"/>
       <c r="B228" s="110"/>
       <c r="C228" s="101"/>
@@ -9543,7 +9546,7 @@
       <c r="O228" s="88"/>
       <c r="P228" s="91"/>
     </row>
-    <row r="229" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" ht="14.4" customHeight="1">
       <c r="A229" s="7"/>
       <c r="B229" s="110"/>
       <c r="C229" s="101"/>
@@ -9565,7 +9568,7 @@
       <c r="O229" s="88"/>
       <c r="P229" s="91"/>
     </row>
-    <row r="230" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" ht="14.4" customHeight="1">
       <c r="A230" s="7"/>
       <c r="B230" s="110"/>
       <c r="C230" s="101"/>
@@ -9587,7 +9590,7 @@
       <c r="O230" s="88"/>
       <c r="P230" s="91"/>
     </row>
-    <row r="231" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" ht="14.4" customHeight="1">
       <c r="A231" s="7"/>
       <c r="B231" s="110"/>
       <c r="C231" s="101"/>
@@ -9607,7 +9610,7 @@
       <c r="O231" s="88"/>
       <c r="P231" s="91"/>
     </row>
-    <row r="232" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" ht="14.4" customHeight="1">
       <c r="A232" s="7"/>
       <c r="B232" s="110"/>
       <c r="C232" s="101"/>
@@ -9627,7 +9630,7 @@
       <c r="O232" s="88"/>
       <c r="P232" s="91"/>
     </row>
-    <row r="233" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" ht="14.4" customHeight="1">
       <c r="A233" s="7"/>
       <c r="B233" s="110"/>
       <c r="C233" s="101"/>
@@ -9647,7 +9650,7 @@
       <c r="O233" s="88"/>
       <c r="P233" s="91"/>
     </row>
-    <row r="234" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" ht="14.4" customHeight="1">
       <c r="A234" s="7"/>
       <c r="B234" s="110"/>
       <c r="C234" s="101"/>
@@ -9667,7 +9670,7 @@
       <c r="O234" s="88"/>
       <c r="P234" s="91"/>
     </row>
-    <row r="235" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" ht="14.4" customHeight="1">
       <c r="A235" s="7"/>
       <c r="B235" s="111"/>
       <c r="C235" s="102"/>
@@ -9687,7 +9690,7 @@
       <c r="O235" s="89"/>
       <c r="P235" s="92"/>
     </row>
-    <row r="236" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" ht="14.4" customHeight="1">
       <c r="A236" s="7"/>
       <c r="B236" s="110">
         <v>27</v>
@@ -9721,7 +9724,7 @@
       <c r="O236" s="106"/>
       <c r="P236" s="107"/>
     </row>
-    <row r="237" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" ht="14.4" customHeight="1">
       <c r="A237" s="7"/>
       <c r="B237" s="110"/>
       <c r="C237" s="101"/>
@@ -9745,7 +9748,7 @@
       <c r="O237" s="88"/>
       <c r="P237" s="91"/>
     </row>
-    <row r="238" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" ht="14.4" customHeight="1">
       <c r="A238" s="7"/>
       <c r="B238" s="110"/>
       <c r="C238" s="101"/>
@@ -9767,7 +9770,7 @@
       <c r="O238" s="88"/>
       <c r="P238" s="91"/>
     </row>
-    <row r="239" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" ht="14.4" customHeight="1">
       <c r="A239" s="7"/>
       <c r="B239" s="110"/>
       <c r="C239" s="101"/>
@@ -9791,7 +9794,7 @@
       <c r="O239" s="88"/>
       <c r="P239" s="91"/>
     </row>
-    <row r="240" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" ht="14.4" customHeight="1">
       <c r="A240" s="7"/>
       <c r="B240" s="110"/>
       <c r="C240" s="101"/>
@@ -9813,7 +9816,7 @@
       <c r="O240" s="88"/>
       <c r="P240" s="91"/>
     </row>
-    <row r="241" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" ht="14.4" customHeight="1">
       <c r="A241" s="7"/>
       <c r="B241" s="110"/>
       <c r="C241" s="101"/>
@@ -9835,7 +9838,7 @@
       <c r="O241" s="88"/>
       <c r="P241" s="91"/>
     </row>
-    <row r="242" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" ht="14.4" customHeight="1">
       <c r="A242" s="7"/>
       <c r="B242" s="110"/>
       <c r="C242" s="101"/>
@@ -9857,7 +9860,7 @@
       <c r="O242" s="88"/>
       <c r="P242" s="91"/>
     </row>
-    <row r="243" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" ht="14.4" customHeight="1">
       <c r="A243" s="7"/>
       <c r="B243" s="110"/>
       <c r="C243" s="101"/>
@@ -9877,7 +9880,7 @@
       <c r="O243" s="88"/>
       <c r="P243" s="91"/>
     </row>
-    <row r="244" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" ht="14.4" customHeight="1">
       <c r="A244" s="7"/>
       <c r="B244" s="110"/>
       <c r="C244" s="101"/>
@@ -9897,7 +9900,7 @@
       <c r="O244" s="88"/>
       <c r="P244" s="91"/>
     </row>
-    <row r="245" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" ht="14.4" customHeight="1">
       <c r="A245" s="7"/>
       <c r="B245" s="111"/>
       <c r="C245" s="102"/>
@@ -9917,7 +9920,7 @@
       <c r="O245" s="89"/>
       <c r="P245" s="92"/>
     </row>
-    <row r="246" spans="1:16" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="246" ht="27.6">
       <c r="A246" s="7"/>
       <c r="B246" s="110">
         <v>28</v>
@@ -9951,7 +9954,7 @@
       <c r="O246" s="88"/>
       <c r="P246" s="90"/>
     </row>
-    <row r="247" spans="1:16" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="247" ht="27.6">
       <c r="A247" s="7"/>
       <c r="B247" s="110"/>
       <c r="C247" s="101"/>
@@ -9973,7 +9976,7 @@
       <c r="O247" s="88"/>
       <c r="P247" s="91"/>
     </row>
-    <row r="248" spans="1:16" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" ht="13.8" customHeight="1">
       <c r="A248" s="7"/>
       <c r="B248" s="110"/>
       <c r="C248" s="101"/>
@@ -9995,7 +9998,7 @@
       <c r="O248" s="88"/>
       <c r="P248" s="91"/>
     </row>
-    <row r="249" spans="1:16" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" ht="13.8" customHeight="1">
       <c r="A249" s="7"/>
       <c r="B249" s="110"/>
       <c r="C249" s="101"/>
@@ -10017,7 +10020,7 @@
       <c r="O249" s="88"/>
       <c r="P249" s="91"/>
     </row>
-    <row r="250" spans="1:16" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="250" ht="27.6">
       <c r="A250" s="7"/>
       <c r="B250" s="110"/>
       <c r="C250" s="101"/>
@@ -10039,7 +10042,7 @@
       <c r="O250" s="88"/>
       <c r="P250" s="91"/>
     </row>
-    <row r="251" spans="1:16" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="251" ht="27.6">
       <c r="A251" s="7"/>
       <c r="B251" s="110"/>
       <c r="C251" s="101"/>
@@ -10061,7 +10064,7 @@
       <c r="O251" s="88"/>
       <c r="P251" s="91"/>
     </row>
-    <row r="252" spans="1:16" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" ht="13.8" customHeight="1">
       <c r="A252" s="7"/>
       <c r="B252" s="110"/>
       <c r="C252" s="101"/>
@@ -10083,7 +10086,7 @@
       <c r="O252" s="88"/>
       <c r="P252" s="91"/>
     </row>
-    <row r="253" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" ht="14.4" customHeight="1">
       <c r="A253" s="7"/>
       <c r="B253" s="110"/>
       <c r="C253" s="101"/>
@@ -10105,7 +10108,7 @@
       <c r="O253" s="88"/>
       <c r="P253" s="91"/>
     </row>
-    <row r="254" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" ht="14.4" customHeight="1">
       <c r="A254" s="7"/>
       <c r="B254" s="110"/>
       <c r="C254" s="101"/>
@@ -10125,7 +10128,7 @@
       <c r="O254" s="88"/>
       <c r="P254" s="91"/>
     </row>
-    <row r="255" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" ht="14.4" customHeight="1">
       <c r="A255" s="7"/>
       <c r="B255" s="111"/>
       <c r="C255" s="102"/>
@@ -10145,7 +10148,7 @@
       <c r="O255" s="89"/>
       <c r="P255" s="92"/>
     </row>
-    <row r="256" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" ht="14.4" customHeight="1">
       <c r="A256" s="7"/>
       <c r="B256" s="110">
         <v>29</v>
@@ -10179,7 +10182,7 @@
       <c r="O256" s="106"/>
       <c r="P256" s="107"/>
     </row>
-    <row r="257" spans="1:16" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="257" ht="27.6">
       <c r="A257" s="7"/>
       <c r="B257" s="110"/>
       <c r="C257" s="101"/>
@@ -10201,7 +10204,7 @@
       <c r="O257" s="88"/>
       <c r="P257" s="91"/>
     </row>
-    <row r="258" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" ht="14.4" customHeight="1">
       <c r="A258" s="7"/>
       <c r="B258" s="110"/>
       <c r="C258" s="101"/>
@@ -10223,7 +10226,7 @@
       <c r="O258" s="88"/>
       <c r="P258" s="91"/>
     </row>
-    <row r="259" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" ht="14.4" customHeight="1">
       <c r="A259" s="7"/>
       <c r="B259" s="110"/>
       <c r="C259" s="101"/>
@@ -10245,7 +10248,7 @@
       <c r="O259" s="88"/>
       <c r="P259" s="91"/>
     </row>
-    <row r="260" spans="1:16" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="260" ht="27.6">
       <c r="A260" s="7"/>
       <c r="B260" s="110"/>
       <c r="C260" s="101"/>
@@ -10267,7 +10270,7 @@
       <c r="O260" s="88"/>
       <c r="P260" s="91"/>
     </row>
-    <row r="261" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" ht="14.4" customHeight="1">
       <c r="A261" s="7"/>
       <c r="B261" s="110"/>
       <c r="C261" s="101"/>
@@ -10287,7 +10290,7 @@
       <c r="O261" s="88"/>
       <c r="P261" s="91"/>
     </row>
-    <row r="262" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" ht="14.4" customHeight="1">
       <c r="A262" s="7"/>
       <c r="B262" s="110"/>
       <c r="C262" s="101"/>
@@ -10307,7 +10310,7 @@
       <c r="O262" s="88"/>
       <c r="P262" s="91"/>
     </row>
-    <row r="263" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" ht="14.4" customHeight="1">
       <c r="A263" s="7"/>
       <c r="B263" s="110"/>
       <c r="C263" s="101"/>
@@ -10327,7 +10330,7 @@
       <c r="O263" s="88"/>
       <c r="P263" s="91"/>
     </row>
-    <row r="264" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" ht="14.4" customHeight="1">
       <c r="A264" s="7"/>
       <c r="B264" s="110"/>
       <c r="C264" s="101"/>
@@ -10347,7 +10350,7 @@
       <c r="O264" s="88"/>
       <c r="P264" s="91"/>
     </row>
-    <row r="265" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" ht="14.4" customHeight="1">
       <c r="A265" s="7"/>
       <c r="B265" s="111"/>
       <c r="C265" s="102"/>
@@ -10368,7 +10371,7 @@
       <c r="P265" s="92"/>
     </row>
   </sheetData>
-  <mergeCells count="348">
+  <mergeCells>
     <mergeCell ref="C46:C55"/>
     <mergeCell ref="D46:D55"/>
     <mergeCell ref="E46:E55"/>
@@ -10720,10 +10723,11 @@
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="K5" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
-    <hyperlink ref="K10" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
+    <hyperlink ref="K5" r:id="rId1"/>
+    <hyperlink ref="K10" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -10732,14 +10736,14 @@
   <dimension ref="A1:P367"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.19921875" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.59765625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="17.5" style="6" customWidth="1"/>
-    <col min="6" max="6" width="18.59765625" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.3984375" style="6" customWidth="1"/>
-    <col min="8" max="8" width="14.19921875" style="6" customWidth="1"/>
-    <col min="9" max="9" width="6.3984375" style="6" customWidth="1"/>
+    <col min="2" max="2" bestFit="1" width="17.19921875" customWidth="1"/>
+    <col min="3" max="3" bestFit="1" width="19.19921875" customWidth="1" style="6"/>
+    <col min="4" max="4" width="20.59765625" customWidth="1" style="6"/>
+    <col min="5" max="5" width="17.5" customWidth="1" style="6"/>
+    <col min="6" max="6" bestFit="1" width="18.59765625" customWidth="1" style="6"/>
+    <col min="7" max="7" width="18.3984375" customWidth="1" style="6"/>
+    <col min="8" max="8" width="14.19921875" customWidth="1" style="6"/>
+    <col min="9" max="9" width="6.3984375" customWidth="1" style="6"/>
     <col min="10" max="10" width="29.69921875" customWidth="1"/>
     <col min="11" max="11" width="27.3984375" customWidth="1"/>
     <col min="12" max="12" width="16.5" customWidth="1"/>
@@ -10749,7 +10753,7 @@
     <col min="16" max="16" width="11.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="40.2" customHeight="1">
       <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
@@ -10768,7 +10772,7 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
     </row>
-    <row r="2" spans="1:16" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="40.2" customHeight="1">
       <c r="B2" s="4" t="s">
         <v>113</v>
       </c>
@@ -10789,7 +10793,7 @@
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
     </row>
-    <row r="3" spans="1:16" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="40.2" customHeight="1">
       <c r="B3" s="8"/>
       <c r="C3" s="9"/>
       <c r="D3" s="10"/>
@@ -10808,7 +10812,7 @@
       <c r="O3" s="8"/>
       <c r="P3" s="8"/>
     </row>
-    <row r="4" spans="1:16" s="6" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="40.2" customHeight="1" s="6" customFormat="1">
       <c r="A4" s="13"/>
       <c r="B4" s="17" t="s">
         <v>117</v>
@@ -10856,7 +10860,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="14.4" customHeight="1">
       <c r="A5" s="7"/>
       <c r="B5" s="110">
         <v>1</v>
@@ -10890,17 +10894,17 @@
         <v>385</v>
       </c>
       <c r="M5" s="105" t="s">
+        <v>385</v>
+      </c>
+      <c r="N5" s="86" t="s">
+        <v>150</v>
+      </c>
+      <c r="O5" s="106" t="s">
         <v>386</v>
       </c>
-      <c r="N5" s="86" t="s">
-        <v>139</v>
-      </c>
-      <c r="O5" s="106" t="s">
-        <v>387</v>
-      </c>
       <c r="P5" s="107"/>
     </row>
-    <row r="6" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="14.4" customHeight="1">
       <c r="A6" s="7"/>
       <c r="B6" s="110"/>
       <c r="C6" s="101"/>
@@ -10913,7 +10917,7 @@
         <v>2</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="K6" s="14" t="s">
         <v>269</v>
@@ -10924,7 +10928,7 @@
       <c r="O6" s="88"/>
       <c r="P6" s="91"/>
     </row>
-    <row r="7" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="14.4" customHeight="1">
       <c r="A7" s="7"/>
       <c r="B7" s="110"/>
       <c r="C7" s="101"/>
@@ -10937,10 +10941,10 @@
         <v>3</v>
       </c>
       <c r="J7" s="14" t="s">
+        <v>388</v>
+      </c>
+      <c r="K7" s="14" t="s">
         <v>389</v>
-      </c>
-      <c r="K7" s="14" t="s">
-        <v>390</v>
       </c>
       <c r="L7" s="99"/>
       <c r="M7" s="99"/>
@@ -10948,7 +10952,7 @@
       <c r="O7" s="88"/>
       <c r="P7" s="91"/>
     </row>
-    <row r="8" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="14.4" customHeight="1">
       <c r="A8" s="7"/>
       <c r="B8" s="110"/>
       <c r="C8" s="101"/>
@@ -10961,10 +10965,10 @@
         <v>4</v>
       </c>
       <c r="J8" s="14" t="s">
+        <v>390</v>
+      </c>
+      <c r="K8" s="30" t="s">
         <v>391</v>
-      </c>
-      <c r="K8" s="30" t="s">
-        <v>392</v>
       </c>
       <c r="L8" s="99"/>
       <c r="M8" s="99"/>
@@ -10972,7 +10976,7 @@
       <c r="O8" s="88"/>
       <c r="P8" s="91"/>
     </row>
-    <row r="9" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="14.4" customHeight="1">
       <c r="A9" s="7"/>
       <c r="B9" s="110"/>
       <c r="C9" s="101"/>
@@ -10985,10 +10989,10 @@
         <v>5</v>
       </c>
       <c r="J9" s="14" t="s">
+        <v>392</v>
+      </c>
+      <c r="K9" s="14" t="s">
         <v>393</v>
-      </c>
-      <c r="K9" s="14" t="s">
-        <v>394</v>
       </c>
       <c r="L9" s="99"/>
       <c r="M9" s="99"/>
@@ -10996,7 +11000,7 @@
       <c r="O9" s="88"/>
       <c r="P9" s="91"/>
     </row>
-    <row r="10" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="14.4" customHeight="1">
       <c r="A10" s="7"/>
       <c r="B10" s="110"/>
       <c r="C10" s="101"/>
@@ -11009,10 +11013,10 @@
         <v>6</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="K10" s="14" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="L10" s="99"/>
       <c r="M10" s="99"/>
@@ -11020,7 +11024,7 @@
       <c r="O10" s="88"/>
       <c r="P10" s="91"/>
     </row>
-    <row r="11" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="14.4" customHeight="1">
       <c r="A11" s="7"/>
       <c r="B11" s="110"/>
       <c r="C11" s="101"/>
@@ -11033,7 +11037,7 @@
         <v>7</v>
       </c>
       <c r="J11" s="14" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="K11" s="14">
         <v>123456</v>
@@ -11044,7 +11048,7 @@
       <c r="O11" s="88"/>
       <c r="P11" s="91"/>
     </row>
-    <row r="12" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="14.4" customHeight="1">
       <c r="A12" s="7"/>
       <c r="B12" s="110"/>
       <c r="C12" s="101"/>
@@ -11057,7 +11061,7 @@
         <v>8</v>
       </c>
       <c r="J12" s="14" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="K12" s="14">
         <v>325458998</v>
@@ -11068,7 +11072,7 @@
       <c r="O12" s="88"/>
       <c r="P12" s="91"/>
     </row>
-    <row r="13" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="14.4" customHeight="1">
       <c r="A13" s="7"/>
       <c r="B13" s="110"/>
       <c r="C13" s="101"/>
@@ -11081,7 +11085,7 @@
         <v>9</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="K13" s="14">
         <v>12312561558</v>
@@ -11092,7 +11096,7 @@
       <c r="O13" s="88"/>
       <c r="P13" s="91"/>
     </row>
-    <row r="14" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="14.4" customHeight="1">
       <c r="A14" s="7"/>
       <c r="B14" s="110"/>
       <c r="C14" s="101"/>
@@ -11116,7 +11120,7 @@
       <c r="O14" s="132"/>
       <c r="P14" s="123"/>
     </row>
-    <row r="15" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="14.4" customHeight="1">
       <c r="A15" s="7"/>
       <c r="B15" s="110"/>
       <c r="C15" s="101"/>
@@ -11140,7 +11144,7 @@
       <c r="O15" s="132"/>
       <c r="P15" s="123"/>
     </row>
-    <row r="16" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="14.4" customHeight="1">
       <c r="A16" s="7"/>
       <c r="B16" s="110"/>
       <c r="C16" s="101"/>
@@ -11153,7 +11157,7 @@
         <v>12</v>
       </c>
       <c r="J16" s="31" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="K16" s="31">
         <v>123</v>
@@ -11164,7 +11168,7 @@
       <c r="O16" s="132"/>
       <c r="P16" s="123"/>
     </row>
-    <row r="17" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" ht="14.4" customHeight="1">
       <c r="A17" s="7"/>
       <c r="B17" s="111"/>
       <c r="C17" s="102"/>
@@ -11177,7 +11181,7 @@
         <v>13</v>
       </c>
       <c r="J17" s="15" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="K17" s="15"/>
       <c r="L17" s="100"/>
@@ -11186,7 +11190,7 @@
       <c r="O17" s="89"/>
       <c r="P17" s="92"/>
     </row>
-    <row r="18" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" ht="14.4" customHeight="1">
       <c r="A18" s="7"/>
       <c r="B18" s="110">
         <v>2</v>
@@ -11204,7 +11208,7 @@
         <v>381</v>
       </c>
       <c r="G18" s="101" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H18" s="112"/>
       <c r="I18" s="3">
@@ -11215,14 +11219,14 @@
       </c>
       <c r="K18" s="16"/>
       <c r="L18" s="99" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="M18" s="99"/>
       <c r="N18" s="85"/>
       <c r="O18" s="88"/>
       <c r="P18" s="90"/>
     </row>
-    <row r="19" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" ht="14.4" customHeight="1">
       <c r="A19" s="7"/>
       <c r="B19" s="110"/>
       <c r="C19" s="101"/>
@@ -11235,7 +11239,7 @@
         <v>2</v>
       </c>
       <c r="J19" s="14" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="K19" s="14" t="s">
         <v>269</v>
@@ -11246,7 +11250,7 @@
       <c r="O19" s="88"/>
       <c r="P19" s="91"/>
     </row>
-    <row r="20" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" ht="14.4" customHeight="1">
       <c r="A20" s="7"/>
       <c r="B20" s="110"/>
       <c r="C20" s="101"/>
@@ -11259,10 +11263,10 @@
         <v>3</v>
       </c>
       <c r="J20" s="14" t="s">
+        <v>388</v>
+      </c>
+      <c r="K20" s="14" t="s">
         <v>389</v>
-      </c>
-      <c r="K20" s="14" t="s">
-        <v>390</v>
       </c>
       <c r="L20" s="99"/>
       <c r="M20" s="99"/>
@@ -11270,7 +11274,7 @@
       <c r="O20" s="88"/>
       <c r="P20" s="91"/>
     </row>
-    <row r="21" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" ht="14.4" customHeight="1">
       <c r="A21" s="7"/>
       <c r="B21" s="110"/>
       <c r="C21" s="101"/>
@@ -11283,10 +11287,10 @@
         <v>4</v>
       </c>
       <c r="J21" s="14" t="s">
+        <v>390</v>
+      </c>
+      <c r="K21" s="30" t="s">
         <v>391</v>
-      </c>
-      <c r="K21" s="30" t="s">
-        <v>392</v>
       </c>
       <c r="L21" s="99"/>
       <c r="M21" s="99"/>
@@ -11294,7 +11298,7 @@
       <c r="O21" s="88"/>
       <c r="P21" s="91"/>
     </row>
-    <row r="22" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" ht="14.4" customHeight="1">
       <c r="A22" s="7"/>
       <c r="B22" s="110"/>
       <c r="C22" s="101"/>
@@ -11307,10 +11311,10 @@
         <v>5</v>
       </c>
       <c r="J22" s="14" t="s">
+        <v>392</v>
+      </c>
+      <c r="K22" s="14" t="s">
         <v>393</v>
-      </c>
-      <c r="K22" s="14" t="s">
-        <v>394</v>
       </c>
       <c r="L22" s="99"/>
       <c r="M22" s="99"/>
@@ -11318,7 +11322,7 @@
       <c r="O22" s="88"/>
       <c r="P22" s="91"/>
     </row>
-    <row r="23" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" ht="14.4" customHeight="1">
       <c r="A23" s="7"/>
       <c r="B23" s="110"/>
       <c r="C23" s="101"/>
@@ -11331,7 +11335,7 @@
         <v>6</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="K23" s="14"/>
       <c r="L23" s="99"/>
@@ -11340,7 +11344,7 @@
       <c r="O23" s="88"/>
       <c r="P23" s="91"/>
     </row>
-    <row r="24" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" ht="14.4" customHeight="1">
       <c r="A24" s="7"/>
       <c r="B24" s="110"/>
       <c r="C24" s="101"/>
@@ -11353,7 +11357,7 @@
         <v>7</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="K24" s="14"/>
       <c r="L24" s="99"/>
@@ -11362,7 +11366,7 @@
       <c r="O24" s="88"/>
       <c r="P24" s="91"/>
     </row>
-    <row r="25" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" ht="14.4" customHeight="1">
       <c r="A25" s="7"/>
       <c r="B25" s="110"/>
       <c r="C25" s="101"/>
@@ -11375,7 +11379,7 @@
         <v>8</v>
       </c>
       <c r="J25" s="14" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="K25" s="14">
         <v>325458998</v>
@@ -11386,7 +11390,7 @@
       <c r="O25" s="88"/>
       <c r="P25" s="91"/>
     </row>
-    <row r="26" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" ht="14.4" customHeight="1">
       <c r="A26" s="7"/>
       <c r="B26" s="110"/>
       <c r="C26" s="101"/>
@@ -11399,7 +11403,7 @@
         <v>9</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="K26" s="14"/>
       <c r="L26" s="99"/>
@@ -11408,7 +11412,7 @@
       <c r="O26" s="88"/>
       <c r="P26" s="91"/>
     </row>
-    <row r="27" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" ht="14.4" customHeight="1">
       <c r="A27" s="7"/>
       <c r="B27" s="110"/>
       <c r="C27" s="101"/>
@@ -11432,7 +11436,7 @@
       <c r="O27" s="88"/>
       <c r="P27" s="91"/>
     </row>
-    <row r="28" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" ht="14.4" customHeight="1">
       <c r="A28" s="7"/>
       <c r="B28" s="110"/>
       <c r="C28" s="101"/>
@@ -11456,7 +11460,7 @@
       <c r="O28" s="88"/>
       <c r="P28" s="91"/>
     </row>
-    <row r="29" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" ht="14.4" customHeight="1">
       <c r="A29" s="7"/>
       <c r="B29" s="110"/>
       <c r="C29" s="101"/>
@@ -11469,7 +11473,7 @@
         <v>12</v>
       </c>
       <c r="J29" s="31" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="K29" s="31">
         <v>123</v>
@@ -11480,7 +11484,7 @@
       <c r="O29" s="132"/>
       <c r="P29" s="123"/>
     </row>
-    <row r="30" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" ht="14.4" customHeight="1">
       <c r="A30" s="7"/>
       <c r="B30" s="111"/>
       <c r="C30" s="102"/>
@@ -11493,7 +11497,7 @@
         <v>13</v>
       </c>
       <c r="J30" s="15" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="K30" s="15"/>
       <c r="L30" s="100"/>
@@ -11502,7 +11506,7 @@
       <c r="O30" s="89"/>
       <c r="P30" s="92"/>
     </row>
-    <row r="31" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" ht="14.4" customHeight="1">
       <c r="A31" s="7"/>
       <c r="B31" s="110">
         <v>3</v>
@@ -11520,10 +11524,10 @@
         <v>381</v>
       </c>
       <c r="G31" s="101" t="s">
+        <v>402</v>
+      </c>
+      <c r="H31" s="112" t="s">
         <v>403</v>
-      </c>
-      <c r="H31" s="112" t="s">
-        <v>404</v>
       </c>
       <c r="I31" s="3">
         <v>1</v>
@@ -11533,10 +11537,10 @@
       </c>
       <c r="K31" s="16"/>
       <c r="L31" s="105" t="s">
-        <v>386</v>
+        <v>404</v>
       </c>
       <c r="M31" s="105" t="s">
-        <v>386</v>
+        <v>404</v>
       </c>
       <c r="N31" s="86" t="s">
         <v>150</v>
@@ -11544,7 +11548,7 @@
       <c r="O31" s="106"/>
       <c r="P31" s="107"/>
     </row>
-    <row r="32" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" ht="14.4" customHeight="1">
       <c r="A32" s="7"/>
       <c r="B32" s="110"/>
       <c r="C32" s="101"/>
@@ -11557,7 +11561,7 @@
         <v>2</v>
       </c>
       <c r="J32" s="14" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="K32" s="14" t="s">
         <v>269</v>
@@ -11568,7 +11572,7 @@
       <c r="O32" s="88"/>
       <c r="P32" s="91"/>
     </row>
-    <row r="33" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" ht="14.4" customHeight="1">
       <c r="A33" s="7"/>
       <c r="B33" s="110"/>
       <c r="C33" s="101"/>
@@ -11581,10 +11585,10 @@
         <v>3</v>
       </c>
       <c r="J33" s="14" t="s">
+        <v>388</v>
+      </c>
+      <c r="K33" s="14" t="s">
         <v>389</v>
-      </c>
-      <c r="K33" s="14" t="s">
-        <v>390</v>
       </c>
       <c r="L33" s="99"/>
       <c r="M33" s="99"/>
@@ -11592,7 +11596,7 @@
       <c r="O33" s="88"/>
       <c r="P33" s="91"/>
     </row>
-    <row r="34" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" ht="14.4" customHeight="1">
       <c r="A34" s="7"/>
       <c r="B34" s="110"/>
       <c r="C34" s="101"/>
@@ -11605,10 +11609,10 @@
         <v>4</v>
       </c>
       <c r="J34" s="14" t="s">
+        <v>390</v>
+      </c>
+      <c r="K34" s="30" t="s">
         <v>391</v>
-      </c>
-      <c r="K34" s="30" t="s">
-        <v>392</v>
       </c>
       <c r="L34" s="99"/>
       <c r="M34" s="99"/>
@@ -11616,7 +11620,7 @@
       <c r="O34" s="88"/>
       <c r="P34" s="91"/>
     </row>
-    <row r="35" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" ht="14.4" customHeight="1">
       <c r="A35" s="7"/>
       <c r="B35" s="110"/>
       <c r="C35" s="101"/>
@@ -11629,10 +11633,10 @@
         <v>5</v>
       </c>
       <c r="J35" s="14" t="s">
+        <v>392</v>
+      </c>
+      <c r="K35" s="14" t="s">
         <v>393</v>
-      </c>
-      <c r="K35" s="14" t="s">
-        <v>394</v>
       </c>
       <c r="L35" s="99"/>
       <c r="M35" s="99"/>
@@ -11640,7 +11644,7 @@
       <c r="O35" s="88"/>
       <c r="P35" s="91"/>
     </row>
-    <row r="36" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" ht="14.4" customHeight="1">
       <c r="A36" s="7"/>
       <c r="B36" s="110"/>
       <c r="C36" s="101"/>
@@ -11653,10 +11657,10 @@
         <v>6</v>
       </c>
       <c r="J36" s="14" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="K36" s="14" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="L36" s="99"/>
       <c r="M36" s="99"/>
@@ -11664,7 +11668,7 @@
       <c r="O36" s="88"/>
       <c r="P36" s="91"/>
     </row>
-    <row r="37" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" ht="14.4" customHeight="1">
       <c r="A37" s="7"/>
       <c r="B37" s="110"/>
       <c r="C37" s="101"/>
@@ -11677,7 +11681,7 @@
         <v>7</v>
       </c>
       <c r="J37" s="14" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="K37" s="14">
         <v>123456</v>
@@ -11688,7 +11692,7 @@
       <c r="O37" s="88"/>
       <c r="P37" s="91"/>
     </row>
-    <row r="38" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" ht="14.4" customHeight="1">
       <c r="A38" s="7"/>
       <c r="B38" s="110"/>
       <c r="C38" s="101"/>
@@ -11701,7 +11705,7 @@
         <v>8</v>
       </c>
       <c r="J38" s="14" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="K38" s="14">
         <v>325458998</v>
@@ -11712,7 +11716,7 @@
       <c r="O38" s="88"/>
       <c r="P38" s="91"/>
     </row>
-    <row r="39" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" ht="14.4" customHeight="1">
       <c r="A39" s="7"/>
       <c r="B39" s="110"/>
       <c r="C39" s="101"/>
@@ -11725,7 +11729,7 @@
         <v>9</v>
       </c>
       <c r="J39" s="14" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="K39" s="14">
         <v>12312561558</v>
@@ -11736,7 +11740,7 @@
       <c r="O39" s="88"/>
       <c r="P39" s="91"/>
     </row>
-    <row r="40" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" ht="14.4" customHeight="1">
       <c r="A40" s="7"/>
       <c r="B40" s="110"/>
       <c r="C40" s="101"/>
@@ -11760,7 +11764,7 @@
       <c r="O40" s="88"/>
       <c r="P40" s="91"/>
     </row>
-    <row r="41" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" ht="14.4" customHeight="1">
       <c r="A41" s="7"/>
       <c r="B41" s="110"/>
       <c r="C41" s="101"/>
@@ -11784,7 +11788,7 @@
       <c r="O41" s="88"/>
       <c r="P41" s="91"/>
     </row>
-    <row r="42" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" ht="14.4" customHeight="1">
       <c r="A42" s="7"/>
       <c r="B42" s="110"/>
       <c r="C42" s="101"/>
@@ -11797,7 +11801,7 @@
         <v>12</v>
       </c>
       <c r="J42" s="31" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="K42" s="31">
         <v>123</v>
@@ -11808,7 +11812,7 @@
       <c r="O42" s="88"/>
       <c r="P42" s="91"/>
     </row>
-    <row r="43" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" ht="14.4" customHeight="1">
       <c r="A43" s="7"/>
       <c r="B43" s="111"/>
       <c r="C43" s="102"/>
@@ -11821,7 +11825,7 @@
         <v>13</v>
       </c>
       <c r="J43" s="15" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="K43" s="15"/>
       <c r="L43" s="100"/>
@@ -11830,7 +11834,7 @@
       <c r="O43" s="89"/>
       <c r="P43" s="92"/>
     </row>
-    <row r="44" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" ht="14.4" customHeight="1">
       <c r="A44" s="7"/>
       <c r="B44" s="110">
         <v>4</v>
@@ -11866,7 +11870,7 @@
       <c r="O44" s="88"/>
       <c r="P44" s="90"/>
     </row>
-    <row r="45" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" ht="14.4" customHeight="1">
       <c r="A45" s="7"/>
       <c r="B45" s="110"/>
       <c r="C45" s="101"/>
@@ -11879,7 +11883,7 @@
         <v>2</v>
       </c>
       <c r="J45" s="14" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="K45" s="14" t="s">
         <v>269</v>
@@ -11890,7 +11894,7 @@
       <c r="O45" s="88"/>
       <c r="P45" s="91"/>
     </row>
-    <row r="46" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" ht="14.4" customHeight="1">
       <c r="A46" s="7"/>
       <c r="B46" s="110"/>
       <c r="C46" s="101"/>
@@ -11903,10 +11907,10 @@
         <v>3</v>
       </c>
       <c r="J46" s="14" t="s">
+        <v>388</v>
+      </c>
+      <c r="K46" s="14" t="s">
         <v>389</v>
-      </c>
-      <c r="K46" s="14" t="s">
-        <v>390</v>
       </c>
       <c r="L46" s="99"/>
       <c r="M46" s="99"/>
@@ -11914,7 +11918,7 @@
       <c r="O46" s="88"/>
       <c r="P46" s="91"/>
     </row>
-    <row r="47" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" ht="14.4" customHeight="1">
       <c r="A47" s="7"/>
       <c r="B47" s="110"/>
       <c r="C47" s="101"/>
@@ -11927,10 +11931,10 @@
         <v>4</v>
       </c>
       <c r="J47" s="14" t="s">
+        <v>390</v>
+      </c>
+      <c r="K47" s="30" t="s">
         <v>391</v>
-      </c>
-      <c r="K47" s="30" t="s">
-        <v>392</v>
       </c>
       <c r="L47" s="99"/>
       <c r="M47" s="99"/>
@@ -11938,7 +11942,7 @@
       <c r="O47" s="88"/>
       <c r="P47" s="91"/>
     </row>
-    <row r="48" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" ht="14.4" customHeight="1">
       <c r="A48" s="7"/>
       <c r="B48" s="110"/>
       <c r="C48" s="101"/>
@@ -11951,10 +11955,10 @@
         <v>5</v>
       </c>
       <c r="J48" s="14" t="s">
+        <v>392</v>
+      </c>
+      <c r="K48" s="14" t="s">
         <v>393</v>
-      </c>
-      <c r="K48" s="14" t="s">
-        <v>394</v>
       </c>
       <c r="L48" s="99"/>
       <c r="M48" s="99"/>
@@ -11962,7 +11966,7 @@
       <c r="O48" s="88"/>
       <c r="P48" s="91"/>
     </row>
-    <row r="49" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" ht="14.4" customHeight="1">
       <c r="A49" s="7"/>
       <c r="B49" s="110"/>
       <c r="C49" s="101"/>
@@ -11975,10 +11979,10 @@
         <v>6</v>
       </c>
       <c r="J49" s="14" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="K49" s="14" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="L49" s="99"/>
       <c r="M49" s="99"/>
@@ -11986,7 +11990,7 @@
       <c r="O49" s="88"/>
       <c r="P49" s="91"/>
     </row>
-    <row r="50" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" ht="14.4" customHeight="1">
       <c r="A50" s="7"/>
       <c r="B50" s="110"/>
       <c r="C50" s="101"/>
@@ -11999,7 +12003,7 @@
         <v>7</v>
       </c>
       <c r="J50" s="14" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="K50" s="14">
         <v>123456</v>
@@ -12010,7 +12014,7 @@
       <c r="O50" s="88"/>
       <c r="P50" s="91"/>
     </row>
-    <row r="51" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" ht="14.4" customHeight="1">
       <c r="A51" s="7"/>
       <c r="B51" s="110"/>
       <c r="C51" s="101"/>
@@ -12023,7 +12027,7 @@
         <v>8</v>
       </c>
       <c r="J51" s="14" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="K51" s="14">
         <v>325458998</v>
@@ -12034,7 +12038,7 @@
       <c r="O51" s="88"/>
       <c r="P51" s="91"/>
     </row>
-    <row r="52" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" ht="14.4" customHeight="1">
       <c r="A52" s="7"/>
       <c r="B52" s="110"/>
       <c r="C52" s="101"/>
@@ -12047,7 +12051,7 @@
         <v>9</v>
       </c>
       <c r="J52" s="14" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="K52" s="14">
         <v>12312561558</v>
@@ -12058,7 +12062,7 @@
       <c r="O52" s="88"/>
       <c r="P52" s="91"/>
     </row>
-    <row r="53" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" ht="14.4" customHeight="1">
       <c r="A53" s="7"/>
       <c r="B53" s="110"/>
       <c r="C53" s="101"/>
@@ -12082,7 +12086,7 @@
       <c r="O53" s="88"/>
       <c r="P53" s="91"/>
     </row>
-    <row r="54" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" ht="14.4" customHeight="1">
       <c r="A54" s="7"/>
       <c r="B54" s="110"/>
       <c r="C54" s="101"/>
@@ -12106,7 +12110,7 @@
       <c r="O54" s="88"/>
       <c r="P54" s="91"/>
     </row>
-    <row r="55" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" ht="14.4" customHeight="1">
       <c r="A55" s="7"/>
       <c r="B55" s="110"/>
       <c r="C55" s="101"/>
@@ -12119,7 +12123,7 @@
         <v>12</v>
       </c>
       <c r="J55" s="31" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="K55" s="31">
         <v>1</v>
@@ -12130,7 +12134,7 @@
       <c r="O55" s="132"/>
       <c r="P55" s="123"/>
     </row>
-    <row r="56" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" ht="14.4" customHeight="1">
       <c r="A56" s="7"/>
       <c r="B56" s="111"/>
       <c r="C56" s="102"/>
@@ -12143,7 +12147,7 @@
         <v>13</v>
       </c>
       <c r="J56" s="15" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="K56" s="15"/>
       <c r="L56" s="100"/>
@@ -12152,7 +12156,7 @@
       <c r="O56" s="89"/>
       <c r="P56" s="92"/>
     </row>
-    <row r="57" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" ht="14.4" customHeight="1">
       <c r="A57" s="7"/>
       <c r="B57" s="110">
         <v>5</v>
@@ -12192,7 +12196,7 @@
       <c r="O57" s="106"/>
       <c r="P57" s="107"/>
     </row>
-    <row r="58" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" ht="14.4" customHeight="1">
       <c r="A58" s="7"/>
       <c r="B58" s="110"/>
       <c r="C58" s="101"/>
@@ -12205,7 +12209,7 @@
         <v>2</v>
       </c>
       <c r="J58" s="14" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="K58" s="14" t="s">
         <v>269</v>
@@ -12216,7 +12220,7 @@
       <c r="O58" s="88"/>
       <c r="P58" s="91"/>
     </row>
-    <row r="59" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" ht="14.4" customHeight="1">
       <c r="A59" s="7"/>
       <c r="B59" s="110"/>
       <c r="C59" s="101"/>
@@ -12229,10 +12233,10 @@
         <v>3</v>
       </c>
       <c r="J59" s="14" t="s">
+        <v>388</v>
+      </c>
+      <c r="K59" s="14" t="s">
         <v>389</v>
-      </c>
-      <c r="K59" s="14" t="s">
-        <v>390</v>
       </c>
       <c r="L59" s="99"/>
       <c r="M59" s="99"/>
@@ -12240,7 +12244,7 @@
       <c r="O59" s="88"/>
       <c r="P59" s="91"/>
     </row>
-    <row r="60" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" ht="14.4" customHeight="1">
       <c r="A60" s="7"/>
       <c r="B60" s="110"/>
       <c r="C60" s="101"/>
@@ -12253,10 +12257,10 @@
         <v>4</v>
       </c>
       <c r="J60" s="14" t="s">
+        <v>390</v>
+      </c>
+      <c r="K60" s="30" t="s">
         <v>391</v>
-      </c>
-      <c r="K60" s="30" t="s">
-        <v>392</v>
       </c>
       <c r="L60" s="99"/>
       <c r="M60" s="99"/>
@@ -12264,7 +12268,7 @@
       <c r="O60" s="88"/>
       <c r="P60" s="91"/>
     </row>
-    <row r="61" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" ht="14.4" customHeight="1">
       <c r="A61" s="7"/>
       <c r="B61" s="110"/>
       <c r="C61" s="101"/>
@@ -12277,10 +12281,10 @@
         <v>5</v>
       </c>
       <c r="J61" s="14" t="s">
+        <v>392</v>
+      </c>
+      <c r="K61" s="14" t="s">
         <v>393</v>
-      </c>
-      <c r="K61" s="14" t="s">
-        <v>394</v>
       </c>
       <c r="L61" s="99"/>
       <c r="M61" s="99"/>
@@ -12288,7 +12292,7 @@
       <c r="O61" s="88"/>
       <c r="P61" s="91"/>
     </row>
-    <row r="62" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" ht="14.4" customHeight="1">
       <c r="A62" s="7"/>
       <c r="B62" s="110"/>
       <c r="C62" s="101"/>
@@ -12301,10 +12305,10 @@
         <v>6</v>
       </c>
       <c r="J62" s="14" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="K62" s="14" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="L62" s="99"/>
       <c r="M62" s="99"/>
@@ -12312,7 +12316,7 @@
       <c r="O62" s="88"/>
       <c r="P62" s="91"/>
     </row>
-    <row r="63" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" ht="14.4" customHeight="1">
       <c r="A63" s="7"/>
       <c r="B63" s="110"/>
       <c r="C63" s="101"/>
@@ -12325,7 +12329,7 @@
         <v>7</v>
       </c>
       <c r="J63" s="14" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="K63" s="14">
         <v>16525152772.6667</v>
@@ -12336,7 +12340,7 @@
       <c r="O63" s="88"/>
       <c r="P63" s="91"/>
     </row>
-    <row r="64" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" ht="14.4" customHeight="1">
       <c r="A64" s="7"/>
       <c r="B64" s="110"/>
       <c r="C64" s="101"/>
@@ -12349,10 +12353,10 @@
         <v>8</v>
       </c>
       <c r="J64" s="14" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="K64" s="14">
-        <v>22681371823.666698</v>
+        <v>22681371823.6667</v>
       </c>
       <c r="L64" s="99"/>
       <c r="M64" s="99"/>
@@ -12360,7 +12364,7 @@
       <c r="O64" s="88"/>
       <c r="P64" s="91"/>
     </row>
-    <row r="65" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" ht="14.4" customHeight="1">
       <c r="A65" s="7"/>
       <c r="B65" s="110"/>
       <c r="C65" s="101"/>
@@ -12373,10 +12377,10 @@
         <v>9</v>
       </c>
       <c r="J65" s="14" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="K65" s="14">
-        <v>28837590874.666698</v>
+        <v>28837590874.6667</v>
       </c>
       <c r="L65" s="99"/>
       <c r="M65" s="99"/>
@@ -12384,7 +12388,7 @@
       <c r="O65" s="88"/>
       <c r="P65" s="91"/>
     </row>
-    <row r="66" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" ht="14.4" customHeight="1">
       <c r="A66" s="7"/>
       <c r="B66" s="110"/>
       <c r="C66" s="101"/>
@@ -12408,7 +12412,7 @@
       <c r="O66" s="88"/>
       <c r="P66" s="91"/>
     </row>
-    <row r="67" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" ht="14.4" customHeight="1">
       <c r="A67" s="7"/>
       <c r="B67" s="110"/>
       <c r="C67" s="101"/>
@@ -12432,7 +12436,7 @@
       <c r="O67" s="88"/>
       <c r="P67" s="91"/>
     </row>
-    <row r="68" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" ht="14.4" customHeight="1">
       <c r="A68" s="7"/>
       <c r="B68" s="110"/>
       <c r="C68" s="101"/>
@@ -12445,7 +12449,7 @@
         <v>12</v>
       </c>
       <c r="J68" s="31" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="K68" s="31">
         <v>1</v>
@@ -12456,7 +12460,7 @@
       <c r="O68" s="132"/>
       <c r="P68" s="123"/>
     </row>
-    <row r="69" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" ht="14.4" customHeight="1">
       <c r="A69" s="7"/>
       <c r="B69" s="111"/>
       <c r="C69" s="102"/>
@@ -12469,7 +12473,7 @@
         <v>13</v>
       </c>
       <c r="J69" s="15" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="K69" s="15"/>
       <c r="L69" s="100"/>
@@ -12478,7 +12482,7 @@
       <c r="O69" s="89"/>
       <c r="P69" s="92"/>
     </row>
-    <row r="70" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" ht="14.4" customHeight="1">
       <c r="A70" s="7"/>
       <c r="B70" s="110">
         <v>6</v>
@@ -12522,7 +12526,7 @@
       </c>
       <c r="P70" s="90"/>
     </row>
-    <row r="71" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" ht="14.4" customHeight="1">
       <c r="A71" s="7"/>
       <c r="B71" s="110"/>
       <c r="C71" s="101"/>
@@ -12546,7 +12550,7 @@
       <c r="O71" s="88"/>
       <c r="P71" s="91"/>
     </row>
-    <row r="72" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" ht="14.4" customHeight="1">
       <c r="A72" s="7"/>
       <c r="B72" s="110"/>
       <c r="C72" s="101"/>
@@ -12570,7 +12574,7 @@
       <c r="O72" s="88"/>
       <c r="P72" s="91"/>
     </row>
-    <row r="73" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" ht="14.4" customHeight="1">
       <c r="A73" s="7"/>
       <c r="B73" s="110"/>
       <c r="C73" s="101"/>
@@ -12583,7 +12587,7 @@
         <v>4</v>
       </c>
       <c r="J73" s="14" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="K73" s="14" t="s">
         <v>422</v>
@@ -12594,7 +12598,7 @@
       <c r="O73" s="88"/>
       <c r="P73" s="91"/>
     </row>
-    <row r="74" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" ht="14.4" customHeight="1">
       <c r="A74" s="7"/>
       <c r="B74" s="110"/>
       <c r="C74" s="101"/>
@@ -12607,7 +12611,7 @@
         <v>5</v>
       </c>
       <c r="J74" s="14" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="K74" s="14" t="s">
         <v>423</v>
@@ -12618,7 +12622,7 @@
       <c r="O74" s="88"/>
       <c r="P74" s="91"/>
     </row>
-    <row r="75" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" ht="14.4" customHeight="1">
       <c r="A75" s="7"/>
       <c r="B75" s="110"/>
       <c r="C75" s="101"/>
@@ -12631,7 +12635,7 @@
         <v>6</v>
       </c>
       <c r="J75" s="14" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="K75" s="14">
         <v>90001</v>
@@ -12642,7 +12646,7 @@
       <c r="O75" s="88"/>
       <c r="P75" s="91"/>
     </row>
-    <row r="76" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" ht="14.4" customHeight="1">
       <c r="A76" s="7"/>
       <c r="B76" s="110"/>
       <c r="C76" s="101"/>
@@ -12655,7 +12659,7 @@
         <v>7</v>
       </c>
       <c r="J76" s="14" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="K76" s="14">
         <v>2135557890</v>
@@ -12666,7 +12670,7 @@
       <c r="O76" s="88"/>
       <c r="P76" s="91"/>
     </row>
-    <row r="77" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" ht="14.4" customHeight="1">
       <c r="A77" s="7"/>
       <c r="B77" s="110"/>
       <c r="C77" s="101"/>
@@ -12690,7 +12694,7 @@
       <c r="O77" s="88"/>
       <c r="P77" s="91"/>
     </row>
-    <row r="78" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" ht="14.4" customHeight="1">
       <c r="A78" s="7"/>
       <c r="B78" s="110"/>
       <c r="C78" s="101"/>
@@ -12714,7 +12718,7 @@
       <c r="O78" s="88"/>
       <c r="P78" s="91"/>
     </row>
-    <row r="79" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" ht="14.4" customHeight="1">
       <c r="A79" s="7"/>
       <c r="B79" s="110"/>
       <c r="C79" s="101"/>
@@ -12738,7 +12742,7 @@
       <c r="O79" s="132"/>
       <c r="P79" s="123"/>
     </row>
-    <row r="80" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" ht="14.4" customHeight="1">
       <c r="A80" s="7"/>
       <c r="B80" s="111"/>
       <c r="C80" s="102"/>
@@ -12760,7 +12764,7 @@
       <c r="O80" s="89"/>
       <c r="P80" s="92"/>
     </row>
-    <row r="81" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" ht="14.4" customHeight="1">
       <c r="A81" s="7"/>
       <c r="B81" s="110">
         <v>7</v>
@@ -12798,7 +12802,7 @@
       <c r="O81" s="106"/>
       <c r="P81" s="107"/>
     </row>
-    <row r="82" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" ht="14.4" customHeight="1">
       <c r="A82" s="7"/>
       <c r="B82" s="110"/>
       <c r="C82" s="101"/>
@@ -12822,7 +12826,7 @@
       <c r="O82" s="88"/>
       <c r="P82" s="91"/>
     </row>
-    <row r="83" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" ht="14.4" customHeight="1">
       <c r="A83" s="7"/>
       <c r="B83" s="110"/>
       <c r="C83" s="101"/>
@@ -12846,7 +12850,7 @@
       <c r="O83" s="88"/>
       <c r="P83" s="91"/>
     </row>
-    <row r="84" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" ht="14.4" customHeight="1">
       <c r="A84" s="7"/>
       <c r="B84" s="110"/>
       <c r="C84" s="101"/>
@@ -12859,7 +12863,7 @@
         <v>4</v>
       </c>
       <c r="J84" s="14" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="K84" s="14" t="s">
         <v>422</v>
@@ -12870,7 +12874,7 @@
       <c r="O84" s="88"/>
       <c r="P84" s="91"/>
     </row>
-    <row r="85" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" ht="14.4" customHeight="1">
       <c r="A85" s="7"/>
       <c r="B85" s="110"/>
       <c r="C85" s="101"/>
@@ -12883,7 +12887,7 @@
         <v>5</v>
       </c>
       <c r="J85" s="14" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="K85" s="14" t="s">
         <v>423</v>
@@ -12894,7 +12898,7 @@
       <c r="O85" s="88"/>
       <c r="P85" s="91"/>
     </row>
-    <row r="86" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" ht="14.4" customHeight="1">
       <c r="A86" s="7"/>
       <c r="B86" s="110"/>
       <c r="C86" s="101"/>
@@ -12907,7 +12911,7 @@
         <v>6</v>
       </c>
       <c r="J86" s="14" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="K86" s="14">
         <v>90001</v>
@@ -12918,7 +12922,7 @@
       <c r="O86" s="88"/>
       <c r="P86" s="91"/>
     </row>
-    <row r="87" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" ht="14.4" customHeight="1">
       <c r="A87" s="7"/>
       <c r="B87" s="110"/>
       <c r="C87" s="101"/>
@@ -12931,7 +12935,7 @@
         <v>7</v>
       </c>
       <c r="J87" s="14" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="K87" s="14">
         <v>2135557890</v>
@@ -12942,7 +12946,7 @@
       <c r="O87" s="88"/>
       <c r="P87" s="91"/>
     </row>
-    <row r="88" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" ht="14.4" customHeight="1">
       <c r="A88" s="7"/>
       <c r="B88" s="110"/>
       <c r="C88" s="101"/>
@@ -12966,7 +12970,7 @@
       <c r="O88" s="88"/>
       <c r="P88" s="91"/>
     </row>
-    <row r="89" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" ht="14.4" customHeight="1">
       <c r="A89" s="7"/>
       <c r="B89" s="110"/>
       <c r="C89" s="101"/>
@@ -12990,7 +12994,7 @@
       <c r="O89" s="88"/>
       <c r="P89" s="91"/>
     </row>
-    <row r="90" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" ht="14.4" customHeight="1">
       <c r="A90" s="7"/>
       <c r="B90" s="110"/>
       <c r="C90" s="101"/>
@@ -13014,7 +13018,7 @@
       <c r="O90" s="132"/>
       <c r="P90" s="123"/>
     </row>
-    <row r="91" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" ht="14.4" customHeight="1">
       <c r="A91" s="7"/>
       <c r="B91" s="111"/>
       <c r="C91" s="102"/>
@@ -13036,7 +13040,7 @@
       <c r="O91" s="89"/>
       <c r="P91" s="92"/>
     </row>
-    <row r="92" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" ht="14.4" customHeight="1">
       <c r="A92" s="7"/>
       <c r="B92" s="110">
         <v>8</v>
@@ -13080,7 +13084,7 @@
       </c>
       <c r="P92" s="90"/>
     </row>
-    <row r="93" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" ht="14.4" customHeight="1">
       <c r="A93" s="7"/>
       <c r="B93" s="110"/>
       <c r="C93" s="101"/>
@@ -13104,7 +13108,7 @@
       <c r="O93" s="88"/>
       <c r="P93" s="91"/>
     </row>
-    <row r="94" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" ht="14.4" customHeight="1">
       <c r="A94" s="7"/>
       <c r="B94" s="110"/>
       <c r="C94" s="101"/>
@@ -13128,7 +13132,7 @@
       <c r="O94" s="88"/>
       <c r="P94" s="91"/>
     </row>
-    <row r="95" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" ht="14.4" customHeight="1">
       <c r="A95" s="7"/>
       <c r="B95" s="110"/>
       <c r="C95" s="101"/>
@@ -13141,7 +13145,7 @@
         <v>4</v>
       </c>
       <c r="J95" s="14" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="K95" s="14" t="s">
         <v>422</v>
@@ -13152,7 +13156,7 @@
       <c r="O95" s="88"/>
       <c r="P95" s="91"/>
     </row>
-    <row r="96" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" ht="14.4" customHeight="1">
       <c r="A96" s="7"/>
       <c r="B96" s="110"/>
       <c r="C96" s="101"/>
@@ -13165,7 +13169,7 @@
         <v>5</v>
       </c>
       <c r="J96" s="14" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="K96" s="14" t="s">
         <v>423</v>
@@ -13176,7 +13180,7 @@
       <c r="O96" s="88"/>
       <c r="P96" s="91"/>
     </row>
-    <row r="97" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" ht="14.4" customHeight="1">
       <c r="A97" s="7"/>
       <c r="B97" s="110"/>
       <c r="C97" s="101"/>
@@ -13189,7 +13193,7 @@
         <v>6</v>
       </c>
       <c r="J97" s="14" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="K97" s="14">
         <v>90001</v>
@@ -13200,7 +13204,7 @@
       <c r="O97" s="88"/>
       <c r="P97" s="91"/>
     </row>
-    <row r="98" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" ht="14.4" customHeight="1">
       <c r="A98" s="7"/>
       <c r="B98" s="110"/>
       <c r="C98" s="101"/>
@@ -13213,7 +13217,7 @@
         <v>7</v>
       </c>
       <c r="J98" s="14" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="K98" s="14">
         <v>2135557890</v>
@@ -13224,7 +13228,7 @@
       <c r="O98" s="88"/>
       <c r="P98" s="91"/>
     </row>
-    <row r="99" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" ht="14.4" customHeight="1">
       <c r="A99" s="7"/>
       <c r="B99" s="110"/>
       <c r="C99" s="101"/>
@@ -13248,7 +13252,7 @@
       <c r="O99" s="88"/>
       <c r="P99" s="91"/>
     </row>
-    <row r="100" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" ht="14.4" customHeight="1">
       <c r="A100" s="7"/>
       <c r="B100" s="110"/>
       <c r="C100" s="101"/>
@@ -13272,7 +13276,7 @@
       <c r="O100" s="88"/>
       <c r="P100" s="91"/>
     </row>
-    <row r="101" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" ht="14.4" customHeight="1">
       <c r="A101" s="7"/>
       <c r="B101" s="110"/>
       <c r="C101" s="101"/>
@@ -13296,7 +13300,7 @@
       <c r="O101" s="132"/>
       <c r="P101" s="123"/>
     </row>
-    <row r="102" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" ht="14.4" customHeight="1">
       <c r="A102" s="7"/>
       <c r="B102" s="111"/>
       <c r="C102" s="102"/>
@@ -13318,7 +13322,7 @@
       <c r="O102" s="89"/>
       <c r="P102" s="92"/>
     </row>
-    <row r="103" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" ht="14.4" customHeight="1">
       <c r="A103" s="7"/>
       <c r="B103" s="110">
         <v>9</v>
@@ -13356,7 +13360,7 @@
       <c r="O103" s="106"/>
       <c r="P103" s="107"/>
     </row>
-    <row r="104" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" ht="14.4" customHeight="1">
       <c r="A104" s="7"/>
       <c r="B104" s="110"/>
       <c r="C104" s="101"/>
@@ -13380,7 +13384,7 @@
       <c r="O104" s="88"/>
       <c r="P104" s="91"/>
     </row>
-    <row r="105" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" ht="14.4" customHeight="1">
       <c r="A105" s="7"/>
       <c r="B105" s="110"/>
       <c r="C105" s="101"/>
@@ -13404,7 +13408,7 @@
       <c r="O105" s="88"/>
       <c r="P105" s="91"/>
     </row>
-    <row r="106" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" ht="14.4" customHeight="1">
       <c r="A106" s="7"/>
       <c r="B106" s="110"/>
       <c r="C106" s="101"/>
@@ -13417,7 +13421,7 @@
         <v>4</v>
       </c>
       <c r="J106" s="14" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="K106" s="14" t="s">
         <v>422</v>
@@ -13428,7 +13432,7 @@
       <c r="O106" s="88"/>
       <c r="P106" s="91"/>
     </row>
-    <row r="107" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" ht="14.4" customHeight="1">
       <c r="A107" s="7"/>
       <c r="B107" s="110"/>
       <c r="C107" s="101"/>
@@ -13441,7 +13445,7 @@
         <v>5</v>
       </c>
       <c r="J107" s="14" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="K107" s="14" t="s">
         <v>423</v>
@@ -13452,7 +13456,7 @@
       <c r="O107" s="88"/>
       <c r="P107" s="91"/>
     </row>
-    <row r="108" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" ht="14.4" customHeight="1">
       <c r="A108" s="7"/>
       <c r="B108" s="110"/>
       <c r="C108" s="101"/>
@@ -13465,7 +13469,7 @@
         <v>6</v>
       </c>
       <c r="J108" s="14" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="K108" s="14">
         <v>477766155</v>
@@ -13476,7 +13480,7 @@
       <c r="O108" s="88"/>
       <c r="P108" s="91"/>
     </row>
-    <row r="109" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" ht="14.4" customHeight="1">
       <c r="A109" s="7"/>
       <c r="B109" s="110"/>
       <c r="C109" s="101"/>
@@ -13489,7 +13493,7 @@
         <v>7</v>
       </c>
       <c r="J109" s="14" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="K109" s="14">
         <v>362957778</v>
@@ -13500,7 +13504,7 @@
       <c r="O109" s="88"/>
       <c r="P109" s="91"/>
     </row>
-    <row r="110" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" ht="14.4" customHeight="1">
       <c r="A110" s="7"/>
       <c r="B110" s="110"/>
       <c r="C110" s="101"/>
@@ -13524,7 +13528,7 @@
       <c r="O110" s="88"/>
       <c r="P110" s="91"/>
     </row>
-    <row r="111" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" ht="14.4" customHeight="1">
       <c r="A111" s="7"/>
       <c r="B111" s="110"/>
       <c r="C111" s="101"/>
@@ -13548,7 +13552,7 @@
       <c r="O111" s="88"/>
       <c r="P111" s="91"/>
     </row>
-    <row r="112" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" ht="14.4" customHeight="1">
       <c r="A112" s="7"/>
       <c r="B112" s="110"/>
       <c r="C112" s="101"/>
@@ -13570,7 +13574,7 @@
       <c r="O112" s="132"/>
       <c r="P112" s="123"/>
     </row>
-    <row r="113" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" ht="14.4" customHeight="1">
       <c r="A113" s="7"/>
       <c r="B113" s="111"/>
       <c r="C113" s="102"/>
@@ -13592,7 +13596,7 @@
       <c r="O113" s="89"/>
       <c r="P113" s="92"/>
     </row>
-    <row r="114" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" ht="14.4" customHeight="1">
       <c r="A114" s="7"/>
       <c r="B114" s="110">
         <v>10</v>
@@ -13630,7 +13634,7 @@
       <c r="O114" s="88"/>
       <c r="P114" s="90"/>
     </row>
-    <row r="115" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" ht="14.4" customHeight="1">
       <c r="A115" s="7"/>
       <c r="B115" s="110"/>
       <c r="C115" s="101"/>
@@ -13654,7 +13658,7 @@
       <c r="O115" s="88"/>
       <c r="P115" s="91"/>
     </row>
-    <row r="116" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" ht="14.4" customHeight="1">
       <c r="A116" s="7"/>
       <c r="B116" s="110"/>
       <c r="C116" s="101"/>
@@ -13676,7 +13680,7 @@
       <c r="O116" s="88"/>
       <c r="P116" s="91"/>
     </row>
-    <row r="117" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" ht="14.4" customHeight="1">
       <c r="A117" s="7"/>
       <c r="B117" s="110"/>
       <c r="C117" s="101"/>
@@ -13696,7 +13700,7 @@
       <c r="O117" s="88"/>
       <c r="P117" s="91"/>
     </row>
-    <row r="118" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" ht="14.4" customHeight="1">
       <c r="A118" s="7"/>
       <c r="B118" s="110"/>
       <c r="C118" s="101"/>
@@ -13716,7 +13720,7 @@
       <c r="O118" s="88"/>
       <c r="P118" s="91"/>
     </row>
-    <row r="119" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" ht="14.4" customHeight="1">
       <c r="A119" s="7"/>
       <c r="B119" s="110"/>
       <c r="C119" s="101"/>
@@ -13736,7 +13740,7 @@
       <c r="O119" s="88"/>
       <c r="P119" s="91"/>
     </row>
-    <row r="120" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" ht="14.4" customHeight="1">
       <c r="A120" s="7"/>
       <c r="B120" s="110"/>
       <c r="C120" s="101"/>
@@ -13756,7 +13760,7 @@
       <c r="O120" s="88"/>
       <c r="P120" s="91"/>
     </row>
-    <row r="121" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" ht="14.4" customHeight="1">
       <c r="A121" s="7"/>
       <c r="B121" s="110"/>
       <c r="C121" s="101"/>
@@ -13776,7 +13780,7 @@
       <c r="O121" s="88"/>
       <c r="P121" s="91"/>
     </row>
-    <row r="122" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" ht="14.4" customHeight="1">
       <c r="A122" s="7"/>
       <c r="B122" s="110"/>
       <c r="C122" s="101"/>
@@ -13796,7 +13800,7 @@
       <c r="O122" s="88"/>
       <c r="P122" s="91"/>
     </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="123">
       <c r="A123" s="7"/>
       <c r="B123" s="111"/>
       <c r="C123" s="102"/>
@@ -13816,7 +13820,7 @@
       <c r="O123" s="89"/>
       <c r="P123" s="92"/>
     </row>
-    <row r="124" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" ht="14.4" customHeight="1">
       <c r="A124" s="7"/>
       <c r="B124" s="110">
         <v>11</v>
@@ -13854,7 +13858,7 @@
       <c r="O124" s="106"/>
       <c r="P124" s="107"/>
     </row>
-    <row r="125" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" ht="14.4" customHeight="1">
       <c r="A125" s="7"/>
       <c r="B125" s="110"/>
       <c r="C125" s="101"/>
@@ -13878,7 +13882,7 @@
       <c r="O125" s="88"/>
       <c r="P125" s="91"/>
     </row>
-    <row r="126" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" ht="14.4" customHeight="1">
       <c r="A126" s="7"/>
       <c r="B126" s="110"/>
       <c r="C126" s="101"/>
@@ -13900,7 +13904,7 @@
       <c r="O126" s="88"/>
       <c r="P126" s="91"/>
     </row>
-    <row r="127" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" ht="14.4" customHeight="1">
       <c r="A127" s="7"/>
       <c r="B127" s="110"/>
       <c r="C127" s="101"/>
@@ -13920,7 +13924,7 @@
       <c r="O127" s="88"/>
       <c r="P127" s="91"/>
     </row>
-    <row r="128" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" ht="14.4" customHeight="1">
       <c r="A128" s="7"/>
       <c r="B128" s="110"/>
       <c r="C128" s="101"/>
@@ -13940,7 +13944,7 @@
       <c r="O128" s="88"/>
       <c r="P128" s="91"/>
     </row>
-    <row r="129" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" ht="14.4" customHeight="1">
       <c r="A129" s="7"/>
       <c r="B129" s="110"/>
       <c r="C129" s="101"/>
@@ -13960,7 +13964,7 @@
       <c r="O129" s="88"/>
       <c r="P129" s="91"/>
     </row>
-    <row r="130" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" ht="14.4" customHeight="1">
       <c r="A130" s="7"/>
       <c r="B130" s="110"/>
       <c r="C130" s="101"/>
@@ -13980,7 +13984,7 @@
       <c r="O130" s="88"/>
       <c r="P130" s="91"/>
     </row>
-    <row r="131" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" ht="14.4" customHeight="1">
       <c r="A131" s="7"/>
       <c r="B131" s="110"/>
       <c r="C131" s="101"/>
@@ -14000,7 +14004,7 @@
       <c r="O131" s="88"/>
       <c r="P131" s="91"/>
     </row>
-    <row r="132" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" ht="14.4" customHeight="1">
       <c r="A132" s="7"/>
       <c r="B132" s="110"/>
       <c r="C132" s="101"/>
@@ -14020,7 +14024,7 @@
       <c r="O132" s="88"/>
       <c r="P132" s="91"/>
     </row>
-    <row r="133" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" ht="14.4" customHeight="1">
       <c r="A133" s="7"/>
       <c r="B133" s="111"/>
       <c r="C133" s="102"/>
@@ -14040,7 +14044,7 @@
       <c r="O133" s="89"/>
       <c r="P133" s="92"/>
     </row>
-    <row r="134" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" ht="14.4" customHeight="1">
       <c r="A134" s="7"/>
       <c r="B134" s="110">
         <v>12</v>
@@ -14078,7 +14082,7 @@
       <c r="O134" s="88"/>
       <c r="P134" s="90"/>
     </row>
-    <row r="135" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" ht="14.4" customHeight="1">
       <c r="A135" s="7"/>
       <c r="B135" s="110"/>
       <c r="C135" s="101"/>
@@ -14102,7 +14106,7 @@
       <c r="O135" s="88"/>
       <c r="P135" s="91"/>
     </row>
-    <row r="136" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" ht="14.4" customHeight="1">
       <c r="A136" s="7"/>
       <c r="B136" s="110"/>
       <c r="C136" s="101"/>
@@ -14124,7 +14128,7 @@
       <c r="O136" s="88"/>
       <c r="P136" s="91"/>
     </row>
-    <row r="137" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" ht="14.4" customHeight="1">
       <c r="A137" s="7"/>
       <c r="B137" s="110"/>
       <c r="C137" s="101"/>
@@ -14144,7 +14148,7 @@
       <c r="O137" s="88"/>
       <c r="P137" s="91"/>
     </row>
-    <row r="138" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" ht="14.4" customHeight="1">
       <c r="A138" s="7"/>
       <c r="B138" s="110"/>
       <c r="C138" s="101"/>
@@ -14164,7 +14168,7 @@
       <c r="O138" s="88"/>
       <c r="P138" s="91"/>
     </row>
-    <row r="139" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" ht="14.4" customHeight="1">
       <c r="A139" s="7"/>
       <c r="B139" s="110"/>
       <c r="C139" s="101"/>
@@ -14184,7 +14188,7 @@
       <c r="O139" s="88"/>
       <c r="P139" s="91"/>
     </row>
-    <row r="140" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" ht="14.4" customHeight="1">
       <c r="A140" s="7"/>
       <c r="B140" s="110"/>
       <c r="C140" s="101"/>
@@ -14204,7 +14208,7 @@
       <c r="O140" s="88"/>
       <c r="P140" s="91"/>
     </row>
-    <row r="141" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" ht="14.4" customHeight="1">
       <c r="A141" s="7"/>
       <c r="B141" s="110"/>
       <c r="C141" s="101"/>
@@ -14224,7 +14228,7 @@
       <c r="O141" s="88"/>
       <c r="P141" s="91"/>
     </row>
-    <row r="142" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" ht="14.4" customHeight="1">
       <c r="A142" s="7"/>
       <c r="B142" s="110"/>
       <c r="C142" s="101"/>
@@ -14244,7 +14248,7 @@
       <c r="O142" s="88"/>
       <c r="P142" s="91"/>
     </row>
-    <row r="143" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" ht="14.4" customHeight="1">
       <c r="A143" s="7"/>
       <c r="B143" s="111"/>
       <c r="C143" s="102"/>
@@ -14264,7 +14268,7 @@
       <c r="O143" s="89"/>
       <c r="P143" s="92"/>
     </row>
-    <row r="144" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" ht="14.4" customHeight="1">
       <c r="A144" s="7"/>
       <c r="B144" s="110">
         <v>13</v>
@@ -14302,7 +14306,7 @@
       <c r="O144" s="106"/>
       <c r="P144" s="107"/>
     </row>
-    <row r="145" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" ht="14.4" customHeight="1">
       <c r="A145" s="7"/>
       <c r="B145" s="110"/>
       <c r="C145" s="101"/>
@@ -14326,7 +14330,7 @@
       <c r="O145" s="88"/>
       <c r="P145" s="91"/>
     </row>
-    <row r="146" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" ht="14.4" customHeight="1">
       <c r="A146" s="7"/>
       <c r="B146" s="110"/>
       <c r="C146" s="101"/>
@@ -14348,7 +14352,7 @@
       <c r="O146" s="88"/>
       <c r="P146" s="91"/>
     </row>
-    <row r="147" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" ht="14.4" customHeight="1">
       <c r="A147" s="7"/>
       <c r="B147" s="110"/>
       <c r="C147" s="101"/>
@@ -14368,7 +14372,7 @@
       <c r="O147" s="88"/>
       <c r="P147" s="91"/>
     </row>
-    <row r="148" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" ht="14.4" customHeight="1">
       <c r="A148" s="7"/>
       <c r="B148" s="110"/>
       <c r="C148" s="101"/>
@@ -14388,7 +14392,7 @@
       <c r="O148" s="88"/>
       <c r="P148" s="91"/>
     </row>
-    <row r="149" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" ht="14.4" customHeight="1">
       <c r="A149" s="7"/>
       <c r="B149" s="110"/>
       <c r="C149" s="101"/>
@@ -14408,7 +14412,7 @@
       <c r="O149" s="88"/>
       <c r="P149" s="91"/>
     </row>
-    <row r="150" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" ht="14.4" customHeight="1">
       <c r="A150" s="7"/>
       <c r="B150" s="110"/>
       <c r="C150" s="101"/>
@@ -14428,7 +14432,7 @@
       <c r="O150" s="88"/>
       <c r="P150" s="91"/>
     </row>
-    <row r="151" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" ht="14.4" customHeight="1">
       <c r="A151" s="7"/>
       <c r="B151" s="110"/>
       <c r="C151" s="101"/>
@@ -14448,7 +14452,7 @@
       <c r="O151" s="88"/>
       <c r="P151" s="91"/>
     </row>
-    <row r="152" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" ht="14.4" customHeight="1">
       <c r="A152" s="7"/>
       <c r="B152" s="110"/>
       <c r="C152" s="101"/>
@@ -14468,7 +14472,7 @@
       <c r="O152" s="88"/>
       <c r="P152" s="91"/>
     </row>
-    <row r="153" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" ht="14.4" customHeight="1">
       <c r="A153" s="7"/>
       <c r="B153" s="111"/>
       <c r="C153" s="102"/>
@@ -14488,7 +14492,7 @@
       <c r="O153" s="89"/>
       <c r="P153" s="92"/>
     </row>
-    <row r="154" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" ht="14.4" customHeight="1">
       <c r="A154" s="7"/>
       <c r="B154" s="110">
         <v>14</v>
@@ -14526,7 +14530,7 @@
       <c r="O154" s="88"/>
       <c r="P154" s="90"/>
     </row>
-    <row r="155" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" ht="14.4" customHeight="1">
       <c r="A155" s="7"/>
       <c r="B155" s="110"/>
       <c r="C155" s="101"/>
@@ -14550,7 +14554,7 @@
       <c r="O155" s="88"/>
       <c r="P155" s="91"/>
     </row>
-    <row r="156" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" ht="14.4" customHeight="1">
       <c r="A156" s="7"/>
       <c r="B156" s="110"/>
       <c r="C156" s="101"/>
@@ -14572,7 +14576,7 @@
       <c r="O156" s="88"/>
       <c r="P156" s="91"/>
     </row>
-    <row r="157" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" ht="14.4" customHeight="1">
       <c r="A157" s="7"/>
       <c r="B157" s="110"/>
       <c r="C157" s="101"/>
@@ -14592,7 +14596,7 @@
       <c r="O157" s="88"/>
       <c r="P157" s="91"/>
     </row>
-    <row r="158" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" ht="14.4" customHeight="1">
       <c r="A158" s="7"/>
       <c r="B158" s="110"/>
       <c r="C158" s="101"/>
@@ -14612,7 +14616,7 @@
       <c r="O158" s="88"/>
       <c r="P158" s="91"/>
     </row>
-    <row r="159" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" ht="14.4" customHeight="1">
       <c r="A159" s="7"/>
       <c r="B159" s="110"/>
       <c r="C159" s="101"/>
@@ -14632,7 +14636,7 @@
       <c r="O159" s="88"/>
       <c r="P159" s="91"/>
     </row>
-    <row r="160" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" ht="14.4" customHeight="1">
       <c r="A160" s="7"/>
       <c r="B160" s="110"/>
       <c r="C160" s="101"/>
@@ -14652,7 +14656,7 @@
       <c r="O160" s="88"/>
       <c r="P160" s="91"/>
     </row>
-    <row r="161" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" ht="14.4" customHeight="1">
       <c r="A161" s="7"/>
       <c r="B161" s="110"/>
       <c r="C161" s="101"/>
@@ -14672,7 +14676,7 @@
       <c r="O161" s="88"/>
       <c r="P161" s="91"/>
     </row>
-    <row r="162" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" ht="14.4" customHeight="1">
       <c r="A162" s="7"/>
       <c r="B162" s="110"/>
       <c r="C162" s="101"/>
@@ -14692,7 +14696,7 @@
       <c r="O162" s="88"/>
       <c r="P162" s="91"/>
     </row>
-    <row r="163" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" ht="14.4" customHeight="1">
       <c r="A163" s="7"/>
       <c r="B163" s="111"/>
       <c r="C163" s="102"/>
@@ -14712,7 +14716,7 @@
       <c r="O163" s="89"/>
       <c r="P163" s="92"/>
     </row>
-    <row r="164" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" ht="14.4" customHeight="1">
       <c r="A164" s="7"/>
       <c r="B164" s="110">
         <v>15</v>
@@ -14750,7 +14754,7 @@
       <c r="O164" s="106"/>
       <c r="P164" s="107"/>
     </row>
-    <row r="165" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" ht="14.4" customHeight="1">
       <c r="A165" s="7"/>
       <c r="B165" s="110"/>
       <c r="C165" s="101"/>
@@ -14774,7 +14778,7 @@
       <c r="O165" s="88"/>
       <c r="P165" s="91"/>
     </row>
-    <row r="166" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" ht="14.4" customHeight="1">
       <c r="A166" s="7"/>
       <c r="B166" s="110"/>
       <c r="C166" s="101"/>
@@ -14796,7 +14800,7 @@
       <c r="O166" s="88"/>
       <c r="P166" s="91"/>
     </row>
-    <row r="167" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" ht="14.4" customHeight="1">
       <c r="A167" s="7"/>
       <c r="B167" s="110"/>
       <c r="C167" s="101"/>
@@ -14816,7 +14820,7 @@
       <c r="O167" s="88"/>
       <c r="P167" s="91"/>
     </row>
-    <row r="168" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" ht="14.4" customHeight="1">
       <c r="A168" s="7"/>
       <c r="B168" s="110"/>
       <c r="C168" s="101"/>
@@ -14836,7 +14840,7 @@
       <c r="O168" s="88"/>
       <c r="P168" s="91"/>
     </row>
-    <row r="169" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" ht="14.4" customHeight="1">
       <c r="A169" s="7"/>
       <c r="B169" s="110"/>
       <c r="C169" s="101"/>
@@ -14856,7 +14860,7 @@
       <c r="O169" s="88"/>
       <c r="P169" s="91"/>
     </row>
-    <row r="170" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" ht="14.4" customHeight="1">
       <c r="A170" s="7"/>
       <c r="B170" s="110"/>
       <c r="C170" s="101"/>
@@ -14876,7 +14880,7 @@
       <c r="O170" s="88"/>
       <c r="P170" s="91"/>
     </row>
-    <row r="171" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" ht="14.4" customHeight="1">
       <c r="A171" s="7"/>
       <c r="B171" s="110"/>
       <c r="C171" s="101"/>
@@ -14896,7 +14900,7 @@
       <c r="O171" s="88"/>
       <c r="P171" s="91"/>
     </row>
-    <row r="172" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" ht="14.4" customHeight="1">
       <c r="A172" s="7"/>
       <c r="B172" s="110"/>
       <c r="C172" s="101"/>
@@ -14916,7 +14920,7 @@
       <c r="O172" s="88"/>
       <c r="P172" s="91"/>
     </row>
-    <row r="173" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" ht="14.4" customHeight="1">
       <c r="A173" s="7"/>
       <c r="B173" s="111"/>
       <c r="C173" s="102"/>
@@ -14936,7 +14940,7 @@
       <c r="O173" s="89"/>
       <c r="P173" s="92"/>
     </row>
-    <row r="174" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" ht="14.4" customHeight="1">
       <c r="A174" s="7"/>
       <c r="B174" s="110">
         <v>16</v>
@@ -14978,7 +14982,7 @@
       <c r="O174" s="106"/>
       <c r="P174" s="107"/>
     </row>
-    <row r="175" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" ht="14.4" customHeight="1">
       <c r="A175" s="7"/>
       <c r="B175" s="110"/>
       <c r="C175" s="101"/>
@@ -15002,7 +15006,7 @@
       <c r="O175" s="88"/>
       <c r="P175" s="91"/>
     </row>
-    <row r="176" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" ht="14.4" customHeight="1">
       <c r="A176" s="7"/>
       <c r="B176" s="110"/>
       <c r="C176" s="101"/>
@@ -15024,7 +15028,7 @@
       <c r="O176" s="88"/>
       <c r="P176" s="91"/>
     </row>
-    <row r="177" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" ht="14.4" customHeight="1">
       <c r="A177" s="7"/>
       <c r="B177" s="110"/>
       <c r="C177" s="101"/>
@@ -15044,7 +15048,7 @@
       <c r="O177" s="88"/>
       <c r="P177" s="91"/>
     </row>
-    <row r="178" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" ht="14.4" customHeight="1">
       <c r="A178" s="7"/>
       <c r="B178" s="110"/>
       <c r="C178" s="101"/>
@@ -15064,7 +15068,7 @@
       <c r="O178" s="88"/>
       <c r="P178" s="91"/>
     </row>
-    <row r="179" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" ht="14.4" customHeight="1">
       <c r="A179" s="7"/>
       <c r="B179" s="110"/>
       <c r="C179" s="101"/>
@@ -15084,7 +15088,7 @@
       <c r="O179" s="88"/>
       <c r="P179" s="91"/>
     </row>
-    <row r="180" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" ht="14.4" customHeight="1">
       <c r="A180" s="7"/>
       <c r="B180" s="110"/>
       <c r="C180" s="101"/>
@@ -15104,7 +15108,7 @@
       <c r="O180" s="88"/>
       <c r="P180" s="91"/>
     </row>
-    <row r="181" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" ht="14.4" customHeight="1">
       <c r="A181" s="7"/>
       <c r="B181" s="110"/>
       <c r="C181" s="101"/>
@@ -15124,7 +15128,7 @@
       <c r="O181" s="88"/>
       <c r="P181" s="91"/>
     </row>
-    <row r="182" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" ht="14.4" customHeight="1">
       <c r="A182" s="7"/>
       <c r="B182" s="110"/>
       <c r="C182" s="101"/>
@@ -15144,7 +15148,7 @@
       <c r="O182" s="88"/>
       <c r="P182" s="91"/>
     </row>
-    <row r="183" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" ht="14.4" customHeight="1">
       <c r="A183" s="7"/>
       <c r="B183" s="111"/>
       <c r="C183" s="102"/>
@@ -15164,7 +15168,7 @@
       <c r="O183" s="89"/>
       <c r="P183" s="92"/>
     </row>
-    <row r="184" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" ht="14.4" customHeight="1">
       <c r="A184" s="7"/>
       <c r="B184" s="110">
         <v>17</v>
@@ -15200,7 +15204,7 @@
       <c r="O184" s="88"/>
       <c r="P184" s="90"/>
     </row>
-    <row r="185" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" ht="14.4" customHeight="1">
       <c r="A185" s="7"/>
       <c r="B185" s="110"/>
       <c r="C185" s="101"/>
@@ -15222,7 +15226,7 @@
       <c r="O185" s="88"/>
       <c r="P185" s="91"/>
     </row>
-    <row r="186" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" ht="14.4" customHeight="1">
       <c r="A186" s="7"/>
       <c r="B186" s="110"/>
       <c r="C186" s="101"/>
@@ -15244,7 +15248,7 @@
       <c r="O186" s="88"/>
       <c r="P186" s="91"/>
     </row>
-    <row r="187" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" ht="14.4" customHeight="1">
       <c r="A187" s="7"/>
       <c r="B187" s="110"/>
       <c r="C187" s="101"/>
@@ -15264,7 +15268,7 @@
       <c r="O187" s="88"/>
       <c r="P187" s="91"/>
     </row>
-    <row r="188" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" ht="14.4" customHeight="1">
       <c r="A188" s="7"/>
       <c r="B188" s="110"/>
       <c r="C188" s="101"/>
@@ -15284,7 +15288,7 @@
       <c r="O188" s="88"/>
       <c r="P188" s="91"/>
     </row>
-    <row r="189" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" ht="14.4" customHeight="1">
       <c r="A189" s="7"/>
       <c r="B189" s="110"/>
       <c r="C189" s="101"/>
@@ -15304,7 +15308,7 @@
       <c r="O189" s="88"/>
       <c r="P189" s="91"/>
     </row>
-    <row r="190" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" ht="14.4" customHeight="1">
       <c r="A190" s="7"/>
       <c r="B190" s="110"/>
       <c r="C190" s="101"/>
@@ -15324,7 +15328,7 @@
       <c r="O190" s="88"/>
       <c r="P190" s="91"/>
     </row>
-    <row r="191" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" ht="14.4" customHeight="1">
       <c r="A191" s="7"/>
       <c r="B191" s="110"/>
       <c r="C191" s="101"/>
@@ -15344,7 +15348,7 @@
       <c r="O191" s="88"/>
       <c r="P191" s="91"/>
     </row>
-    <row r="192" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" ht="14.4" customHeight="1">
       <c r="A192" s="7"/>
       <c r="B192" s="110"/>
       <c r="C192" s="101"/>
@@ -15364,7 +15368,7 @@
       <c r="O192" s="88"/>
       <c r="P192" s="91"/>
     </row>
-    <row r="193" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" ht="14.4" customHeight="1">
       <c r="A193" s="7"/>
       <c r="B193" s="111"/>
       <c r="C193" s="102"/>
@@ -15384,7 +15388,7 @@
       <c r="O193" s="89"/>
       <c r="P193" s="92"/>
     </row>
-    <row r="194" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" ht="14.4" customHeight="1">
       <c r="A194" s="7"/>
       <c r="B194" s="110">
         <v>18</v>
@@ -15420,7 +15424,7 @@
       <c r="O194" s="106"/>
       <c r="P194" s="107"/>
     </row>
-    <row r="195" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" ht="14.4" customHeight="1">
       <c r="A195" s="7"/>
       <c r="B195" s="110"/>
       <c r="C195" s="101"/>
@@ -15442,7 +15446,7 @@
       <c r="O195" s="88"/>
       <c r="P195" s="91"/>
     </row>
-    <row r="196" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" ht="14.4" customHeight="1">
       <c r="A196" s="7"/>
       <c r="B196" s="110"/>
       <c r="C196" s="101"/>
@@ -15464,7 +15468,7 @@
       <c r="O196" s="88"/>
       <c r="P196" s="91"/>
     </row>
-    <row r="197" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" ht="14.4" customHeight="1">
       <c r="A197" s="7"/>
       <c r="B197" s="110"/>
       <c r="C197" s="101"/>
@@ -15484,7 +15488,7 @@
       <c r="O197" s="88"/>
       <c r="P197" s="91"/>
     </row>
-    <row r="198" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" ht="14.4" customHeight="1">
       <c r="A198" s="7"/>
       <c r="B198" s="110"/>
       <c r="C198" s="101"/>
@@ -15504,7 +15508,7 @@
       <c r="O198" s="88"/>
       <c r="P198" s="91"/>
     </row>
-    <row r="199" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" ht="14.4" customHeight="1">
       <c r="A199" s="7"/>
       <c r="B199" s="110"/>
       <c r="C199" s="101"/>
@@ -15524,7 +15528,7 @@
       <c r="O199" s="88"/>
       <c r="P199" s="91"/>
     </row>
-    <row r="200" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" ht="14.4" customHeight="1">
       <c r="A200" s="7"/>
       <c r="B200" s="110"/>
       <c r="C200" s="101"/>
@@ -15544,7 +15548,7 @@
       <c r="O200" s="88"/>
       <c r="P200" s="91"/>
     </row>
-    <row r="201" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" ht="14.4" customHeight="1">
       <c r="A201" s="7"/>
       <c r="B201" s="110"/>
       <c r="C201" s="101"/>
@@ -15564,7 +15568,7 @@
       <c r="O201" s="88"/>
       <c r="P201" s="91"/>
     </row>
-    <row r="202" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" ht="14.4" customHeight="1">
       <c r="A202" s="7"/>
       <c r="B202" s="110"/>
       <c r="C202" s="101"/>
@@ -15584,7 +15588,7 @@
       <c r="O202" s="88"/>
       <c r="P202" s="91"/>
     </row>
-    <row r="203" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" ht="14.4" customHeight="1">
       <c r="A203" s="7"/>
       <c r="B203" s="111"/>
       <c r="C203" s="102"/>
@@ -15604,7 +15608,7 @@
       <c r="O203" s="89"/>
       <c r="P203" s="92"/>
     </row>
-    <row r="204" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" ht="14.4" customHeight="1">
       <c r="A204" s="7"/>
       <c r="B204" s="110">
         <v>19</v>
@@ -15640,7 +15644,7 @@
       <c r="O204" s="88"/>
       <c r="P204" s="90"/>
     </row>
-    <row r="205" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" ht="14.4" customHeight="1">
       <c r="A205" s="7"/>
       <c r="B205" s="110"/>
       <c r="C205" s="101"/>
@@ -15662,7 +15666,7 @@
       <c r="O205" s="88"/>
       <c r="P205" s="91"/>
     </row>
-    <row r="206" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" ht="14.4" customHeight="1">
       <c r="A206" s="7"/>
       <c r="B206" s="110"/>
       <c r="C206" s="101"/>
@@ -15684,7 +15688,7 @@
       <c r="O206" s="88"/>
       <c r="P206" s="91"/>
     </row>
-    <row r="207" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" ht="14.4" customHeight="1">
       <c r="A207" s="7"/>
       <c r="B207" s="110"/>
       <c r="C207" s="101"/>
@@ -15704,7 +15708,7 @@
       <c r="O207" s="88"/>
       <c r="P207" s="91"/>
     </row>
-    <row r="208" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" ht="14.4" customHeight="1">
       <c r="A208" s="7"/>
       <c r="B208" s="110"/>
       <c r="C208" s="101"/>
@@ -15724,7 +15728,7 @@
       <c r="O208" s="88"/>
       <c r="P208" s="91"/>
     </row>
-    <row r="209" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" ht="14.4" customHeight="1">
       <c r="A209" s="7"/>
       <c r="B209" s="110"/>
       <c r="C209" s="101"/>
@@ -15744,7 +15748,7 @@
       <c r="O209" s="88"/>
       <c r="P209" s="91"/>
     </row>
-    <row r="210" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" ht="14.4" customHeight="1">
       <c r="A210" s="7"/>
       <c r="B210" s="110"/>
       <c r="C210" s="101"/>
@@ -15764,7 +15768,7 @@
       <c r="O210" s="88"/>
       <c r="P210" s="91"/>
     </row>
-    <row r="211" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" ht="14.4" customHeight="1">
       <c r="A211" s="7"/>
       <c r="B211" s="110"/>
       <c r="C211" s="101"/>
@@ -15784,7 +15788,7 @@
       <c r="O211" s="88"/>
       <c r="P211" s="91"/>
     </row>
-    <row r="212" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" ht="14.4" customHeight="1">
       <c r="A212" s="7"/>
       <c r="B212" s="110"/>
       <c r="C212" s="101"/>
@@ -15804,7 +15808,7 @@
       <c r="O212" s="88"/>
       <c r="P212" s="91"/>
     </row>
-    <row r="213" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" ht="14.4" customHeight="1">
       <c r="A213" s="7"/>
       <c r="B213" s="111"/>
       <c r="C213" s="102"/>
@@ -15824,7 +15828,7 @@
       <c r="O213" s="89"/>
       <c r="P213" s="92"/>
     </row>
-    <row r="214" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" ht="14.4" customHeight="1">
       <c r="A214" s="7"/>
       <c r="B214" s="110">
         <v>20</v>
@@ -15860,7 +15864,7 @@
       <c r="O214" s="106"/>
       <c r="P214" s="107"/>
     </row>
-    <row r="215" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" ht="14.4" customHeight="1">
       <c r="A215" s="7"/>
       <c r="B215" s="110"/>
       <c r="C215" s="101"/>
@@ -15882,7 +15886,7 @@
       <c r="O215" s="88"/>
       <c r="P215" s="91"/>
     </row>
-    <row r="216" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" ht="14.4" customHeight="1">
       <c r="A216" s="7"/>
       <c r="B216" s="110"/>
       <c r="C216" s="101"/>
@@ -15904,7 +15908,7 @@
       <c r="O216" s="88"/>
       <c r="P216" s="91"/>
     </row>
-    <row r="217" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" ht="14.4" customHeight="1">
       <c r="A217" s="7"/>
       <c r="B217" s="110"/>
       <c r="C217" s="101"/>
@@ -15924,7 +15928,7 @@
       <c r="O217" s="88"/>
       <c r="P217" s="91"/>
     </row>
-    <row r="218" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" ht="14.4" customHeight="1">
       <c r="A218" s="7"/>
       <c r="B218" s="110"/>
       <c r="C218" s="101"/>
@@ -15944,7 +15948,7 @@
       <c r="O218" s="88"/>
       <c r="P218" s="91"/>
     </row>
-    <row r="219" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" ht="14.4" customHeight="1">
       <c r="A219" s="7"/>
       <c r="B219" s="110"/>
       <c r="C219" s="101"/>
@@ -15964,7 +15968,7 @@
       <c r="O219" s="88"/>
       <c r="P219" s="91"/>
     </row>
-    <row r="220" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" ht="14.4" customHeight="1">
       <c r="A220" s="7"/>
       <c r="B220" s="110"/>
       <c r="C220" s="101"/>
@@ -15984,7 +15988,7 @@
       <c r="O220" s="88"/>
       <c r="P220" s="91"/>
     </row>
-    <row r="221" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" ht="14.4" customHeight="1">
       <c r="A221" s="7"/>
       <c r="B221" s="110"/>
       <c r="C221" s="101"/>
@@ -16004,7 +16008,7 @@
       <c r="O221" s="88"/>
       <c r="P221" s="91"/>
     </row>
-    <row r="222" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" ht="14.4" customHeight="1">
       <c r="A222" s="7"/>
       <c r="B222" s="110"/>
       <c r="C222" s="101"/>
@@ -16024,7 +16028,7 @@
       <c r="O222" s="88"/>
       <c r="P222" s="91"/>
     </row>
-    <row r="223" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" ht="14.4" customHeight="1">
       <c r="A223" s="7"/>
       <c r="B223" s="111"/>
       <c r="C223" s="102"/>
@@ -16044,7 +16048,7 @@
       <c r="O223" s="89"/>
       <c r="P223" s="92"/>
     </row>
-    <row r="224" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" ht="14.4" customHeight="1">
       <c r="A224" s="7"/>
       <c r="B224" s="110">
         <v>21</v>
@@ -16082,7 +16086,7 @@
       <c r="O224" s="88"/>
       <c r="P224" s="90"/>
     </row>
-    <row r="225" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" ht="14.4" customHeight="1">
       <c r="A225" s="7"/>
       <c r="B225" s="110"/>
       <c r="C225" s="101"/>
@@ -16106,7 +16110,7 @@
       <c r="O225" s="88"/>
       <c r="P225" s="91"/>
     </row>
-    <row r="226" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" ht="14.4" customHeight="1">
       <c r="A226" s="7"/>
       <c r="B226" s="110"/>
       <c r="C226" s="101"/>
@@ -16130,7 +16134,7 @@
       <c r="O226" s="88"/>
       <c r="P226" s="91"/>
     </row>
-    <row r="227" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" ht="14.4" customHeight="1">
       <c r="A227" s="7"/>
       <c r="B227" s="110"/>
       <c r="C227" s="101"/>
@@ -16154,7 +16158,7 @@
       <c r="O227" s="88"/>
       <c r="P227" s="91"/>
     </row>
-    <row r="228" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" ht="14.4" customHeight="1">
       <c r="A228" s="7"/>
       <c r="B228" s="110"/>
       <c r="C228" s="101"/>
@@ -16176,7 +16180,7 @@
       <c r="O228" s="88"/>
       <c r="P228" s="91"/>
     </row>
-    <row r="229" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" ht="14.4" customHeight="1">
       <c r="A229" s="7"/>
       <c r="B229" s="110"/>
       <c r="C229" s="101"/>
@@ -16196,7 +16200,7 @@
       <c r="O229" s="88"/>
       <c r="P229" s="91"/>
     </row>
-    <row r="230" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" ht="14.4" customHeight="1">
       <c r="A230" s="7"/>
       <c r="B230" s="110"/>
       <c r="C230" s="101"/>
@@ -16216,7 +16220,7 @@
       <c r="O230" s="88"/>
       <c r="P230" s="91"/>
     </row>
-    <row r="231" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" ht="14.4" customHeight="1">
       <c r="A231" s="7"/>
       <c r="B231" s="110"/>
       <c r="C231" s="101"/>
@@ -16236,7 +16240,7 @@
       <c r="O231" s="88"/>
       <c r="P231" s="91"/>
     </row>
-    <row r="232" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" ht="14.4" customHeight="1">
       <c r="A232" s="7"/>
       <c r="B232" s="110"/>
       <c r="C232" s="101"/>
@@ -16256,7 +16260,7 @@
       <c r="O232" s="88"/>
       <c r="P232" s="91"/>
     </row>
-    <row r="233" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" ht="14.4" customHeight="1">
       <c r="A233" s="7"/>
       <c r="B233" s="111"/>
       <c r="C233" s="102"/>
@@ -16276,7 +16280,7 @@
       <c r="O233" s="89"/>
       <c r="P233" s="92"/>
     </row>
-    <row r="234" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" ht="14.4" customHeight="1">
       <c r="A234" s="7"/>
       <c r="B234" s="110">
         <v>22</v>
@@ -16314,7 +16318,7 @@
       <c r="O234" s="106"/>
       <c r="P234" s="107"/>
     </row>
-    <row r="235" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" ht="14.4" customHeight="1">
       <c r="A235" s="7"/>
       <c r="B235" s="110"/>
       <c r="C235" s="101"/>
@@ -16338,7 +16342,7 @@
       <c r="O235" s="88"/>
       <c r="P235" s="91"/>
     </row>
-    <row r="236" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" ht="14.4" customHeight="1">
       <c r="A236" s="7"/>
       <c r="B236" s="110"/>
       <c r="C236" s="101"/>
@@ -16362,7 +16366,7 @@
       <c r="O236" s="88"/>
       <c r="P236" s="91"/>
     </row>
-    <row r="237" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" ht="14.4" customHeight="1">
       <c r="A237" s="7"/>
       <c r="B237" s="110"/>
       <c r="C237" s="101"/>
@@ -16386,7 +16390,7 @@
       <c r="O237" s="88"/>
       <c r="P237" s="91"/>
     </row>
-    <row r="238" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" ht="14.4" customHeight="1">
       <c r="A238" s="7"/>
       <c r="B238" s="110"/>
       <c r="C238" s="101"/>
@@ -16408,7 +16412,7 @@
       <c r="O238" s="88"/>
       <c r="P238" s="91"/>
     </row>
-    <row r="239" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" ht="14.4" customHeight="1">
       <c r="A239" s="7"/>
       <c r="B239" s="110"/>
       <c r="C239" s="101"/>
@@ -16428,7 +16432,7 @@
       <c r="O239" s="88"/>
       <c r="P239" s="91"/>
     </row>
-    <row r="240" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" ht="14.4" customHeight="1">
       <c r="A240" s="7"/>
       <c r="B240" s="110"/>
       <c r="C240" s="101"/>
@@ -16448,7 +16452,7 @@
       <c r="O240" s="88"/>
       <c r="P240" s="91"/>
     </row>
-    <row r="241" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" ht="14.4" customHeight="1">
       <c r="A241" s="7"/>
       <c r="B241" s="110"/>
       <c r="C241" s="101"/>
@@ -16468,7 +16472,7 @@
       <c r="O241" s="88"/>
       <c r="P241" s="91"/>
     </row>
-    <row r="242" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" ht="14.4" customHeight="1">
       <c r="A242" s="7"/>
       <c r="B242" s="110"/>
       <c r="C242" s="101"/>
@@ -16488,7 +16492,7 @@
       <c r="O242" s="88"/>
       <c r="P242" s="91"/>
     </row>
-    <row r="243" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="243">
       <c r="A243" s="7"/>
       <c r="B243" s="111"/>
       <c r="C243" s="102"/>
@@ -16508,7 +16512,7 @@
       <c r="O243" s="89"/>
       <c r="P243" s="92"/>
     </row>
-    <row r="244" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" ht="14.4" customHeight="1">
       <c r="A244" s="7"/>
       <c r="B244" s="110">
         <v>23</v>
@@ -16546,7 +16550,7 @@
       <c r="O244" s="88"/>
       <c r="P244" s="90"/>
     </row>
-    <row r="245" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" ht="14.4" customHeight="1">
       <c r="A245" s="7"/>
       <c r="B245" s="110"/>
       <c r="C245" s="101"/>
@@ -16570,7 +16574,7 @@
       <c r="O245" s="88"/>
       <c r="P245" s="91"/>
     </row>
-    <row r="246" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" ht="14.4" customHeight="1">
       <c r="A246" s="7"/>
       <c r="B246" s="110"/>
       <c r="C246" s="101"/>
@@ -16594,7 +16598,7 @@
       <c r="O246" s="88"/>
       <c r="P246" s="91"/>
     </row>
-    <row r="247" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" ht="14.4" customHeight="1">
       <c r="A247" s="7"/>
       <c r="B247" s="110"/>
       <c r="C247" s="101"/>
@@ -16618,7 +16622,7 @@
       <c r="O247" s="88"/>
       <c r="P247" s="91"/>
     </row>
-    <row r="248" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" ht="14.4" customHeight="1">
       <c r="A248" s="7"/>
       <c r="B248" s="110"/>
       <c r="C248" s="101"/>
@@ -16640,7 +16644,7 @@
       <c r="O248" s="88"/>
       <c r="P248" s="91"/>
     </row>
-    <row r="249" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" ht="14.4" customHeight="1">
       <c r="A249" s="7"/>
       <c r="B249" s="110"/>
       <c r="C249" s="101"/>
@@ -16660,7 +16664,7 @@
       <c r="O249" s="88"/>
       <c r="P249" s="91"/>
     </row>
-    <row r="250" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" ht="14.4" customHeight="1">
       <c r="A250" s="7"/>
       <c r="B250" s="110"/>
       <c r="C250" s="101"/>
@@ -16680,7 +16684,7 @@
       <c r="O250" s="88"/>
       <c r="P250" s="91"/>
     </row>
-    <row r="251" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" ht="14.4" customHeight="1">
       <c r="A251" s="7"/>
       <c r="B251" s="110"/>
       <c r="C251" s="101"/>
@@ -16700,7 +16704,7 @@
       <c r="O251" s="88"/>
       <c r="P251" s="91"/>
     </row>
-    <row r="252" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" ht="14.4" customHeight="1">
       <c r="A252" s="7"/>
       <c r="B252" s="110"/>
       <c r="C252" s="101"/>
@@ -16720,7 +16724,7 @@
       <c r="O252" s="88"/>
       <c r="P252" s="91"/>
     </row>
-    <row r="253" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="253">
       <c r="A253" s="7"/>
       <c r="B253" s="111"/>
       <c r="C253" s="102"/>
@@ -16740,7 +16744,7 @@
       <c r="O253" s="89"/>
       <c r="P253" s="92"/>
     </row>
-    <row r="254" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" ht="14.4" customHeight="1">
       <c r="A254" s="7"/>
       <c r="B254" s="110">
         <v>24</v>
@@ -16778,7 +16782,7 @@
       <c r="O254" s="106"/>
       <c r="P254" s="107"/>
     </row>
-    <row r="255" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" ht="14.4" customHeight="1">
       <c r="A255" s="7"/>
       <c r="B255" s="110"/>
       <c r="C255" s="101"/>
@@ -16800,7 +16804,7 @@
       <c r="O255" s="88"/>
       <c r="P255" s="91"/>
     </row>
-    <row r="256" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" ht="14.4" customHeight="1">
       <c r="A256" s="7"/>
       <c r="B256" s="110"/>
       <c r="C256" s="101"/>
@@ -16824,7 +16828,7 @@
       <c r="O256" s="88"/>
       <c r="P256" s="91"/>
     </row>
-    <row r="257" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" ht="14.4" customHeight="1">
       <c r="A257" s="7"/>
       <c r="B257" s="110"/>
       <c r="C257" s="101"/>
@@ -16848,7 +16852,7 @@
       <c r="O257" s="88"/>
       <c r="P257" s="91"/>
     </row>
-    <row r="258" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" ht="14.4" customHeight="1">
       <c r="A258" s="7"/>
       <c r="B258" s="110"/>
       <c r="C258" s="101"/>
@@ -16870,7 +16874,7 @@
       <c r="O258" s="88"/>
       <c r="P258" s="91"/>
     </row>
-    <row r="259" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" ht="14.4" customHeight="1">
       <c r="A259" s="7"/>
       <c r="B259" s="110"/>
       <c r="C259" s="101"/>
@@ -16890,7 +16894,7 @@
       <c r="O259" s="88"/>
       <c r="P259" s="91"/>
     </row>
-    <row r="260" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" ht="14.4" customHeight="1">
       <c r="A260" s="7"/>
       <c r="B260" s="110"/>
       <c r="C260" s="101"/>
@@ -16910,7 +16914,7 @@
       <c r="O260" s="88"/>
       <c r="P260" s="91"/>
     </row>
-    <row r="261" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" ht="14.4" customHeight="1">
       <c r="A261" s="7"/>
       <c r="B261" s="110"/>
       <c r="C261" s="101"/>
@@ -16930,7 +16934,7 @@
       <c r="O261" s="88"/>
       <c r="P261" s="91"/>
     </row>
-    <row r="262" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" ht="14.4" customHeight="1">
       <c r="A262" s="7"/>
       <c r="B262" s="110"/>
       <c r="C262" s="101"/>
@@ -16950,7 +16954,7 @@
       <c r="O262" s="88"/>
       <c r="P262" s="91"/>
     </row>
-    <row r="263" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="263">
       <c r="A263" s="7"/>
       <c r="B263" s="111"/>
       <c r="C263" s="102"/>
@@ -16970,7 +16974,7 @@
       <c r="O263" s="89"/>
       <c r="P263" s="92"/>
     </row>
-    <row r="264" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" ht="14.4" customHeight="1">
       <c r="A264" s="7"/>
       <c r="B264" s="110">
         <v>25</v>
@@ -17008,7 +17012,7 @@
       <c r="O264" s="88"/>
       <c r="P264" s="90"/>
     </row>
-    <row r="265" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" ht="14.4" customHeight="1">
       <c r="A265" s="7"/>
       <c r="B265" s="110"/>
       <c r="C265" s="101"/>
@@ -17032,7 +17036,7 @@
       <c r="O265" s="88"/>
       <c r="P265" s="91"/>
     </row>
-    <row r="266" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" ht="14.4" customHeight="1">
       <c r="A266" s="7"/>
       <c r="B266" s="110"/>
       <c r="C266" s="101"/>
@@ -17054,7 +17058,7 @@
       <c r="O266" s="88"/>
       <c r="P266" s="91"/>
     </row>
-    <row r="267" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" ht="14.4" customHeight="1">
       <c r="A267" s="7"/>
       <c r="B267" s="110"/>
       <c r="C267" s="101"/>
@@ -17078,7 +17082,7 @@
       <c r="O267" s="88"/>
       <c r="P267" s="91"/>
     </row>
-    <row r="268" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" ht="14.4" customHeight="1">
       <c r="A268" s="7"/>
       <c r="B268" s="110"/>
       <c r="C268" s="101"/>
@@ -17100,7 +17104,7 @@
       <c r="O268" s="88"/>
       <c r="P268" s="91"/>
     </row>
-    <row r="269" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" ht="14.4" customHeight="1">
       <c r="A269" s="7"/>
       <c r="B269" s="110"/>
       <c r="C269" s="101"/>
@@ -17120,7 +17124,7 @@
       <c r="O269" s="88"/>
       <c r="P269" s="91"/>
     </row>
-    <row r="270" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" ht="14.4" customHeight="1">
       <c r="A270" s="7"/>
       <c r="B270" s="110"/>
       <c r="C270" s="101"/>
@@ -17140,7 +17144,7 @@
       <c r="O270" s="88"/>
       <c r="P270" s="91"/>
     </row>
-    <row r="271" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" ht="14.4" customHeight="1">
       <c r="A271" s="7"/>
       <c r="B271" s="110"/>
       <c r="C271" s="101"/>
@@ -17160,7 +17164,7 @@
       <c r="O271" s="88"/>
       <c r="P271" s="91"/>
     </row>
-    <row r="272" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" ht="14.4" customHeight="1">
       <c r="A272" s="7"/>
       <c r="B272" s="110"/>
       <c r="C272" s="101"/>
@@ -17180,7 +17184,7 @@
       <c r="O272" s="88"/>
       <c r="P272" s="91"/>
     </row>
-    <row r="273" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" ht="14.4" customHeight="1">
       <c r="A273" s="7"/>
       <c r="B273" s="111"/>
       <c r="C273" s="102"/>
@@ -17200,7 +17204,7 @@
       <c r="O273" s="89"/>
       <c r="P273" s="92"/>
     </row>
-    <row r="274" spans="1:16" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" ht="21" customHeight="1">
       <c r="A274" s="7"/>
       <c r="B274" s="110">
         <v>26</v>
@@ -17236,7 +17240,7 @@
       <c r="O274" s="106"/>
       <c r="P274" s="107"/>
     </row>
-    <row r="275" spans="1:16" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" ht="33.6" customHeight="1">
       <c r="A275" s="7"/>
       <c r="B275" s="110"/>
       <c r="C275" s="101"/>
@@ -17258,7 +17262,7 @@
       <c r="O275" s="88"/>
       <c r="P275" s="91"/>
     </row>
-    <row r="276" spans="1:16" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" ht="29.4" customHeight="1">
       <c r="A276" s="7"/>
       <c r="B276" s="110"/>
       <c r="C276" s="101"/>
@@ -17280,7 +17284,7 @@
       <c r="O276" s="88"/>
       <c r="P276" s="91"/>
     </row>
-    <row r="277" spans="1:16" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" ht="40.2" customHeight="1">
       <c r="A277" s="7"/>
       <c r="B277" s="110"/>
       <c r="C277" s="101"/>
@@ -17304,7 +17308,7 @@
       <c r="O277" s="88"/>
       <c r="P277" s="91"/>
     </row>
-    <row r="278" spans="1:16" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" ht="31.2" customHeight="1">
       <c r="A278" s="7"/>
       <c r="B278" s="110"/>
       <c r="C278" s="101"/>
@@ -17328,7 +17332,7 @@
       <c r="O278" s="88"/>
       <c r="P278" s="91"/>
     </row>
-    <row r="279" spans="1:16" ht="32.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" ht="32.4" customHeight="1">
       <c r="A279" s="7"/>
       <c r="B279" s="110"/>
       <c r="C279" s="101"/>
@@ -17350,7 +17354,7 @@
       <c r="O279" s="88"/>
       <c r="P279" s="91"/>
     </row>
-    <row r="280" spans="1:16" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" ht="26.4" customHeight="1">
       <c r="A280" s="7"/>
       <c r="B280" s="110"/>
       <c r="C280" s="101"/>
@@ -17372,7 +17376,7 @@
       <c r="O280" s="88"/>
       <c r="P280" s="91"/>
     </row>
-    <row r="281" spans="1:16" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" ht="30.6" customHeight="1">
       <c r="A281" s="7"/>
       <c r="B281" s="110"/>
       <c r="C281" s="101"/>
@@ -17396,7 +17400,7 @@
       <c r="O281" s="88"/>
       <c r="P281" s="91"/>
     </row>
-    <row r="282" spans="1:16" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" ht="24.6" customHeight="1">
       <c r="A282" s="7"/>
       <c r="B282" s="110"/>
       <c r="C282" s="101"/>
@@ -17420,7 +17424,7 @@
       <c r="O282" s="88"/>
       <c r="P282" s="91"/>
     </row>
-    <row r="283" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" ht="21.6" customHeight="1">
       <c r="A283" s="7"/>
       <c r="B283" s="110"/>
       <c r="C283" s="101"/>
@@ -17442,7 +17446,7 @@
       <c r="O283" s="88"/>
       <c r="P283" s="91"/>
     </row>
-    <row r="284" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" ht="24" customHeight="1">
       <c r="A284" s="7"/>
       <c r="B284" s="110"/>
       <c r="C284" s="101"/>
@@ -17464,7 +17468,7 @@
       <c r="O284" s="88"/>
       <c r="P284" s="91"/>
     </row>
-    <row r="285" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" ht="24" customHeight="1">
       <c r="A285" s="7"/>
       <c r="B285" s="110"/>
       <c r="C285" s="101"/>
@@ -17488,7 +17492,7 @@
       <c r="O285" s="88"/>
       <c r="P285" s="91"/>
     </row>
-    <row r="286" spans="1:16" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" ht="22.8" customHeight="1">
       <c r="A286" s="7"/>
       <c r="B286" s="110"/>
       <c r="C286" s="101"/>
@@ -17512,7 +17516,7 @@
       <c r="O286" s="88"/>
       <c r="P286" s="91"/>
     </row>
-    <row r="287" spans="1:16" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" ht="22.8" customHeight="1">
       <c r="A287" s="7"/>
       <c r="B287" s="110"/>
       <c r="C287" s="101"/>
@@ -17534,7 +17538,7 @@
       <c r="O287" s="88"/>
       <c r="P287" s="91"/>
     </row>
-    <row r="288" spans="1:16" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" ht="22.8" customHeight="1">
       <c r="A288" s="7"/>
       <c r="B288" s="110"/>
       <c r="C288" s="101"/>
@@ -17556,7 +17560,7 @@
       <c r="O288" s="88"/>
       <c r="P288" s="91"/>
     </row>
-    <row r="289" spans="1:16" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" ht="22.8" customHeight="1">
       <c r="A289" s="7"/>
       <c r="B289" s="110"/>
       <c r="C289" s="101"/>
@@ -17580,7 +17584,7 @@
       <c r="O289" s="88"/>
       <c r="P289" s="91"/>
     </row>
-    <row r="290" spans="1:16" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" ht="22.8" customHeight="1">
       <c r="A290" s="7"/>
       <c r="B290" s="110"/>
       <c r="C290" s="101"/>
@@ -17604,7 +17608,7 @@
       <c r="O290" s="88"/>
       <c r="P290" s="91"/>
     </row>
-    <row r="291" spans="1:16" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" ht="22.8" customHeight="1">
       <c r="A291" s="7"/>
       <c r="B291" s="110"/>
       <c r="C291" s="101"/>
@@ -17626,7 +17630,7 @@
       <c r="O291" s="88"/>
       <c r="P291" s="91"/>
     </row>
-    <row r="292" spans="1:16" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" ht="22.8" customHeight="1">
       <c r="A292" s="7"/>
       <c r="B292" s="110"/>
       <c r="C292" s="101"/>
@@ -17648,7 +17652,7 @@
       <c r="O292" s="88"/>
       <c r="P292" s="91"/>
     </row>
-    <row r="293" spans="1:16" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" ht="22.8" customHeight="1">
       <c r="A293" s="7"/>
       <c r="B293" s="110"/>
       <c r="C293" s="101"/>
@@ -17672,7 +17676,7 @@
       <c r="O293" s="88"/>
       <c r="P293" s="91"/>
     </row>
-    <row r="294" spans="1:16" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" ht="22.8" customHeight="1">
       <c r="A294" s="7"/>
       <c r="B294" s="110"/>
       <c r="C294" s="101"/>
@@ -17696,7 +17700,7 @@
       <c r="O294" s="88"/>
       <c r="P294" s="91"/>
     </row>
-    <row r="295" spans="1:16" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" ht="22.8" customHeight="1">
       <c r="A295" s="7"/>
       <c r="B295" s="110"/>
       <c r="C295" s="101"/>
@@ -17718,7 +17722,7 @@
       <c r="O295" s="88"/>
       <c r="P295" s="91"/>
     </row>
-    <row r="296" spans="1:16" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" ht="22.8" customHeight="1">
       <c r="A296" s="7"/>
       <c r="B296" s="110"/>
       <c r="C296" s="101"/>
@@ -17740,7 +17744,7 @@
       <c r="O296" s="88"/>
       <c r="P296" s="91"/>
     </row>
-    <row r="297" spans="1:16" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" ht="22.8" customHeight="1">
       <c r="A297" s="7"/>
       <c r="B297" s="110"/>
       <c r="C297" s="101"/>
@@ -17764,7 +17768,7 @@
       <c r="O297" s="88"/>
       <c r="P297" s="91"/>
     </row>
-    <row r="298" spans="1:16" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" ht="22.8" customHeight="1">
       <c r="A298" s="7"/>
       <c r="B298" s="110"/>
       <c r="C298" s="101"/>
@@ -17788,7 +17792,7 @@
       <c r="O298" s="88"/>
       <c r="P298" s="91"/>
     </row>
-    <row r="299" spans="1:16" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" ht="22.8" customHeight="1">
       <c r="A299" s="7"/>
       <c r="B299" s="110"/>
       <c r="C299" s="101"/>
@@ -17810,7 +17814,7 @@
       <c r="O299" s="88"/>
       <c r="P299" s="91"/>
     </row>
-    <row r="300" spans="1:16" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" ht="22.8" customHeight="1">
       <c r="A300" s="7"/>
       <c r="B300" s="110"/>
       <c r="C300" s="101"/>
@@ -17832,7 +17836,7 @@
       <c r="O300" s="88"/>
       <c r="P300" s="91"/>
     </row>
-    <row r="301" spans="1:16" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" ht="22.8" customHeight="1">
       <c r="A301" s="7"/>
       <c r="B301" s="110"/>
       <c r="C301" s="101"/>
@@ -17856,7 +17860,7 @@
       <c r="O301" s="88"/>
       <c r="P301" s="91"/>
     </row>
-    <row r="302" spans="1:16" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" ht="22.8" customHeight="1">
       <c r="A302" s="7"/>
       <c r="B302" s="110"/>
       <c r="C302" s="101"/>
@@ -17880,7 +17884,7 @@
       <c r="O302" s="88"/>
       <c r="P302" s="91"/>
     </row>
-    <row r="303" spans="1:16" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" ht="22.8" customHeight="1">
       <c r="A303" s="7"/>
       <c r="B303" s="110"/>
       <c r="C303" s="101"/>
@@ -17902,7 +17906,7 @@
       <c r="O303" s="88"/>
       <c r="P303" s="91"/>
     </row>
-    <row r="304" spans="1:16" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" ht="22.8" customHeight="1">
       <c r="A304" s="7"/>
       <c r="B304" s="110"/>
       <c r="C304" s="101"/>
@@ -17924,7 +17928,7 @@
       <c r="O304" s="88"/>
       <c r="P304" s="91"/>
     </row>
-    <row r="305" spans="1:16" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" ht="22.8" customHeight="1">
       <c r="A305" s="7"/>
       <c r="B305" s="110"/>
       <c r="C305" s="101"/>
@@ -17948,7 +17952,7 @@
       <c r="O305" s="88"/>
       <c r="P305" s="91"/>
     </row>
-    <row r="306" spans="1:16" ht="32.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" ht="32.4" customHeight="1">
       <c r="A306" s="7"/>
       <c r="B306" s="111"/>
       <c r="C306" s="102"/>
@@ -17972,7 +17976,7 @@
       <c r="O306" s="89"/>
       <c r="P306" s="92"/>
     </row>
-    <row r="307" spans="1:16" ht="23.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" ht="23.4" customHeight="1">
       <c r="A307" s="7"/>
       <c r="B307" s="110">
         <v>27</v>
@@ -18008,7 +18012,7 @@
       <c r="O307" s="88"/>
       <c r="P307" s="90"/>
     </row>
-    <row r="308" spans="1:16" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" ht="27" customHeight="1">
       <c r="A308" s="7"/>
       <c r="B308" s="110"/>
       <c r="C308" s="101"/>
@@ -18030,7 +18034,7 @@
       <c r="O308" s="88"/>
       <c r="P308" s="91"/>
     </row>
-    <row r="309" spans="1:16" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" ht="28.2" customHeight="1">
       <c r="A309" s="7"/>
       <c r="B309" s="110"/>
       <c r="C309" s="101"/>
@@ -18054,7 +18058,7 @@
       <c r="O309" s="88"/>
       <c r="P309" s="91"/>
     </row>
-    <row r="310" spans="1:16" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" ht="34.8" customHeight="1">
       <c r="A310" s="7"/>
       <c r="B310" s="110"/>
       <c r="C310" s="101"/>
@@ -18078,7 +18082,7 @@
       <c r="O310" s="88"/>
       <c r="P310" s="91"/>
     </row>
-    <row r="311" spans="1:16" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" ht="43.2" customHeight="1">
       <c r="A311" s="7"/>
       <c r="B311" s="110"/>
       <c r="C311" s="101"/>
@@ -18100,7 +18104,7 @@
       <c r="O311" s="88"/>
       <c r="P311" s="91"/>
     </row>
-    <row r="312" spans="1:16" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" ht="24.6" customHeight="1">
       <c r="A312" s="7"/>
       <c r="B312" s="110"/>
       <c r="C312" s="101"/>
@@ -18122,7 +18126,7 @@
       <c r="O312" s="88"/>
       <c r="P312" s="91"/>
     </row>
-    <row r="313" spans="1:16" ht="32.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" ht="32.4" customHeight="1">
       <c r="A313" s="7"/>
       <c r="B313" s="110"/>
       <c r="C313" s="101"/>
@@ -18146,7 +18150,7 @@
       <c r="O313" s="88"/>
       <c r="P313" s="91"/>
     </row>
-    <row r="314" spans="1:16" ht="35.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" ht="35.4" customHeight="1">
       <c r="A314" s="7"/>
       <c r="B314" s="111"/>
       <c r="C314" s="102"/>
@@ -18170,7 +18174,7 @@
       <c r="O314" s="89"/>
       <c r="P314" s="92"/>
     </row>
-    <row r="315" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" ht="14.4" customHeight="1">
       <c r="A315" s="7"/>
       <c r="B315" s="110">
         <v>28</v>
@@ -18206,7 +18210,7 @@
       <c r="O315" s="106"/>
       <c r="P315" s="107"/>
     </row>
-    <row r="316" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" ht="14.4" customHeight="1">
       <c r="A316" s="7"/>
       <c r="B316" s="110"/>
       <c r="C316" s="101"/>
@@ -18228,7 +18232,7 @@
       <c r="O316" s="88"/>
       <c r="P316" s="91"/>
     </row>
-    <row r="317" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" ht="14.4" customHeight="1">
       <c r="A317" s="7"/>
       <c r="B317" s="110"/>
       <c r="C317" s="101"/>
@@ -18250,7 +18254,7 @@
       <c r="O317" s="88"/>
       <c r="P317" s="91"/>
     </row>
-    <row r="318" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" ht="14.4" customHeight="1">
       <c r="A318" s="7"/>
       <c r="B318" s="110"/>
       <c r="C318" s="101"/>
@@ -18272,7 +18276,7 @@
       <c r="O318" s="88"/>
       <c r="P318" s="91"/>
     </row>
-    <row r="319" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" ht="14.4" customHeight="1">
       <c r="A319" s="7"/>
       <c r="B319" s="110"/>
       <c r="C319" s="101"/>
@@ -18292,7 +18296,7 @@
       <c r="O319" s="88"/>
       <c r="P319" s="91"/>
     </row>
-    <row r="320" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" ht="14.4" customHeight="1">
       <c r="A320" s="7"/>
       <c r="B320" s="110"/>
       <c r="C320" s="101"/>
@@ -18312,7 +18316,7 @@
       <c r="O320" s="88"/>
       <c r="P320" s="91"/>
     </row>
-    <row r="321" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" ht="14.4" customHeight="1">
       <c r="A321" s="7"/>
       <c r="B321" s="110"/>
       <c r="C321" s="101"/>
@@ -18332,7 +18336,7 @@
       <c r="O321" s="88"/>
       <c r="P321" s="91"/>
     </row>
-    <row r="322" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" ht="14.4" customHeight="1">
       <c r="A322" s="7"/>
       <c r="B322" s="110"/>
       <c r="C322" s="101"/>
@@ -18352,7 +18356,7 @@
       <c r="O322" s="88"/>
       <c r="P322" s="91"/>
     </row>
-    <row r="323" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" ht="14.4" customHeight="1">
       <c r="A323" s="7"/>
       <c r="B323" s="110"/>
       <c r="C323" s="101"/>
@@ -18372,7 +18376,7 @@
       <c r="O323" s="88"/>
       <c r="P323" s="91"/>
     </row>
-    <row r="324" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" ht="14.4" customHeight="1">
       <c r="A324" s="7"/>
       <c r="B324" s="111"/>
       <c r="C324" s="102"/>
@@ -18392,7 +18396,7 @@
       <c r="O324" s="89"/>
       <c r="P324" s="92"/>
     </row>
-    <row r="325" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" ht="14.4" customHeight="1">
       <c r="A325" s="7"/>
       <c r="B325" s="110">
         <v>29</v>
@@ -18430,7 +18434,7 @@
       <c r="O325" s="88"/>
       <c r="P325" s="90"/>
     </row>
-    <row r="326" spans="1:16" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" ht="30.6" customHeight="1">
       <c r="A326" s="7"/>
       <c r="B326" s="110"/>
       <c r="C326" s="101"/>
@@ -18452,7 +18456,7 @@
       <c r="O326" s="88"/>
       <c r="P326" s="91"/>
     </row>
-    <row r="327" spans="1:16" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" ht="37.2" customHeight="1">
       <c r="A327" s="7"/>
       <c r="B327" s="110"/>
       <c r="C327" s="101"/>
@@ -18474,7 +18478,7 @@
       <c r="O327" s="88"/>
       <c r="P327" s="91"/>
     </row>
-    <row r="328" spans="1:16" ht="32.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" ht="32.4" customHeight="1">
       <c r="A328" s="7"/>
       <c r="B328" s="110"/>
       <c r="C328" s="101"/>
@@ -18496,7 +18500,7 @@
       <c r="O328" s="88"/>
       <c r="P328" s="91"/>
     </row>
-    <row r="329" spans="1:16" ht="32.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" ht="32.4" customHeight="1">
       <c r="A329" s="7"/>
       <c r="B329" s="110"/>
       <c r="C329" s="101"/>
@@ -18518,7 +18522,7 @@
       <c r="O329" s="88"/>
       <c r="P329" s="91"/>
     </row>
-    <row r="330" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" ht="33" customHeight="1">
       <c r="A330" s="7"/>
       <c r="B330" s="110"/>
       <c r="C330" s="101"/>
@@ -18542,7 +18546,7 @@
       <c r="O330" s="88"/>
       <c r="P330" s="91"/>
     </row>
-    <row r="331" spans="1:16" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" ht="27" customHeight="1">
       <c r="A331" s="7"/>
       <c r="B331" s="110"/>
       <c r="C331" s="101"/>
@@ -18566,7 +18570,7 @@
       <c r="O331" s="88"/>
       <c r="P331" s="91"/>
     </row>
-    <row r="332" spans="1:16" ht="32.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" ht="32.4" customHeight="1">
       <c r="A332" s="7"/>
       <c r="B332" s="110"/>
       <c r="C332" s="101"/>
@@ -18588,7 +18592,7 @@
       <c r="O332" s="88"/>
       <c r="P332" s="91"/>
     </row>
-    <row r="333" spans="1:16" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" ht="21" customHeight="1">
       <c r="A333" s="7"/>
       <c r="B333" s="110"/>
       <c r="C333" s="101"/>
@@ -18612,7 +18616,7 @@
       <c r="O333" s="88"/>
       <c r="P333" s="91"/>
     </row>
-    <row r="334" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" ht="42" customHeight="1">
       <c r="A334" s="7"/>
       <c r="B334" s="111"/>
       <c r="C334" s="102"/>
@@ -18636,7 +18640,7 @@
       <c r="O334" s="89"/>
       <c r="P334" s="92"/>
     </row>
-    <row r="335" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" ht="14.4" customHeight="1">
       <c r="A335" s="7"/>
       <c r="B335" s="110">
         <v>30</v>
@@ -18670,7 +18674,7 @@
       <c r="O335" s="106"/>
       <c r="P335" s="107"/>
     </row>
-    <row r="336" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" ht="14.4" customHeight="1">
       <c r="A336" s="7"/>
       <c r="B336" s="110"/>
       <c r="C336" s="101"/>
@@ -18692,7 +18696,7 @@
       <c r="O336" s="88"/>
       <c r="P336" s="91"/>
     </row>
-    <row r="337" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" ht="14.4" customHeight="1">
       <c r="A337" s="7"/>
       <c r="B337" s="110"/>
       <c r="C337" s="101"/>
@@ -18714,7 +18718,7 @@
       <c r="O337" s="88"/>
       <c r="P337" s="91"/>
     </row>
-    <row r="338" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" ht="14.4" customHeight="1">
       <c r="A338" s="7"/>
       <c r="B338" s="110"/>
       <c r="C338" s="101"/>
@@ -18738,7 +18742,7 @@
       <c r="O338" s="88"/>
       <c r="P338" s="91"/>
     </row>
-    <row r="339" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" ht="14.4" customHeight="1">
       <c r="A339" s="7"/>
       <c r="B339" s="110"/>
       <c r="C339" s="101"/>
@@ -18762,7 +18766,7 @@
       <c r="O339" s="88"/>
       <c r="P339" s="91"/>
     </row>
-    <row r="340" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" ht="14.4" customHeight="1">
       <c r="A340" s="7"/>
       <c r="B340" s="110"/>
       <c r="C340" s="101"/>
@@ -18786,7 +18790,7 @@
       <c r="O340" s="88"/>
       <c r="P340" s="91"/>
     </row>
-    <row r="341" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" ht="14.4" customHeight="1">
       <c r="A341" s="7"/>
       <c r="B341" s="110"/>
       <c r="C341" s="101"/>
@@ -18799,7 +18803,7 @@
         <v>7</v>
       </c>
       <c r="J341" s="14" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="K341" s="14" t="s">
         <v>553</v>
@@ -18810,7 +18814,7 @@
       <c r="O341" s="88"/>
       <c r="P341" s="91"/>
     </row>
-    <row r="342" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" ht="14.4" customHeight="1">
       <c r="A342" s="7"/>
       <c r="B342" s="110"/>
       <c r="C342" s="101"/>
@@ -18823,7 +18827,7 @@
         <v>8</v>
       </c>
       <c r="J342" s="14" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="K342" s="14" t="s">
         <v>423</v>
@@ -18834,7 +18838,7 @@
       <c r="O342" s="88"/>
       <c r="P342" s="91"/>
     </row>
-    <row r="343" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" ht="14.4" customHeight="1">
       <c r="A343" s="7"/>
       <c r="B343" s="110"/>
       <c r="C343" s="101"/>
@@ -18847,7 +18851,7 @@
         <v>9</v>
       </c>
       <c r="J343" s="14" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="K343" s="14">
         <v>12345</v>
@@ -18858,7 +18862,7 @@
       <c r="O343" s="88"/>
       <c r="P343" s="91"/>
     </row>
-    <row r="344" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" ht="14.4" customHeight="1">
       <c r="A344" s="7"/>
       <c r="B344" s="110"/>
       <c r="C344" s="101"/>
@@ -18882,7 +18886,7 @@
       <c r="O344" s="88"/>
       <c r="P344" s="91"/>
     </row>
-    <row r="345" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" ht="14.4" customHeight="1">
       <c r="A345" s="7"/>
       <c r="B345" s="110"/>
       <c r="C345" s="101"/>
@@ -18895,7 +18899,7 @@
         <v>11</v>
       </c>
       <c r="J345" s="38" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="K345" s="14">
         <v>12345</v>
@@ -18906,7 +18910,7 @@
       <c r="O345" s="88"/>
       <c r="P345" s="91"/>
     </row>
-    <row r="346" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" ht="14.4" customHeight="1">
       <c r="A346" s="7"/>
       <c r="B346" s="110"/>
       <c r="C346" s="101"/>
@@ -18930,7 +18934,7 @@
       <c r="O346" s="88"/>
       <c r="P346" s="91"/>
     </row>
-    <row r="347" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" ht="14.4" customHeight="1">
       <c r="A347" s="7"/>
       <c r="B347" s="110"/>
       <c r="C347" s="101"/>
@@ -18954,7 +18958,7 @@
       <c r="O347" s="88"/>
       <c r="P347" s="91"/>
     </row>
-    <row r="348" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" ht="14.4" customHeight="1">
       <c r="A348" s="7"/>
       <c r="B348" s="110"/>
       <c r="C348" s="101"/>
@@ -18978,7 +18982,7 @@
       <c r="O348" s="88"/>
       <c r="P348" s="91"/>
     </row>
-    <row r="349" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" ht="14.4" customHeight="1">
       <c r="A349" s="7"/>
       <c r="B349" s="110"/>
       <c r="C349" s="101"/>
@@ -19000,7 +19004,7 @@
       <c r="O349" s="88"/>
       <c r="P349" s="91"/>
     </row>
-    <row r="350" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" ht="14.4" customHeight="1">
       <c r="A350" s="7"/>
       <c r="B350" s="110"/>
       <c r="C350" s="101"/>
@@ -19022,7 +19026,7 @@
       <c r="O350" s="88"/>
       <c r="P350" s="91"/>
     </row>
-    <row r="351" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" ht="14.4" customHeight="1">
       <c r="A351" s="7"/>
       <c r="B351" s="110"/>
       <c r="C351" s="101"/>
@@ -19044,7 +19048,7 @@
       <c r="O351" s="88"/>
       <c r="P351" s="91"/>
     </row>
-    <row r="352" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" ht="14.4" customHeight="1">
       <c r="A352" s="7"/>
       <c r="B352" s="110"/>
       <c r="C352" s="101"/>
@@ -19068,7 +19072,7 @@
       <c r="O352" s="88"/>
       <c r="P352" s="91"/>
     </row>
-    <row r="353" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="353" ht="14.4" customHeight="1">
       <c r="A353" s="7"/>
       <c r="B353" s="110"/>
       <c r="C353" s="101"/>
@@ -19090,7 +19094,7 @@
       <c r="O353" s="88"/>
       <c r="P353" s="91"/>
     </row>
-    <row r="354" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" ht="14.4" customHeight="1">
       <c r="A354" s="7"/>
       <c r="B354" s="110"/>
       <c r="C354" s="101"/>
@@ -19112,7 +19116,7 @@
       <c r="O354" s="88"/>
       <c r="P354" s="91"/>
     </row>
-    <row r="355" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" ht="14.4" customHeight="1">
       <c r="A355" s="7"/>
       <c r="B355" s="110"/>
       <c r="C355" s="101"/>
@@ -19136,7 +19140,7 @@
       <c r="O355" s="88"/>
       <c r="P355" s="91"/>
     </row>
-    <row r="356" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" ht="14.4" customHeight="1">
       <c r="A356" s="7"/>
       <c r="B356" s="110"/>
       <c r="C356" s="101"/>
@@ -19160,7 +19164,7 @@
       <c r="O356" s="88"/>
       <c r="P356" s="91"/>
     </row>
-    <row r="357" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" ht="14.4" customHeight="1">
       <c r="A357" s="7"/>
       <c r="B357" s="110"/>
       <c r="C357" s="101"/>
@@ -19173,7 +19177,7 @@
         <v>23</v>
       </c>
       <c r="J357" s="14" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="K357" s="14" t="s">
         <v>567</v>
@@ -19184,7 +19188,7 @@
       <c r="O357" s="88"/>
       <c r="P357" s="91"/>
     </row>
-    <row r="358" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" ht="14.4" customHeight="1">
       <c r="A358" s="7"/>
       <c r="B358" s="110"/>
       <c r="C358" s="101"/>
@@ -19197,7 +19201,7 @@
         <v>24</v>
       </c>
       <c r="J358" s="14" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="K358" s="14" t="s">
         <v>423</v>
@@ -19208,7 +19212,7 @@
       <c r="O358" s="88"/>
       <c r="P358" s="91"/>
     </row>
-    <row r="359" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" ht="14.4" customHeight="1">
       <c r="A359" s="7"/>
       <c r="B359" s="110"/>
       <c r="C359" s="101"/>
@@ -19221,7 +19225,7 @@
         <v>25</v>
       </c>
       <c r="J359" s="14" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="K359" s="14">
         <v>12345</v>
@@ -19232,7 +19236,7 @@
       <c r="O359" s="88"/>
       <c r="P359" s="91"/>
     </row>
-    <row r="360" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="360" ht="14.4" customHeight="1">
       <c r="A360" s="7"/>
       <c r="B360" s="110"/>
       <c r="C360" s="101"/>
@@ -19256,7 +19260,7 @@
       <c r="O360" s="88"/>
       <c r="P360" s="91"/>
     </row>
-    <row r="361" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" ht="14.4" customHeight="1">
       <c r="A361" s="7"/>
       <c r="B361" s="110"/>
       <c r="C361" s="101"/>
@@ -19280,7 +19284,7 @@
       <c r="O361" s="88"/>
       <c r="P361" s="91"/>
     </row>
-    <row r="362" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="362" ht="14.4" customHeight="1">
       <c r="A362" s="7"/>
       <c r="B362" s="110"/>
       <c r="C362" s="101"/>
@@ -19304,7 +19308,7 @@
       <c r="O362" s="88"/>
       <c r="P362" s="91"/>
     </row>
-    <row r="363" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" ht="14.4" customHeight="1">
       <c r="A363" s="7"/>
       <c r="B363" s="110"/>
       <c r="C363" s="101"/>
@@ -19328,7 +19332,7 @@
       <c r="O363" s="88"/>
       <c r="P363" s="91"/>
     </row>
-    <row r="364" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" ht="14.4" customHeight="1">
       <c r="A364" s="7"/>
       <c r="B364" s="110"/>
       <c r="C364" s="101"/>
@@ -19350,7 +19354,7 @@
       <c r="O364" s="88"/>
       <c r="P364" s="91"/>
     </row>
-    <row r="365" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="365" ht="14.4" customHeight="1">
       <c r="A365" s="7"/>
       <c r="B365" s="110"/>
       <c r="C365" s="101"/>
@@ -19372,7 +19376,7 @@
       <c r="O365" s="88"/>
       <c r="P365" s="91"/>
     </row>
-    <row r="366" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="366" ht="14.4" customHeight="1">
       <c r="A366" s="7"/>
       <c r="B366" s="110"/>
       <c r="C366" s="101"/>
@@ -19394,7 +19398,7 @@
       <c r="O366" s="88"/>
       <c r="P366" s="91"/>
     </row>
-    <row r="367" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" ht="14.4" customHeight="1">
       <c r="A367" s="7"/>
       <c r="B367" s="111"/>
       <c r="C367" s="102"/>
@@ -19417,7 +19421,7 @@
       <c r="P367" s="92"/>
     </row>
   </sheetData>
-  <mergeCells count="360">
+  <mergeCells>
     <mergeCell ref="P335:P367"/>
     <mergeCell ref="B335:B367"/>
     <mergeCell ref="C335:C367"/>
@@ -19781,5 +19785,11 @@
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
+</file>
+
+<file path=EPPlusLicense.txt>This workbook was created with the EPPlus library, licensed to DoAnCuoiKy_TH under the Polyform Noncommercial license, see https://polyformproject.org/licenses/noncommercial/1.0.0
+For more information about EPPlus, see https://epplussoftware.com/
+
 </file>